--- a/data/flat/tennis.xlsx
+++ b/data/flat/tennis.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR194" headerRowCount="1">
-  <autoFilter ref="A1:CR194"/>
-  <tableColumns count="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS194" headerRowCount="1">
+  <autoFilter ref="A1:CS194"/>
+  <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -393,12 +393,13 @@
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
     <tableColumn id="90" name="bullpen_weakness_gap"/>
-    <tableColumn id="91" name="rest_disparity"/>
-    <tableColumn id="92" name="back_to_back_gap"/>
-    <tableColumn id="93" name="games_last_7_gap"/>
-    <tableColumn id="94" name="schedule_missingness"/>
-    <tableColumn id="95" name="market_residual_probability"/>
-    <tableColumn id="96" name="trade_candidate"/>
+    <tableColumn id="91" name="starter_era_gap"/>
+    <tableColumn id="92" name="rest_disparity"/>
+    <tableColumn id="93" name="back_to_back_gap"/>
+    <tableColumn id="94" name="games_last_7_gap"/>
+    <tableColumn id="95" name="schedule_missingness"/>
+    <tableColumn id="96" name="market_residual_probability"/>
+    <tableColumn id="97" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1013,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CR194"/>
+  <dimension ref="A1:CS194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,12 +1107,13 @@
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
     <col width="22" customWidth="1" min="90" max="90"/>
-    <col width="16" customWidth="1" min="91" max="91"/>
-    <col width="18" customWidth="1" min="92" max="92"/>
+    <col width="17" customWidth="1" min="91" max="91"/>
+    <col width="16" customWidth="1" min="92" max="92"/>
     <col width="18" customWidth="1" min="93" max="93"/>
-    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
     <col width="22" customWidth="1" min="95" max="95"/>
-    <col width="17" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="96" max="96"/>
+    <col width="17" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1567,30 +1569,35 @@
       </c>
       <c r="CM1" s="23" t="inlineStr">
         <is>
+          <t>starter_era_gap</t>
+        </is>
+      </c>
+      <c r="CN1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CR1" s="23" t="inlineStr">
+      <c r="CS1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1875,6 +1882,7 @@
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
       <c r="CR2" s="24" t="n"/>
+      <c r="CS2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2155,6 +2163,7 @@
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
       <c r="CR3" s="24" t="n"/>
+      <c r="CS3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2435,6 +2444,7 @@
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
       <c r="CR4" s="24" t="n"/>
+      <c r="CS4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2715,6 +2725,7 @@
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
       <c r="CR5" s="24" t="n"/>
+      <c r="CS5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -2995,6 +3006,7 @@
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
       <c r="CR6" s="24" t="n"/>
+      <c r="CS6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3275,6 +3287,7 @@
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
       <c r="CR7" s="24" t="n"/>
+      <c r="CS7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3555,6 +3568,7 @@
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
       <c r="CR8" s="24" t="n"/>
+      <c r="CS8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3835,6 +3849,7 @@
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
       <c r="CR9" s="24" t="n"/>
+      <c r="CS9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4115,6 +4130,7 @@
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
       <c r="CR10" s="24" t="n"/>
+      <c r="CS10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4395,6 +4411,7 @@
       <c r="CP11" s="24" t="n"/>
       <c r="CQ11" s="24" t="n"/>
       <c r="CR11" s="24" t="n"/>
+      <c r="CS11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4675,6 +4692,7 @@
       <c r="CP12" s="24" t="n"/>
       <c r="CQ12" s="24" t="n"/>
       <c r="CR12" s="24" t="n"/>
+      <c r="CS12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -4955,6 +4973,7 @@
       <c r="CP13" s="24" t="n"/>
       <c r="CQ13" s="24" t="n"/>
       <c r="CR13" s="24" t="n"/>
+      <c r="CS13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5235,6 +5254,7 @@
       <c r="CP14" s="24" t="n"/>
       <c r="CQ14" s="24" t="n"/>
       <c r="CR14" s="24" t="n"/>
+      <c r="CS14" s="24" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -5515,6 +5535,7 @@
       <c r="CP15" s="24" t="n"/>
       <c r="CQ15" s="24" t="n"/>
       <c r="CR15" s="24" t="n"/>
+      <c r="CS15" s="24" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -5795,6 +5816,7 @@
       <c r="CP16" s="24" t="n"/>
       <c r="CQ16" s="24" t="n"/>
       <c r="CR16" s="24" t="n"/>
+      <c r="CS16" s="24" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
@@ -6075,6 +6097,7 @@
       <c r="CP17" s="24" t="n"/>
       <c r="CQ17" s="24" t="n"/>
       <c r="CR17" s="24" t="n"/>
+      <c r="CS17" s="24" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
@@ -6355,6 +6378,7 @@
       <c r="CP18" s="24" t="n"/>
       <c r="CQ18" s="24" t="n"/>
       <c r="CR18" s="24" t="n"/>
+      <c r="CS18" s="24" t="n"/>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
@@ -6635,6 +6659,7 @@
       <c r="CP19" s="24" t="n"/>
       <c r="CQ19" s="24" t="n"/>
       <c r="CR19" s="24" t="n"/>
+      <c r="CS19" s="24" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
@@ -6915,6 +6940,7 @@
       <c r="CP20" s="24" t="n"/>
       <c r="CQ20" s="24" t="n"/>
       <c r="CR20" s="24" t="n"/>
+      <c r="CS20" s="24" t="n"/>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
@@ -7195,6 +7221,7 @@
       <c r="CP21" s="24" t="n"/>
       <c r="CQ21" s="24" t="n"/>
       <c r="CR21" s="24" t="n"/>
+      <c r="CS21" s="24" t="n"/>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
@@ -7475,6 +7502,7 @@
       <c r="CP22" s="24" t="n"/>
       <c r="CQ22" s="24" t="n"/>
       <c r="CR22" s="24" t="n"/>
+      <c r="CS22" s="24" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
@@ -7755,6 +7783,7 @@
       <c r="CP23" s="24" t="n"/>
       <c r="CQ23" s="24" t="n"/>
       <c r="CR23" s="24" t="n"/>
+      <c r="CS23" s="24" t="n"/>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
@@ -8035,6 +8064,7 @@
       <c r="CP24" s="24" t="n"/>
       <c r="CQ24" s="24" t="n"/>
       <c r="CR24" s="24" t="n"/>
+      <c r="CS24" s="24" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
@@ -8315,6 +8345,7 @@
       <c r="CP25" s="24" t="n"/>
       <c r="CQ25" s="24" t="n"/>
       <c r="CR25" s="24" t="n"/>
+      <c r="CS25" s="24" t="n"/>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
@@ -8595,6 +8626,7 @@
       <c r="CP26" s="24" t="n"/>
       <c r="CQ26" s="24" t="n"/>
       <c r="CR26" s="24" t="n"/>
+      <c r="CS26" s="24" t="n"/>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
@@ -8875,6 +8907,7 @@
       <c r="CP27" s="24" t="n"/>
       <c r="CQ27" s="24" t="n"/>
       <c r="CR27" s="24" t="n"/>
+      <c r="CS27" s="24" t="n"/>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
@@ -9155,6 +9188,7 @@
       <c r="CP28" s="24" t="n"/>
       <c r="CQ28" s="24" t="n"/>
       <c r="CR28" s="24" t="n"/>
+      <c r="CS28" s="24" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
@@ -9435,6 +9469,7 @@
       <c r="CP29" s="24" t="n"/>
       <c r="CQ29" s="24" t="n"/>
       <c r="CR29" s="24" t="n"/>
+      <c r="CS29" s="24" t="n"/>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
@@ -9715,6 +9750,7 @@
       <c r="CP30" s="24" t="n"/>
       <c r="CQ30" s="24" t="n"/>
       <c r="CR30" s="24" t="n"/>
+      <c r="CS30" s="24" t="n"/>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
@@ -9995,6 +10031,7 @@
       <c r="CP31" s="24" t="n"/>
       <c r="CQ31" s="24" t="n"/>
       <c r="CR31" s="24" t="n"/>
+      <c r="CS31" s="24" t="n"/>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
@@ -10275,6 +10312,7 @@
       <c r="CP32" s="24" t="n"/>
       <c r="CQ32" s="24" t="n"/>
       <c r="CR32" s="24" t="n"/>
+      <c r="CS32" s="24" t="n"/>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
@@ -10555,6 +10593,7 @@
       <c r="CP33" s="24" t="n"/>
       <c r="CQ33" s="24" t="n"/>
       <c r="CR33" s="24" t="n"/>
+      <c r="CS33" s="24" t="n"/>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
@@ -10835,6 +10874,7 @@
       <c r="CP34" s="24" t="n"/>
       <c r="CQ34" s="24" t="n"/>
       <c r="CR34" s="24" t="n"/>
+      <c r="CS34" s="24" t="n"/>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
@@ -11115,6 +11155,7 @@
       <c r="CP35" s="24" t="n"/>
       <c r="CQ35" s="24" t="n"/>
       <c r="CR35" s="24" t="n"/>
+      <c r="CS35" s="24" t="n"/>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
@@ -11395,6 +11436,7 @@
       <c r="CP36" s="24" t="n"/>
       <c r="CQ36" s="24" t="n"/>
       <c r="CR36" s="24" t="n"/>
+      <c r="CS36" s="24" t="n"/>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
@@ -11675,6 +11717,7 @@
       <c r="CP37" s="24" t="n"/>
       <c r="CQ37" s="24" t="n"/>
       <c r="CR37" s="24" t="n"/>
+      <c r="CS37" s="24" t="n"/>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
@@ -11955,6 +11998,7 @@
       <c r="CP38" s="24" t="n"/>
       <c r="CQ38" s="24" t="n"/>
       <c r="CR38" s="24" t="n"/>
+      <c r="CS38" s="24" t="n"/>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
@@ -12235,6 +12279,7 @@
       <c r="CP39" s="24" t="n"/>
       <c r="CQ39" s="24" t="n"/>
       <c r="CR39" s="24" t="n"/>
+      <c r="CS39" s="24" t="n"/>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
@@ -12515,6 +12560,7 @@
       <c r="CP40" s="24" t="n"/>
       <c r="CQ40" s="24" t="n"/>
       <c r="CR40" s="24" t="n"/>
+      <c r="CS40" s="24" t="n"/>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="24" t="inlineStr">
@@ -12795,6 +12841,7 @@
       <c r="CP41" s="24" t="n"/>
       <c r="CQ41" s="24" t="n"/>
       <c r="CR41" s="24" t="n"/>
+      <c r="CS41" s="24" t="n"/>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
@@ -13075,6 +13122,7 @@
       <c r="CP42" s="24" t="n"/>
       <c r="CQ42" s="24" t="n"/>
       <c r="CR42" s="24" t="n"/>
+      <c r="CS42" s="24" t="n"/>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
@@ -13355,6 +13403,7 @@
       <c r="CP43" s="24" t="n"/>
       <c r="CQ43" s="24" t="n"/>
       <c r="CR43" s="24" t="n"/>
+      <c r="CS43" s="24" t="n"/>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
@@ -13635,6 +13684,7 @@
       <c r="CP44" s="24" t="n"/>
       <c r="CQ44" s="24" t="n"/>
       <c r="CR44" s="24" t="n"/>
+      <c r="CS44" s="24" t="n"/>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
@@ -13915,6 +13965,7 @@
       <c r="CP45" s="24" t="n"/>
       <c r="CQ45" s="24" t="n"/>
       <c r="CR45" s="24" t="n"/>
+      <c r="CS45" s="24" t="n"/>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
@@ -14195,6 +14246,7 @@
       <c r="CP46" s="24" t="n"/>
       <c r="CQ46" s="24" t="n"/>
       <c r="CR46" s="24" t="n"/>
+      <c r="CS46" s="24" t="n"/>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
@@ -14475,6 +14527,7 @@
       <c r="CP47" s="24" t="n"/>
       <c r="CQ47" s="24" t="n"/>
       <c r="CR47" s="24" t="n"/>
+      <c r="CS47" s="24" t="n"/>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
@@ -14755,6 +14808,7 @@
       <c r="CP48" s="24" t="n"/>
       <c r="CQ48" s="24" t="n"/>
       <c r="CR48" s="24" t="n"/>
+      <c r="CS48" s="24" t="n"/>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
@@ -15035,6 +15089,7 @@
       <c r="CP49" s="24" t="n"/>
       <c r="CQ49" s="24" t="n"/>
       <c r="CR49" s="24" t="n"/>
+      <c r="CS49" s="24" t="n"/>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
@@ -15315,6 +15370,7 @@
       <c r="CP50" s="24" t="n"/>
       <c r="CQ50" s="24" t="n"/>
       <c r="CR50" s="24" t="n"/>
+      <c r="CS50" s="24" t="n"/>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
@@ -15595,6 +15651,7 @@
       <c r="CP51" s="24" t="n"/>
       <c r="CQ51" s="24" t="n"/>
       <c r="CR51" s="24" t="n"/>
+      <c r="CS51" s="24" t="n"/>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
@@ -15875,6 +15932,7 @@
       <c r="CP52" s="24" t="n"/>
       <c r="CQ52" s="24" t="n"/>
       <c r="CR52" s="24" t="n"/>
+      <c r="CS52" s="24" t="n"/>
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="24" t="inlineStr">
@@ -16155,6 +16213,7 @@
       <c r="CP53" s="24" t="n"/>
       <c r="CQ53" s="24" t="n"/>
       <c r="CR53" s="24" t="n"/>
+      <c r="CS53" s="24" t="n"/>
     </row>
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="24" t="inlineStr">
@@ -16435,6 +16494,7 @@
       <c r="CP54" s="24" t="n"/>
       <c r="CQ54" s="24" t="n"/>
       <c r="CR54" s="24" t="n"/>
+      <c r="CS54" s="24" t="n"/>
     </row>
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="24" t="inlineStr">
@@ -16715,6 +16775,7 @@
       <c r="CP55" s="24" t="n"/>
       <c r="CQ55" s="24" t="n"/>
       <c r="CR55" s="24" t="n"/>
+      <c r="CS55" s="24" t="n"/>
     </row>
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="24" t="inlineStr">
@@ -16995,6 +17056,7 @@
       <c r="CP56" s="24" t="n"/>
       <c r="CQ56" s="24" t="n"/>
       <c r="CR56" s="24" t="n"/>
+      <c r="CS56" s="24" t="n"/>
     </row>
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
@@ -17275,6 +17337,7 @@
       <c r="CP57" s="24" t="n"/>
       <c r="CQ57" s="24" t="n"/>
       <c r="CR57" s="24" t="n"/>
+      <c r="CS57" s="24" t="n"/>
     </row>
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
@@ -17555,6 +17618,7 @@
       <c r="CP58" s="24" t="n"/>
       <c r="CQ58" s="24" t="n"/>
       <c r="CR58" s="24" t="n"/>
+      <c r="CS58" s="24" t="n"/>
     </row>
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
@@ -17835,6 +17899,7 @@
       <c r="CP59" s="24" t="n"/>
       <c r="CQ59" s="24" t="n"/>
       <c r="CR59" s="24" t="n"/>
+      <c r="CS59" s="24" t="n"/>
     </row>
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
@@ -18115,6 +18180,7 @@
       <c r="CP60" s="24" t="n"/>
       <c r="CQ60" s="24" t="n"/>
       <c r="CR60" s="24" t="n"/>
+      <c r="CS60" s="24" t="n"/>
     </row>
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
@@ -18395,6 +18461,7 @@
       <c r="CP61" s="24" t="n"/>
       <c r="CQ61" s="24" t="n"/>
       <c r="CR61" s="24" t="n"/>
+      <c r="CS61" s="24" t="n"/>
     </row>
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
@@ -18675,6 +18742,7 @@
       <c r="CP62" s="24" t="n"/>
       <c r="CQ62" s="24" t="n"/>
       <c r="CR62" s="24" t="n"/>
+      <c r="CS62" s="24" t="n"/>
     </row>
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
@@ -18955,6 +19023,7 @@
       <c r="CP63" s="24" t="n"/>
       <c r="CQ63" s="24" t="n"/>
       <c r="CR63" s="24" t="n"/>
+      <c r="CS63" s="24" t="n"/>
     </row>
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
@@ -19235,6 +19304,7 @@
       <c r="CP64" s="24" t="n"/>
       <c r="CQ64" s="24" t="n"/>
       <c r="CR64" s="24" t="n"/>
+      <c r="CS64" s="24" t="n"/>
     </row>
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
@@ -19515,6 +19585,7 @@
       <c r="CP65" s="24" t="n"/>
       <c r="CQ65" s="24" t="n"/>
       <c r="CR65" s="24" t="n"/>
+      <c r="CS65" s="24" t="n"/>
     </row>
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
@@ -19795,6 +19866,7 @@
       <c r="CP66" s="24" t="n"/>
       <c r="CQ66" s="24" t="n"/>
       <c r="CR66" s="24" t="n"/>
+      <c r="CS66" s="24" t="n"/>
     </row>
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
@@ -20075,6 +20147,7 @@
       <c r="CP67" s="24" t="n"/>
       <c r="CQ67" s="24" t="n"/>
       <c r="CR67" s="24" t="n"/>
+      <c r="CS67" s="24" t="n"/>
     </row>
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="24" t="inlineStr">
@@ -20365,6 +20438,7 @@
       <c r="CP68" s="24" t="n"/>
       <c r="CQ68" s="24" t="n"/>
       <c r="CR68" s="24" t="n"/>
+      <c r="CS68" s="24" t="n"/>
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
@@ -20655,6 +20729,7 @@
       <c r="CP69" s="24" t="n"/>
       <c r="CQ69" s="24" t="n"/>
       <c r="CR69" s="24" t="n"/>
+      <c r="CS69" s="24" t="n"/>
     </row>
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
@@ -20945,6 +21020,7 @@
       <c r="CP70" s="24" t="n"/>
       <c r="CQ70" s="24" t="n"/>
       <c r="CR70" s="24" t="n"/>
+      <c r="CS70" s="24" t="n"/>
     </row>
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="24" t="inlineStr">
@@ -21235,6 +21311,7 @@
       <c r="CP71" s="24" t="n"/>
       <c r="CQ71" s="24" t="n"/>
       <c r="CR71" s="24" t="n"/>
+      <c r="CS71" s="24" t="n"/>
     </row>
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="24" t="inlineStr">
@@ -21525,6 +21602,7 @@
       <c r="CP72" s="24" t="n"/>
       <c r="CQ72" s="24" t="n"/>
       <c r="CR72" s="24" t="n"/>
+      <c r="CS72" s="24" t="n"/>
     </row>
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="24" t="inlineStr">
@@ -21815,6 +21893,7 @@
       <c r="CP73" s="24" t="n"/>
       <c r="CQ73" s="24" t="n"/>
       <c r="CR73" s="24" t="n"/>
+      <c r="CS73" s="24" t="n"/>
     </row>
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="24" t="inlineStr">
@@ -22105,6 +22184,7 @@
       <c r="CP74" s="24" t="n"/>
       <c r="CQ74" s="24" t="n"/>
       <c r="CR74" s="24" t="n"/>
+      <c r="CS74" s="24" t="n"/>
     </row>
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="24" t="inlineStr">
@@ -22395,6 +22475,7 @@
       <c r="CP75" s="24" t="n"/>
       <c r="CQ75" s="24" t="n"/>
       <c r="CR75" s="24" t="n"/>
+      <c r="CS75" s="24" t="n"/>
     </row>
     <row r="76" ht="36" customHeight="1">
       <c r="A76" s="24" t="inlineStr">
@@ -22685,6 +22766,7 @@
       <c r="CP76" s="24" t="n"/>
       <c r="CQ76" s="24" t="n"/>
       <c r="CR76" s="24" t="n"/>
+      <c r="CS76" s="24" t="n"/>
     </row>
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="24" t="inlineStr">
@@ -22975,6 +23057,7 @@
       <c r="CP77" s="24" t="n"/>
       <c r="CQ77" s="24" t="n"/>
       <c r="CR77" s="24" t="n"/>
+      <c r="CS77" s="24" t="n"/>
     </row>
     <row r="78" ht="36" customHeight="1">
       <c r="A78" s="24" t="inlineStr">
@@ -23265,6 +23348,7 @@
       <c r="CP78" s="24" t="n"/>
       <c r="CQ78" s="24" t="n"/>
       <c r="CR78" s="24" t="n"/>
+      <c r="CS78" s="24" t="n"/>
     </row>
     <row r="79" ht="36" customHeight="1">
       <c r="A79" s="24" t="inlineStr">
@@ -23555,6 +23639,7 @@
       <c r="CP79" s="24" t="n"/>
       <c r="CQ79" s="24" t="n"/>
       <c r="CR79" s="24" t="n"/>
+      <c r="CS79" s="24" t="n"/>
     </row>
     <row r="80" ht="36" customHeight="1">
       <c r="A80" s="24" t="inlineStr">
@@ -23845,6 +23930,7 @@
       <c r="CP80" s="24" t="n"/>
       <c r="CQ80" s="24" t="n"/>
       <c r="CR80" s="24" t="n"/>
+      <c r="CS80" s="24" t="n"/>
     </row>
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="24" t="inlineStr">
@@ -24135,6 +24221,7 @@
       <c r="CP81" s="24" t="n"/>
       <c r="CQ81" s="24" t="n"/>
       <c r="CR81" s="24" t="n"/>
+      <c r="CS81" s="24" t="n"/>
     </row>
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="24" t="inlineStr">
@@ -24425,6 +24512,7 @@
       <c r="CP82" s="24" t="n"/>
       <c r="CQ82" s="24" t="n"/>
       <c r="CR82" s="24" t="n"/>
+      <c r="CS82" s="24" t="n"/>
     </row>
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="24" t="inlineStr">
@@ -24715,6 +24803,7 @@
       <c r="CP83" s="24" t="n"/>
       <c r="CQ83" s="24" t="n"/>
       <c r="CR83" s="24" t="n"/>
+      <c r="CS83" s="24" t="n"/>
     </row>
     <row r="84" ht="36" customHeight="1">
       <c r="A84" s="24" t="inlineStr">
@@ -25005,6 +25094,7 @@
       <c r="CP84" s="24" t="n"/>
       <c r="CQ84" s="24" t="n"/>
       <c r="CR84" s="24" t="n"/>
+      <c r="CS84" s="24" t="n"/>
     </row>
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="24" t="inlineStr">
@@ -25295,6 +25385,7 @@
       <c r="CP85" s="24" t="n"/>
       <c r="CQ85" s="24" t="n"/>
       <c r="CR85" s="24" t="n"/>
+      <c r="CS85" s="24" t="n"/>
     </row>
     <row r="86" ht="36" customHeight="1">
       <c r="A86" s="24" t="inlineStr">
@@ -25585,6 +25676,7 @@
       <c r="CP86" s="24" t="n"/>
       <c r="CQ86" s="24" t="n"/>
       <c r="CR86" s="24" t="n"/>
+      <c r="CS86" s="24" t="n"/>
     </row>
     <row r="87" ht="36" customHeight="1">
       <c r="A87" s="24" t="inlineStr">
@@ -25865,6 +25957,7 @@
       <c r="CP87" s="24" t="n"/>
       <c r="CQ87" s="24" t="n"/>
       <c r="CR87" s="24" t="n"/>
+      <c r="CS87" s="24" t="n"/>
     </row>
     <row r="88" ht="36" customHeight="1">
       <c r="A88" s="24" t="inlineStr">
@@ -26155,6 +26248,7 @@
       <c r="CP88" s="24" t="n"/>
       <c r="CQ88" s="24" t="n"/>
       <c r="CR88" s="24" t="n"/>
+      <c r="CS88" s="24" t="n"/>
     </row>
     <row r="89" ht="36" customHeight="1">
       <c r="A89" s="24" t="inlineStr">
@@ -26445,6 +26539,7 @@
       <c r="CP89" s="24" t="n"/>
       <c r="CQ89" s="24" t="n"/>
       <c r="CR89" s="24" t="n"/>
+      <c r="CS89" s="24" t="n"/>
     </row>
     <row r="90" ht="36" customHeight="1">
       <c r="A90" s="24" t="inlineStr">
@@ -26735,6 +26830,7 @@
       <c r="CP90" s="24" t="n"/>
       <c r="CQ90" s="24" t="n"/>
       <c r="CR90" s="24" t="n"/>
+      <c r="CS90" s="24" t="n"/>
     </row>
     <row r="91" ht="36" customHeight="1">
       <c r="A91" s="24" t="inlineStr">
@@ -27025,6 +27121,7 @@
       <c r="CP91" s="24" t="n"/>
       <c r="CQ91" s="24" t="n"/>
       <c r="CR91" s="24" t="n"/>
+      <c r="CS91" s="24" t="n"/>
     </row>
     <row r="92" ht="36" customHeight="1">
       <c r="A92" s="24" t="inlineStr">
@@ -27315,6 +27412,7 @@
       <c r="CP92" s="24" t="n"/>
       <c r="CQ92" s="24" t="n"/>
       <c r="CR92" s="24" t="n"/>
+      <c r="CS92" s="24" t="n"/>
     </row>
     <row r="93" ht="36" customHeight="1">
       <c r="A93" s="24" t="inlineStr">
@@ -27605,6 +27703,7 @@
       <c r="CP93" s="24" t="n"/>
       <c r="CQ93" s="24" t="n"/>
       <c r="CR93" s="24" t="n"/>
+      <c r="CS93" s="24" t="n"/>
     </row>
     <row r="94" ht="36" customHeight="1">
       <c r="A94" s="24" t="inlineStr">
@@ -27895,6 +27994,7 @@
       <c r="CP94" s="24" t="n"/>
       <c r="CQ94" s="24" t="n"/>
       <c r="CR94" s="24" t="n"/>
+      <c r="CS94" s="24" t="n"/>
     </row>
     <row r="95" ht="36" customHeight="1">
       <c r="A95" s="24" t="inlineStr">
@@ -28185,6 +28285,7 @@
       <c r="CP95" s="24" t="n"/>
       <c r="CQ95" s="24" t="n"/>
       <c r="CR95" s="24" t="n"/>
+      <c r="CS95" s="24" t="n"/>
     </row>
     <row r="96" ht="36" customHeight="1">
       <c r="A96" s="24" t="inlineStr">
@@ -28475,6 +28576,7 @@
       <c r="CP96" s="24" t="n"/>
       <c r="CQ96" s="24" t="n"/>
       <c r="CR96" s="24" t="n"/>
+      <c r="CS96" s="24" t="n"/>
     </row>
     <row r="97" ht="36" customHeight="1">
       <c r="A97" s="24" t="inlineStr">
@@ -28765,6 +28867,7 @@
       <c r="CP97" s="24" t="n"/>
       <c r="CQ97" s="24" t="n"/>
       <c r="CR97" s="24" t="n"/>
+      <c r="CS97" s="24" t="n"/>
     </row>
     <row r="98" ht="36" customHeight="1">
       <c r="A98" s="24" t="inlineStr">
@@ -29055,6 +29158,7 @@
       <c r="CP98" s="24" t="n"/>
       <c r="CQ98" s="24" t="n"/>
       <c r="CR98" s="24" t="n"/>
+      <c r="CS98" s="24" t="n"/>
     </row>
     <row r="99" ht="36" customHeight="1">
       <c r="A99" s="24" t="inlineStr">
@@ -29345,6 +29449,7 @@
       <c r="CP99" s="24" t="n"/>
       <c r="CQ99" s="24" t="n"/>
       <c r="CR99" s="24" t="n"/>
+      <c r="CS99" s="24" t="n"/>
     </row>
     <row r="100" ht="36" customHeight="1">
       <c r="A100" s="24" t="inlineStr">
@@ -29634,7 +29739,8 @@
       <c r="CO100" s="24" t="n"/>
       <c r="CP100" s="24" t="n"/>
       <c r="CQ100" s="24" t="n"/>
-      <c r="CR100" s="24" t="inlineStr">
+      <c r="CR100" s="24" t="n"/>
+      <c r="CS100" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -29928,7 +30034,8 @@
       <c r="CO101" s="24" t="n"/>
       <c r="CP101" s="24" t="n"/>
       <c r="CQ101" s="24" t="n"/>
-      <c r="CR101" s="24" t="inlineStr">
+      <c r="CR101" s="24" t="n"/>
+      <c r="CS101" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -30222,7 +30329,8 @@
       <c r="CO102" s="24" t="n"/>
       <c r="CP102" s="24" t="n"/>
       <c r="CQ102" s="24" t="n"/>
-      <c r="CR102" s="24" t="inlineStr">
+      <c r="CR102" s="24" t="n"/>
+      <c r="CS102" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -30516,7 +30624,8 @@
       <c r="CO103" s="24" t="n"/>
       <c r="CP103" s="24" t="n"/>
       <c r="CQ103" s="24" t="n"/>
-      <c r="CR103" s="24" t="inlineStr">
+      <c r="CR103" s="24" t="n"/>
+      <c r="CS103" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -30810,7 +30919,8 @@
       <c r="CO104" s="24" t="n"/>
       <c r="CP104" s="24" t="n"/>
       <c r="CQ104" s="24" t="n"/>
-      <c r="CR104" s="24" t="inlineStr">
+      <c r="CR104" s="24" t="n"/>
+      <c r="CS104" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -31104,7 +31214,8 @@
       <c r="CO105" s="24" t="n"/>
       <c r="CP105" s="24" t="n"/>
       <c r="CQ105" s="24" t="n"/>
-      <c r="CR105" s="24" t="inlineStr">
+      <c r="CR105" s="24" t="n"/>
+      <c r="CS105" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -31398,7 +31509,8 @@
       <c r="CO106" s="24" t="n"/>
       <c r="CP106" s="24" t="n"/>
       <c r="CQ106" s="24" t="n"/>
-      <c r="CR106" s="24" t="inlineStr">
+      <c r="CR106" s="24" t="n"/>
+      <c r="CS106" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -31692,7 +31804,8 @@
       <c r="CO107" s="24" t="n"/>
       <c r="CP107" s="24" t="n"/>
       <c r="CQ107" s="24" t="n"/>
-      <c r="CR107" s="24" t="inlineStr">
+      <c r="CR107" s="24" t="n"/>
+      <c r="CS107" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -31986,7 +32099,8 @@
       <c r="CO108" s="24" t="n"/>
       <c r="CP108" s="24" t="n"/>
       <c r="CQ108" s="24" t="n"/>
-      <c r="CR108" s="24" t="inlineStr">
+      <c r="CR108" s="24" t="n"/>
+      <c r="CS108" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -32280,7 +32394,8 @@
       <c r="CO109" s="24" t="n"/>
       <c r="CP109" s="24" t="n"/>
       <c r="CQ109" s="24" t="n"/>
-      <c r="CR109" s="24" t="inlineStr">
+      <c r="CR109" s="24" t="n"/>
+      <c r="CS109" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -32574,7 +32689,8 @@
       <c r="CO110" s="24" t="n"/>
       <c r="CP110" s="24" t="n"/>
       <c r="CQ110" s="24" t="n"/>
-      <c r="CR110" s="24" t="inlineStr">
+      <c r="CR110" s="24" t="n"/>
+      <c r="CS110" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -32868,7 +32984,8 @@
       <c r="CO111" s="24" t="n"/>
       <c r="CP111" s="24" t="n"/>
       <c r="CQ111" s="24" t="n"/>
-      <c r="CR111" s="24" t="inlineStr">
+      <c r="CR111" s="24" t="n"/>
+      <c r="CS111" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -33162,7 +33279,8 @@
       <c r="CO112" s="24" t="n"/>
       <c r="CP112" s="24" t="n"/>
       <c r="CQ112" s="24" t="n"/>
-      <c r="CR112" s="24" t="inlineStr">
+      <c r="CR112" s="24" t="n"/>
+      <c r="CS112" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -33456,7 +33574,8 @@
       <c r="CO113" s="24" t="n"/>
       <c r="CP113" s="24" t="n"/>
       <c r="CQ113" s="24" t="n"/>
-      <c r="CR113" s="24" t="inlineStr">
+      <c r="CR113" s="24" t="n"/>
+      <c r="CS113" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -33750,7 +33869,8 @@
       <c r="CO114" s="24" t="n"/>
       <c r="CP114" s="24" t="n"/>
       <c r="CQ114" s="24" t="n"/>
-      <c r="CR114" s="24" t="inlineStr">
+      <c r="CR114" s="24" t="n"/>
+      <c r="CS114" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -34044,7 +34164,8 @@
       <c r="CO115" s="24" t="n"/>
       <c r="CP115" s="24" t="n"/>
       <c r="CQ115" s="24" t="n"/>
-      <c r="CR115" s="24" t="inlineStr">
+      <c r="CR115" s="24" t="n"/>
+      <c r="CS115" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -34338,7 +34459,8 @@
       <c r="CO116" s="24" t="n"/>
       <c r="CP116" s="24" t="n"/>
       <c r="CQ116" s="24" t="n"/>
-      <c r="CR116" s="24" t="inlineStr">
+      <c r="CR116" s="24" t="n"/>
+      <c r="CS116" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -34632,7 +34754,8 @@
       <c r="CO117" s="24" t="n"/>
       <c r="CP117" s="24" t="n"/>
       <c r="CQ117" s="24" t="n"/>
-      <c r="CR117" s="24" t="inlineStr">
+      <c r="CR117" s="24" t="n"/>
+      <c r="CS117" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -34926,7 +35049,8 @@
       <c r="CO118" s="24" t="n"/>
       <c r="CP118" s="24" t="n"/>
       <c r="CQ118" s="24" t="n"/>
-      <c r="CR118" s="24" t="inlineStr">
+      <c r="CR118" s="24" t="n"/>
+      <c r="CS118" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -35220,7 +35344,8 @@
       <c r="CO119" s="24" t="n"/>
       <c r="CP119" s="24" t="n"/>
       <c r="CQ119" s="24" t="n"/>
-      <c r="CR119" s="24" t="inlineStr">
+      <c r="CR119" s="24" t="n"/>
+      <c r="CS119" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -35514,7 +35639,8 @@
       <c r="CO120" s="24" t="n"/>
       <c r="CP120" s="24" t="n"/>
       <c r="CQ120" s="24" t="n"/>
-      <c r="CR120" s="24" t="inlineStr">
+      <c r="CR120" s="24" t="n"/>
+      <c r="CS120" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -35798,7 +35924,8 @@
       <c r="CO121" s="24" t="n"/>
       <c r="CP121" s="24" t="n"/>
       <c r="CQ121" s="24" t="n"/>
-      <c r="CR121" s="24" t="inlineStr">
+      <c r="CR121" s="24" t="n"/>
+      <c r="CS121" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -36092,7 +36219,8 @@
       <c r="CO122" s="24" t="n"/>
       <c r="CP122" s="24" t="n"/>
       <c r="CQ122" s="24" t="n"/>
-      <c r="CR122" s="24" t="inlineStr">
+      <c r="CR122" s="24" t="n"/>
+      <c r="CS122" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -36386,7 +36514,8 @@
       <c r="CO123" s="24" t="n"/>
       <c r="CP123" s="24" t="n"/>
       <c r="CQ123" s="24" t="n"/>
-      <c r="CR123" s="24" t="inlineStr">
+      <c r="CR123" s="24" t="n"/>
+      <c r="CS123" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -36680,7 +36809,8 @@
       <c r="CO124" s="24" t="n"/>
       <c r="CP124" s="24" t="n"/>
       <c r="CQ124" s="24" t="n"/>
-      <c r="CR124" s="24" t="inlineStr">
+      <c r="CR124" s="24" t="n"/>
+      <c r="CS124" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -36974,7 +37104,8 @@
       <c r="CO125" s="24" t="n"/>
       <c r="CP125" s="24" t="n"/>
       <c r="CQ125" s="24" t="n"/>
-      <c r="CR125" s="24" t="inlineStr">
+      <c r="CR125" s="24" t="n"/>
+      <c r="CS125" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -37268,7 +37399,8 @@
       <c r="CO126" s="24" t="n"/>
       <c r="CP126" s="24" t="n"/>
       <c r="CQ126" s="24" t="n"/>
-      <c r="CR126" s="24" t="inlineStr">
+      <c r="CR126" s="24" t="n"/>
+      <c r="CS126" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -37562,7 +37694,8 @@
       <c r="CO127" s="24" t="n"/>
       <c r="CP127" s="24" t="n"/>
       <c r="CQ127" s="24" t="n"/>
-      <c r="CR127" s="24" t="inlineStr">
+      <c r="CR127" s="24" t="n"/>
+      <c r="CS127" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -37856,7 +37989,8 @@
       <c r="CO128" s="24" t="n"/>
       <c r="CP128" s="24" t="n"/>
       <c r="CQ128" s="24" t="n"/>
-      <c r="CR128" s="24" t="inlineStr">
+      <c r="CR128" s="24" t="n"/>
+      <c r="CS128" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -38150,7 +38284,8 @@
       <c r="CO129" s="24" t="n"/>
       <c r="CP129" s="24" t="n"/>
       <c r="CQ129" s="24" t="n"/>
-      <c r="CR129" s="24" t="inlineStr">
+      <c r="CR129" s="24" t="n"/>
+      <c r="CS129" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -38444,7 +38579,8 @@
       <c r="CO130" s="24" t="n"/>
       <c r="CP130" s="24" t="n"/>
       <c r="CQ130" s="24" t="n"/>
-      <c r="CR130" s="24" t="inlineStr">
+      <c r="CR130" s="24" t="n"/>
+      <c r="CS130" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -38738,7 +38874,8 @@
       <c r="CO131" s="24" t="n"/>
       <c r="CP131" s="24" t="n"/>
       <c r="CQ131" s="24" t="n"/>
-      <c r="CR131" s="24" t="inlineStr">
+      <c r="CR131" s="24" t="n"/>
+      <c r="CS131" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -39032,7 +39169,8 @@
       <c r="CO132" s="24" t="n"/>
       <c r="CP132" s="24" t="n"/>
       <c r="CQ132" s="24" t="n"/>
-      <c r="CR132" s="24" t="inlineStr">
+      <c r="CR132" s="24" t="n"/>
+      <c r="CS132" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -39326,7 +39464,8 @@
       <c r="CO133" s="24" t="n"/>
       <c r="CP133" s="24" t="n"/>
       <c r="CQ133" s="24" t="n"/>
-      <c r="CR133" s="24" t="inlineStr">
+      <c r="CR133" s="24" t="n"/>
+      <c r="CS133" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -39620,7 +39759,8 @@
       <c r="CO134" s="24" t="n"/>
       <c r="CP134" s="24" t="n"/>
       <c r="CQ134" s="24" t="n"/>
-      <c r="CR134" s="24" t="inlineStr">
+      <c r="CR134" s="24" t="n"/>
+      <c r="CS134" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -39914,7 +40054,8 @@
       <c r="CO135" s="24" t="n"/>
       <c r="CP135" s="24" t="n"/>
       <c r="CQ135" s="24" t="n"/>
-      <c r="CR135" s="24" t="inlineStr">
+      <c r="CR135" s="24" t="n"/>
+      <c r="CS135" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -40208,7 +40349,8 @@
       <c r="CO136" s="24" t="n"/>
       <c r="CP136" s="24" t="n"/>
       <c r="CQ136" s="24" t="n"/>
-      <c r="CR136" s="24" t="inlineStr">
+      <c r="CR136" s="24" t="n"/>
+      <c r="CS136" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -40502,7 +40644,8 @@
       <c r="CO137" s="24" t="n"/>
       <c r="CP137" s="24" t="n"/>
       <c r="CQ137" s="24" t="n"/>
-      <c r="CR137" s="24" t="inlineStr">
+      <c r="CR137" s="24" t="n"/>
+      <c r="CS137" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -40796,7 +40939,8 @@
       <c r="CO138" s="24" t="n"/>
       <c r="CP138" s="24" t="n"/>
       <c r="CQ138" s="24" t="n"/>
-      <c r="CR138" s="24" t="inlineStr">
+      <c r="CR138" s="24" t="n"/>
+      <c r="CS138" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -41090,7 +41234,8 @@
       <c r="CO139" s="24" t="n"/>
       <c r="CP139" s="24" t="n"/>
       <c r="CQ139" s="24" t="n"/>
-      <c r="CR139" s="24" t="inlineStr">
+      <c r="CR139" s="24" t="n"/>
+      <c r="CS139" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -41384,7 +41529,8 @@
       <c r="CO140" s="24" t="n"/>
       <c r="CP140" s="24" t="n"/>
       <c r="CQ140" s="24" t="n"/>
-      <c r="CR140" s="24" t="inlineStr">
+      <c r="CR140" s="24" t="n"/>
+      <c r="CS140" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -41678,7 +41824,8 @@
       <c r="CO141" s="24" t="n"/>
       <c r="CP141" s="24" t="n"/>
       <c r="CQ141" s="24" t="n"/>
-      <c r="CR141" s="24" t="inlineStr">
+      <c r="CR141" s="24" t="n"/>
+      <c r="CS141" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -41948,7 +42095,8 @@
       <c r="CO142" s="24" t="n"/>
       <c r="CP142" s="24" t="n"/>
       <c r="CQ142" s="24" t="n"/>
-      <c r="CR142" s="24" t="inlineStr">
+      <c r="CR142" s="24" t="n"/>
+      <c r="CS142" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -42242,7 +42390,8 @@
       <c r="CO143" s="24" t="n"/>
       <c r="CP143" s="24" t="n"/>
       <c r="CQ143" s="24" t="n"/>
-      <c r="CR143" s="24" t="inlineStr">
+      <c r="CR143" s="24" t="n"/>
+      <c r="CS143" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -42536,7 +42685,8 @@
       <c r="CO144" s="24" t="n"/>
       <c r="CP144" s="24" t="n"/>
       <c r="CQ144" s="24" t="n"/>
-      <c r="CR144" s="24" t="inlineStr">
+      <c r="CR144" s="24" t="n"/>
+      <c r="CS144" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -42830,7 +42980,8 @@
       <c r="CO145" s="24" t="n"/>
       <c r="CP145" s="24" t="n"/>
       <c r="CQ145" s="24" t="n"/>
-      <c r="CR145" s="24" t="inlineStr">
+      <c r="CR145" s="24" t="n"/>
+      <c r="CS145" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -43124,7 +43275,8 @@
       <c r="CO146" s="24" t="n"/>
       <c r="CP146" s="24" t="n"/>
       <c r="CQ146" s="24" t="n"/>
-      <c r="CR146" s="24" t="inlineStr">
+      <c r="CR146" s="24" t="n"/>
+      <c r="CS146" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -43418,7 +43570,8 @@
       <c r="CO147" s="24" t="n"/>
       <c r="CP147" s="24" t="n"/>
       <c r="CQ147" s="24" t="n"/>
-      <c r="CR147" s="24" t="inlineStr">
+      <c r="CR147" s="24" t="n"/>
+      <c r="CS147" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -43712,7 +43865,8 @@
       <c r="CO148" s="24" t="n"/>
       <c r="CP148" s="24" t="n"/>
       <c r="CQ148" s="24" t="n"/>
-      <c r="CR148" s="24" t="inlineStr">
+      <c r="CR148" s="24" t="n"/>
+      <c r="CS148" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -44006,7 +44160,8 @@
       <c r="CO149" s="24" t="n"/>
       <c r="CP149" s="24" t="n"/>
       <c r="CQ149" s="24" t="n"/>
-      <c r="CR149" s="24" t="inlineStr">
+      <c r="CR149" s="24" t="n"/>
+      <c r="CS149" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -44300,7 +44455,8 @@
       <c r="CO150" s="24" t="n"/>
       <c r="CP150" s="24" t="n"/>
       <c r="CQ150" s="24" t="n"/>
-      <c r="CR150" s="24" t="inlineStr">
+      <c r="CR150" s="24" t="n"/>
+      <c r="CS150" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -44309,7 +44465,7 @@
     <row r="151" ht="36" customHeight="1">
       <c r="A151" s="24" t="inlineStr">
         <is>
-          <t>0c44e4a6dc5e44c4</t>
+          <t>b89c107ad5ba4209</t>
         </is>
       </c>
       <c r="B151" s="24" t="inlineStr">
@@ -44319,12 +44475,12 @@
       </c>
       <c r="C151" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T15:00Z</t>
+          <t>2026-08-04T09:00Z</t>
         </is>
       </c>
       <c r="D151" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182185</t>
+          <t>961-2026:182094</t>
         </is>
       </c>
       <c r="E151" s="24" t="inlineStr">
@@ -44334,12 +44490,12 @@
       </c>
       <c r="F151" s="24" t="inlineStr">
         <is>
-          <t>Jessica Bouzas Maneiro</t>
+          <t>Justina Mikulskyte</t>
         </is>
       </c>
       <c r="G151" s="24" t="inlineStr">
         <is>
-          <t>Elina Svitolina</t>
+          <t>Weronika Ewald</t>
         </is>
       </c>
       <c r="H151" s="24" t="inlineStr">
@@ -44359,28 +44515,28 @@
         </is>
       </c>
       <c r="L151" s="26" t="n">
-        <v>-525</v>
+        <v>127</v>
       </c>
       <c r="M151" s="27" t="n">
-        <v>1.190476</v>
+        <v>2.27</v>
       </c>
       <c r="N151" s="28" t="n">
-        <v>0.84</v>
+        <v>0.440529</v>
       </c>
       <c r="O151" s="28" t="n">
-        <v>0.855057</v>
+        <v>0.589516</v>
       </c>
       <c r="P151" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q151" s="28" t="n">
-        <v>0.015057</v>
+        <v>0.148987</v>
       </c>
       <c r="R151" s="26" t="n">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="S151" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T151" s="24" t="inlineStr">
         <is>
@@ -44389,21 +44545,41 @@
       </c>
       <c r="U151" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V151" s="24" t="n"/>
-      <c r="W151" s="26" t="n"/>
-      <c r="X151" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V151" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W151" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X151" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y151" s="25" t="n"/>
-      <c r="Z151" s="26" t="n"/>
-      <c r="AA151" s="28" t="n"/>
-      <c r="AB151" s="28" t="n"/>
-      <c r="AC151" s="30" t="n"/>
-      <c r="AD151" s="24" t="n"/>
+      <c r="Z151" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="AA151" s="28" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AB151" s="28" t="n">
+        <v>-0.000529</v>
+      </c>
+      <c r="AC151" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD151" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:57:31.690972Z</t>
+        </is>
+      </c>
       <c r="AE151" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Jessica Bouzas Maneiro p=0.145 vs Elina Svitolina. Executable ask 0.8400 (aec-wta-elisvi-jesman-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Justina Mikulskyte p=0.410 vs Weronika Ewald. Executable ask 0.4400 (aec-wta-werewa-jusmik-2026-08-03).</t>
         </is>
       </c>
       <c r="AF151" s="31" t="inlineStr">
@@ -44413,7 +44589,7 @@
       </c>
       <c r="AG151" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH151" s="24" t="n"/>
@@ -44439,37 +44615,37 @@
       </c>
       <c r="AO151" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP151" s="24" t="inlineStr">
         <is>
-          <t>Jessica Bouzas Maneiro</t>
+          <t>Justina Mikulskyte</t>
         </is>
       </c>
       <c r="AQ151" s="24" t="inlineStr">
         <is>
-          <t>Jessica Bouzas Maneiro</t>
+          <t>Justina Mikulskyte</t>
         </is>
       </c>
       <c r="AR151" s="24" t="inlineStr">
         <is>
-          <t>Jessica Bouzas Maneiro</t>
+          <t>Justina Mikulskyte</t>
         </is>
       </c>
       <c r="AS151" s="24" t="inlineStr">
         <is>
-          <t>Elina Svitolina</t>
+          <t>Weronika Ewald</t>
         </is>
       </c>
       <c r="AT151" s="24" t="inlineStr">
         <is>
-          <t>Elina Svitolina</t>
+          <t>Weronika Ewald</t>
         </is>
       </c>
       <c r="AU151" s="24" t="inlineStr">
         <is>
-          <t>Elina Svitolina</t>
+          <t>Weronika Ewald</t>
         </is>
       </c>
       <c r="AV151" s="24" t="n"/>
@@ -44522,7 +44698,7 @@
       </c>
       <c r="BH151" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:31.879231Z</t>
+          <t>2026-08-04T08:53:31.682126Z</t>
         </is>
       </c>
       <c r="BI151" s="24" t="inlineStr">
@@ -44532,19 +44708,23 @@
       </c>
       <c r="BJ151" s="25" t="n"/>
       <c r="BK151" s="26" t="n">
-        <v>-525</v>
+        <v>127</v>
       </c>
       <c r="BL151" s="27" t="n">
-        <v>1.190476</v>
+        <v>2.27</v>
       </c>
       <c r="BM151" s="28" t="n">
-        <v>0.84</v>
+        <v>0.440529</v>
       </c>
       <c r="BN151" s="28" t="n"/>
       <c r="BO151" s="28" t="n"/>
       <c r="BP151" s="25" t="n"/>
-      <c r="BQ151" s="27" t="n"/>
-      <c r="BR151" s="28" t="n"/>
+      <c r="BQ151" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BR151" s="28" t="n">
+        <v>0.44</v>
+      </c>
       <c r="BS151" s="28" t="n"/>
       <c r="BT151" s="28" t="n"/>
       <c r="BU151" s="25" t="n"/>
@@ -44570,7 +44750,8 @@
       <c r="CO151" s="24" t="n"/>
       <c r="CP151" s="24" t="n"/>
       <c r="CQ151" s="24" t="n"/>
-      <c r="CR151" s="24" t="inlineStr">
+      <c r="CR151" s="24" t="n"/>
+      <c r="CS151" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -44579,7 +44760,7 @@
     <row r="152" ht="36" customHeight="1">
       <c r="A152" s="24" t="inlineStr">
         <is>
-          <t>73dbe4c06f8a487c</t>
+          <t>8612244b5fd64414</t>
         </is>
       </c>
       <c r="B152" s="24" t="inlineStr">
@@ -44589,12 +44770,12 @@
       </c>
       <c r="C152" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T16:30Z</t>
+          <t>2026-08-04T09:00Z</t>
         </is>
       </c>
       <c r="D152" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182173</t>
+          <t>961-2026:182089</t>
         </is>
       </c>
       <c r="E152" s="24" t="inlineStr">
@@ -44604,12 +44785,12 @@
       </c>
       <c r="F152" s="24" t="inlineStr">
         <is>
-          <t>Diana Shnaider</t>
+          <t>Carol Young Suh Lee</t>
         </is>
       </c>
       <c r="G152" s="24" t="inlineStr">
         <is>
-          <t>Rebecca Sramkova</t>
+          <t>Elsa Jacquemot</t>
         </is>
       </c>
       <c r="H152" s="24" t="inlineStr">
@@ -44629,51 +44810,71 @@
         </is>
       </c>
       <c r="L152" s="26" t="n">
-        <v>-426</v>
+        <v>-163</v>
       </c>
       <c r="M152" s="27" t="n">
-        <v>1.234742</v>
+        <v>1.613497</v>
       </c>
       <c r="N152" s="28" t="n">
-        <v>0.809886</v>
+        <v>0.619772</v>
       </c>
       <c r="O152" s="28" t="n">
-        <v>0.69013</v>
+        <v>0.60078</v>
       </c>
       <c r="P152" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q152" s="28" t="n">
-        <v>-0.119756</v>
+        <v>-0.018992</v>
       </c>
       <c r="R152" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="S152" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T152" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U152" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V152" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W152" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X152" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="S152" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T152" s="24" t="inlineStr">
-        <is>
-          <t>tennis-surface-elo-v1</t>
-        </is>
-      </c>
-      <c r="U152" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V152" s="24" t="n"/>
-      <c r="W152" s="26" t="n"/>
-      <c r="X152" s="26" t="n"/>
       <c r="Y152" s="25" t="n"/>
-      <c r="Z152" s="26" t="n"/>
-      <c r="AA152" s="28" t="n"/>
-      <c r="AB152" s="28" t="n"/>
-      <c r="AC152" s="30" t="n"/>
-      <c r="AD152" s="24" t="n"/>
+      <c r="Z152" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="AA152" s="28" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AB152" s="28" t="n">
+        <v>0.000228</v>
+      </c>
+      <c r="AC152" s="30" t="n">
+        <v>0.7669</v>
+      </c>
+      <c r="AD152" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:57:32.547692Z</t>
+        </is>
+      </c>
       <c r="AE152" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Diana Shnaider p=0.690 vs Rebecca Sramkova. Executable ask 0.8100 (aec-wta-rebsra-diashn-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Carol Young Suh Lee p=0.601 vs Elsa Jacquemot. Executable ask 0.6200 (aec-wta-elsjac-carlee-2026-08-03).</t>
         </is>
       </c>
       <c r="AF152" s="31" t="inlineStr">
@@ -44714,32 +44915,32 @@
       </c>
       <c r="AP152" s="24" t="inlineStr">
         <is>
-          <t>Diana Shnaider</t>
+          <t>Carol Young Suh Lee</t>
         </is>
       </c>
       <c r="AQ152" s="24" t="inlineStr">
         <is>
-          <t>Diana Shnaider</t>
+          <t>Carol Young Suh Lee</t>
         </is>
       </c>
       <c r="AR152" s="24" t="inlineStr">
         <is>
-          <t>Diana Shnaider</t>
+          <t>Carol Young Suh Lee</t>
         </is>
       </c>
       <c r="AS152" s="24" t="inlineStr">
         <is>
-          <t>Rebecca Sramkova</t>
+          <t>Elsa Jacquemot</t>
         </is>
       </c>
       <c r="AT152" s="24" t="inlineStr">
         <is>
-          <t>Rebecca Sramkova</t>
+          <t>Elsa Jacquemot</t>
         </is>
       </c>
       <c r="AU152" s="24" t="inlineStr">
         <is>
-          <t>Rebecca Sramkova</t>
+          <t>Elsa Jacquemot</t>
         </is>
       </c>
       <c r="AV152" s="24" t="n"/>
@@ -44792,7 +44993,7 @@
       </c>
       <c r="BH152" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:33.928684Z</t>
+          <t>2026-08-04T08:53:31.683641Z</t>
         </is>
       </c>
       <c r="BI152" s="24" t="inlineStr">
@@ -44802,19 +45003,23 @@
       </c>
       <c r="BJ152" s="25" t="n"/>
       <c r="BK152" s="26" t="n">
-        <v>-426</v>
+        <v>-163</v>
       </c>
       <c r="BL152" s="27" t="n">
-        <v>1.234742</v>
+        <v>1.613497</v>
       </c>
       <c r="BM152" s="28" t="n">
-        <v>0.809886</v>
+        <v>0.619772</v>
       </c>
       <c r="BN152" s="28" t="n"/>
       <c r="BO152" s="28" t="n"/>
       <c r="BP152" s="25" t="n"/>
-      <c r="BQ152" s="27" t="n"/>
-      <c r="BR152" s="28" t="n"/>
+      <c r="BQ152" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BR152" s="28" t="n">
+        <v>0.62</v>
+      </c>
       <c r="BS152" s="28" t="n"/>
       <c r="BT152" s="28" t="n"/>
       <c r="BU152" s="25" t="n"/>
@@ -44840,7 +45045,8 @@
       <c r="CO152" s="24" t="n"/>
       <c r="CP152" s="24" t="n"/>
       <c r="CQ152" s="24" t="n"/>
-      <c r="CR152" s="24" t="inlineStr">
+      <c r="CR152" s="24" t="n"/>
+      <c r="CS152" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -44849,7 +45055,7 @@
     <row r="153" ht="36" customHeight="1">
       <c r="A153" s="24" t="inlineStr">
         <is>
-          <t>5ae550dd6a2342d3</t>
+          <t>a89260ea60b44bd5</t>
         </is>
       </c>
       <c r="B153" s="24" t="inlineStr">
@@ -44859,12 +45065,12 @@
       </c>
       <c r="C153" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T16:30Z</t>
+          <t>2026-08-04T09:00Z</t>
         </is>
       </c>
       <c r="D153" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182175</t>
+          <t>961-2026:182083</t>
         </is>
       </c>
       <c r="E153" s="24" t="inlineStr">
@@ -44874,12 +45080,12 @@
       </c>
       <c r="F153" s="24" t="inlineStr">
         <is>
-          <t>Viktorija Golubic</t>
+          <t>Susan Bandecchi</t>
         </is>
       </c>
       <c r="G153" s="24" t="inlineStr">
         <is>
-          <t>Donna Vekic</t>
+          <t>Viktoria Hruncakova</t>
         </is>
       </c>
       <c r="H153" s="24" t="inlineStr">
@@ -44889,7 +45095,7 @@
       </c>
       <c r="I153" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J153" s="25" t="n"/>
@@ -44899,28 +45105,28 @@
         </is>
       </c>
       <c r="L153" s="26" t="n">
-        <v>-133</v>
+        <v>100</v>
       </c>
       <c r="M153" s="27" t="n">
-        <v>1.75188</v>
+        <v>2</v>
       </c>
       <c r="N153" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.5</v>
       </c>
       <c r="O153" s="28" t="n">
-        <v>0.600871</v>
+        <v>0.548768</v>
       </c>
       <c r="P153" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q153" s="28" t="n">
-        <v>0.030056</v>
+        <v>0.048768</v>
       </c>
       <c r="R153" s="26" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S153" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T153" s="24" t="inlineStr">
         <is>
@@ -44929,21 +45135,41 @@
       </c>
       <c r="U153" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V153" s="24" t="n"/>
-      <c r="W153" s="26" t="n"/>
-      <c r="X153" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V153" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W153" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X153" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y153" s="25" t="n"/>
-      <c r="Z153" s="26" t="n"/>
-      <c r="AA153" s="28" t="n"/>
-      <c r="AB153" s="28" t="n"/>
-      <c r="AC153" s="30" t="n"/>
-      <c r="AD153" s="24" t="n"/>
+      <c r="Z153" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA153" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB153" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC153" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD153" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:57:33.428422Z</t>
+        </is>
+      </c>
       <c r="AE153" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Viktorija Golubic p=0.399 vs Donna Vekic. Executable ask 0.5700 (aec-wta-donvek-vikgol-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Susan Bandecchi p=0.549 vs Viktoria Hruncakova. Executable ask 0.5000 (aec-wta-vikhru-susban-2026-08-03).</t>
         </is>
       </c>
       <c r="AF153" s="31" t="inlineStr">
@@ -44984,32 +45210,32 @@
       </c>
       <c r="AP153" s="24" t="inlineStr">
         <is>
-          <t>Viktorija Golubic</t>
+          <t>Susan Bandecchi</t>
         </is>
       </c>
       <c r="AQ153" s="24" t="inlineStr">
         <is>
-          <t>Viktorija Golubic</t>
+          <t>Susan Bandecchi</t>
         </is>
       </c>
       <c r="AR153" s="24" t="inlineStr">
         <is>
-          <t>Viktorija Golubic</t>
+          <t>Susan Bandecchi</t>
         </is>
       </c>
       <c r="AS153" s="24" t="inlineStr">
         <is>
-          <t>Donna Vekic</t>
+          <t>Viktoria Hruncakova</t>
         </is>
       </c>
       <c r="AT153" s="24" t="inlineStr">
         <is>
-          <t>Donna Vekic</t>
+          <t>Viktoria Hruncakova</t>
         </is>
       </c>
       <c r="AU153" s="24" t="inlineStr">
         <is>
-          <t>Donna Vekic</t>
+          <t>Viktoria Hruncakova</t>
         </is>
       </c>
       <c r="AV153" s="24" t="n"/>
@@ -45062,7 +45288,7 @@
       </c>
       <c r="BH153" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:34.336934Z</t>
+          <t>2026-08-04T08:53:31.509930Z</t>
         </is>
       </c>
       <c r="BI153" s="24" t="inlineStr">
@@ -45072,19 +45298,23 @@
       </c>
       <c r="BJ153" s="25" t="n"/>
       <c r="BK153" s="26" t="n">
-        <v>-133</v>
+        <v>100</v>
       </c>
       <c r="BL153" s="27" t="n">
-        <v>1.75188</v>
+        <v>2</v>
       </c>
       <c r="BM153" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.5</v>
       </c>
       <c r="BN153" s="28" t="n"/>
       <c r="BO153" s="28" t="n"/>
       <c r="BP153" s="25" t="n"/>
-      <c r="BQ153" s="27" t="n"/>
-      <c r="BR153" s="28" t="n"/>
+      <c r="BQ153" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR153" s="28" t="n">
+        <v>0.5</v>
+      </c>
       <c r="BS153" s="28" t="n"/>
       <c r="BT153" s="28" t="n"/>
       <c r="BU153" s="25" t="n"/>
@@ -45110,7 +45340,8 @@
       <c r="CO153" s="24" t="n"/>
       <c r="CP153" s="24" t="n"/>
       <c r="CQ153" s="24" t="n"/>
-      <c r="CR153" s="24" t="inlineStr">
+      <c r="CR153" s="24" t="n"/>
+      <c r="CS153" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -45119,7 +45350,7 @@
     <row r="154" ht="36" customHeight="1">
       <c r="A154" s="24" t="inlineStr">
         <is>
-          <t>74e5f6a58aa04f5a</t>
+          <t>1b49058ee90f436d</t>
         </is>
       </c>
       <c r="B154" s="24" t="inlineStr">
@@ -45129,12 +45360,12 @@
       </c>
       <c r="C154" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T16:30Z</t>
+          <t>2026-08-04T10:30Z</t>
         </is>
       </c>
       <c r="D154" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182182</t>
+          <t>961-2026:182091</t>
         </is>
       </c>
       <c r="E154" s="24" t="inlineStr">
@@ -45144,12 +45375,12 @@
       </c>
       <c r="F154" s="24" t="inlineStr">
         <is>
-          <t>Iga Swiatek</t>
+          <t>Vendula Valdmannova</t>
         </is>
       </c>
       <c r="G154" s="24" t="inlineStr">
         <is>
-          <t>Sara Bejlek</t>
+          <t>Marcelina Podlinska</t>
         </is>
       </c>
       <c r="H154" s="24" t="inlineStr">
@@ -45169,28 +45400,28 @@
         </is>
       </c>
       <c r="L154" s="26" t="n">
-        <v>-900</v>
+        <v>-525</v>
       </c>
       <c r="M154" s="27" t="n">
-        <v>1.111111</v>
+        <v>1.190476</v>
       </c>
       <c r="N154" s="28" t="n">
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
       <c r="O154" s="28" t="n">
-        <v>0.745582</v>
+        <v>0.601999</v>
       </c>
       <c r="P154" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q154" s="28" t="n">
-        <v>-0.154418</v>
+        <v>-0.238001</v>
       </c>
       <c r="R154" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S154" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T154" s="24" t="inlineStr">
         <is>
@@ -45199,21 +45430,41 @@
       </c>
       <c r="U154" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V154" s="24" t="n"/>
-      <c r="W154" s="26" t="n"/>
-      <c r="X154" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V154" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W154" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X154" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y154" s="25" t="n"/>
-      <c r="Z154" s="26" t="n"/>
-      <c r="AA154" s="28" t="n"/>
-      <c r="AB154" s="28" t="n"/>
-      <c r="AC154" s="30" t="n"/>
-      <c r="AD154" s="24" t="n"/>
+      <c r="Z154" s="26" t="n">
+        <v>-525</v>
+      </c>
+      <c r="AA154" s="28" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AB154" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC154" s="30" t="n">
+        <v>0.2381</v>
+      </c>
+      <c r="AD154" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:02:58.204431Z</t>
+        </is>
+      </c>
       <c r="AE154" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Iga Swiatek p=0.746 vs Sara Bejlek. Executable ask 0.9000 (aec-wta-sarbej-igaswi-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Vendula Valdmannova p=0.602 vs Marcelina Podlinska. Executable ask 0.8400 (aec-wta-marpod-venval-2026-08-04).</t>
         </is>
       </c>
       <c r="AF154" s="31" t="inlineStr">
@@ -45249,37 +45500,37 @@
       </c>
       <c r="AO154" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP154" s="24" t="inlineStr">
         <is>
-          <t>Iga Swiatek</t>
+          <t>Vendula Valdmannova</t>
         </is>
       </c>
       <c r="AQ154" s="24" t="inlineStr">
         <is>
-          <t>Iga Swiatek</t>
+          <t>Vendula Valdmannova</t>
         </is>
       </c>
       <c r="AR154" s="24" t="inlineStr">
         <is>
-          <t>Iga Swiatek</t>
+          <t>Vendula Valdmannova</t>
         </is>
       </c>
       <c r="AS154" s="24" t="inlineStr">
         <is>
-          <t>Sara Bejlek</t>
+          <t>Marcelina Podlinska</t>
         </is>
       </c>
       <c r="AT154" s="24" t="inlineStr">
         <is>
-          <t>Sara Bejlek</t>
+          <t>Marcelina Podlinska</t>
         </is>
       </c>
       <c r="AU154" s="24" t="inlineStr">
         <is>
-          <t>Sara Bejlek</t>
+          <t>Marcelina Podlinska</t>
         </is>
       </c>
       <c r="AV154" s="24" t="n"/>
@@ -45332,7 +45583,7 @@
       </c>
       <c r="BH154" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:32.830493Z</t>
+          <t>2026-08-04T08:53:31.401094Z</t>
         </is>
       </c>
       <c r="BI154" s="24" t="inlineStr">
@@ -45342,19 +45593,23 @@
       </c>
       <c r="BJ154" s="25" t="n"/>
       <c r="BK154" s="26" t="n">
-        <v>-900</v>
+        <v>-525</v>
       </c>
       <c r="BL154" s="27" t="n">
-        <v>1.111111</v>
+        <v>1.190476</v>
       </c>
       <c r="BM154" s="28" t="n">
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
       <c r="BN154" s="28" t="n"/>
       <c r="BO154" s="28" t="n"/>
       <c r="BP154" s="25" t="n"/>
-      <c r="BQ154" s="27" t="n"/>
-      <c r="BR154" s="28" t="n"/>
+      <c r="BQ154" s="27" t="n">
+        <v>1.190476</v>
+      </c>
+      <c r="BR154" s="28" t="n">
+        <v>0.84</v>
+      </c>
       <c r="BS154" s="28" t="n"/>
       <c r="BT154" s="28" t="n"/>
       <c r="BU154" s="25" t="n"/>
@@ -45380,7 +45635,8 @@
       <c r="CO154" s="24" t="n"/>
       <c r="CP154" s="24" t="n"/>
       <c r="CQ154" s="24" t="n"/>
-      <c r="CR154" s="24" t="inlineStr">
+      <c r="CR154" s="24" t="n"/>
+      <c r="CS154" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -45389,7 +45645,7 @@
     <row r="155" ht="36" customHeight="1">
       <c r="A155" s="24" t="inlineStr">
         <is>
-          <t>1d7331980093468b</t>
+          <t>947f11183dd046dd</t>
         </is>
       </c>
       <c r="B155" s="24" t="inlineStr">
@@ -45399,12 +45655,12 @@
       </c>
       <c r="C155" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T16:30Z</t>
+          <t>2026-08-04T10:30Z</t>
         </is>
       </c>
       <c r="D155" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182207</t>
+          <t>961-2026:182092</t>
         </is>
       </c>
       <c r="E155" s="24" t="inlineStr">
@@ -45414,12 +45670,12 @@
       </c>
       <c r="F155" s="24" t="inlineStr">
         <is>
-          <t>Ekaterina Alexandrova</t>
+          <t>Ella Seidel</t>
         </is>
       </c>
       <c r="G155" s="24" t="inlineStr">
         <is>
-          <t>Camila Osorio</t>
+          <t>Dalma Galfi</t>
         </is>
       </c>
       <c r="H155" s="24" t="inlineStr">
@@ -45439,25 +45695,25 @@
         </is>
       </c>
       <c r="L155" s="26" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="M155" s="27" t="n">
-        <v>1.961538</v>
+        <v>2</v>
       </c>
       <c r="N155" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.5</v>
       </c>
       <c r="O155" s="28" t="n">
-        <v>0.533657</v>
+        <v>0.511713</v>
       </c>
       <c r="P155" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q155" s="28" t="n">
-        <v>0.023853</v>
+        <v>0.011713</v>
       </c>
       <c r="R155" s="26" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="S155" s="29" t="n">
         <v>1</v>
@@ -45469,21 +45725,41 @@
       </c>
       <c r="U155" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V155" s="24" t="n"/>
-      <c r="W155" s="26" t="n"/>
-      <c r="X155" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V155" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W155" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X155" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y155" s="25" t="n"/>
-      <c r="Z155" s="26" t="n"/>
-      <c r="AA155" s="28" t="n"/>
-      <c r="AB155" s="28" t="n"/>
-      <c r="AC155" s="30" t="n"/>
-      <c r="AD155" s="24" t="n"/>
+      <c r="Z155" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA155" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB155" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC155" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD155" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:02:59.155087Z</t>
+        </is>
+      </c>
       <c r="AE155" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Ekaterina Alexandrova p=0.466 vs Camila Osorio. Executable ask 0.5100 (aec-wta-camoso-ekaale-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Ella Seidel p=0.488 vs Dalma Galfi. Executable ask 0.5000 (aec-wta-dalgal-ellsei-2026-08-03).</t>
         </is>
       </c>
       <c r="AF155" s="31" t="inlineStr">
@@ -45493,7 +45769,7 @@
       </c>
       <c r="AG155" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH155" s="24" t="n"/>
@@ -45524,32 +45800,32 @@
       </c>
       <c r="AP155" s="24" t="inlineStr">
         <is>
-          <t>Ekaterina Alexandrova</t>
+          <t>Ella Seidel</t>
         </is>
       </c>
       <c r="AQ155" s="24" t="inlineStr">
         <is>
-          <t>Ekaterina Alexandrova</t>
+          <t>Ella Seidel</t>
         </is>
       </c>
       <c r="AR155" s="24" t="inlineStr">
         <is>
-          <t>Ekaterina Alexandrova</t>
+          <t>Ella Seidel</t>
         </is>
       </c>
       <c r="AS155" s="24" t="inlineStr">
         <is>
-          <t>Camila Osorio</t>
+          <t>Dalma Galfi</t>
         </is>
       </c>
       <c r="AT155" s="24" t="inlineStr">
         <is>
-          <t>Camila Osorio</t>
+          <t>Dalma Galfi</t>
         </is>
       </c>
       <c r="AU155" s="24" t="inlineStr">
         <is>
-          <t>Camila Osorio</t>
+          <t>Dalma Galfi</t>
         </is>
       </c>
       <c r="AV155" s="24" t="n"/>
@@ -45602,7 +45878,7 @@
       </c>
       <c r="BH155" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:34.995635Z</t>
+          <t>2026-08-04T08:53:31.615874Z</t>
         </is>
       </c>
       <c r="BI155" s="24" t="inlineStr">
@@ -45612,19 +45888,23 @@
       </c>
       <c r="BJ155" s="25" t="n"/>
       <c r="BK155" s="26" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="BL155" s="27" t="n">
-        <v>1.961538</v>
+        <v>2</v>
       </c>
       <c r="BM155" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.5</v>
       </c>
       <c r="BN155" s="28" t="n"/>
       <c r="BO155" s="28" t="n"/>
       <c r="BP155" s="25" t="n"/>
-      <c r="BQ155" s="27" t="n"/>
-      <c r="BR155" s="28" t="n"/>
+      <c r="BQ155" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR155" s="28" t="n">
+        <v>0.5</v>
+      </c>
       <c r="BS155" s="28" t="n"/>
       <c r="BT155" s="28" t="n"/>
       <c r="BU155" s="25" t="n"/>
@@ -45650,7 +45930,8 @@
       <c r="CO155" s="24" t="n"/>
       <c r="CP155" s="24" t="n"/>
       <c r="CQ155" s="24" t="n"/>
-      <c r="CR155" s="24" t="inlineStr">
+      <c r="CR155" s="24" t="n"/>
+      <c r="CS155" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -45659,7 +45940,7 @@
     <row r="156" ht="36" customHeight="1">
       <c r="A156" s="24" t="inlineStr">
         <is>
-          <t>4049f26a9ae043d4</t>
+          <t>f525da2ffd0e4936</t>
         </is>
       </c>
       <c r="B156" s="24" t="inlineStr">
@@ -45669,12 +45950,12 @@
       </c>
       <c r="C156" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T18:00Z</t>
+          <t>2026-08-04T10:30Z</t>
         </is>
       </c>
       <c r="D156" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182166</t>
+          <t>961-2026:182088</t>
         </is>
       </c>
       <c r="E156" s="24" t="inlineStr">
@@ -45684,12 +45965,12 @@
       </c>
       <c r="F156" s="24" t="inlineStr">
         <is>
-          <t>Madison Keys</t>
+          <t>Elizara Yaneva</t>
         </is>
       </c>
       <c r="G156" s="24" t="inlineStr">
         <is>
-          <t>Antonia Ruzic</t>
+          <t>Linda Klimovicova</t>
         </is>
       </c>
       <c r="H156" s="24" t="inlineStr">
@@ -45699,7 +45980,7 @@
       </c>
       <c r="I156" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J156" s="25" t="n"/>
@@ -45709,28 +45990,28 @@
         </is>
       </c>
       <c r="L156" s="26" t="n">
-        <v>-355</v>
+        <v>-104</v>
       </c>
       <c r="M156" s="27" t="n">
-        <v>1.28169</v>
+        <v>1.961538</v>
       </c>
       <c r="N156" s="28" t="n">
-        <v>0.78022</v>
+        <v>0.509804</v>
       </c>
       <c r="O156" s="28" t="n">
-        <v>0.771595</v>
+        <v>0.578623</v>
       </c>
       <c r="P156" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q156" s="28" t="n">
-        <v>-0.008625000000000001</v>
+        <v>0.06881900000000001</v>
       </c>
       <c r="R156" s="26" t="n">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="S156" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T156" s="24" t="inlineStr">
         <is>
@@ -45739,21 +46020,41 @@
       </c>
       <c r="U156" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V156" s="24" t="n"/>
-      <c r="W156" s="26" t="n"/>
-      <c r="X156" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V156" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W156" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X156" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y156" s="25" t="n"/>
-      <c r="Z156" s="26" t="n"/>
-      <c r="AA156" s="28" t="n"/>
-      <c r="AB156" s="28" t="n"/>
-      <c r="AC156" s="30" t="n"/>
-      <c r="AD156" s="24" t="n"/>
+      <c r="Z156" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="AA156" s="28" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AB156" s="28" t="n">
+        <v>0.000196</v>
+      </c>
+      <c r="AC156" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD156" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:03:00.110823Z</t>
+        </is>
+      </c>
       <c r="AE156" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Madison Keys p=0.772 vs Antonia Ruzic. Executable ask 0.7800 (aec-wta-antruz-madkey-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Elizara Yaneva p=0.421 vs Linda Klimovicova. Executable ask 0.5100 (aec-wta-linkli-eliyan-2026-08-03).</t>
         </is>
       </c>
       <c r="AF156" s="31" t="inlineStr">
@@ -45763,7 +46064,7 @@
       </c>
       <c r="AG156" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH156" s="24" t="n"/>
@@ -45771,7 +46072,7 @@
       <c r="AJ156" s="31" t="n"/>
       <c r="AK156" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL156" s="26" t="n">
@@ -45779,47 +46080,47 @@
       </c>
       <c r="AM156" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN156" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO156" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP156" s="24" t="inlineStr">
         <is>
-          <t>Madison Keys</t>
+          <t>Elizara Yaneva</t>
         </is>
       </c>
       <c r="AQ156" s="24" t="inlineStr">
         <is>
-          <t>Madison Keys</t>
+          <t>Elizara Yaneva</t>
         </is>
       </c>
       <c r="AR156" s="24" t="inlineStr">
         <is>
-          <t>Madison Keys</t>
+          <t>Elizara Yaneva</t>
         </is>
       </c>
       <c r="AS156" s="24" t="inlineStr">
         <is>
-          <t>Antonia Ruzic</t>
+          <t>Linda Klimovicova</t>
         </is>
       </c>
       <c r="AT156" s="24" t="inlineStr">
         <is>
-          <t>Antonia Ruzic</t>
+          <t>Linda Klimovicova</t>
         </is>
       </c>
       <c r="AU156" s="24" t="inlineStr">
         <is>
-          <t>Antonia Ruzic</t>
+          <t>Linda Klimovicova</t>
         </is>
       </c>
       <c r="AV156" s="24" t="n"/>
@@ -45872,7 +46173,7 @@
       </c>
       <c r="BH156" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:37.895879Z</t>
+          <t>2026-08-04T08:53:31.464146Z</t>
         </is>
       </c>
       <c r="BI156" s="24" t="inlineStr">
@@ -45882,19 +46183,23 @@
       </c>
       <c r="BJ156" s="25" t="n"/>
       <c r="BK156" s="26" t="n">
-        <v>-355</v>
+        <v>-104</v>
       </c>
       <c r="BL156" s="27" t="n">
-        <v>1.28169</v>
+        <v>1.961538</v>
       </c>
       <c r="BM156" s="28" t="n">
-        <v>0.78022</v>
+        <v>0.509804</v>
       </c>
       <c r="BN156" s="28" t="n"/>
       <c r="BO156" s="28" t="n"/>
       <c r="BP156" s="25" t="n"/>
-      <c r="BQ156" s="27" t="n"/>
-      <c r="BR156" s="28" t="n"/>
+      <c r="BQ156" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BR156" s="28" t="n">
+        <v>0.51</v>
+      </c>
       <c r="BS156" s="28" t="n"/>
       <c r="BT156" s="28" t="n"/>
       <c r="BU156" s="25" t="n"/>
@@ -45920,31 +46225,32 @@
       <c r="CO156" s="24" t="n"/>
       <c r="CP156" s="24" t="n"/>
       <c r="CQ156" s="24" t="n"/>
-      <c r="CR156" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR156" s="24" t="n"/>
+      <c r="CS156" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="157" ht="36" customHeight="1">
       <c r="A157" s="24" t="inlineStr">
         <is>
-          <t>d554bd1fdcdc44d1</t>
+          <t>4d47856d25dc49a4</t>
         </is>
       </c>
       <c r="B157" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T12:00:14.325736Z</t>
         </is>
       </c>
       <c r="C157" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T18:00Z</t>
+          <t>2026-08-04T12:20Z</t>
         </is>
       </c>
       <c r="D157" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182194</t>
+          <t>961-2026:182096</t>
         </is>
       </c>
       <c r="E157" s="24" t="inlineStr">
@@ -45954,12 +46260,12 @@
       </c>
       <c r="F157" s="24" t="inlineStr">
         <is>
-          <t>Katherine Sebov</t>
+          <t>Sofia Costoulas</t>
         </is>
       </c>
       <c r="G157" s="24" t="inlineStr">
         <is>
-          <t>Marta Kostyuk</t>
+          <t>Gabriela Knutson</t>
         </is>
       </c>
       <c r="H157" s="24" t="inlineStr">
@@ -45969,7 +46275,7 @@
       </c>
       <c r="I157" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J157" s="25" t="n"/>
@@ -45979,28 +46285,28 @@
         </is>
       </c>
       <c r="L157" s="26" t="n">
-        <v>-1900</v>
+        <v>-170</v>
       </c>
       <c r="M157" s="27" t="n">
-        <v>1.052632</v>
+        <v>1.588235</v>
       </c>
       <c r="N157" s="28" t="n">
-        <v>0.95</v>
+        <v>0.62963</v>
       </c>
       <c r="O157" s="28" t="n">
-        <v>0.886886</v>
+        <v>0.5347150000000001</v>
       </c>
       <c r="P157" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q157" s="28" t="n">
-        <v>-0.063114</v>
+        <v>-0.094915</v>
       </c>
       <c r="R157" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S157" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T157" s="24" t="inlineStr">
         <is>
@@ -46009,21 +46315,41 @@
       </c>
       <c r="U157" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V157" s="24" t="n"/>
-      <c r="W157" s="26" t="n"/>
-      <c r="X157" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V157" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W157" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X157" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y157" s="25" t="n"/>
-      <c r="Z157" s="26" t="n"/>
-      <c r="AA157" s="28" t="n"/>
-      <c r="AB157" s="28" t="n"/>
-      <c r="AC157" s="30" t="n"/>
-      <c r="AD157" s="24" t="n"/>
+      <c r="Z157" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="AA157" s="28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB157" s="28" t="n">
+        <v>0.00037</v>
+      </c>
+      <c r="AC157" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD157" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:03:01.006466Z</t>
+        </is>
+      </c>
       <c r="AE157" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Katherine Sebov p=0.113 vs Marta Kostyuk. Executable ask 0.9500 (aec-wta-markos-katseb-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Sofia Costoulas p=0.535 vs Gabriela Knutson. Executable ask 0.6300 (aec-wta-gabknu-sofcos-2026-08-03).</t>
         </is>
       </c>
       <c r="AF157" s="31" t="inlineStr">
@@ -46033,7 +46359,7 @@
       </c>
       <c r="AG157" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH157" s="24" t="n"/>
@@ -46064,32 +46390,32 @@
       </c>
       <c r="AP157" s="24" t="inlineStr">
         <is>
-          <t>Katherine Sebov</t>
+          <t>Sofia Costoulas</t>
         </is>
       </c>
       <c r="AQ157" s="24" t="inlineStr">
         <is>
-          <t>Katherine Sebov</t>
+          <t>Sofia Costoulas</t>
         </is>
       </c>
       <c r="AR157" s="24" t="inlineStr">
         <is>
-          <t>Katherine Sebov</t>
+          <t>Sofia Costoulas</t>
         </is>
       </c>
       <c r="AS157" s="24" t="inlineStr">
         <is>
-          <t>Marta Kostyuk</t>
+          <t>Gabriela Knutson</t>
         </is>
       </c>
       <c r="AT157" s="24" t="inlineStr">
         <is>
-          <t>Marta Kostyuk</t>
+          <t>Gabriela Knutson</t>
         </is>
       </c>
       <c r="AU157" s="24" t="inlineStr">
         <is>
-          <t>Marta Kostyuk</t>
+          <t>Gabriela Knutson</t>
         </is>
       </c>
       <c r="AV157" s="24" t="n"/>
@@ -46142,7 +46468,7 @@
       </c>
       <c r="BH157" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:36.220323Z</t>
+          <t>2026-08-04T11:58:51.342720Z</t>
         </is>
       </c>
       <c r="BI157" s="24" t="inlineStr">
@@ -46152,19 +46478,23 @@
       </c>
       <c r="BJ157" s="25" t="n"/>
       <c r="BK157" s="26" t="n">
-        <v>-1900</v>
+        <v>-170</v>
       </c>
       <c r="BL157" s="27" t="n">
-        <v>1.052632</v>
+        <v>1.588235</v>
       </c>
       <c r="BM157" s="28" t="n">
-        <v>0.95</v>
+        <v>0.62963</v>
       </c>
       <c r="BN157" s="28" t="n"/>
       <c r="BO157" s="28" t="n"/>
       <c r="BP157" s="25" t="n"/>
-      <c r="BQ157" s="27" t="n"/>
-      <c r="BR157" s="28" t="n"/>
+      <c r="BQ157" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BR157" s="28" t="n">
+        <v>0.63</v>
+      </c>
       <c r="BS157" s="28" t="n"/>
       <c r="BT157" s="28" t="n"/>
       <c r="BU157" s="25" t="n"/>
@@ -46190,7 +46520,8 @@
       <c r="CO157" s="24" t="n"/>
       <c r="CP157" s="24" t="n"/>
       <c r="CQ157" s="24" t="n"/>
-      <c r="CR157" s="24" t="inlineStr">
+      <c r="CR157" s="24" t="n"/>
+      <c r="CS157" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -46199,22 +46530,22 @@
     <row r="158" ht="36" customHeight="1">
       <c r="A158" s="24" t="inlineStr">
         <is>
-          <t>c8283c1120c74910</t>
+          <t>bfb700c9bc36404e</t>
         </is>
       </c>
       <c r="B158" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T12:00:14.325736Z</t>
         </is>
       </c>
       <c r="C158" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T18:00Z</t>
+          <t>2026-08-04T12:30Z</t>
         </is>
       </c>
       <c r="D158" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182202</t>
+          <t>961-2026:182082</t>
         </is>
       </c>
       <c r="E158" s="24" t="inlineStr">
@@ -46224,12 +46555,12 @@
       </c>
       <c r="F158" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Mona Barthel</t>
         </is>
       </c>
       <c r="G158" s="24" t="inlineStr">
         <is>
-          <t>Maja Chwalinska</t>
+          <t>Laura Samson</t>
         </is>
       </c>
       <c r="H158" s="24" t="inlineStr">
@@ -46249,28 +46580,28 @@
         </is>
       </c>
       <c r="L158" s="26" t="n">
-        <v>133</v>
+        <v>-223</v>
       </c>
       <c r="M158" s="27" t="n">
-        <v>2.33</v>
+        <v>1.44843</v>
       </c>
       <c r="N158" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.690402</v>
       </c>
       <c r="O158" s="28" t="n">
-        <v>0.623502</v>
+        <v>0.523723</v>
       </c>
       <c r="P158" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q158" s="28" t="n">
-        <v>0.194317</v>
+        <v>-0.166679</v>
       </c>
       <c r="R158" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S158" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T158" s="24" t="inlineStr">
         <is>
@@ -46279,21 +46610,41 @@
       </c>
       <c r="U158" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V158" s="24" t="n"/>
-      <c r="W158" s="26" t="n"/>
-      <c r="X158" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V158" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W158" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X158" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y158" s="25" t="n"/>
-      <c r="Z158" s="26" t="n"/>
-      <c r="AA158" s="28" t="n"/>
-      <c r="AB158" s="28" t="n"/>
-      <c r="AC158" s="30" t="n"/>
-      <c r="AD158" s="24" t="n"/>
+      <c r="Z158" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="AA158" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AB158" s="28" t="n">
+        <v>-0.000402</v>
+      </c>
+      <c r="AC158" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD158" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:21:54.127318Z</t>
+        </is>
+      </c>
       <c r="AE158" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Talia Gibson p=0.376 vs Maja Chwalinska. Executable ask 0.4300 (aec-wta-majchw-talgib-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Mona Barthel p=0.476 vs Laura Samson. Executable ask 0.6900 (aec-wta-lausam-monbar-2026-08-03).</t>
         </is>
       </c>
       <c r="AF158" s="31" t="inlineStr">
@@ -46303,7 +46654,7 @@
       </c>
       <c r="AG158" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH158" s="24" t="n"/>
@@ -46311,7 +46662,7 @@
       <c r="AJ158" s="31" t="n"/>
       <c r="AK158" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL158" s="26" t="n">
@@ -46319,47 +46670,47 @@
       </c>
       <c r="AM158" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN158" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO158" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP158" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Mona Barthel</t>
         </is>
       </c>
       <c r="AQ158" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Mona Barthel</t>
         </is>
       </c>
       <c r="AR158" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Mona Barthel</t>
         </is>
       </c>
       <c r="AS158" s="24" t="inlineStr">
         <is>
-          <t>Maja Chwalinska</t>
+          <t>Laura Samson</t>
         </is>
       </c>
       <c r="AT158" s="24" t="inlineStr">
         <is>
-          <t>Maja Chwalinska</t>
+          <t>Laura Samson</t>
         </is>
       </c>
       <c r="AU158" s="24" t="inlineStr">
         <is>
-          <t>Maja Chwalinska</t>
+          <t>Laura Samson</t>
         </is>
       </c>
       <c r="AV158" s="24" t="n"/>
@@ -46412,7 +46763,7 @@
       </c>
       <c r="BH158" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:35.666785Z</t>
+          <t>2026-08-04T11:58:51.378485Z</t>
         </is>
       </c>
       <c r="BI158" s="24" t="inlineStr">
@@ -46422,19 +46773,23 @@
       </c>
       <c r="BJ158" s="25" t="n"/>
       <c r="BK158" s="26" t="n">
-        <v>133</v>
+        <v>-223</v>
       </c>
       <c r="BL158" s="27" t="n">
-        <v>2.33</v>
+        <v>1.44843</v>
       </c>
       <c r="BM158" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.690402</v>
       </c>
       <c r="BN158" s="28" t="n"/>
       <c r="BO158" s="28" t="n"/>
       <c r="BP158" s="25" t="n"/>
-      <c r="BQ158" s="27" t="n"/>
-      <c r="BR158" s="28" t="n"/>
+      <c r="BQ158" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BR158" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="BS158" s="28" t="n"/>
       <c r="BT158" s="28" t="n"/>
       <c r="BU158" s="25" t="n"/>
@@ -46460,31 +46815,32 @@
       <c r="CO158" s="24" t="n"/>
       <c r="CP158" s="24" t="n"/>
       <c r="CQ158" s="24" t="n"/>
-      <c r="CR158" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CR158" s="24" t="n"/>
+      <c r="CS158" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="159" ht="36" customHeight="1">
       <c r="A159" s="24" t="inlineStr">
         <is>
-          <t>4716354e959543fb</t>
+          <t>82d8ca996b744234</t>
         </is>
       </c>
       <c r="B159" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T12:00:14.325736Z</t>
         </is>
       </c>
       <c r="C159" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T19:30Z</t>
+          <t>2026-08-04T12:30Z</t>
         </is>
       </c>
       <c r="D159" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182203</t>
+          <t>961-2026:182093</t>
         </is>
       </c>
       <c r="E159" s="24" t="inlineStr">
@@ -46494,12 +46850,12 @@
       </c>
       <c r="F159" s="24" t="inlineStr">
         <is>
-          <t>Jelena Ostapenko</t>
+          <t>Lia Karatancheva</t>
         </is>
       </c>
       <c r="G159" s="24" t="inlineStr">
         <is>
-          <t>Zhang Shuai</t>
+          <t>Zuzanna Pawlikowska</t>
         </is>
       </c>
       <c r="H159" s="24" t="inlineStr">
@@ -46509,7 +46865,7 @@
       </c>
       <c r="I159" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J159" s="25" t="n"/>
@@ -46519,28 +46875,28 @@
         </is>
       </c>
       <c r="L159" s="26" t="n">
-        <v>-257</v>
+        <v>203</v>
       </c>
       <c r="M159" s="27" t="n">
-        <v>1.389105</v>
+        <v>3.03</v>
       </c>
       <c r="N159" s="28" t="n">
-        <v>0.719888</v>
+        <v>0.330033</v>
       </c>
       <c r="O159" s="28" t="n">
-        <v>0.660541</v>
+        <v>0.6278049999999999</v>
       </c>
       <c r="P159" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q159" s="28" t="n">
-        <v>-0.059347</v>
+        <v>0.297772</v>
       </c>
       <c r="R159" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S159" s="29" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="T159" s="24" t="inlineStr">
         <is>
@@ -46563,7 +46919,7 @@
       <c r="AD159" s="24" t="n"/>
       <c r="AE159" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Jelena Ostapenko p=0.661 vs Zhang Shuai. Executable ask 0.7200 (aec-wta-shuzha-jelost-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Lia Karatancheva p=0.372 vs Zuzanna Pawlikowska. Executable ask 0.3300 (aec-wta-zuzpaw-liakar-2026-08-04).</t>
         </is>
       </c>
       <c r="AF159" s="31" t="inlineStr">
@@ -46599,37 +46955,37 @@
       </c>
       <c r="AO159" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP159" s="24" t="inlineStr">
         <is>
-          <t>Jelena Ostapenko</t>
+          <t>Lia Karatancheva</t>
         </is>
       </c>
       <c r="AQ159" s="24" t="inlineStr">
         <is>
-          <t>Jelena Ostapenko</t>
+          <t>Lia Karatancheva</t>
         </is>
       </c>
       <c r="AR159" s="24" t="inlineStr">
         <is>
-          <t>Jelena Ostapenko</t>
+          <t>Lia Karatancheva</t>
         </is>
       </c>
       <c r="AS159" s="24" t="inlineStr">
         <is>
-          <t>Zhang Shuai</t>
+          <t>Zuzanna Pawlikowska</t>
         </is>
       </c>
       <c r="AT159" s="24" t="inlineStr">
         <is>
-          <t>Zhang Shuai</t>
+          <t>Zuzanna Pawlikowska</t>
         </is>
       </c>
       <c r="AU159" s="24" t="inlineStr">
         <is>
-          <t>Zhang Shuai</t>
+          <t>Zuzanna Pawlikowska</t>
         </is>
       </c>
       <c r="AV159" s="24" t="n"/>
@@ -46682,7 +47038,7 @@
       </c>
       <c r="BH159" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:38.783015Z</t>
+          <t>2026-08-04T11:58:51.460940Z</t>
         </is>
       </c>
       <c r="BI159" s="24" t="inlineStr">
@@ -46692,13 +47048,13 @@
       </c>
       <c r="BJ159" s="25" t="n"/>
       <c r="BK159" s="26" t="n">
-        <v>-257</v>
+        <v>203</v>
       </c>
       <c r="BL159" s="27" t="n">
-        <v>1.389105</v>
+        <v>3.03</v>
       </c>
       <c r="BM159" s="28" t="n">
-        <v>0.719888</v>
+        <v>0.330033</v>
       </c>
       <c r="BN159" s="28" t="n"/>
       <c r="BO159" s="28" t="n"/>
@@ -46730,31 +47086,32 @@
       <c r="CO159" s="24" t="n"/>
       <c r="CP159" s="24" t="n"/>
       <c r="CQ159" s="24" t="n"/>
-      <c r="CR159" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR159" s="24" t="n"/>
+      <c r="CS159" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="160" ht="36" customHeight="1">
       <c r="A160" s="24" t="inlineStr">
         <is>
-          <t>cf9ba4046ede4acd</t>
+          <t>f96416c790394c01</t>
         </is>
       </c>
       <c r="B160" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C160" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T21:00Z</t>
+          <t>2026-08-04T15:00Z</t>
         </is>
       </c>
       <c r="D160" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182167</t>
+          <t>421-2026:182185</t>
         </is>
       </c>
       <c r="E160" s="24" t="inlineStr">
@@ -46764,12 +47121,12 @@
       </c>
       <c r="F160" s="24" t="inlineStr">
         <is>
-          <t>McCartney Kessler</t>
+          <t>Jessica Bouzas Maneiro</t>
         </is>
       </c>
       <c r="G160" s="24" t="inlineStr">
         <is>
-          <t>Anna Kalinskaya</t>
+          <t>Elina Svitolina</t>
         </is>
       </c>
       <c r="H160" s="24" t="inlineStr">
@@ -46789,28 +47146,28 @@
         </is>
       </c>
       <c r="L160" s="26" t="n">
-        <v>-156</v>
+        <v>-567</v>
       </c>
       <c r="M160" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.176367</v>
       </c>
       <c r="N160" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.850075</v>
       </c>
       <c r="O160" s="28" t="n">
-        <v>0.605938</v>
+        <v>0.855057</v>
       </c>
       <c r="P160" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q160" s="28" t="n">
-        <v>-0.003437</v>
+        <v>0.004982</v>
       </c>
       <c r="R160" s="26" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="S160" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T160" s="24" t="inlineStr">
         <is>
@@ -46833,7 +47190,7 @@
       <c r="AD160" s="24" t="n"/>
       <c r="AE160" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: McCartney Kessler p=0.394 vs Anna Kalinskaya. Executable ask 0.6100 (aec-wta-annkal-mcckes-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Jessica Bouzas Maneiro p=0.145 vs Elina Svitolina. Executable ask 0.8500 (aec-wta-elisvi-jesman-2026-08-03).</t>
         </is>
       </c>
       <c r="AF160" s="31" t="inlineStr">
@@ -46874,32 +47231,32 @@
       </c>
       <c r="AP160" s="24" t="inlineStr">
         <is>
-          <t>McCartney Kessler</t>
+          <t>Jessica Bouzas Maneiro</t>
         </is>
       </c>
       <c r="AQ160" s="24" t="inlineStr">
         <is>
-          <t>McCartney Kessler</t>
+          <t>Jessica Bouzas Maneiro</t>
         </is>
       </c>
       <c r="AR160" s="24" t="inlineStr">
         <is>
-          <t>McCartney Kessler</t>
+          <t>Jessica Bouzas Maneiro</t>
         </is>
       </c>
       <c r="AS160" s="24" t="inlineStr">
         <is>
-          <t>Anna Kalinskaya</t>
+          <t>Elina Svitolina</t>
         </is>
       </c>
       <c r="AT160" s="24" t="inlineStr">
         <is>
-          <t>Anna Kalinskaya</t>
+          <t>Elina Svitolina</t>
         </is>
       </c>
       <c r="AU160" s="24" t="inlineStr">
         <is>
-          <t>Anna Kalinskaya</t>
+          <t>Elina Svitolina</t>
         </is>
       </c>
       <c r="AV160" s="24" t="n"/>
@@ -46952,7 +47309,7 @@
       </c>
       <c r="BH160" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:40.069254Z</t>
+          <t>2026-08-04T14:23:21.702360Z</t>
         </is>
       </c>
       <c r="BI160" s="24" t="inlineStr">
@@ -46962,13 +47319,13 @@
       </c>
       <c r="BJ160" s="25" t="n"/>
       <c r="BK160" s="26" t="n">
-        <v>-156</v>
+        <v>-567</v>
       </c>
       <c r="BL160" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.176367</v>
       </c>
       <c r="BM160" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.850075</v>
       </c>
       <c r="BN160" s="28" t="n"/>
       <c r="BO160" s="28" t="n"/>
@@ -47000,31 +47357,32 @@
       <c r="CO160" s="24" t="n"/>
       <c r="CP160" s="24" t="n"/>
       <c r="CQ160" s="24" t="n"/>
-      <c r="CR160" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR160" s="24" t="n"/>
+      <c r="CS160" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="161" ht="36" customHeight="1">
       <c r="A161" s="24" t="inlineStr">
         <is>
-          <t>403f1f5943a64004</t>
+          <t>abf97926dd5648b1</t>
         </is>
       </c>
       <c r="B161" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C161" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T21:00Z</t>
+          <t>2026-08-04T16:30Z</t>
         </is>
       </c>
       <c r="D161" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182168</t>
+          <t>421-2026:182173</t>
         </is>
       </c>
       <c r="E161" s="24" t="inlineStr">
@@ -47034,12 +47392,12 @@
       </c>
       <c r="F161" s="24" t="inlineStr">
         <is>
-          <t>Katerina Siniakova</t>
+          <t>Diana Shnaider</t>
         </is>
       </c>
       <c r="G161" s="24" t="inlineStr">
         <is>
-          <t>Kamilla Rakhimova</t>
+          <t>Rebecca Sramkova</t>
         </is>
       </c>
       <c r="H161" s="24" t="inlineStr">
@@ -47059,28 +47417,28 @@
         </is>
       </c>
       <c r="L161" s="26" t="n">
-        <v>-194</v>
+        <v>-400</v>
       </c>
       <c r="M161" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.25</v>
       </c>
       <c r="N161" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.8</v>
       </c>
       <c r="O161" s="28" t="n">
-        <v>0.66176</v>
+        <v>0.69013</v>
       </c>
       <c r="P161" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q161" s="28" t="n">
-        <v>0.001896</v>
+        <v>-0.10987</v>
       </c>
       <c r="R161" s="26" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S161" s="29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T161" s="24" t="inlineStr">
         <is>
@@ -47103,7 +47461,7 @@
       <c r="AD161" s="24" t="n"/>
       <c r="AE161" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Katerina Siniakova p=0.662 vs Kamilla Rakhimova. Executable ask 0.6600 (aec-wta-kamrak-katsin-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Diana Shnaider p=0.690 vs Rebecca Sramkova. Executable ask 0.8000 (aec-wta-rebsra-diashn-2026-08-04).</t>
         </is>
       </c>
       <c r="AF161" s="31" t="inlineStr">
@@ -47144,32 +47502,32 @@
       </c>
       <c r="AP161" s="24" t="inlineStr">
         <is>
-          <t>Katerina Siniakova</t>
+          <t>Diana Shnaider</t>
         </is>
       </c>
       <c r="AQ161" s="24" t="inlineStr">
         <is>
-          <t>Katerina Siniakova</t>
+          <t>Diana Shnaider</t>
         </is>
       </c>
       <c r="AR161" s="24" t="inlineStr">
         <is>
-          <t>Katerina Siniakova</t>
+          <t>Diana Shnaider</t>
         </is>
       </c>
       <c r="AS161" s="24" t="inlineStr">
         <is>
-          <t>Kamilla Rakhimova</t>
+          <t>Rebecca Sramkova</t>
         </is>
       </c>
       <c r="AT161" s="24" t="inlineStr">
         <is>
-          <t>Kamilla Rakhimova</t>
+          <t>Rebecca Sramkova</t>
         </is>
       </c>
       <c r="AU161" s="24" t="inlineStr">
         <is>
-          <t>Kamilla Rakhimova</t>
+          <t>Rebecca Sramkova</t>
         </is>
       </c>
       <c r="AV161" s="24" t="n"/>
@@ -47222,7 +47580,7 @@
       </c>
       <c r="BH161" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:39.130120Z</t>
+          <t>2026-08-04T14:23:26.341443Z</t>
         </is>
       </c>
       <c r="BI161" s="24" t="inlineStr">
@@ -47232,13 +47590,13 @@
       </c>
       <c r="BJ161" s="25" t="n"/>
       <c r="BK161" s="26" t="n">
-        <v>-194</v>
+        <v>-400</v>
       </c>
       <c r="BL161" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.25</v>
       </c>
       <c r="BM161" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.8</v>
       </c>
       <c r="BN161" s="28" t="n"/>
       <c r="BO161" s="28" t="n"/>
@@ -47270,31 +47628,32 @@
       <c r="CO161" s="24" t="n"/>
       <c r="CP161" s="24" t="n"/>
       <c r="CQ161" s="24" t="n"/>
-      <c r="CR161" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CR161" s="24" t="n"/>
+      <c r="CS161" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="162" ht="36" customHeight="1">
       <c r="A162" s="24" t="inlineStr">
         <is>
-          <t>afc199c56dcd4b6d</t>
+          <t>d6638734fcd04894</t>
         </is>
       </c>
       <c r="B162" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C162" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T22:30Z</t>
+          <t>2026-08-04T16:30Z</t>
         </is>
       </c>
       <c r="D162" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182188</t>
+          <t>421-2026:182175</t>
         </is>
       </c>
       <c r="E162" s="24" t="inlineStr">
@@ -47304,12 +47663,12 @@
       </c>
       <c r="F162" s="24" t="inlineStr">
         <is>
-          <t>Nikola Bartunkova</t>
+          <t>Viktorija Golubic</t>
         </is>
       </c>
       <c r="G162" s="24" t="inlineStr">
         <is>
-          <t>Clara Tauson</t>
+          <t>Donna Vekic</t>
         </is>
       </c>
       <c r="H162" s="24" t="inlineStr">
@@ -47329,28 +47688,28 @@
         </is>
       </c>
       <c r="L162" s="26" t="n">
-        <v>-117</v>
+        <v>-133</v>
       </c>
       <c r="M162" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.75188</v>
       </c>
       <c r="N162" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.570815</v>
       </c>
       <c r="O162" s="28" t="n">
-        <v>0.540992</v>
+        <v>0.600871</v>
       </c>
       <c r="P162" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q162" s="28" t="n">
-        <v>0.001821</v>
+        <v>0.030056</v>
       </c>
       <c r="R162" s="26" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="S162" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T162" s="24" t="inlineStr">
         <is>
@@ -47373,7 +47732,7 @@
       <c r="AD162" s="24" t="n"/>
       <c r="AE162" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Nikola Bartunkova p=0.459 vs Clara Tauson. Executable ask 0.5400 (aec-wta-clatau-nikbar-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Viktorija Golubic p=0.399 vs Donna Vekic. Executable ask 0.5700 (aec-wta-donvek-vikgol-2026-08-03).</t>
         </is>
       </c>
       <c r="AF162" s="31" t="inlineStr">
@@ -47414,32 +47773,32 @@
       </c>
       <c r="AP162" s="24" t="inlineStr">
         <is>
-          <t>Nikola Bartunkova</t>
+          <t>Viktorija Golubic</t>
         </is>
       </c>
       <c r="AQ162" s="24" t="inlineStr">
         <is>
-          <t>Nikola Bartunkova</t>
+          <t>Viktorija Golubic</t>
         </is>
       </c>
       <c r="AR162" s="24" t="inlineStr">
         <is>
-          <t>Nikola Bartunkova</t>
+          <t>Viktorija Golubic</t>
         </is>
       </c>
       <c r="AS162" s="24" t="inlineStr">
         <is>
-          <t>Clara Tauson</t>
+          <t>Donna Vekic</t>
         </is>
       </c>
       <c r="AT162" s="24" t="inlineStr">
         <is>
-          <t>Clara Tauson</t>
+          <t>Donna Vekic</t>
         </is>
       </c>
       <c r="AU162" s="24" t="inlineStr">
         <is>
-          <t>Clara Tauson</t>
+          <t>Donna Vekic</t>
         </is>
       </c>
       <c r="AV162" s="24" t="n"/>
@@ -47492,7 +47851,7 @@
       </c>
       <c r="BH162" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:40.814085Z</t>
+          <t>2026-08-04T14:23:22.697774Z</t>
         </is>
       </c>
       <c r="BI162" s="24" t="inlineStr">
@@ -47502,13 +47861,13 @@
       </c>
       <c r="BJ162" s="25" t="n"/>
       <c r="BK162" s="26" t="n">
-        <v>-117</v>
+        <v>-133</v>
       </c>
       <c r="BL162" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.75188</v>
       </c>
       <c r="BM162" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.570815</v>
       </c>
       <c r="BN162" s="28" t="n"/>
       <c r="BO162" s="28" t="n"/>
@@ -47540,7 +47899,8 @@
       <c r="CO162" s="24" t="n"/>
       <c r="CP162" s="24" t="n"/>
       <c r="CQ162" s="24" t="n"/>
-      <c r="CR162" s="24" t="inlineStr">
+      <c r="CR162" s="24" t="n"/>
+      <c r="CS162" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -47549,22 +47909,22 @@
     <row r="163" ht="36" customHeight="1">
       <c r="A163" s="24" t="inlineStr">
         <is>
-          <t>ca8e290526504475</t>
+          <t>28e316caeb494e0c</t>
         </is>
       </c>
       <c r="B163" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C163" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:00Z</t>
+          <t>2026-08-04T16:30Z</t>
         </is>
       </c>
       <c r="D163" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182199</t>
+          <t>421-2026:182182</t>
         </is>
       </c>
       <c r="E163" s="24" t="inlineStr">
@@ -47574,12 +47934,12 @@
       </c>
       <c r="F163" s="24" t="inlineStr">
         <is>
-          <t>Moyuka Uchijima</t>
+          <t>Iga Swiatek</t>
         </is>
       </c>
       <c r="G163" s="24" t="inlineStr">
         <is>
-          <t>Aryna Sabalenka</t>
+          <t>Sara Bejlek</t>
         </is>
       </c>
       <c r="H163" s="24" t="inlineStr">
@@ -47589,7 +47949,7 @@
       </c>
       <c r="I163" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J163" s="25" t="n"/>
@@ -47599,25 +47959,25 @@
         </is>
       </c>
       <c r="L163" s="26" t="n">
-        <v>-1900</v>
+        <v>-809</v>
       </c>
       <c r="M163" s="27" t="n">
-        <v>1.052632</v>
+        <v>1.123609</v>
       </c>
       <c r="N163" s="28" t="n">
-        <v>0.95</v>
+        <v>0.889989</v>
       </c>
       <c r="O163" s="28" t="n">
-        <v>0.939322</v>
+        <v>0.745582</v>
       </c>
       <c r="P163" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q163" s="28" t="n">
-        <v>-0.010678</v>
+        <v>-0.144407</v>
       </c>
       <c r="R163" s="26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S163" s="29" t="n">
         <v>2</v>
@@ -47643,7 +48003,7 @@
       <c r="AD163" s="24" t="n"/>
       <c r="AE163" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Moyuka Uchijima p=0.061 vs Aryna Sabalenka. Executable ask 0.9500 (aec-wta-arysab-moyuch-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Iga Swiatek p=0.746 vs Sara Bejlek. Executable ask 0.8900 (aec-wta-sarbej-igaswi-2026-08-03).</t>
         </is>
       </c>
       <c r="AF163" s="31" t="inlineStr">
@@ -47684,32 +48044,32 @@
       </c>
       <c r="AP163" s="24" t="inlineStr">
         <is>
-          <t>Moyuka Uchijima</t>
+          <t>Iga Swiatek</t>
         </is>
       </c>
       <c r="AQ163" s="24" t="inlineStr">
         <is>
-          <t>Moyuka Uchijima</t>
+          <t>Iga Swiatek</t>
         </is>
       </c>
       <c r="AR163" s="24" t="inlineStr">
         <is>
-          <t>Moyuka Uchijima</t>
+          <t>Iga Swiatek</t>
         </is>
       </c>
       <c r="AS163" s="24" t="inlineStr">
         <is>
-          <t>Aryna Sabalenka</t>
+          <t>Sara Bejlek</t>
         </is>
       </c>
       <c r="AT163" s="24" t="inlineStr">
         <is>
-          <t>Aryna Sabalenka</t>
+          <t>Sara Bejlek</t>
         </is>
       </c>
       <c r="AU163" s="24" t="inlineStr">
         <is>
-          <t>Aryna Sabalenka</t>
+          <t>Sara Bejlek</t>
         </is>
       </c>
       <c r="AV163" s="24" t="n"/>
@@ -47762,7 +48122,7 @@
       </c>
       <c r="BH163" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:41.356996Z</t>
+          <t>2026-08-04T14:23:23.345824Z</t>
         </is>
       </c>
       <c r="BI163" s="24" t="inlineStr">
@@ -47772,13 +48132,13 @@
       </c>
       <c r="BJ163" s="25" t="n"/>
       <c r="BK163" s="26" t="n">
-        <v>-1900</v>
+        <v>-809</v>
       </c>
       <c r="BL163" s="27" t="n">
-        <v>1.052632</v>
+        <v>1.123609</v>
       </c>
       <c r="BM163" s="28" t="n">
-        <v>0.95</v>
+        <v>0.889989</v>
       </c>
       <c r="BN163" s="28" t="n"/>
       <c r="BO163" s="28" t="n"/>
@@ -47810,7 +48170,8 @@
       <c r="CO163" s="24" t="n"/>
       <c r="CP163" s="24" t="n"/>
       <c r="CQ163" s="24" t="n"/>
-      <c r="CR163" s="24" t="inlineStr">
+      <c r="CR163" s="24" t="n"/>
+      <c r="CS163" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -47819,22 +48180,22 @@
     <row r="164" ht="36" customHeight="1">
       <c r="A164" s="24" t="inlineStr">
         <is>
-          <t>880352d54c9e48c4</t>
+          <t>5c20822296194a65</t>
         </is>
       </c>
       <c r="B164" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C164" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:30Z</t>
+          <t>2026-08-04T16:30Z</t>
         </is>
       </c>
       <c r="D164" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182187</t>
+          <t>421-2026:182207</t>
         </is>
       </c>
       <c r="E164" s="24" t="inlineStr">
@@ -47844,12 +48205,12 @@
       </c>
       <c r="F164" s="24" t="inlineStr">
         <is>
-          <t>Amanda Anisimova</t>
+          <t>Ekaterina Alexandrova</t>
         </is>
       </c>
       <c r="G164" s="24" t="inlineStr">
         <is>
-          <t>Lanlana Tararudee</t>
+          <t>Camila Osorio</t>
         </is>
       </c>
       <c r="H164" s="24" t="inlineStr">
@@ -47859,7 +48220,7 @@
       </c>
       <c r="I164" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J164" s="25" t="n"/>
@@ -47869,28 +48230,28 @@
         </is>
       </c>
       <c r="L164" s="26" t="n">
-        <v>-257</v>
+        <v>-117</v>
       </c>
       <c r="M164" s="27" t="n">
-        <v>1.389105</v>
+        <v>1.854701</v>
       </c>
       <c r="N164" s="28" t="n">
-        <v>0.719888</v>
+        <v>0.539171</v>
       </c>
       <c r="O164" s="28" t="n">
-        <v>0.669885</v>
+        <v>0.533657</v>
       </c>
       <c r="P164" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q164" s="28" t="n">
-        <v>-0.050003</v>
+        <v>-0.005514</v>
       </c>
       <c r="R164" s="26" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S164" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T164" s="24" t="inlineStr">
         <is>
@@ -47913,7 +48274,7 @@
       <c r="AD164" s="24" t="n"/>
       <c r="AE164" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Amanda Anisimova p=0.670 vs Lanlana Tararudee. Executable ask 0.7200 (aec-wta-lantar-amaani-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Ekaterina Alexandrova p=0.466 vs Camila Osorio. Executable ask 0.5400 (aec-wta-camoso-ekaale-2026-08-03).</t>
         </is>
       </c>
       <c r="AF164" s="31" t="inlineStr">
@@ -47954,32 +48315,32 @@
       </c>
       <c r="AP164" s="24" t="inlineStr">
         <is>
-          <t>Amanda Anisimova</t>
+          <t>Ekaterina Alexandrova</t>
         </is>
       </c>
       <c r="AQ164" s="24" t="inlineStr">
         <is>
-          <t>Amanda Anisimova</t>
+          <t>Ekaterina Alexandrova</t>
         </is>
       </c>
       <c r="AR164" s="24" t="inlineStr">
         <is>
-          <t>Amanda Anisimova</t>
+          <t>Ekaterina Alexandrova</t>
         </is>
       </c>
       <c r="AS164" s="24" t="inlineStr">
         <is>
-          <t>Lanlana Tararudee</t>
+          <t>Camila Osorio</t>
         </is>
       </c>
       <c r="AT164" s="24" t="inlineStr">
         <is>
-          <t>Lanlana Tararudee</t>
+          <t>Camila Osorio</t>
         </is>
       </c>
       <c r="AU164" s="24" t="inlineStr">
         <is>
-          <t>Lanlana Tararudee</t>
+          <t>Camila Osorio</t>
         </is>
       </c>
       <c r="AV164" s="24" t="n"/>
@@ -48032,7 +48393,7 @@
       </c>
       <c r="BH164" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:42.022758Z</t>
+          <t>2026-08-04T14:23:24.523404Z</t>
         </is>
       </c>
       <c r="BI164" s="24" t="inlineStr">
@@ -48042,13 +48403,13 @@
       </c>
       <c r="BJ164" s="25" t="n"/>
       <c r="BK164" s="26" t="n">
-        <v>-257</v>
+        <v>-117</v>
       </c>
       <c r="BL164" s="27" t="n">
-        <v>1.389105</v>
+        <v>1.854701</v>
       </c>
       <c r="BM164" s="28" t="n">
-        <v>0.719888</v>
+        <v>0.539171</v>
       </c>
       <c r="BN164" s="28" t="n"/>
       <c r="BO164" s="28" t="n"/>
@@ -48080,7 +48441,8 @@
       <c r="CO164" s="24" t="n"/>
       <c r="CP164" s="24" t="n"/>
       <c r="CQ164" s="24" t="n"/>
-      <c r="CR164" s="24" t="inlineStr">
+      <c r="CR164" s="24" t="n"/>
+      <c r="CS164" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -48089,22 +48451,22 @@
     <row r="165" ht="36" customHeight="1">
       <c r="A165" s="24" t="inlineStr">
         <is>
-          <t>b89c107ad5ba4209</t>
+          <t>953f8420edeb4dfb</t>
         </is>
       </c>
       <c r="B165" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C165" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T09:00Z</t>
+          <t>2026-08-04T18:00Z</t>
         </is>
       </c>
       <c r="D165" s="24" t="inlineStr">
         <is>
-          <t>961-2026:182094</t>
+          <t>421-2026:182166</t>
         </is>
       </c>
       <c r="E165" s="24" t="inlineStr">
@@ -48114,12 +48476,12 @@
       </c>
       <c r="F165" s="24" t="inlineStr">
         <is>
-          <t>Justina Mikulskyte</t>
+          <t>Madison Keys</t>
         </is>
       </c>
       <c r="G165" s="24" t="inlineStr">
         <is>
-          <t>Weronika Ewald</t>
+          <t>Antonia Ruzic</t>
         </is>
       </c>
       <c r="H165" s="24" t="inlineStr">
@@ -48129,7 +48491,7 @@
       </c>
       <c r="I165" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J165" s="25" t="n"/>
@@ -48139,28 +48501,28 @@
         </is>
       </c>
       <c r="L165" s="26" t="n">
-        <v>127</v>
+        <v>-456</v>
       </c>
       <c r="M165" s="27" t="n">
-        <v>2.27</v>
+        <v>1.219298</v>
       </c>
       <c r="N165" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.820144</v>
       </c>
       <c r="O165" s="28" t="n">
-        <v>0.589516</v>
+        <v>0.771595</v>
       </c>
       <c r="P165" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q165" s="28" t="n">
-        <v>0.148987</v>
+        <v>-0.048549</v>
       </c>
       <c r="R165" s="26" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="S165" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T165" s="24" t="inlineStr">
         <is>
@@ -48183,7 +48545,7 @@
       <c r="AD165" s="24" t="n"/>
       <c r="AE165" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Justina Mikulskyte p=0.410 vs Weronika Ewald. Executable ask 0.4400 (aec-wta-werewa-jusmik-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Madison Keys p=0.772 vs Antonia Ruzic. Executable ask 0.8200 (aec-wta-antruz-madkey-2026-08-04).</t>
         </is>
       </c>
       <c r="AF165" s="31" t="inlineStr">
@@ -48219,37 +48581,37 @@
       </c>
       <c r="AO165" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP165" s="24" t="inlineStr">
         <is>
-          <t>Justina Mikulskyte</t>
+          <t>Madison Keys</t>
         </is>
       </c>
       <c r="AQ165" s="24" t="inlineStr">
         <is>
-          <t>Justina Mikulskyte</t>
+          <t>Madison Keys</t>
         </is>
       </c>
       <c r="AR165" s="24" t="inlineStr">
         <is>
-          <t>Justina Mikulskyte</t>
+          <t>Madison Keys</t>
         </is>
       </c>
       <c r="AS165" s="24" t="inlineStr">
         <is>
-          <t>Weronika Ewald</t>
+          <t>Antonia Ruzic</t>
         </is>
       </c>
       <c r="AT165" s="24" t="inlineStr">
         <is>
-          <t>Weronika Ewald</t>
+          <t>Antonia Ruzic</t>
         </is>
       </c>
       <c r="AU165" s="24" t="inlineStr">
         <is>
-          <t>Weronika Ewald</t>
+          <t>Antonia Ruzic</t>
         </is>
       </c>
       <c r="AV165" s="24" t="n"/>
@@ -48302,7 +48664,7 @@
       </c>
       <c r="BH165" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:31.682126Z</t>
+          <t>2026-08-04T14:23:30.714186Z</t>
         </is>
       </c>
       <c r="BI165" s="24" t="inlineStr">
@@ -48312,13 +48674,13 @@
       </c>
       <c r="BJ165" s="25" t="n"/>
       <c r="BK165" s="26" t="n">
-        <v>127</v>
+        <v>-456</v>
       </c>
       <c r="BL165" s="27" t="n">
-        <v>2.27</v>
+        <v>1.219298</v>
       </c>
       <c r="BM165" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.820144</v>
       </c>
       <c r="BN165" s="28" t="n"/>
       <c r="BO165" s="28" t="n"/>
@@ -48350,31 +48712,32 @@
       <c r="CO165" s="24" t="n"/>
       <c r="CP165" s="24" t="n"/>
       <c r="CQ165" s="24" t="n"/>
-      <c r="CR165" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CR165" s="24" t="n"/>
+      <c r="CS165" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="166" ht="36" customHeight="1">
       <c r="A166" s="24" t="inlineStr">
         <is>
-          <t>8612244b5fd64414</t>
+          <t>011f78a84f47452a</t>
         </is>
       </c>
       <c r="B166" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C166" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T09:00Z</t>
+          <t>2026-08-04T18:00Z</t>
         </is>
       </c>
       <c r="D166" s="24" t="inlineStr">
         <is>
-          <t>961-2026:182089</t>
+          <t>421-2026:182194</t>
         </is>
       </c>
       <c r="E166" s="24" t="inlineStr">
@@ -48384,12 +48747,12 @@
       </c>
       <c r="F166" s="24" t="inlineStr">
         <is>
-          <t>Carol Young Suh Lee</t>
+          <t>Katherine Sebov</t>
         </is>
       </c>
       <c r="G166" s="24" t="inlineStr">
         <is>
-          <t>Elsa Jacquemot</t>
+          <t>Marta Kostyuk</t>
         </is>
       </c>
       <c r="H166" s="24" t="inlineStr">
@@ -48399,7 +48762,7 @@
       </c>
       <c r="I166" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J166" s="25" t="n"/>
@@ -48409,28 +48772,28 @@
         </is>
       </c>
       <c r="L166" s="26" t="n">
-        <v>-163</v>
+        <v>-2400</v>
       </c>
       <c r="M166" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.041667</v>
       </c>
       <c r="N166" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.96</v>
       </c>
       <c r="O166" s="28" t="n">
-        <v>0.60078</v>
+        <v>0.886886</v>
       </c>
       <c r="P166" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q166" s="28" t="n">
-        <v>-0.018992</v>
+        <v>-0.073114</v>
       </c>
       <c r="R166" s="26" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S166" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T166" s="24" t="inlineStr">
         <is>
@@ -48453,7 +48816,7 @@
       <c r="AD166" s="24" t="n"/>
       <c r="AE166" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Carol Young Suh Lee p=0.601 vs Elsa Jacquemot. Executable ask 0.6200 (aec-wta-elsjac-carlee-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Katherine Sebov p=0.113 vs Marta Kostyuk. Executable ask 0.9600 (aec-wta-markos-katseb-2026-08-03).</t>
         </is>
       </c>
       <c r="AF166" s="31" t="inlineStr">
@@ -48494,32 +48857,32 @@
       </c>
       <c r="AP166" s="24" t="inlineStr">
         <is>
-          <t>Carol Young Suh Lee</t>
+          <t>Katherine Sebov</t>
         </is>
       </c>
       <c r="AQ166" s="24" t="inlineStr">
         <is>
-          <t>Carol Young Suh Lee</t>
+          <t>Katherine Sebov</t>
         </is>
       </c>
       <c r="AR166" s="24" t="inlineStr">
         <is>
-          <t>Carol Young Suh Lee</t>
+          <t>Katherine Sebov</t>
         </is>
       </c>
       <c r="AS166" s="24" t="inlineStr">
         <is>
-          <t>Elsa Jacquemot</t>
+          <t>Marta Kostyuk</t>
         </is>
       </c>
       <c r="AT166" s="24" t="inlineStr">
         <is>
-          <t>Elsa Jacquemot</t>
+          <t>Marta Kostyuk</t>
         </is>
       </c>
       <c r="AU166" s="24" t="inlineStr">
         <is>
-          <t>Elsa Jacquemot</t>
+          <t>Marta Kostyuk</t>
         </is>
       </c>
       <c r="AV166" s="24" t="n"/>
@@ -48572,7 +48935,7 @@
       </c>
       <c r="BH166" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:31.683641Z</t>
+          <t>2026-08-04T14:23:28.644063Z</t>
         </is>
       </c>
       <c r="BI166" s="24" t="inlineStr">
@@ -48582,13 +48945,13 @@
       </c>
       <c r="BJ166" s="25" t="n"/>
       <c r="BK166" s="26" t="n">
-        <v>-163</v>
+        <v>-2400</v>
       </c>
       <c r="BL166" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.041667</v>
       </c>
       <c r="BM166" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.96</v>
       </c>
       <c r="BN166" s="28" t="n"/>
       <c r="BO166" s="28" t="n"/>
@@ -48620,7 +48983,8 @@
       <c r="CO166" s="24" t="n"/>
       <c r="CP166" s="24" t="n"/>
       <c r="CQ166" s="24" t="n"/>
-      <c r="CR166" s="24" t="inlineStr">
+      <c r="CR166" s="24" t="n"/>
+      <c r="CS166" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -48629,22 +48993,22 @@
     <row r="167" ht="36" customHeight="1">
       <c r="A167" s="24" t="inlineStr">
         <is>
-          <t>a89260ea60b44bd5</t>
+          <t>1a5b40675426470c</t>
         </is>
       </c>
       <c r="B167" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C167" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T09:00Z</t>
+          <t>2026-08-04T18:00Z</t>
         </is>
       </c>
       <c r="D167" s="24" t="inlineStr">
         <is>
-          <t>961-2026:182083</t>
+          <t>421-2026:182202</t>
         </is>
       </c>
       <c r="E167" s="24" t="inlineStr">
@@ -48654,12 +49018,12 @@
       </c>
       <c r="F167" s="24" t="inlineStr">
         <is>
-          <t>Susan Bandecchi</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="G167" s="24" t="inlineStr">
         <is>
-          <t>Viktoria Hruncakova</t>
+          <t>Maja Chwalinska</t>
         </is>
       </c>
       <c r="H167" s="24" t="inlineStr">
@@ -48669,7 +49033,7 @@
       </c>
       <c r="I167" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J167" s="25" t="n"/>
@@ -48679,28 +49043,28 @@
         </is>
       </c>
       <c r="L167" s="26" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="M167" s="27" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="N167" s="28" t="n">
-        <v>0.5</v>
+        <v>0.460829</v>
       </c>
       <c r="O167" s="28" t="n">
-        <v>0.548768</v>
+        <v>0.623502</v>
       </c>
       <c r="P167" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q167" s="28" t="n">
-        <v>0.048768</v>
+        <v>0.162673</v>
       </c>
       <c r="R167" s="26" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="S167" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T167" s="24" t="inlineStr">
         <is>
@@ -48723,7 +49087,7 @@
       <c r="AD167" s="24" t="n"/>
       <c r="AE167" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Susan Bandecchi p=0.549 vs Viktoria Hruncakova. Executable ask 0.5000 (aec-wta-vikhru-susban-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Talia Gibson p=0.376 vs Maja Chwalinska. Executable ask 0.4600 (aec-wta-majchw-talgib-2026-08-04).</t>
         </is>
       </c>
       <c r="AF167" s="31" t="inlineStr">
@@ -48741,7 +49105,7 @@
       <c r="AJ167" s="31" t="n"/>
       <c r="AK167" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL167" s="26" t="n">
@@ -48749,47 +49113,47 @@
       </c>
       <c r="AM167" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN167" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO167" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP167" s="24" t="inlineStr">
         <is>
-          <t>Susan Bandecchi</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="AQ167" s="24" t="inlineStr">
         <is>
-          <t>Susan Bandecchi</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="AR167" s="24" t="inlineStr">
         <is>
-          <t>Susan Bandecchi</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="AS167" s="24" t="inlineStr">
         <is>
-          <t>Viktoria Hruncakova</t>
+          <t>Maja Chwalinska</t>
         </is>
       </c>
       <c r="AT167" s="24" t="inlineStr">
         <is>
-          <t>Viktoria Hruncakova</t>
+          <t>Maja Chwalinska</t>
         </is>
       </c>
       <c r="AU167" s="24" t="inlineStr">
         <is>
-          <t>Viktoria Hruncakova</t>
+          <t>Maja Chwalinska</t>
         </is>
       </c>
       <c r="AV167" s="24" t="n"/>
@@ -48842,7 +49206,7 @@
       </c>
       <c r="BH167" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:31.509930Z</t>
+          <t>2026-08-04T14:23:27.218479Z</t>
         </is>
       </c>
       <c r="BI167" s="24" t="inlineStr">
@@ -48852,13 +49216,13 @@
       </c>
       <c r="BJ167" s="25" t="n"/>
       <c r="BK167" s="26" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="BL167" s="27" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="BM167" s="28" t="n">
-        <v>0.5</v>
+        <v>0.460829</v>
       </c>
       <c r="BN167" s="28" t="n"/>
       <c r="BO167" s="28" t="n"/>
@@ -48890,7 +49254,8 @@
       <c r="CO167" s="24" t="n"/>
       <c r="CP167" s="24" t="n"/>
       <c r="CQ167" s="24" t="n"/>
-      <c r="CR167" s="24" t="inlineStr">
+      <c r="CR167" s="24" t="n"/>
+      <c r="CS167" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -48899,22 +49264,22 @@
     <row r="168" ht="36" customHeight="1">
       <c r="A168" s="24" t="inlineStr">
         <is>
-          <t>1b49058ee90f436d</t>
+          <t>31b03912b8b044d2</t>
         </is>
       </c>
       <c r="B168" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C168" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T10:30Z</t>
+          <t>2026-08-04T19:30Z</t>
         </is>
       </c>
       <c r="D168" s="24" t="inlineStr">
         <is>
-          <t>961-2026:182091</t>
+          <t>421-2026:182203</t>
         </is>
       </c>
       <c r="E168" s="24" t="inlineStr">
@@ -48924,12 +49289,12 @@
       </c>
       <c r="F168" s="24" t="inlineStr">
         <is>
-          <t>Vendula Valdmannova</t>
+          <t>Jelena Ostapenko</t>
         </is>
       </c>
       <c r="G168" s="24" t="inlineStr">
         <is>
-          <t>Marcelina Podlinska</t>
+          <t>Zhang Shuai</t>
         </is>
       </c>
       <c r="H168" s="24" t="inlineStr">
@@ -48949,28 +49314,28 @@
         </is>
       </c>
       <c r="L168" s="26" t="n">
-        <v>-525</v>
+        <v>-223</v>
       </c>
       <c r="M168" s="27" t="n">
-        <v>1.190476</v>
+        <v>1.44843</v>
       </c>
       <c r="N168" s="28" t="n">
-        <v>0.84</v>
+        <v>0.690402</v>
       </c>
       <c r="O168" s="28" t="n">
-        <v>0.601999</v>
+        <v>0.660541</v>
       </c>
       <c r="P168" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q168" s="28" t="n">
-        <v>-0.238001</v>
+        <v>-0.029861</v>
       </c>
       <c r="R168" s="26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S168" s="29" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="T168" s="24" t="inlineStr">
         <is>
@@ -48993,7 +49358,7 @@
       <c r="AD168" s="24" t="n"/>
       <c r="AE168" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Vendula Valdmannova p=0.602 vs Marcelina Podlinska. Executable ask 0.8400 (aec-wta-marpod-venval-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Jelena Ostapenko p=0.661 vs Zhang Shuai. Executable ask 0.6900 (aec-wta-shuzha-jelost-2026-08-04).</t>
         </is>
       </c>
       <c r="AF168" s="31" t="inlineStr">
@@ -49029,37 +49394,37 @@
       </c>
       <c r="AO168" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP168" s="24" t="inlineStr">
         <is>
-          <t>Vendula Valdmannova</t>
+          <t>Jelena Ostapenko</t>
         </is>
       </c>
       <c r="AQ168" s="24" t="inlineStr">
         <is>
-          <t>Vendula Valdmannova</t>
+          <t>Jelena Ostapenko</t>
         </is>
       </c>
       <c r="AR168" s="24" t="inlineStr">
         <is>
-          <t>Vendula Valdmannova</t>
+          <t>Jelena Ostapenko</t>
         </is>
       </c>
       <c r="AS168" s="24" t="inlineStr">
         <is>
-          <t>Marcelina Podlinska</t>
+          <t>Zhang Shuai</t>
         </is>
       </c>
       <c r="AT168" s="24" t="inlineStr">
         <is>
-          <t>Marcelina Podlinska</t>
+          <t>Zhang Shuai</t>
         </is>
       </c>
       <c r="AU168" s="24" t="inlineStr">
         <is>
-          <t>Marcelina Podlinska</t>
+          <t>Zhang Shuai</t>
         </is>
       </c>
       <c r="AV168" s="24" t="n"/>
@@ -49112,7 +49477,7 @@
       </c>
       <c r="BH168" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:31.401094Z</t>
+          <t>2026-08-04T14:23:32.042757Z</t>
         </is>
       </c>
       <c r="BI168" s="24" t="inlineStr">
@@ -49122,13 +49487,13 @@
       </c>
       <c r="BJ168" s="25" t="n"/>
       <c r="BK168" s="26" t="n">
-        <v>-525</v>
+        <v>-223</v>
       </c>
       <c r="BL168" s="27" t="n">
-        <v>1.190476</v>
+        <v>1.44843</v>
       </c>
       <c r="BM168" s="28" t="n">
-        <v>0.84</v>
+        <v>0.690402</v>
       </c>
       <c r="BN168" s="28" t="n"/>
       <c r="BO168" s="28" t="n"/>
@@ -49160,7 +49525,8 @@
       <c r="CO168" s="24" t="n"/>
       <c r="CP168" s="24" t="n"/>
       <c r="CQ168" s="24" t="n"/>
-      <c r="CR168" s="24" t="inlineStr">
+      <c r="CR168" s="24" t="n"/>
+      <c r="CS168" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -49169,22 +49535,22 @@
     <row r="169" ht="36" customHeight="1">
       <c r="A169" s="24" t="inlineStr">
         <is>
-          <t>947f11183dd046dd</t>
+          <t>26f96e7a16f74c02</t>
         </is>
       </c>
       <c r="B169" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C169" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T10:30Z</t>
+          <t>2026-08-04T21:00Z</t>
         </is>
       </c>
       <c r="D169" s="24" t="inlineStr">
         <is>
-          <t>961-2026:182092</t>
+          <t>421-2026:182167</t>
         </is>
       </c>
       <c r="E169" s="24" t="inlineStr">
@@ -49194,12 +49560,12 @@
       </c>
       <c r="F169" s="24" t="inlineStr">
         <is>
-          <t>Ella Seidel</t>
+          <t>McCartney Kessler</t>
         </is>
       </c>
       <c r="G169" s="24" t="inlineStr">
         <is>
-          <t>Dalma Galfi</t>
+          <t>Anna Kalinskaya</t>
         </is>
       </c>
       <c r="H169" s="24" t="inlineStr">
@@ -49219,28 +49585,28 @@
         </is>
       </c>
       <c r="L169" s="26" t="n">
-        <v>100</v>
+        <v>-163</v>
       </c>
       <c r="M169" s="27" t="n">
-        <v>2</v>
+        <v>1.613497</v>
       </c>
       <c r="N169" s="28" t="n">
-        <v>0.5</v>
+        <v>0.619772</v>
       </c>
       <c r="O169" s="28" t="n">
-        <v>0.511713</v>
+        <v>0.605938</v>
       </c>
       <c r="P169" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q169" s="28" t="n">
-        <v>0.011713</v>
+        <v>-0.013834</v>
       </c>
       <c r="R169" s="26" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S169" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T169" s="24" t="inlineStr">
         <is>
@@ -49263,7 +49629,7 @@
       <c r="AD169" s="24" t="n"/>
       <c r="AE169" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Ella Seidel p=0.488 vs Dalma Galfi. Executable ask 0.5000 (aec-wta-dalgal-ellsei-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: McCartney Kessler p=0.394 vs Anna Kalinskaya. Executable ask 0.6200 (aec-wta-annkal-mcckes-2026-08-04).</t>
         </is>
       </c>
       <c r="AF169" s="31" t="inlineStr">
@@ -49304,32 +49670,32 @@
       </c>
       <c r="AP169" s="24" t="inlineStr">
         <is>
-          <t>Ella Seidel</t>
+          <t>McCartney Kessler</t>
         </is>
       </c>
       <c r="AQ169" s="24" t="inlineStr">
         <is>
-          <t>Ella Seidel</t>
+          <t>McCartney Kessler</t>
         </is>
       </c>
       <c r="AR169" s="24" t="inlineStr">
         <is>
-          <t>Ella Seidel</t>
+          <t>McCartney Kessler</t>
         </is>
       </c>
       <c r="AS169" s="24" t="inlineStr">
         <is>
-          <t>Dalma Galfi</t>
+          <t>Anna Kalinskaya</t>
         </is>
       </c>
       <c r="AT169" s="24" t="inlineStr">
         <is>
-          <t>Dalma Galfi</t>
+          <t>Anna Kalinskaya</t>
         </is>
       </c>
       <c r="AU169" s="24" t="inlineStr">
         <is>
-          <t>Dalma Galfi</t>
+          <t>Anna Kalinskaya</t>
         </is>
       </c>
       <c r="AV169" s="24" t="n"/>
@@ -49382,7 +49748,7 @@
       </c>
       <c r="BH169" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:31.615874Z</t>
+          <t>2026-08-04T14:23:33.276581Z</t>
         </is>
       </c>
       <c r="BI169" s="24" t="inlineStr">
@@ -49392,13 +49758,13 @@
       </c>
       <c r="BJ169" s="25" t="n"/>
       <c r="BK169" s="26" t="n">
-        <v>100</v>
+        <v>-163</v>
       </c>
       <c r="BL169" s="27" t="n">
-        <v>2</v>
+        <v>1.613497</v>
       </c>
       <c r="BM169" s="28" t="n">
-        <v>0.5</v>
+        <v>0.619772</v>
       </c>
       <c r="BN169" s="28" t="n"/>
       <c r="BO169" s="28" t="n"/>
@@ -49430,31 +49796,32 @@
       <c r="CO169" s="24" t="n"/>
       <c r="CP169" s="24" t="n"/>
       <c r="CQ169" s="24" t="n"/>
-      <c r="CR169" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CR169" s="24" t="n"/>
+      <c r="CS169" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="170" ht="36" customHeight="1">
       <c r="A170" s="24" t="inlineStr">
         <is>
-          <t>f525da2ffd0e4936</t>
+          <t>f9b6cec702b74c8a</t>
         </is>
       </c>
       <c r="B170" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C170" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T10:30Z</t>
+          <t>2026-08-04T21:00Z</t>
         </is>
       </c>
       <c r="D170" s="24" t="inlineStr">
         <is>
-          <t>961-2026:182088</t>
+          <t>421-2026:182168</t>
         </is>
       </c>
       <c r="E170" s="24" t="inlineStr">
@@ -49464,12 +49831,12 @@
       </c>
       <c r="F170" s="24" t="inlineStr">
         <is>
-          <t>Elizara Yaneva</t>
+          <t>Katerina Siniakova</t>
         </is>
       </c>
       <c r="G170" s="24" t="inlineStr">
         <is>
-          <t>Linda Klimovicova</t>
+          <t>Kamilla Rakhimova</t>
         </is>
       </c>
       <c r="H170" s="24" t="inlineStr">
@@ -49479,7 +49846,7 @@
       </c>
       <c r="I170" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J170" s="25" t="n"/>
@@ -49489,28 +49856,28 @@
         </is>
       </c>
       <c r="L170" s="26" t="n">
-        <v>-104</v>
+        <v>-194</v>
       </c>
       <c r="M170" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.515464</v>
       </c>
       <c r="N170" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.659864</v>
       </c>
       <c r="O170" s="28" t="n">
-        <v>0.578623</v>
+        <v>0.66176</v>
       </c>
       <c r="P170" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q170" s="28" t="n">
-        <v>0.06881900000000001</v>
+        <v>0.001896</v>
       </c>
       <c r="R170" s="26" t="n">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="S170" s="29" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="T170" s="24" t="inlineStr">
         <is>
@@ -49533,7 +49900,7 @@
       <c r="AD170" s="24" t="n"/>
       <c r="AE170" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Elizara Yaneva p=0.421 vs Linda Klimovicova. Executable ask 0.5100 (aec-wta-linkli-eliyan-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Katerina Siniakova p=0.662 vs Kamilla Rakhimova. Executable ask 0.6600 (aec-wta-kamrak-katsin-2026-08-03).</t>
         </is>
       </c>
       <c r="AF170" s="31" t="inlineStr">
@@ -49551,7 +49918,7 @@
       <c r="AJ170" s="31" t="n"/>
       <c r="AK170" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL170" s="26" t="n">
@@ -49559,47 +49926,47 @@
       </c>
       <c r="AM170" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN170" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO170" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP170" s="24" t="inlineStr">
         <is>
-          <t>Elizara Yaneva</t>
+          <t>Katerina Siniakova</t>
         </is>
       </c>
       <c r="AQ170" s="24" t="inlineStr">
         <is>
-          <t>Elizara Yaneva</t>
+          <t>Katerina Siniakova</t>
         </is>
       </c>
       <c r="AR170" s="24" t="inlineStr">
         <is>
-          <t>Elizara Yaneva</t>
+          <t>Katerina Siniakova</t>
         </is>
       </c>
       <c r="AS170" s="24" t="inlineStr">
         <is>
-          <t>Linda Klimovicova</t>
+          <t>Kamilla Rakhimova</t>
         </is>
       </c>
       <c r="AT170" s="24" t="inlineStr">
         <is>
-          <t>Linda Klimovicova</t>
+          <t>Kamilla Rakhimova</t>
         </is>
       </c>
       <c r="AU170" s="24" t="inlineStr">
         <is>
-          <t>Linda Klimovicova</t>
+          <t>Kamilla Rakhimova</t>
         </is>
       </c>
       <c r="AV170" s="24" t="n"/>
@@ -49652,7 +50019,7 @@
       </c>
       <c r="BH170" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:31.464146Z</t>
+          <t>2026-08-04T14:23:32.455927Z</t>
         </is>
       </c>
       <c r="BI170" s="24" t="inlineStr">
@@ -49662,13 +50029,13 @@
       </c>
       <c r="BJ170" s="25" t="n"/>
       <c r="BK170" s="26" t="n">
-        <v>-104</v>
+        <v>-194</v>
       </c>
       <c r="BL170" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.515464</v>
       </c>
       <c r="BM170" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.659864</v>
       </c>
       <c r="BN170" s="28" t="n"/>
       <c r="BO170" s="28" t="n"/>
@@ -49700,7 +50067,8 @@
       <c r="CO170" s="24" t="n"/>
       <c r="CP170" s="24" t="n"/>
       <c r="CQ170" s="24" t="n"/>
-      <c r="CR170" s="24" t="inlineStr">
+      <c r="CR170" s="24" t="n"/>
+      <c r="CS170" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -49709,22 +50077,22 @@
     <row r="171" ht="36" customHeight="1">
       <c r="A171" s="24" t="inlineStr">
         <is>
-          <t>ce895cf5430d4869</t>
+          <t>b3ddab122d5c4281</t>
         </is>
       </c>
       <c r="B171" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C171" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T12:00Z</t>
+          <t>2026-08-04T22:30Z</t>
         </is>
       </c>
       <c r="D171" s="24" t="inlineStr">
         <is>
-          <t>961-2026:182082</t>
+          <t>421-2026:182188</t>
         </is>
       </c>
       <c r="E171" s="24" t="inlineStr">
@@ -49734,12 +50102,12 @@
       </c>
       <c r="F171" s="24" t="inlineStr">
         <is>
-          <t>Mona Barthel</t>
+          <t>Nikola Bartunkova</t>
         </is>
       </c>
       <c r="G171" s="24" t="inlineStr">
         <is>
-          <t>Laura Samson</t>
+          <t>Clara Tauson</t>
         </is>
       </c>
       <c r="H171" s="24" t="inlineStr">
@@ -49759,25 +50127,25 @@
         </is>
       </c>
       <c r="L171" s="26" t="n">
-        <v>-213</v>
+        <v>-108</v>
       </c>
       <c r="M171" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.925926</v>
       </c>
       <c r="N171" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.519231</v>
       </c>
       <c r="O171" s="28" t="n">
-        <v>0.523723</v>
+        <v>0.540992</v>
       </c>
       <c r="P171" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q171" s="28" t="n">
-        <v>-0.156788</v>
+        <v>0.021761</v>
       </c>
       <c r="R171" s="26" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="S171" s="29" t="n">
         <v>1</v>
@@ -49803,7 +50171,7 @@
       <c r="AD171" s="24" t="n"/>
       <c r="AE171" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Mona Barthel p=0.476 vs Laura Samson. Executable ask 0.6800 (aec-wta-lausam-monbar-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Nikola Bartunkova p=0.459 vs Clara Tauson. Executable ask 0.5200 (aec-wta-clatau-nikbar-2026-08-04).</t>
         </is>
       </c>
       <c r="AF171" s="31" t="inlineStr">
@@ -49844,32 +50212,32 @@
       </c>
       <c r="AP171" s="24" t="inlineStr">
         <is>
-          <t>Mona Barthel</t>
+          <t>Nikola Bartunkova</t>
         </is>
       </c>
       <c r="AQ171" s="24" t="inlineStr">
         <is>
-          <t>Mona Barthel</t>
+          <t>Nikola Bartunkova</t>
         </is>
       </c>
       <c r="AR171" s="24" t="inlineStr">
         <is>
-          <t>Mona Barthel</t>
+          <t>Nikola Bartunkova</t>
         </is>
       </c>
       <c r="AS171" s="24" t="inlineStr">
         <is>
-          <t>Laura Samson</t>
+          <t>Clara Tauson</t>
         </is>
       </c>
       <c r="AT171" s="24" t="inlineStr">
         <is>
-          <t>Laura Samson</t>
+          <t>Clara Tauson</t>
         </is>
       </c>
       <c r="AU171" s="24" t="inlineStr">
         <is>
-          <t>Laura Samson</t>
+          <t>Clara Tauson</t>
         </is>
       </c>
       <c r="AV171" s="24" t="n"/>
@@ -49922,7 +50290,7 @@
       </c>
       <c r="BH171" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:31.722797Z</t>
+          <t>2026-08-04T14:23:33.957089Z</t>
         </is>
       </c>
       <c r="BI171" s="24" t="inlineStr">
@@ -49932,13 +50300,13 @@
       </c>
       <c r="BJ171" s="25" t="n"/>
       <c r="BK171" s="26" t="n">
-        <v>-213</v>
+        <v>-108</v>
       </c>
       <c r="BL171" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.925926</v>
       </c>
       <c r="BM171" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.519231</v>
       </c>
       <c r="BN171" s="28" t="n"/>
       <c r="BO171" s="28" t="n"/>
@@ -49970,31 +50338,32 @@
       <c r="CO171" s="24" t="n"/>
       <c r="CP171" s="24" t="n"/>
       <c r="CQ171" s="24" t="n"/>
-      <c r="CR171" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR171" s="24" t="n"/>
+      <c r="CS171" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="172" ht="36" customHeight="1">
       <c r="A172" s="24" t="inlineStr">
         <is>
-          <t>b4985bd834cd497e</t>
+          <t>4e6b18e01f7d457d</t>
         </is>
       </c>
       <c r="B172" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C172" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T12:00Z</t>
+          <t>2026-08-04T23:00Z</t>
         </is>
       </c>
       <c r="D172" s="24" t="inlineStr">
         <is>
-          <t>961-2026:182093</t>
+          <t>421-2026:182199</t>
         </is>
       </c>
       <c r="E172" s="24" t="inlineStr">
@@ -50004,12 +50373,12 @@
       </c>
       <c r="F172" s="24" t="inlineStr">
         <is>
-          <t>Lia Karatancheva</t>
+          <t>Moyuka Uchijima</t>
         </is>
       </c>
       <c r="G172" s="24" t="inlineStr">
         <is>
-          <t>Zuzanna Pawlikowska</t>
+          <t>Aryna Sabalenka</t>
         </is>
       </c>
       <c r="H172" s="24" t="inlineStr">
@@ -50029,28 +50398,28 @@
         </is>
       </c>
       <c r="L172" s="26" t="n">
-        <v>203</v>
+        <v>-1900</v>
       </c>
       <c r="M172" s="27" t="n">
-        <v>3.03</v>
+        <v>1.052632</v>
       </c>
       <c r="N172" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.95</v>
       </c>
       <c r="O172" s="28" t="n">
-        <v>0.6278049999999999</v>
+        <v>0.939322</v>
       </c>
       <c r="P172" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q172" s="28" t="n">
-        <v>0.297772</v>
+        <v>-0.010678</v>
       </c>
       <c r="R172" s="26" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="S172" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T172" s="24" t="inlineStr">
         <is>
@@ -50073,7 +50442,7 @@
       <c r="AD172" s="24" t="n"/>
       <c r="AE172" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Lia Karatancheva p=0.372 vs Zuzanna Pawlikowska. Executable ask 0.3300 (aec-wta-zuzpaw-liakar-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Moyuka Uchijima p=0.061 vs Aryna Sabalenka. Executable ask 0.9500 (aec-wta-arysab-moyuch-2026-08-03).</t>
         </is>
       </c>
       <c r="AF172" s="31" t="inlineStr">
@@ -50109,37 +50478,37 @@
       </c>
       <c r="AO172" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP172" s="24" t="inlineStr">
         <is>
-          <t>Lia Karatancheva</t>
+          <t>Moyuka Uchijima</t>
         </is>
       </c>
       <c r="AQ172" s="24" t="inlineStr">
         <is>
-          <t>Lia Karatancheva</t>
+          <t>Moyuka Uchijima</t>
         </is>
       </c>
       <c r="AR172" s="24" t="inlineStr">
         <is>
-          <t>Lia Karatancheva</t>
+          <t>Moyuka Uchijima</t>
         </is>
       </c>
       <c r="AS172" s="24" t="inlineStr">
         <is>
-          <t>Zuzanna Pawlikowska</t>
+          <t>Aryna Sabalenka</t>
         </is>
       </c>
       <c r="AT172" s="24" t="inlineStr">
         <is>
-          <t>Zuzanna Pawlikowska</t>
+          <t>Aryna Sabalenka</t>
         </is>
       </c>
       <c r="AU172" s="24" t="inlineStr">
         <is>
-          <t>Zuzanna Pawlikowska</t>
+          <t>Aryna Sabalenka</t>
         </is>
       </c>
       <c r="AV172" s="24" t="n"/>
@@ -50192,7 +50561,7 @@
       </c>
       <c r="BH172" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:31.820806Z</t>
+          <t>2026-08-04T14:23:34.911863Z</t>
         </is>
       </c>
       <c r="BI172" s="24" t="inlineStr">
@@ -50202,13 +50571,13 @@
       </c>
       <c r="BJ172" s="25" t="n"/>
       <c r="BK172" s="26" t="n">
-        <v>203</v>
+        <v>-1900</v>
       </c>
       <c r="BL172" s="27" t="n">
-        <v>3.03</v>
+        <v>1.052632</v>
       </c>
       <c r="BM172" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.95</v>
       </c>
       <c r="BN172" s="28" t="n"/>
       <c r="BO172" s="28" t="n"/>
@@ -50240,31 +50609,32 @@
       <c r="CO172" s="24" t="n"/>
       <c r="CP172" s="24" t="n"/>
       <c r="CQ172" s="24" t="n"/>
-      <c r="CR172" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CR172" s="24" t="n"/>
+      <c r="CS172" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="173" ht="36" customHeight="1">
       <c r="A173" s="24" t="inlineStr">
         <is>
-          <t>5a3c0b54550b4fb8</t>
+          <t>ff3c62439c944ae0</t>
         </is>
       </c>
       <c r="B173" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C173" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T12:00Z</t>
+          <t>2026-08-05T00:30Z</t>
         </is>
       </c>
       <c r="D173" s="24" t="inlineStr">
         <is>
-          <t>961-2026:182096</t>
+          <t>421-2026:182187</t>
         </is>
       </c>
       <c r="E173" s="24" t="inlineStr">
@@ -50274,12 +50644,12 @@
       </c>
       <c r="F173" s="24" t="inlineStr">
         <is>
-          <t>Sofia Costoulas</t>
+          <t>Amanda Anisimova</t>
         </is>
       </c>
       <c r="G173" s="24" t="inlineStr">
         <is>
-          <t>Gabriela Knutson</t>
+          <t>Lanlana Tararudee</t>
         </is>
       </c>
       <c r="H173" s="24" t="inlineStr">
@@ -50299,28 +50669,28 @@
         </is>
       </c>
       <c r="L173" s="26" t="n">
-        <v>-170</v>
+        <v>-245</v>
       </c>
       <c r="M173" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.408163</v>
       </c>
       <c r="N173" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.710145</v>
       </c>
       <c r="O173" s="28" t="n">
-        <v>0.5347150000000001</v>
+        <v>0.669885</v>
       </c>
       <c r="P173" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q173" s="28" t="n">
-        <v>-0.094915</v>
+        <v>-0.04026</v>
       </c>
       <c r="R173" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S173" s="29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="T173" s="24" t="inlineStr">
         <is>
@@ -50343,7 +50713,7 @@
       <c r="AD173" s="24" t="n"/>
       <c r="AE173" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Sofia Costoulas p=0.535 vs Gabriela Knutson. Executable ask 0.6300 (aec-wta-gabknu-sofcos-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Amanda Anisimova p=0.670 vs Lanlana Tararudee. Executable ask 0.7100 (aec-wta-lantar-amaani-2026-08-04).</t>
         </is>
       </c>
       <c r="AF173" s="31" t="inlineStr">
@@ -50384,32 +50754,32 @@
       </c>
       <c r="AP173" s="24" t="inlineStr">
         <is>
-          <t>Sofia Costoulas</t>
+          <t>Amanda Anisimova</t>
         </is>
       </c>
       <c r="AQ173" s="24" t="inlineStr">
         <is>
-          <t>Sofia Costoulas</t>
+          <t>Amanda Anisimova</t>
         </is>
       </c>
       <c r="AR173" s="24" t="inlineStr">
         <is>
-          <t>Sofia Costoulas</t>
+          <t>Amanda Anisimova</t>
         </is>
       </c>
       <c r="AS173" s="24" t="inlineStr">
         <is>
-          <t>Gabriela Knutson</t>
+          <t>Lanlana Tararudee</t>
         </is>
       </c>
       <c r="AT173" s="24" t="inlineStr">
         <is>
-          <t>Gabriela Knutson</t>
+          <t>Lanlana Tararudee</t>
         </is>
       </c>
       <c r="AU173" s="24" t="inlineStr">
         <is>
-          <t>Gabriela Knutson</t>
+          <t>Lanlana Tararudee</t>
         </is>
       </c>
       <c r="AV173" s="24" t="n"/>
@@ -50462,7 +50832,7 @@
       </c>
       <c r="BH173" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:31.801243Z</t>
+          <t>2026-08-04T14:23:35.573123Z</t>
         </is>
       </c>
       <c r="BI173" s="24" t="inlineStr">
@@ -50472,13 +50842,13 @@
       </c>
       <c r="BJ173" s="25" t="n"/>
       <c r="BK173" s="26" t="n">
-        <v>-170</v>
+        <v>-245</v>
       </c>
       <c r="BL173" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.408163</v>
       </c>
       <c r="BM173" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.710145</v>
       </c>
       <c r="BN173" s="28" t="n"/>
       <c r="BO173" s="28" t="n"/>
@@ -50510,7 +50880,8 @@
       <c r="CO173" s="24" t="n"/>
       <c r="CP173" s="24" t="n"/>
       <c r="CQ173" s="24" t="n"/>
-      <c r="CR173" s="24" t="inlineStr">
+      <c r="CR173" s="24" t="n"/>
+      <c r="CS173" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -50519,12 +50890,12 @@
     <row r="174" ht="36" customHeight="1">
       <c r="A174" s="24" t="inlineStr">
         <is>
-          <t>bcff1fafb03f4fbb</t>
+          <t>d4594d4187e045ac</t>
         </is>
       </c>
       <c r="B174" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C174" s="24" t="inlineStr">
@@ -50732,7 +51103,7 @@
       </c>
       <c r="BH174" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:44.778344Z</t>
+          <t>2026-08-04T14:23:37.811283Z</t>
         </is>
       </c>
       <c r="BI174" s="24" t="inlineStr">
@@ -50780,7 +51151,8 @@
       <c r="CO174" s="24" t="n"/>
       <c r="CP174" s="24" t="n"/>
       <c r="CQ174" s="24" t="n"/>
-      <c r="CR174" s="24" t="inlineStr">
+      <c r="CR174" s="24" t="n"/>
+      <c r="CS174" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -50789,12 +51161,12 @@
     <row r="175" ht="36" customHeight="1">
       <c r="A175" s="24" t="inlineStr">
         <is>
-          <t>c0eb350a432b4ddc</t>
+          <t>b1e7434525d24f1d</t>
         </is>
       </c>
       <c r="B175" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C175" s="24" t="inlineStr">
@@ -50839,13 +51211,13 @@
         </is>
       </c>
       <c r="L175" s="26" t="n">
-        <v>-108</v>
+        <v>-117</v>
       </c>
       <c r="M175" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.854701</v>
       </c>
       <c r="N175" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.539171</v>
       </c>
       <c r="O175" s="28" t="n">
         <v>0.559835</v>
@@ -50854,10 +51226,10 @@
         <v>0.05</v>
       </c>
       <c r="Q175" s="28" t="n">
-        <v>0.040604</v>
+        <v>0.020664</v>
       </c>
       <c r="R175" s="26" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="S175" s="29" t="n">
         <v>1</v>
@@ -50883,7 +51255,7 @@
       <c r="AD175" s="24" t="n"/>
       <c r="AE175" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Mattia Bellucci p=0.440 vs Sebastian Baez. Executable ask 0.5200 (aec-atp-sebbae-matbel-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Mattia Bellucci p=0.440 vs Sebastian Baez. Executable ask 0.5400 (aec-atp-sebbae-matbel-2026-08-03).</t>
         </is>
       </c>
       <c r="AF175" s="31" t="inlineStr">
@@ -51002,7 +51374,7 @@
       </c>
       <c r="BH175" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:43.563914Z</t>
+          <t>2026-08-04T14:23:36.155240Z</t>
         </is>
       </c>
       <c r="BI175" s="24" t="inlineStr">
@@ -51012,13 +51384,13 @@
       </c>
       <c r="BJ175" s="25" t="n"/>
       <c r="BK175" s="26" t="n">
-        <v>-108</v>
+        <v>-117</v>
       </c>
       <c r="BL175" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.854701</v>
       </c>
       <c r="BM175" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.539171</v>
       </c>
       <c r="BN175" s="28" t="n"/>
       <c r="BO175" s="28" t="n"/>
@@ -51050,7 +51422,8 @@
       <c r="CO175" s="24" t="n"/>
       <c r="CP175" s="24" t="n"/>
       <c r="CQ175" s="24" t="n"/>
-      <c r="CR175" s="24" t="inlineStr">
+      <c r="CR175" s="24" t="n"/>
+      <c r="CS175" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -51059,12 +51432,12 @@
     <row r="176" ht="36" customHeight="1">
       <c r="A176" s="24" t="inlineStr">
         <is>
-          <t>da76208f26424d34</t>
+          <t>219c58a8b2b245b8</t>
         </is>
       </c>
       <c r="B176" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C176" s="24" t="inlineStr">
@@ -51109,13 +51482,13 @@
         </is>
       </c>
       <c r="L176" s="26" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="M176" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.787402</v>
       </c>
       <c r="N176" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O176" s="28" t="n">
         <v>0.568221</v>
@@ -51124,10 +51497,10 @@
         <v>0.05</v>
       </c>
       <c r="Q176" s="28" t="n">
-        <v>0.018671</v>
+        <v>0.008750000000000001</v>
       </c>
       <c r="R176" s="26" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="S176" s="29" t="n">
         <v>1</v>
@@ -51153,7 +51526,7 @@
       <c r="AD176" s="24" t="n"/>
       <c r="AE176" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Jenson Brooksby p=0.568 vs Adam Walton. Executable ask 0.5500 (aec-atp-adawal-jenbro-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Jenson Brooksby p=0.568 vs Adam Walton. Executable ask 0.5600 (aec-atp-adawal-jenbro-2026-08-03).</t>
         </is>
       </c>
       <c r="AF176" s="31" t="inlineStr">
@@ -51272,7 +51645,7 @@
       </c>
       <c r="BH176" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:46.890318Z</t>
+          <t>2026-08-04T14:23:39.663692Z</t>
         </is>
       </c>
       <c r="BI176" s="24" t="inlineStr">
@@ -51282,13 +51655,13 @@
       </c>
       <c r="BJ176" s="25" t="n"/>
       <c r="BK176" s="26" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="BL176" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.787402</v>
       </c>
       <c r="BM176" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN176" s="28" t="n"/>
       <c r="BO176" s="28" t="n"/>
@@ -51320,7 +51693,8 @@
       <c r="CO176" s="24" t="n"/>
       <c r="CP176" s="24" t="n"/>
       <c r="CQ176" s="24" t="n"/>
-      <c r="CR176" s="24" t="inlineStr">
+      <c r="CR176" s="24" t="n"/>
+      <c r="CS176" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -51329,12 +51703,12 @@
     <row r="177" ht="36" customHeight="1">
       <c r="A177" s="24" t="inlineStr">
         <is>
-          <t>8fb07b3df63a4f65</t>
+          <t>db06ce7fe7e84145</t>
         </is>
       </c>
       <c r="B177" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C177" s="24" t="inlineStr">
@@ -51379,13 +51753,13 @@
         </is>
       </c>
       <c r="L177" s="26" t="n">
-        <v>-170</v>
+        <v>-186</v>
       </c>
       <c r="M177" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.537634</v>
       </c>
       <c r="N177" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.65035</v>
       </c>
       <c r="O177" s="28" t="n">
         <v>0.514482</v>
@@ -51394,7 +51768,7 @@
         <v>0.05</v>
       </c>
       <c r="Q177" s="28" t="n">
-        <v>-0.115148</v>
+        <v>-0.135868</v>
       </c>
       <c r="R177" s="26" t="n">
         <v>0</v>
@@ -51423,7 +51797,7 @@
       <c r="AD177" s="24" t="n"/>
       <c r="AE177" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Stefanos Tsitsipas p=0.514 vs Martin Damm. Executable ask 0.6300 (aec-atp-mardam-stetsi-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Stefanos Tsitsipas p=0.514 vs Martin Damm. Executable ask 0.6500 (aec-atp-mardam-stetsi-2026-08-03).</t>
         </is>
       </c>
       <c r="AF177" s="31" t="inlineStr">
@@ -51542,7 +51916,7 @@
       </c>
       <c r="BH177" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:45.972655Z</t>
+          <t>2026-08-04T14:23:38.853444Z</t>
         </is>
       </c>
       <c r="BI177" s="24" t="inlineStr">
@@ -51552,13 +51926,13 @@
       </c>
       <c r="BJ177" s="25" t="n"/>
       <c r="BK177" s="26" t="n">
-        <v>-170</v>
+        <v>-186</v>
       </c>
       <c r="BL177" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.537634</v>
       </c>
       <c r="BM177" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.65035</v>
       </c>
       <c r="BN177" s="28" t="n"/>
       <c r="BO177" s="28" t="n"/>
@@ -51590,7 +51964,8 @@
       <c r="CO177" s="24" t="n"/>
       <c r="CP177" s="24" t="n"/>
       <c r="CQ177" s="24" t="n"/>
-      <c r="CR177" s="24" t="inlineStr">
+      <c r="CR177" s="24" t="n"/>
+      <c r="CS177" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -51599,12 +51974,12 @@
     <row r="178" ht="36" customHeight="1">
       <c r="A178" s="24" t="inlineStr">
         <is>
-          <t>c8a02066f8684928</t>
+          <t>bb57c803540c45fb</t>
         </is>
       </c>
       <c r="B178" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C178" s="24" t="inlineStr">
@@ -51812,7 +52187,7 @@
       </c>
       <c r="BH178" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:49.747408Z</t>
+          <t>2026-08-04T14:23:42.520768Z</t>
         </is>
       </c>
       <c r="BI178" s="24" t="inlineStr">
@@ -51860,7 +52235,8 @@
       <c r="CO178" s="24" t="n"/>
       <c r="CP178" s="24" t="n"/>
       <c r="CQ178" s="24" t="n"/>
-      <c r="CR178" s="24" t="inlineStr">
+      <c r="CR178" s="24" t="n"/>
+      <c r="CS178" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -51869,12 +52245,12 @@
     <row r="179" ht="36" customHeight="1">
       <c r="A179" s="24" t="inlineStr">
         <is>
-          <t>09ea9e9a95344dd3</t>
+          <t>40583882508740f1</t>
         </is>
       </c>
       <c r="B179" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C179" s="24" t="inlineStr">
@@ -51919,13 +52295,13 @@
         </is>
       </c>
       <c r="L179" s="26" t="n">
-        <v>-138</v>
+        <v>-144</v>
       </c>
       <c r="M179" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.694444</v>
       </c>
       <c r="N179" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.590164</v>
       </c>
       <c r="O179" s="28" t="n">
         <v>0.69073</v>
@@ -51934,10 +52310,10 @@
         <v>0.05</v>
       </c>
       <c r="Q179" s="28" t="n">
-        <v>0.110898</v>
+        <v>0.100566</v>
       </c>
       <c r="R179" s="26" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="S179" s="29" t="n">
         <v>2</v>
@@ -51963,7 +52339,7 @@
       <c r="AD179" s="24" t="n"/>
       <c r="AE179" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Liam Draxl p=0.309 vs Daniel Merida. Executable ask 0.5800 (aec-atp-danagu-liadra-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Liam Draxl p=0.309 vs Daniel Merida. Executable ask 0.5900 (aec-atp-danagu-liadra-2026-08-03).</t>
         </is>
       </c>
       <c r="AF179" s="31" t="inlineStr">
@@ -52082,7 +52458,7 @@
       </c>
       <c r="BH179" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:50.946314Z</t>
+          <t>2026-08-04T14:23:40.504586Z</t>
         </is>
       </c>
       <c r="BI179" s="24" t="inlineStr">
@@ -52092,13 +52468,13 @@
       </c>
       <c r="BJ179" s="25" t="n"/>
       <c r="BK179" s="26" t="n">
-        <v>-138</v>
+        <v>-144</v>
       </c>
       <c r="BL179" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.694444</v>
       </c>
       <c r="BM179" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.590164</v>
       </c>
       <c r="BN179" s="28" t="n"/>
       <c r="BO179" s="28" t="n"/>
@@ -52130,7 +52506,8 @@
       <c r="CO179" s="24" t="n"/>
       <c r="CP179" s="24" t="n"/>
       <c r="CQ179" s="24" t="n"/>
-      <c r="CR179" s="24" t="inlineStr">
+      <c r="CR179" s="24" t="n"/>
+      <c r="CS179" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -52139,12 +52516,12 @@
     <row r="180" ht="36" customHeight="1">
       <c r="A180" s="24" t="inlineStr">
         <is>
-          <t>f60d5c66ca944eea</t>
+          <t>8b1d1d4c380f4fae</t>
         </is>
       </c>
       <c r="B180" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C180" s="24" t="inlineStr">
@@ -52189,13 +52566,13 @@
         </is>
       </c>
       <c r="L180" s="26" t="n">
-        <v>-194</v>
+        <v>-203</v>
       </c>
       <c r="M180" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.492611</v>
       </c>
       <c r="N180" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.669967</v>
       </c>
       <c r="O180" s="28" t="n">
         <v>0.627342</v>
@@ -52204,10 +52581,10 @@
         <v>0.05</v>
       </c>
       <c r="Q180" s="28" t="n">
-        <v>-0.032522</v>
+        <v>-0.042625</v>
       </c>
       <c r="R180" s="26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S180" s="29" t="n">
         <v>1.5</v>
@@ -52233,7 +52610,7 @@
       <c r="AD180" s="24" t="n"/>
       <c r="AE180" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Valentin Royer p=0.373 vs Pablo Carreno Busta. Executable ask 0.6600 (aec-atp-pabbus-valroy-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Valentin Royer p=0.373 vs Pablo Carreno Busta. Executable ask 0.6700 (aec-atp-pabbus-valroy-2026-08-03).</t>
         </is>
       </c>
       <c r="AF180" s="31" t="inlineStr">
@@ -52352,7 +52729,7 @@
       </c>
       <c r="BH180" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:50.213634Z</t>
+          <t>2026-08-04T14:23:42.998144Z</t>
         </is>
       </c>
       <c r="BI180" s="24" t="inlineStr">
@@ -52362,13 +52739,13 @@
       </c>
       <c r="BJ180" s="25" t="n"/>
       <c r="BK180" s="26" t="n">
-        <v>-194</v>
+        <v>-203</v>
       </c>
       <c r="BL180" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.492611</v>
       </c>
       <c r="BM180" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.669967</v>
       </c>
       <c r="BN180" s="28" t="n"/>
       <c r="BO180" s="28" t="n"/>
@@ -52400,7 +52777,8 @@
       <c r="CO180" s="24" t="n"/>
       <c r="CP180" s="24" t="n"/>
       <c r="CQ180" s="24" t="n"/>
-      <c r="CR180" s="24" t="inlineStr">
+      <c r="CR180" s="24" t="n"/>
+      <c r="CS180" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -52409,12 +52787,12 @@
     <row r="181" ht="36" customHeight="1">
       <c r="A181" s="24" t="inlineStr">
         <is>
-          <t>f1bb8b4fd20d4ee4</t>
+          <t>c82edb11ac4240cb</t>
         </is>
       </c>
       <c r="B181" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C181" s="24" t="inlineStr">
@@ -52459,13 +52837,13 @@
         </is>
       </c>
       <c r="L181" s="26" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="M181" s="27" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="N181" s="28" t="n">
-        <v>0.4</v>
+        <v>0.390625</v>
       </c>
       <c r="O181" s="28" t="n">
         <v>0.51802</v>
@@ -52474,10 +52852,10 @@
         <v>0.05</v>
       </c>
       <c r="Q181" s="28" t="n">
-        <v>0.11802</v>
+        <v>0.127395</v>
       </c>
       <c r="R181" s="26" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="S181" s="29" t="n">
         <v>1</v>
@@ -52503,7 +52881,7 @@
       <c r="AD181" s="24" t="n"/>
       <c r="AE181" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Roman Andres Burruchaga p=0.518 vs Alexei Popyrin. Executable ask 0.4000 (aec-atp-alepop-rombur-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Roman Andres Burruchaga p=0.518 vs Alexei Popyrin. Executable ask 0.3900 (aec-atp-alepop-rombur-2026-08-03).</t>
         </is>
       </c>
       <c r="AF181" s="31" t="inlineStr">
@@ -52622,7 +53000,7 @@
       </c>
       <c r="BH181" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:48.641413Z</t>
+          <t>2026-08-04T14:23:41.482867Z</t>
         </is>
       </c>
       <c r="BI181" s="24" t="inlineStr">
@@ -52632,13 +53010,13 @@
       </c>
       <c r="BJ181" s="25" t="n"/>
       <c r="BK181" s="26" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="BL181" s="27" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BM181" s="28" t="n">
-        <v>0.4</v>
+        <v>0.390625</v>
       </c>
       <c r="BN181" s="28" t="n"/>
       <c r="BO181" s="28" t="n"/>
@@ -52670,7 +53048,8 @@
       <c r="CO181" s="24" t="n"/>
       <c r="CP181" s="24" t="n"/>
       <c r="CQ181" s="24" t="n"/>
-      <c r="CR181" s="24" t="inlineStr">
+      <c r="CR181" s="24" t="n"/>
+      <c r="CS181" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -52679,12 +53058,12 @@
     <row r="182" ht="36" customHeight="1">
       <c r="A182" s="24" t="inlineStr">
         <is>
-          <t>b818c068bd7e4851</t>
+          <t>099541b05ab04a2b</t>
         </is>
       </c>
       <c r="B182" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C182" s="24" t="inlineStr">
@@ -52892,7 +53271,7 @@
       </c>
       <c r="BH182" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:52.807217Z</t>
+          <t>2026-08-04T14:23:46.218511Z</t>
         </is>
       </c>
       <c r="BI182" s="24" t="inlineStr">
@@ -52940,7 +53319,8 @@
       <c r="CO182" s="24" t="n"/>
       <c r="CP182" s="24" t="n"/>
       <c r="CQ182" s="24" t="n"/>
-      <c r="CR182" s="24" t="inlineStr">
+      <c r="CR182" s="24" t="n"/>
+      <c r="CS182" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -52949,12 +53329,12 @@
     <row r="183" ht="36" customHeight="1">
       <c r="A183" s="24" t="inlineStr">
         <is>
-          <t>ba0ec3670fa347b3</t>
+          <t>04ece78aae634ca4</t>
         </is>
       </c>
       <c r="B183" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C183" s="24" t="inlineStr">
@@ -52999,13 +53379,13 @@
         </is>
       </c>
       <c r="L183" s="26" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="M183" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.925926</v>
       </c>
       <c r="N183" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.519231</v>
       </c>
       <c r="O183" s="28" t="n">
         <v>0.506379</v>
@@ -53014,10 +53394,10 @@
         <v>0.05</v>
       </c>
       <c r="Q183" s="28" t="n">
-        <v>-0.003425</v>
+        <v>-0.012852</v>
       </c>
       <c r="R183" s="26" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="S183" s="29" t="n">
         <v>1</v>
@@ -53043,7 +53423,7 @@
       <c r="AD183" s="24" t="n"/>
       <c r="AE183" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Tallon Griekspoor p=0.506 vs Lorenzo Sonego. Executable ask 0.5100 (aec-atp-lorson-talgri-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Tallon Griekspoor p=0.506 vs Lorenzo Sonego. Executable ask 0.5200 (aec-atp-lorson-talgri-2026-08-03).</t>
         </is>
       </c>
       <c r="AF183" s="31" t="inlineStr">
@@ -53162,7 +53542,7 @@
       </c>
       <c r="BH183" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:53.527933Z</t>
+          <t>2026-08-04T14:23:46.583118Z</t>
         </is>
       </c>
       <c r="BI183" s="24" t="inlineStr">
@@ -53172,13 +53552,13 @@
       </c>
       <c r="BJ183" s="25" t="n"/>
       <c r="BK183" s="26" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="BL183" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.925926</v>
       </c>
       <c r="BM183" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.519231</v>
       </c>
       <c r="BN183" s="28" t="n"/>
       <c r="BO183" s="28" t="n"/>
@@ -53210,7 +53590,8 @@
       <c r="CO183" s="24" t="n"/>
       <c r="CP183" s="24" t="n"/>
       <c r="CQ183" s="24" t="n"/>
-      <c r="CR183" s="24" t="inlineStr">
+      <c r="CR183" s="24" t="n"/>
+      <c r="CS183" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -53219,12 +53600,12 @@
     <row r="184" ht="36" customHeight="1">
       <c r="A184" s="24" t="inlineStr">
         <is>
-          <t>77a8f6d8bff843f0</t>
+          <t>a82fabf49ca14e39</t>
         </is>
       </c>
       <c r="B184" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C184" s="24" t="inlineStr">
@@ -53432,7 +53813,7 @@
       </c>
       <c r="BH184" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:55.134953Z</t>
+          <t>2026-08-04T14:23:48.356638Z</t>
         </is>
       </c>
       <c r="BI184" s="24" t="inlineStr">
@@ -53480,7 +53861,8 @@
       <c r="CO184" s="24" t="n"/>
       <c r="CP184" s="24" t="n"/>
       <c r="CQ184" s="24" t="n"/>
-      <c r="CR184" s="24" t="inlineStr">
+      <c r="CR184" s="24" t="n"/>
+      <c r="CS184" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -53489,12 +53871,12 @@
     <row r="185" ht="36" customHeight="1">
       <c r="A185" s="24" t="inlineStr">
         <is>
-          <t>2d910045d5f748be</t>
+          <t>fc66766cb5fa4682</t>
         </is>
       </c>
       <c r="B185" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C185" s="24" t="inlineStr">
@@ -53702,7 +54084,7 @@
       </c>
       <c r="BH185" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:54.448463Z</t>
+          <t>2026-08-04T14:23:45.147148Z</t>
         </is>
       </c>
       <c r="BI185" s="24" t="inlineStr">
@@ -53750,7 +54132,8 @@
       <c r="CO185" s="24" t="n"/>
       <c r="CP185" s="24" t="n"/>
       <c r="CQ185" s="24" t="n"/>
-      <c r="CR185" s="24" t="inlineStr">
+      <c r="CR185" s="24" t="n"/>
+      <c r="CS185" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -53759,12 +54142,12 @@
     <row r="186" ht="36" customHeight="1">
       <c r="A186" s="24" t="inlineStr">
         <is>
-          <t>6ad322714fc845d5</t>
+          <t>ccfb12ee82884b5f</t>
         </is>
       </c>
       <c r="B186" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C186" s="24" t="inlineStr">
@@ -53972,7 +54355,7 @@
       </c>
       <c r="BH186" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:52.122317Z</t>
+          <t>2026-08-04T14:23:47.750919Z</t>
         </is>
       </c>
       <c r="BI186" s="24" t="inlineStr">
@@ -54020,7 +54403,8 @@
       <c r="CO186" s="24" t="n"/>
       <c r="CP186" s="24" t="n"/>
       <c r="CQ186" s="24" t="n"/>
-      <c r="CR186" s="24" t="inlineStr">
+      <c r="CR186" s="24" t="n"/>
+      <c r="CS186" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -54029,12 +54413,12 @@
     <row r="187" ht="36" customHeight="1">
       <c r="A187" s="24" t="inlineStr">
         <is>
-          <t>e7dbf06e2b4844e9</t>
+          <t>bc82e4b9c900489e</t>
         </is>
       </c>
       <c r="B187" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C187" s="24" t="inlineStr">
@@ -54079,13 +54463,13 @@
         </is>
       </c>
       <c r="L187" s="26" t="n">
-        <v>-567</v>
+        <v>-525</v>
       </c>
       <c r="M187" s="27" t="n">
-        <v>1.176367</v>
+        <v>1.190476</v>
       </c>
       <c r="N187" s="28" t="n">
-        <v>0.850075</v>
+        <v>0.84</v>
       </c>
       <c r="O187" s="28" t="n">
         <v>0.764483</v>
@@ -54094,7 +54478,7 @@
         <v>0.05</v>
       </c>
       <c r="Q187" s="28" t="n">
-        <v>-0.085592</v>
+        <v>-0.075517</v>
       </c>
       <c r="R187" s="26" t="n">
         <v>0</v>
@@ -54123,7 +54507,7 @@
       <c r="AD187" s="24" t="n"/>
       <c r="AE187" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Vit Kopriva p=0.236 vs Jiri Lehecka. Executable ask 0.8500 (aec-atp-jirleh-vitkop-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Vit Kopriva p=0.236 vs Jiri Lehecka. Executable ask 0.8400 (aec-atp-jirleh-vitkop-2026-08-04).</t>
         </is>
       </c>
       <c r="AF187" s="31" t="inlineStr">
@@ -54242,7 +54626,7 @@
       </c>
       <c r="BH187" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:57.596271Z</t>
+          <t>2026-08-04T14:23:49.815541Z</t>
         </is>
       </c>
       <c r="BI187" s="24" t="inlineStr">
@@ -54252,13 +54636,13 @@
       </c>
       <c r="BJ187" s="25" t="n"/>
       <c r="BK187" s="26" t="n">
-        <v>-567</v>
+        <v>-525</v>
       </c>
       <c r="BL187" s="27" t="n">
-        <v>1.176367</v>
+        <v>1.190476</v>
       </c>
       <c r="BM187" s="28" t="n">
-        <v>0.850075</v>
+        <v>0.84</v>
       </c>
       <c r="BN187" s="28" t="n"/>
       <c r="BO187" s="28" t="n"/>
@@ -54290,7 +54674,8 @@
       <c r="CO187" s="24" t="n"/>
       <c r="CP187" s="24" t="n"/>
       <c r="CQ187" s="24" t="n"/>
-      <c r="CR187" s="24" t="inlineStr">
+      <c r="CR187" s="24" t="n"/>
+      <c r="CS187" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -54299,12 +54684,12 @@
     <row r="188" ht="36" customHeight="1">
       <c r="A188" s="24" t="inlineStr">
         <is>
-          <t>7577e1e59b13473b</t>
+          <t>47fc87a981aa4c49</t>
         </is>
       </c>
       <c r="B188" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C188" s="24" t="inlineStr">
@@ -54349,13 +54734,13 @@
         </is>
       </c>
       <c r="L188" s="26" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="M188" s="27" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="N188" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.420168</v>
       </c>
       <c r="O188" s="28" t="n">
         <v>0.523934</v>
@@ -54364,10 +54749,10 @@
         <v>0.05</v>
       </c>
       <c r="Q188" s="28" t="n">
-        <v>0.114098</v>
+        <v>0.103766</v>
       </c>
       <c r="R188" s="26" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="S188" s="29" t="n">
         <v>1</v>
@@ -54393,7 +54778,7 @@
       <c r="AD188" s="24" t="n"/>
       <c r="AE188" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Alexander Blockx p=0.476 vs Jaume Munar. Executable ask 0.4100 (aec-atp-jaumun-aleblo-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Alexander Blockx p=0.476 vs Jaume Munar. Executable ask 0.4200 (aec-atp-jaumun-aleblo-2026-08-03).</t>
         </is>
       </c>
       <c r="AF188" s="31" t="inlineStr">
@@ -54512,7 +54897,7 @@
       </c>
       <c r="BH188" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:56.817049Z</t>
+          <t>2026-08-04T14:23:49.201497Z</t>
         </is>
       </c>
       <c r="BI188" s="24" t="inlineStr">
@@ -54522,13 +54907,13 @@
       </c>
       <c r="BJ188" s="25" t="n"/>
       <c r="BK188" s="26" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="BL188" s="27" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="BM188" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.420168</v>
       </c>
       <c r="BN188" s="28" t="n"/>
       <c r="BO188" s="28" t="n"/>
@@ -54560,7 +54945,8 @@
       <c r="CO188" s="24" t="n"/>
       <c r="CP188" s="24" t="n"/>
       <c r="CQ188" s="24" t="n"/>
-      <c r="CR188" s="24" t="inlineStr">
+      <c r="CR188" s="24" t="n"/>
+      <c r="CS188" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -54569,12 +54955,12 @@
     <row r="189" ht="36" customHeight="1">
       <c r="A189" s="24" t="inlineStr">
         <is>
-          <t>a6e89277573249a5</t>
+          <t>1bb17947625a4f7a</t>
         </is>
       </c>
       <c r="B189" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C189" s="24" t="inlineStr">
@@ -54619,13 +55005,13 @@
         </is>
       </c>
       <c r="L189" s="26" t="n">
-        <v>-163</v>
+        <v>-170</v>
       </c>
       <c r="M189" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.588235</v>
       </c>
       <c r="N189" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.62963</v>
       </c>
       <c r="O189" s="28" t="n">
         <v>0.654828</v>
@@ -54634,10 +55020,10 @@
         <v>0.05</v>
       </c>
       <c r="Q189" s="28" t="n">
-        <v>0.035056</v>
+        <v>0.025198</v>
       </c>
       <c r="R189" s="26" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="S189" s="29" t="n">
         <v>1.75</v>
@@ -54663,7 +55049,7 @@
       <c r="AD189" s="24" t="n"/>
       <c r="AE189" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Fabian Marozsan p=0.655 vs Shintaro Mochizuki. Executable ask 0.6200 (aec-atp-shimoc-fabmar-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Fabian Marozsan p=0.655 vs Shintaro Mochizuki. Executable ask 0.6300 (aec-atp-shimoc-fabmar-2026-08-03).</t>
         </is>
       </c>
       <c r="AF189" s="31" t="inlineStr">
@@ -54782,7 +55168,7 @@
       </c>
       <c r="BH189" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:55.916912Z</t>
+          <t>2026-08-04T14:23:51.024940Z</t>
         </is>
       </c>
       <c r="BI189" s="24" t="inlineStr">
@@ -54792,13 +55178,13 @@
       </c>
       <c r="BJ189" s="25" t="n"/>
       <c r="BK189" s="26" t="n">
-        <v>-163</v>
+        <v>-170</v>
       </c>
       <c r="BL189" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.588235</v>
       </c>
       <c r="BM189" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.62963</v>
       </c>
       <c r="BN189" s="28" t="n"/>
       <c r="BO189" s="28" t="n"/>
@@ -54830,7 +55216,8 @@
       <c r="CO189" s="24" t="n"/>
       <c r="CP189" s="24" t="n"/>
       <c r="CQ189" s="24" t="n"/>
-      <c r="CR189" s="24" t="inlineStr">
+      <c r="CR189" s="24" t="n"/>
+      <c r="CS189" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -54839,12 +55226,12 @@
     <row r="190" ht="36" customHeight="1">
       <c r="A190" s="24" t="inlineStr">
         <is>
-          <t>9dea793c752d4032</t>
+          <t>a35d74c7eadf437b</t>
         </is>
       </c>
       <c r="B190" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C190" s="24" t="inlineStr">
@@ -55052,7 +55439,7 @@
       </c>
       <c r="BH190" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:59.146178Z</t>
+          <t>2026-08-04T14:23:52.273042Z</t>
         </is>
       </c>
       <c r="BI190" s="24" t="inlineStr">
@@ -55100,7 +55487,8 @@
       <c r="CO190" s="24" t="n"/>
       <c r="CP190" s="24" t="n"/>
       <c r="CQ190" s="24" t="n"/>
-      <c r="CR190" s="24" t="inlineStr">
+      <c r="CR190" s="24" t="n"/>
+      <c r="CS190" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -55109,12 +55497,12 @@
     <row r="191" ht="36" customHeight="1">
       <c r="A191" s="24" t="inlineStr">
         <is>
-          <t>443e8e4900754691</t>
+          <t>460f3fb8dd7244f1</t>
         </is>
       </c>
       <c r="B191" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C191" s="24" t="inlineStr">
@@ -55159,13 +55547,13 @@
         </is>
       </c>
       <c r="L191" s="26" t="n">
-        <v>-300</v>
+        <v>-317</v>
       </c>
       <c r="M191" s="27" t="n">
-        <v>1.333333</v>
+        <v>1.315457</v>
       </c>
       <c r="N191" s="28" t="n">
-        <v>0.75</v>
+        <v>0.760192</v>
       </c>
       <c r="O191" s="28" t="n">
         <v>0.686447</v>
@@ -55174,7 +55562,7 @@
         <v>0.05</v>
       </c>
       <c r="Q191" s="28" t="n">
-        <v>-0.063553</v>
+        <v>-0.073745</v>
       </c>
       <c r="R191" s="26" t="n">
         <v>0</v>
@@ -55203,7 +55591,7 @@
       <c r="AD191" s="24" t="n"/>
       <c r="AE191" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Daniel Altmaier p=0.314 vs Brandon Nakashima. Executable ask 0.7500 (aec-atp-branak-danalt-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Daniel Altmaier p=0.314 vs Brandon Nakashima. Executable ask 0.7600 (aec-atp-branak-danalt-2026-08-05).</t>
         </is>
       </c>
       <c r="AF191" s="31" t="inlineStr">
@@ -55322,7 +55710,7 @@
       </c>
       <c r="BH191" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:58.246120Z</t>
+          <t>2026-08-04T14:23:52.637358Z</t>
         </is>
       </c>
       <c r="BI191" s="24" t="inlineStr">
@@ -55332,13 +55720,13 @@
       </c>
       <c r="BJ191" s="25" t="n"/>
       <c r="BK191" s="26" t="n">
-        <v>-300</v>
+        <v>-317</v>
       </c>
       <c r="BL191" s="27" t="n">
-        <v>1.333333</v>
+        <v>1.315457</v>
       </c>
       <c r="BM191" s="28" t="n">
-        <v>0.75</v>
+        <v>0.760192</v>
       </c>
       <c r="BN191" s="28" t="n"/>
       <c r="BO191" s="28" t="n"/>
@@ -55370,7 +55758,8 @@
       <c r="CO191" s="24" t="n"/>
       <c r="CP191" s="24" t="n"/>
       <c r="CQ191" s="24" t="n"/>
-      <c r="CR191" s="24" t="inlineStr">
+      <c r="CR191" s="24" t="n"/>
+      <c r="CS191" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -55379,12 +55768,12 @@
     <row r="192" ht="36" customHeight="1">
       <c r="A192" s="24" t="inlineStr">
         <is>
-          <t>f784585309cf41dd</t>
+          <t>64fcbd5087594e1f</t>
         </is>
       </c>
       <c r="B192" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C192" s="24" t="inlineStr">
@@ -55429,13 +55818,13 @@
         </is>
       </c>
       <c r="L192" s="26" t="n">
-        <v>-170</v>
+        <v>-178</v>
       </c>
       <c r="M192" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.561798</v>
       </c>
       <c r="N192" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.640288</v>
       </c>
       <c r="O192" s="28" t="n">
         <v>0.701855</v>
@@ -55444,10 +55833,10 @@
         <v>0.05</v>
       </c>
       <c r="Q192" s="28" t="n">
-        <v>0.072225</v>
+        <v>0.061567</v>
       </c>
       <c r="R192" s="26" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="S192" s="29" t="n">
         <v>2</v>
@@ -55473,7 +55862,7 @@
       <c r="AD192" s="24" t="n"/>
       <c r="AE192" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Marin Cilic p=0.298 vs Frances Tiafoe. Executable ask 0.6300 (aec-atp-fratia-marcil-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Marin Cilic p=0.298 vs Frances Tiafoe. Executable ask 0.6400 (aec-atp-fratia-marcil-2026-08-05).</t>
         </is>
       </c>
       <c r="AF192" s="31" t="inlineStr">
@@ -55592,7 +55981,7 @@
       </c>
       <c r="BH192" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:59.800144Z</t>
+          <t>2026-08-04T14:23:53.532342Z</t>
         </is>
       </c>
       <c r="BI192" s="24" t="inlineStr">
@@ -55602,13 +55991,13 @@
       </c>
       <c r="BJ192" s="25" t="n"/>
       <c r="BK192" s="26" t="n">
-        <v>-170</v>
+        <v>-178</v>
       </c>
       <c r="BL192" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.561798</v>
       </c>
       <c r="BM192" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.640288</v>
       </c>
       <c r="BN192" s="28" t="n"/>
       <c r="BO192" s="28" t="n"/>
@@ -55640,7 +56029,8 @@
       <c r="CO192" s="24" t="n"/>
       <c r="CP192" s="24" t="n"/>
       <c r="CQ192" s="24" t="n"/>
-      <c r="CR192" s="24" t="inlineStr">
+      <c r="CR192" s="24" t="n"/>
+      <c r="CS192" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -55649,12 +56039,12 @@
     <row r="193" ht="36" customHeight="1">
       <c r="A193" s="24" t="inlineStr">
         <is>
-          <t>230181478f574195</t>
+          <t>8af7498b5e344e52</t>
         </is>
       </c>
       <c r="B193" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C193" s="24" t="inlineStr">
@@ -55699,13 +56089,13 @@
         </is>
       </c>
       <c r="L193" s="26" t="n">
-        <v>-133</v>
+        <v>-127</v>
       </c>
       <c r="M193" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.787402</v>
       </c>
       <c r="N193" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O193" s="28" t="n">
         <v>0.583443</v>
@@ -55714,10 +56104,10 @@
         <v>0.05</v>
       </c>
       <c r="Q193" s="28" t="n">
-        <v>0.012628</v>
+        <v>0.023972</v>
       </c>
       <c r="R193" s="26" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="S193" s="29" t="n">
         <v>1.25</v>
@@ -55743,7 +56133,7 @@
       <c r="AD193" s="24" t="n"/>
       <c r="AE193" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Yannick Hanfmann p=0.417 vs Flavio Cobolli. Executable ask 0.5700 (aec-atp-flacob-yanhan-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Yannick Hanfmann p=0.417 vs Flavio Cobolli. Executable ask 0.5600 (aec-atp-flacob-yanhan-2026-08-04).</t>
         </is>
       </c>
       <c r="AF193" s="31" t="inlineStr">
@@ -55862,7 +56252,7 @@
       </c>
       <c r="BH193" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:00.632213Z</t>
+          <t>2026-08-04T14:23:54.373192Z</t>
         </is>
       </c>
       <c r="BI193" s="24" t="inlineStr">
@@ -55872,13 +56262,13 @@
       </c>
       <c r="BJ193" s="25" t="n"/>
       <c r="BK193" s="26" t="n">
-        <v>-133</v>
+        <v>-127</v>
       </c>
       <c r="BL193" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.787402</v>
       </c>
       <c r="BM193" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN193" s="28" t="n"/>
       <c r="BO193" s="28" t="n"/>
@@ -55910,7 +56300,8 @@
       <c r="CO193" s="24" t="n"/>
       <c r="CP193" s="24" t="n"/>
       <c r="CQ193" s="24" t="n"/>
-      <c r="CR193" s="24" t="inlineStr">
+      <c r="CR193" s="24" t="n"/>
+      <c r="CS193" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -55919,12 +56310,12 @@
     <row r="194" ht="36" customHeight="1">
       <c r="A194" s="24" t="inlineStr">
         <is>
-          <t>6f8871db92a6476b</t>
+          <t>2074c2a4dd6243ef</t>
         </is>
       </c>
       <c r="B194" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C194" s="24" t="inlineStr">
@@ -55969,13 +56360,13 @@
         </is>
       </c>
       <c r="L194" s="26" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="M194" s="27" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="N194" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.469484</v>
       </c>
       <c r="O194" s="28" t="n">
         <v>0.62292</v>
@@ -55984,10 +56375,10 @@
         <v>0.05</v>
       </c>
       <c r="Q194" s="28" t="n">
-        <v>0.132724</v>
+        <v>0.153436</v>
       </c>
       <c r="R194" s="26" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="S194" s="29" t="n">
         <v>1.5</v>
@@ -56013,7 +56404,7 @@
       <c r="AD194" s="24" t="n"/>
       <c r="AE194" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Gabriel Diallo p=0.377 vs Luciano Darderi. Executable ask 0.4900 (aec-atp-lucdar-gabdia-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Gabriel Diallo p=0.377 vs Luciano Darderi. Executable ask 0.4700 (aec-atp-lucdar-gabdia-2026-08-05).</t>
         </is>
       </c>
       <c r="AF194" s="31" t="inlineStr">
@@ -56132,7 +56523,7 @@
       </c>
       <c r="BH194" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:01.150443Z</t>
+          <t>2026-08-04T14:23:55.350978Z</t>
         </is>
       </c>
       <c r="BI194" s="24" t="inlineStr">
@@ -56142,13 +56533,13 @@
       </c>
       <c r="BJ194" s="25" t="n"/>
       <c r="BK194" s="26" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="BL194" s="27" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="BM194" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.469484</v>
       </c>
       <c r="BN194" s="28" t="n"/>
       <c r="BO194" s="28" t="n"/>
@@ -56180,7 +56571,8 @@
       <c r="CO194" s="24" t="n"/>
       <c r="CP194" s="24" t="n"/>
       <c r="CQ194" s="24" t="n"/>
-      <c r="CR194" s="24" t="inlineStr">
+      <c r="CR194" s="24" t="n"/>
+      <c r="CS194" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/flat/tennis.xlsx
+++ b/data/flat/tennis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS234" headerRowCount="1">
-  <autoFilter ref="A1:CS234"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS233" headerRowCount="1">
+  <autoFilter ref="A1:CS233"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$234)</f>
+        <f>COUNTA('Picks'!$A$2:$A$233)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$234,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$233,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$234,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$233,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$234,"settled",'Picks'!$V$2:$V$234,"win")+COUNTIFS('Picks'!$U$2:$U$234,"settled",'Picks'!$V$2:$V$234,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$233,"settled",'Picks'!$V$2:$V$233,"win")+COUNTIFS('Picks'!$U$2:$U$233,"settled",'Picks'!$V$2:$V$233,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$234,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$233,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$234,"&gt;0",'Picks'!$V$2:$V$234,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$234,"&gt;0",'Picks'!$V$2:$V$234,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$233,"&gt;0",'Picks'!$V$2:$V$233,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$233,"&gt;0",'Picks'!$V$2:$V$233,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$234,"&gt;0",'Picks'!$V$2:$V$234,"win")/(COUNTIFS('Picks'!$BX$2:$BX$234,"&gt;0",'Picks'!$V$2:$V$234,"win")+COUNTIFS('Picks'!$BX$2:$BX$234,"&gt;0",'Picks'!$V$2:$V$234,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$233,"&gt;0",'Picks'!$V$2:$V$233,"win")/(COUNTIFS('Picks'!$BX$2:$BX$233,"&gt;0",'Picks'!$V$2:$V$233,"win")+COUNTIFS('Picks'!$BX$2:$BX$233,"&gt;0",'Picks'!$V$2:$V$233,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$234)/SUM('Picks'!$BX$2:$BX$234),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$233)/SUM('Picks'!$BX$2:$BX$233),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$234)</f>
+        <f>SUM('Picks'!$BY$2:$BY$233)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$234,"&lt;&gt;",'Picks'!$AB$2:$AB$234),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$233,"&lt;&gt;",'Picks'!$AB$2:$AB$233),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$234,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$234,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$233,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$233,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$234,'Picks'!$AM$2:$AM$234,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$233,'Picks'!$AM$2:$AM$233,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$234,$A14,'Picks'!$U$2:$U$234,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$233,$A14,'Picks'!$U$2:$U$233,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$234,$A14,'Picks'!$U$2:$U$234,"settled",'Picks'!$V$2:$V$234,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$233,$A14,'Picks'!$U$2:$U$233,"settled",'Picks'!$V$2:$V$233,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$234,$A14,'Picks'!$U$2:$U$234,"settled",'Picks'!$V$2:$V$234,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$233,$A14,'Picks'!$U$2:$U$233,"settled",'Picks'!$V$2:$V$233,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$234,'Picks'!$H$2:$H$234,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$233,'Picks'!$H$2:$H$233,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$234,'Picks'!$H$2:$H$234,$A14,'Picks'!$U$2:$U$234,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$233,'Picks'!$H$2:$H$233,$A14,'Picks'!$U$2:$U$233,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$234,$A15,'Picks'!$U$2:$U$234,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$233,$A15,'Picks'!$U$2:$U$233,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$234,$A15,'Picks'!$U$2:$U$234,"settled",'Picks'!$V$2:$V$234,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$233,$A15,'Picks'!$U$2:$U$233,"settled",'Picks'!$V$2:$V$233,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$234,$A15,'Picks'!$U$2:$U$234,"settled",'Picks'!$V$2:$V$234,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$233,$A15,'Picks'!$U$2:$U$233,"settled",'Picks'!$V$2:$V$233,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$234,'Picks'!$H$2:$H$234,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$233,'Picks'!$H$2:$H$233,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$234,'Picks'!$H$2:$H$234,$A15,'Picks'!$U$2:$U$234,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$233,'Picks'!$H$2:$H$233,$A15,'Picks'!$U$2:$U$233,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$234,$A16,'Picks'!$U$2:$U$234,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$233,$A16,'Picks'!$U$2:$U$233,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$234,$A16,'Picks'!$U$2:$U$234,"settled",'Picks'!$V$2:$V$234,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$233,$A16,'Picks'!$U$2:$U$233,"settled",'Picks'!$V$2:$V$233,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$234,$A16,'Picks'!$U$2:$U$234,"settled",'Picks'!$V$2:$V$234,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$233,$A16,'Picks'!$U$2:$U$233,"settled",'Picks'!$V$2:$V$233,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$234,'Picks'!$H$2:$H$234,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$233,'Picks'!$H$2:$H$233,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$234,'Picks'!$H$2:$H$234,$A16,'Picks'!$U$2:$U$234,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$233,'Picks'!$H$2:$H$233,$A16,'Picks'!$U$2:$U$233,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS234"/>
+  <dimension ref="A1:CS233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -55404,7 +55404,7 @@
     <row r="188" ht="36" customHeight="1">
       <c r="A188" s="24" t="inlineStr">
         <is>
-          <t>bf3e250c3e5c4242</t>
+          <t>639381b79e134a1a</t>
         </is>
       </c>
       <c r="B188" s="24" t="inlineStr">
@@ -55414,12 +55414,12 @@
       </c>
       <c r="C188" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T15:00Z</t>
+          <t>2026-08-05T09:00Z</t>
         </is>
       </c>
       <c r="D188" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182220</t>
+          <t>961-2026:182103</t>
         </is>
       </c>
       <c r="E188" s="24" t="inlineStr">
@@ -55429,12 +55429,12 @@
       </c>
       <c r="F188" s="24" t="inlineStr">
         <is>
-          <t>Kayla Cross</t>
+          <t>Justina Mikulskyte</t>
         </is>
       </c>
       <c r="G188" s="24" t="inlineStr">
         <is>
-          <t>Ann Li</t>
+          <t>Katarzyna Kawa</t>
         </is>
       </c>
       <c r="H188" s="24" t="inlineStr">
@@ -55454,25 +55454,25 @@
         </is>
       </c>
       <c r="L188" s="26" t="n">
-        <v>-285</v>
+        <v>-317</v>
       </c>
       <c r="M188" s="27" t="n">
-        <v>1.350877</v>
+        <v>1.315457</v>
       </c>
       <c r="N188" s="28" t="n">
-        <v>0.74026</v>
+        <v>0.760192</v>
       </c>
       <c r="O188" s="28" t="n">
-        <v>0.795002</v>
+        <v>0.782547</v>
       </c>
       <c r="P188" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q188" s="28" t="n">
-        <v>0.054742</v>
+        <v>0.022355</v>
       </c>
       <c r="R188" s="26" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="S188" s="29" t="n">
         <v>2</v>
@@ -55484,21 +55484,41 @@
       </c>
       <c r="U188" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V188" s="24" t="n"/>
-      <c r="W188" s="26" t="n"/>
-      <c r="X188" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V188" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W188" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X188" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y188" s="25" t="n"/>
-      <c r="Z188" s="26" t="n"/>
-      <c r="AA188" s="28" t="n"/>
-      <c r="AB188" s="28" t="n"/>
-      <c r="AC188" s="30" t="n"/>
-      <c r="AD188" s="24" t="n"/>
+      <c r="Z188" s="26" t="n">
+        <v>-317</v>
+      </c>
+      <c r="AA188" s="28" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AB188" s="28" t="n">
+        <v>-0.000192</v>
+      </c>
+      <c r="AC188" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD188" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:50:01.101421Z</t>
+        </is>
+      </c>
       <c r="AE188" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Kayla Cross p=0.205 vs Ann Li. Executable ask 0.7400 (aec-wta-annli-kaycro-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Justina Mikulskyte p=0.217 vs Katarzyna Kawa. Executable ask 0.7600 (aec-wta-katkaw-jusmik-2026-08-05).</t>
         </is>
       </c>
       <c r="AF188" s="31" t="inlineStr">
@@ -55508,7 +55528,7 @@
       </c>
       <c r="AG188" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH188" s="24" t="n"/>
@@ -55516,7 +55536,7 @@
       <c r="AJ188" s="31" t="n"/>
       <c r="AK188" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL188" s="26" t="n">
@@ -55524,47 +55544,47 @@
       </c>
       <c r="AM188" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN188" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO188" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP188" s="24" t="inlineStr">
         <is>
-          <t>Kayla Cross</t>
+          <t>Justina Mikulskyte</t>
         </is>
       </c>
       <c r="AQ188" s="24" t="inlineStr">
         <is>
-          <t>Kayla Cross</t>
+          <t>Justina Mikulskyte</t>
         </is>
       </c>
       <c r="AR188" s="24" t="inlineStr">
         <is>
-          <t>Kayla Cross</t>
+          <t>Justina Mikulskyte</t>
         </is>
       </c>
       <c r="AS188" s="24" t="inlineStr">
         <is>
-          <t>Ann Li</t>
+          <t>Katarzyna Kawa</t>
         </is>
       </c>
       <c r="AT188" s="24" t="inlineStr">
         <is>
-          <t>Ann Li</t>
+          <t>Katarzyna Kawa</t>
         </is>
       </c>
       <c r="AU188" s="24" t="inlineStr">
         <is>
-          <t>Ann Li</t>
+          <t>Katarzyna Kawa</t>
         </is>
       </c>
       <c r="AV188" s="24" t="n"/>
@@ -55617,7 +55637,7 @@
       </c>
       <c r="BH188" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:10.491214Z</t>
+          <t>2026-08-05T04:34:10.082069Z</t>
         </is>
       </c>
       <c r="BI188" s="24" t="inlineStr">
@@ -55627,19 +55647,23 @@
       </c>
       <c r="BJ188" s="25" t="n"/>
       <c r="BK188" s="26" t="n">
-        <v>-285</v>
+        <v>-317</v>
       </c>
       <c r="BL188" s="27" t="n">
-        <v>1.350877</v>
+        <v>1.315457</v>
       </c>
       <c r="BM188" s="28" t="n">
-        <v>0.74026</v>
+        <v>0.760192</v>
       </c>
       <c r="BN188" s="28" t="n"/>
       <c r="BO188" s="28" t="n"/>
       <c r="BP188" s="25" t="n"/>
-      <c r="BQ188" s="27" t="n"/>
-      <c r="BR188" s="28" t="n"/>
+      <c r="BQ188" s="27" t="n">
+        <v>1.315457</v>
+      </c>
+      <c r="BR188" s="28" t="n">
+        <v>0.76</v>
+      </c>
       <c r="BS188" s="28" t="n"/>
       <c r="BT188" s="28" t="n"/>
       <c r="BU188" s="25" t="n"/>
@@ -55675,7 +55699,7 @@
     <row r="189" ht="36" customHeight="1">
       <c r="A189" s="24" t="inlineStr">
         <is>
-          <t>df942e31be214dee</t>
+          <t>0428483b2fae4598</t>
         </is>
       </c>
       <c r="B189" s="24" t="inlineStr">
@@ -55685,12 +55709,12 @@
       </c>
       <c r="C189" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T16:30Z</t>
+          <t>2026-08-05T09:00Z</t>
         </is>
       </c>
       <c r="D189" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182196</t>
+          <t>961-2026:182104</t>
         </is>
       </c>
       <c r="E189" s="24" t="inlineStr">
@@ -55700,12 +55724,12 @@
       </c>
       <c r="F189" s="24" t="inlineStr">
         <is>
-          <t>Magdalena Frech</t>
+          <t>Aliona Falei</t>
         </is>
       </c>
       <c r="G189" s="24" t="inlineStr">
         <is>
-          <t>Jessica Pegula</t>
+          <t>Carol Young Suh Lee</t>
         </is>
       </c>
       <c r="H189" s="24" t="inlineStr">
@@ -55725,28 +55749,28 @@
         </is>
       </c>
       <c r="L189" s="26" t="n">
-        <v>-733</v>
+        <v>-156</v>
       </c>
       <c r="M189" s="27" t="n">
-        <v>1.136426</v>
+        <v>1.641026</v>
       </c>
       <c r="N189" s="28" t="n">
-        <v>0.879952</v>
+        <v>0.609375</v>
       </c>
       <c r="O189" s="28" t="n">
-        <v>0.9137729999999999</v>
+        <v>0.589246</v>
       </c>
       <c r="P189" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q189" s="28" t="n">
-        <v>0.033821</v>
+        <v>-0.020129</v>
       </c>
       <c r="R189" s="26" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="S189" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T189" s="24" t="inlineStr">
         <is>
@@ -55755,21 +55779,41 @@
       </c>
       <c r="U189" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V189" s="24" t="n"/>
-      <c r="W189" s="26" t="n"/>
-      <c r="X189" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V189" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W189" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X189" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y189" s="25" t="n"/>
-      <c r="Z189" s="26" t="n"/>
-      <c r="AA189" s="28" t="n"/>
-      <c r="AB189" s="28" t="n"/>
-      <c r="AC189" s="30" t="n"/>
-      <c r="AD189" s="24" t="n"/>
+      <c r="Z189" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="AA189" s="28" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AB189" s="28" t="n">
+        <v>0.000625</v>
+      </c>
+      <c r="AC189" s="30" t="n">
+        <v>0.8013</v>
+      </c>
+      <c r="AD189" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:50:03.420509Z</t>
+        </is>
+      </c>
       <c r="AE189" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Magdalena Frech p=0.086 vs Jessica Pegula. Executable ask 0.8800 (aec-wta-jespeg-magfre-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Aliona Falei p=0.411 vs Carol Young Suh Lee. Executable ask 0.6100 (aec-wta-carlee-alifal-2026-08-05).</t>
         </is>
       </c>
       <c r="AF189" s="31" t="inlineStr">
@@ -55810,32 +55854,32 @@
       </c>
       <c r="AP189" s="24" t="inlineStr">
         <is>
-          <t>Magdalena Frech</t>
+          <t>Aliona Falei</t>
         </is>
       </c>
       <c r="AQ189" s="24" t="inlineStr">
         <is>
-          <t>Magdalena Frech</t>
+          <t>Aliona Falei</t>
         </is>
       </c>
       <c r="AR189" s="24" t="inlineStr">
         <is>
-          <t>Magdalena Frech</t>
+          <t>Aliona Falei</t>
         </is>
       </c>
       <c r="AS189" s="24" t="inlineStr">
         <is>
-          <t>Jessica Pegula</t>
+          <t>Carol Young Suh Lee</t>
         </is>
       </c>
       <c r="AT189" s="24" t="inlineStr">
         <is>
-          <t>Jessica Pegula</t>
+          <t>Carol Young Suh Lee</t>
         </is>
       </c>
       <c r="AU189" s="24" t="inlineStr">
         <is>
-          <t>Jessica Pegula</t>
+          <t>Carol Young Suh Lee</t>
         </is>
       </c>
       <c r="AV189" s="24" t="n"/>
@@ -55888,7 +55932,7 @@
       </c>
       <c r="BH189" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:11.907535Z</t>
+          <t>2026-08-05T04:34:10.066030Z</t>
         </is>
       </c>
       <c r="BI189" s="24" t="inlineStr">
@@ -55898,19 +55942,23 @@
       </c>
       <c r="BJ189" s="25" t="n"/>
       <c r="BK189" s="26" t="n">
-        <v>-733</v>
+        <v>-156</v>
       </c>
       <c r="BL189" s="27" t="n">
-        <v>1.136426</v>
+        <v>1.641026</v>
       </c>
       <c r="BM189" s="28" t="n">
-        <v>0.879952</v>
+        <v>0.609375</v>
       </c>
       <c r="BN189" s="28" t="n"/>
       <c r="BO189" s="28" t="n"/>
       <c r="BP189" s="25" t="n"/>
-      <c r="BQ189" s="27" t="n"/>
-      <c r="BR189" s="28" t="n"/>
+      <c r="BQ189" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BR189" s="28" t="n">
+        <v>0.61</v>
+      </c>
       <c r="BS189" s="28" t="n"/>
       <c r="BT189" s="28" t="n"/>
       <c r="BU189" s="25" t="n"/>
@@ -55939,29 +55987,29 @@
       <c r="CR189" s="24" t="n"/>
       <c r="CS189" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="190" ht="36" customHeight="1">
       <c r="A190" s="24" t="inlineStr">
         <is>
-          <t>173a610e144b42f5</t>
+          <t>bc559a134fa74fa9</t>
         </is>
       </c>
       <c r="B190" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T10:21:33.669433Z</t>
         </is>
       </c>
       <c r="C190" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T16:30Z</t>
+          <t>2026-08-05T10:30Z</t>
         </is>
       </c>
       <c r="D190" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182201</t>
+          <t>961-2026:182101</t>
         </is>
       </c>
       <c r="E190" s="24" t="inlineStr">
@@ -55971,12 +56019,12 @@
       </c>
       <c r="F190" s="24" t="inlineStr">
         <is>
-          <t>Belinda Bencic</t>
+          <t>Ella Seidel</t>
         </is>
       </c>
       <c r="G190" s="24" t="inlineStr">
         <is>
-          <t>Sloane Stephens</t>
+          <t>Gabriela Knutson</t>
         </is>
       </c>
       <c r="H190" s="24" t="inlineStr">
@@ -55986,7 +56034,7 @@
       </c>
       <c r="I190" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J190" s="25" t="n"/>
@@ -55996,28 +56044,28 @@
         </is>
       </c>
       <c r="L190" s="26" t="n">
-        <v>-614</v>
+        <v>178</v>
       </c>
       <c r="M190" s="27" t="n">
-        <v>1.162866</v>
+        <v>2.78</v>
       </c>
       <c r="N190" s="28" t="n">
-        <v>0.859944</v>
+        <v>0.359712</v>
       </c>
       <c r="O190" s="28" t="n">
-        <v>0.887489</v>
+        <v>0.518196</v>
       </c>
       <c r="P190" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q190" s="28" t="n">
-        <v>0.027545</v>
+        <v>0.158484</v>
       </c>
       <c r="R190" s="26" t="n">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="S190" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T190" s="24" t="inlineStr">
         <is>
@@ -56026,21 +56074,41 @@
       </c>
       <c r="U190" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V190" s="24" t="n"/>
-      <c r="W190" s="26" t="n"/>
-      <c r="X190" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V190" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W190" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X190" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y190" s="25" t="n"/>
-      <c r="Z190" s="26" t="n"/>
-      <c r="AA190" s="28" t="n"/>
-      <c r="AB190" s="28" t="n"/>
-      <c r="AC190" s="30" t="n"/>
-      <c r="AD190" s="24" t="n"/>
+      <c r="Z190" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="AA190" s="28" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB190" s="28" t="n">
+        <v>0.000288</v>
+      </c>
+      <c r="AC190" s="30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD190" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:50:05.648156Z</t>
+        </is>
+      </c>
       <c r="AE190" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Belinda Bencic p=0.887 vs Sloane Stephens. Executable ask 0.8600 (aec-wta-sloste-belben-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Ella Seidel p=0.482 vs Gabriela Knutson. Executable ask 0.3600 (aec-wta-gabknu-ellsei-2026-08-05).</t>
         </is>
       </c>
       <c r="AF190" s="31" t="inlineStr">
@@ -56081,32 +56149,32 @@
       </c>
       <c r="AP190" s="24" t="inlineStr">
         <is>
-          <t>Belinda Bencic</t>
+          <t>Ella Seidel</t>
         </is>
       </c>
       <c r="AQ190" s="24" t="inlineStr">
         <is>
-          <t>Belinda Bencic</t>
+          <t>Ella Seidel</t>
         </is>
       </c>
       <c r="AR190" s="24" t="inlineStr">
         <is>
-          <t>Belinda Bencic</t>
+          <t>Ella Seidel</t>
         </is>
       </c>
       <c r="AS190" s="24" t="inlineStr">
         <is>
-          <t>Sloane Stephens</t>
+          <t>Gabriela Knutson</t>
         </is>
       </c>
       <c r="AT190" s="24" t="inlineStr">
         <is>
-          <t>Sloane Stephens</t>
+          <t>Gabriela Knutson</t>
         </is>
       </c>
       <c r="AU190" s="24" t="inlineStr">
         <is>
-          <t>Sloane Stephens</t>
+          <t>Gabriela Knutson</t>
         </is>
       </c>
       <c r="AV190" s="24" t="n"/>
@@ -56159,7 +56227,7 @@
       </c>
       <c r="BH190" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:11.864845Z</t>
+          <t>2026-08-05T10:19:06.147146Z</t>
         </is>
       </c>
       <c r="BI190" s="24" t="inlineStr">
@@ -56169,19 +56237,23 @@
       </c>
       <c r="BJ190" s="25" t="n"/>
       <c r="BK190" s="26" t="n">
-        <v>-614</v>
+        <v>178</v>
       </c>
       <c r="BL190" s="27" t="n">
-        <v>1.162866</v>
+        <v>2.78</v>
       </c>
       <c r="BM190" s="28" t="n">
-        <v>0.859944</v>
+        <v>0.359712</v>
       </c>
       <c r="BN190" s="28" t="n"/>
       <c r="BO190" s="28" t="n"/>
       <c r="BP190" s="25" t="n"/>
-      <c r="BQ190" s="27" t="n"/>
-      <c r="BR190" s="28" t="n"/>
+      <c r="BQ190" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BR190" s="28" t="n">
+        <v>0.36</v>
+      </c>
       <c r="BS190" s="28" t="n"/>
       <c r="BT190" s="28" t="n"/>
       <c r="BU190" s="25" t="n"/>
@@ -56217,22 +56289,22 @@
     <row r="191" ht="36" customHeight="1">
       <c r="A191" s="24" t="inlineStr">
         <is>
-          <t>2710521e2ce84118</t>
+          <t>d3c5b1d1eaf54153</t>
         </is>
       </c>
       <c r="B191" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T10:21:33.669433Z</t>
         </is>
       </c>
       <c r="C191" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T16:30Z</t>
+          <t>2026-08-05T10:30Z</t>
         </is>
       </c>
       <c r="D191" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182218</t>
+          <t>961-2026:182098</t>
         </is>
       </c>
       <c r="E191" s="24" t="inlineStr">
@@ -56242,12 +56314,12 @@
       </c>
       <c r="F191" s="24" t="inlineStr">
         <is>
-          <t>Elena Rybakina</t>
+          <t>Mona Barthel</t>
         </is>
       </c>
       <c r="G191" s="24" t="inlineStr">
         <is>
-          <t>Daria Kasatkina</t>
+          <t>Martyna Kubka</t>
         </is>
       </c>
       <c r="H191" s="24" t="inlineStr">
@@ -56267,28 +56339,28 @@
         </is>
       </c>
       <c r="L191" s="26" t="n">
-        <v>-669</v>
+        <v>156</v>
       </c>
       <c r="M191" s="27" t="n">
-        <v>1.149477</v>
+        <v>2.56</v>
       </c>
       <c r="N191" s="28" t="n">
-        <v>0.869961</v>
+        <v>0.390625</v>
       </c>
       <c r="O191" s="28" t="n">
-        <v>0.8561839999999999</v>
+        <v>0.5849800000000001</v>
       </c>
       <c r="P191" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q191" s="28" t="n">
-        <v>-0.013777</v>
+        <v>0.194355</v>
       </c>
       <c r="R191" s="26" t="n">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="S191" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T191" s="24" t="inlineStr">
         <is>
@@ -56297,21 +56369,41 @@
       </c>
       <c r="U191" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V191" s="24" t="n"/>
-      <c r="W191" s="26" t="n"/>
-      <c r="X191" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V191" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W191" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X191" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y191" s="25" t="n"/>
-      <c r="Z191" s="26" t="n"/>
-      <c r="AA191" s="28" t="n"/>
-      <c r="AB191" s="28" t="n"/>
-      <c r="AC191" s="30" t="n"/>
-      <c r="AD191" s="24" t="n"/>
+      <c r="Z191" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="AA191" s="28" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AB191" s="28" t="n">
+        <v>-0.000625</v>
+      </c>
+      <c r="AC191" s="30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD191" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:50:07.965679Z</t>
+        </is>
+      </c>
       <c r="AE191" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Elena Rybakina p=0.856 vs Daria Kasatkina. Executable ask 0.8700 (aec-wta-darkas-eleryb-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Mona Barthel p=0.585 vs Martyna Kubka. Executable ask 0.3900 (aec-wta-markub-monbar-2026-08-05).</t>
         </is>
       </c>
       <c r="AF191" s="31" t="inlineStr">
@@ -56329,7 +56421,7 @@
       <c r="AJ191" s="31" t="n"/>
       <c r="AK191" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL191" s="26" t="n">
@@ -56337,47 +56429,47 @@
       </c>
       <c r="AM191" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN191" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO191" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP191" s="24" t="inlineStr">
         <is>
-          <t>Elena Rybakina</t>
+          <t>Mona Barthel</t>
         </is>
       </c>
       <c r="AQ191" s="24" t="inlineStr">
         <is>
-          <t>Elena Rybakina</t>
+          <t>Mona Barthel</t>
         </is>
       </c>
       <c r="AR191" s="24" t="inlineStr">
         <is>
-          <t>Elena Rybakina</t>
+          <t>Mona Barthel</t>
         </is>
       </c>
       <c r="AS191" s="24" t="inlineStr">
         <is>
-          <t>Daria Kasatkina</t>
+          <t>Martyna Kubka</t>
         </is>
       </c>
       <c r="AT191" s="24" t="inlineStr">
         <is>
-          <t>Daria Kasatkina</t>
+          <t>Martyna Kubka</t>
         </is>
       </c>
       <c r="AU191" s="24" t="inlineStr">
         <is>
-          <t>Daria Kasatkina</t>
+          <t>Martyna Kubka</t>
         </is>
       </c>
       <c r="AV191" s="24" t="n"/>
@@ -56430,7 +56522,7 @@
       </c>
       <c r="BH191" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:13.912345Z</t>
+          <t>2026-08-05T10:19:06.246493Z</t>
         </is>
       </c>
       <c r="BI191" s="24" t="inlineStr">
@@ -56440,19 +56532,23 @@
       </c>
       <c r="BJ191" s="25" t="n"/>
       <c r="BK191" s="26" t="n">
-        <v>-669</v>
+        <v>156</v>
       </c>
       <c r="BL191" s="27" t="n">
-        <v>1.149477</v>
+        <v>2.56</v>
       </c>
       <c r="BM191" s="28" t="n">
-        <v>0.869961</v>
+        <v>0.390625</v>
       </c>
       <c r="BN191" s="28" t="n"/>
       <c r="BO191" s="28" t="n"/>
       <c r="BP191" s="25" t="n"/>
-      <c r="BQ191" s="27" t="n"/>
-      <c r="BR191" s="28" t="n"/>
+      <c r="BQ191" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BR191" s="28" t="n">
+        <v>0.39</v>
+      </c>
       <c r="BS191" s="28" t="n"/>
       <c r="BT191" s="28" t="n"/>
       <c r="BU191" s="25" t="n"/>
@@ -56481,29 +56577,29 @@
       <c r="CR191" s="24" t="n"/>
       <c r="CS191" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="192" ht="36" customHeight="1">
       <c r="A192" s="24" t="inlineStr">
         <is>
-          <t>7544e69f01c549fc</t>
+          <t>27f1b617c765418f</t>
         </is>
       </c>
       <c r="B192" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T10:21:33.669433Z</t>
         </is>
       </c>
       <c r="C192" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T16:30Z</t>
+          <t>2026-08-05T10:30Z</t>
         </is>
       </c>
       <c r="D192" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182225</t>
+          <t>961-2026:182102</t>
         </is>
       </c>
       <c r="E192" s="24" t="inlineStr">
@@ -56513,12 +56609,12 @@
       </c>
       <c r="F192" s="24" t="inlineStr">
         <is>
-          <t>Taylor Townsend</t>
+          <t>Yuan Yue</t>
         </is>
       </c>
       <c r="G192" s="24" t="inlineStr">
         <is>
-          <t>Marie Bouzkova</t>
+          <t>Elizara Yaneva</t>
         </is>
       </c>
       <c r="H192" s="24" t="inlineStr">
@@ -56528,7 +56624,7 @@
       </c>
       <c r="I192" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J192" s="25" t="n"/>
@@ -56538,25 +56634,25 @@
         </is>
       </c>
       <c r="L192" s="26" t="n">
-        <v>-138</v>
+        <v>-150</v>
       </c>
       <c r="M192" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.666667</v>
       </c>
       <c r="N192" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.6</v>
       </c>
       <c r="O192" s="28" t="n">
-        <v>0.56035</v>
+        <v>0.549241</v>
       </c>
       <c r="P192" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q192" s="28" t="n">
-        <v>-0.019482</v>
+        <v>-0.050759</v>
       </c>
       <c r="R192" s="26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S192" s="29" t="n">
         <v>1</v>
@@ -56582,7 +56678,7 @@
       <c r="AD192" s="24" t="n"/>
       <c r="AE192" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Taylor Townsend p=0.440 vs Marie Bouzkova. Executable ask 0.5800 (aec-wta-marbou-taytow-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Yuan Yue p=0.549 vs Elizara Yaneva. Executable ask 0.6000 (aec-wta-eliyan-yueyua-2026-08-05).</t>
         </is>
       </c>
       <c r="AF192" s="31" t="inlineStr">
@@ -56623,32 +56719,32 @@
       </c>
       <c r="AP192" s="24" t="inlineStr">
         <is>
-          <t>Taylor Townsend</t>
+          <t>Yuan Yue</t>
         </is>
       </c>
       <c r="AQ192" s="24" t="inlineStr">
         <is>
-          <t>Taylor Townsend</t>
+          <t>Yuan Yue</t>
         </is>
       </c>
       <c r="AR192" s="24" t="inlineStr">
         <is>
-          <t>Taylor Townsend</t>
+          <t>Yuan Yue</t>
         </is>
       </c>
       <c r="AS192" s="24" t="inlineStr">
         <is>
-          <t>Marie Bouzkova</t>
+          <t>Elizara Yaneva</t>
         </is>
       </c>
       <c r="AT192" s="24" t="inlineStr">
         <is>
-          <t>Marie Bouzkova</t>
+          <t>Elizara Yaneva</t>
         </is>
       </c>
       <c r="AU192" s="24" t="inlineStr">
         <is>
-          <t>Marie Bouzkova</t>
+          <t>Elizara Yaneva</t>
         </is>
       </c>
       <c r="AV192" s="24" t="n"/>
@@ -56701,7 +56797,7 @@
       </c>
       <c r="BH192" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:14.403627Z</t>
+          <t>2026-08-05T10:19:06.257511Z</t>
         </is>
       </c>
       <c r="BI192" s="24" t="inlineStr">
@@ -56711,13 +56807,13 @@
       </c>
       <c r="BJ192" s="25" t="n"/>
       <c r="BK192" s="26" t="n">
-        <v>-138</v>
+        <v>-150</v>
       </c>
       <c r="BL192" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.666667</v>
       </c>
       <c r="BM192" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.6</v>
       </c>
       <c r="BN192" s="28" t="n"/>
       <c r="BO192" s="28" t="n"/>
@@ -56759,22 +56855,22 @@
     <row r="193" ht="36" customHeight="1">
       <c r="A193" s="24" t="inlineStr">
         <is>
-          <t>2f5d6656b4d34dcd</t>
+          <t>9527e5d3364349b3</t>
         </is>
       </c>
       <c r="B193" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T10:44:49.997481Z</t>
         </is>
       </c>
       <c r="C193" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T18:00Z</t>
+          <t>2026-08-05T12:00Z</t>
         </is>
       </c>
       <c r="D193" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182190</t>
+          <t>961-2026:182099</t>
         </is>
       </c>
       <c r="E193" s="24" t="inlineStr">
@@ -56784,12 +56880,12 @@
       </c>
       <c r="F193" s="24" t="inlineStr">
         <is>
-          <t>Coco Gauff</t>
+          <t>Noma Noha Akugue</t>
         </is>
       </c>
       <c r="G193" s="24" t="inlineStr">
         <is>
-          <t>Kayla Day</t>
+          <t>Weronika Falkowska</t>
         </is>
       </c>
       <c r="H193" s="24" t="inlineStr">
@@ -56799,7 +56895,7 @@
       </c>
       <c r="I193" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J193" s="25" t="n"/>
@@ -56809,28 +56905,28 @@
         </is>
       </c>
       <c r="L193" s="26" t="n">
-        <v>-900</v>
+        <v>150</v>
       </c>
       <c r="M193" s="27" t="n">
-        <v>1.111111</v>
+        <v>2.5</v>
       </c>
       <c r="N193" s="28" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="O193" s="28" t="n">
-        <v>0.914779</v>
+        <v>0.513857</v>
       </c>
       <c r="P193" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q193" s="28" t="n">
-        <v>0.014779</v>
+        <v>0.113857</v>
       </c>
       <c r="R193" s="26" t="n">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="S193" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T193" s="24" t="inlineStr">
         <is>
@@ -56853,7 +56949,7 @@
       <c r="AD193" s="24" t="n"/>
       <c r="AE193" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Coco Gauff p=0.915 vs Kayla Day. Executable ask 0.9000 (aec-wta-kayday-cocgau-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Noma Noha Akugue p=0.486 vs Weronika Falkowska. Executable ask 0.4000 (aec-wta-werfal-nomaku-2026-08-05).</t>
         </is>
       </c>
       <c r="AF193" s="31" t="inlineStr">
@@ -56894,32 +56990,32 @@
       </c>
       <c r="AP193" s="24" t="inlineStr">
         <is>
-          <t>Coco Gauff</t>
+          <t>Noma Noha Akugue</t>
         </is>
       </c>
       <c r="AQ193" s="24" t="inlineStr">
         <is>
-          <t>Coco Gauff</t>
+          <t>Noma Noha Akugue</t>
         </is>
       </c>
       <c r="AR193" s="24" t="inlineStr">
         <is>
-          <t>Coco Gauff</t>
+          <t>Noma Noha Akugue</t>
         </is>
       </c>
       <c r="AS193" s="24" t="inlineStr">
         <is>
-          <t>Kayla Day</t>
+          <t>Weronika Falkowska</t>
         </is>
       </c>
       <c r="AT193" s="24" t="inlineStr">
         <is>
-          <t>Kayla Day</t>
+          <t>Weronika Falkowska</t>
         </is>
       </c>
       <c r="AU193" s="24" t="inlineStr">
         <is>
-          <t>Kayla Day</t>
+          <t>Weronika Falkowska</t>
         </is>
       </c>
       <c r="AV193" s="24" t="n"/>
@@ -56972,7 +57068,7 @@
       </c>
       <c r="BH193" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:16.374465Z</t>
+          <t>2026-08-05T10:42:35.362081Z</t>
         </is>
       </c>
       <c r="BI193" s="24" t="inlineStr">
@@ -56982,13 +57078,13 @@
       </c>
       <c r="BJ193" s="25" t="n"/>
       <c r="BK193" s="26" t="n">
-        <v>-900</v>
+        <v>150</v>
       </c>
       <c r="BL193" s="27" t="n">
-        <v>1.111111</v>
+        <v>2.5</v>
       </c>
       <c r="BM193" s="28" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="BN193" s="28" t="n"/>
       <c r="BO193" s="28" t="n"/>
@@ -57030,22 +57126,22 @@
     <row r="194" ht="36" customHeight="1">
       <c r="A194" s="24" t="inlineStr">
         <is>
-          <t>94f2498a1e1d4725</t>
+          <t>9bf1639f6c1a421e</t>
         </is>
       </c>
       <c r="B194" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T10:44:49.997481Z</t>
         </is>
       </c>
       <c r="C194" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T18:00Z</t>
+          <t>2026-08-05T12:00Z</t>
         </is>
       </c>
       <c r="D194" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182192</t>
+          <t>961-2026:182097</t>
         </is>
       </c>
       <c r="E194" s="24" t="inlineStr">
@@ -57055,12 +57151,12 @@
       </c>
       <c r="F194" s="24" t="inlineStr">
         <is>
-          <t>Karolina Pliskova</t>
+          <t>Veronika Podrez</t>
         </is>
       </c>
       <c r="G194" s="24" t="inlineStr">
         <is>
-          <t>Mirra Andreeva</t>
+          <t>Susan Bandecchi</t>
         </is>
       </c>
       <c r="H194" s="24" t="inlineStr">
@@ -57070,7 +57166,7 @@
       </c>
       <c r="I194" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J194" s="25" t="n"/>
@@ -57080,25 +57176,25 @@
         </is>
       </c>
       <c r="L194" s="26" t="n">
-        <v>-335</v>
+        <v>-113</v>
       </c>
       <c r="M194" s="27" t="n">
-        <v>1.298507</v>
+        <v>1.884956</v>
       </c>
       <c r="N194" s="28" t="n">
-        <v>0.770115</v>
+        <v>0.530516</v>
       </c>
       <c r="O194" s="28" t="n">
-        <v>0.753053</v>
+        <v>0.684504</v>
       </c>
       <c r="P194" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q194" s="28" t="n">
-        <v>-0.017062</v>
+        <v>0.153988</v>
       </c>
       <c r="R194" s="26" t="n">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="S194" s="29" t="n">
         <v>2</v>
@@ -57124,7 +57220,7 @@
       <c r="AD194" s="24" t="n"/>
       <c r="AE194" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Karolina Pliskova p=0.247 vs Mirra Andreeva. Executable ask 0.7700 (aec-wta-mirand-karpli-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Veronika Podrez p=0.685 vs Susan Bandecchi. Executable ask 0.5300 (aec-wta-susban-verpod-2026-08-05).</t>
         </is>
       </c>
       <c r="AF194" s="31" t="inlineStr">
@@ -57142,7 +57238,7 @@
       <c r="AJ194" s="31" t="n"/>
       <c r="AK194" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL194" s="26" t="n">
@@ -57150,47 +57246,47 @@
       </c>
       <c r="AM194" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN194" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO194" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP194" s="24" t="inlineStr">
         <is>
-          <t>Karolina Pliskova</t>
+          <t>Veronika Podrez</t>
         </is>
       </c>
       <c r="AQ194" s="24" t="inlineStr">
         <is>
-          <t>Karolina Pliskova</t>
+          <t>Veronika Podrez</t>
         </is>
       </c>
       <c r="AR194" s="24" t="inlineStr">
         <is>
-          <t>Karolina Pliskova</t>
+          <t>Veronika Podrez</t>
         </is>
       </c>
       <c r="AS194" s="24" t="inlineStr">
         <is>
-          <t>Mirra Andreeva</t>
+          <t>Susan Bandecchi</t>
         </is>
       </c>
       <c r="AT194" s="24" t="inlineStr">
         <is>
-          <t>Mirra Andreeva</t>
+          <t>Susan Bandecchi</t>
         </is>
       </c>
       <c r="AU194" s="24" t="inlineStr">
         <is>
-          <t>Mirra Andreeva</t>
+          <t>Susan Bandecchi</t>
         </is>
       </c>
       <c r="AV194" s="24" t="n"/>
@@ -57243,7 +57339,7 @@
       </c>
       <c r="BH194" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:15.932130Z</t>
+          <t>2026-08-05T10:42:35.161195Z</t>
         </is>
       </c>
       <c r="BI194" s="24" t="inlineStr">
@@ -57253,13 +57349,13 @@
       </c>
       <c r="BJ194" s="25" t="n"/>
       <c r="BK194" s="26" t="n">
-        <v>-335</v>
+        <v>-113</v>
       </c>
       <c r="BL194" s="27" t="n">
-        <v>1.298507</v>
+        <v>1.884956</v>
       </c>
       <c r="BM194" s="28" t="n">
-        <v>0.770115</v>
+        <v>0.530516</v>
       </c>
       <c r="BN194" s="28" t="n"/>
       <c r="BO194" s="28" t="n"/>
@@ -57294,29 +57390,29 @@
       <c r="CR194" s="24" t="n"/>
       <c r="CS194" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="195" ht="36" customHeight="1">
       <c r="A195" s="24" t="inlineStr">
         <is>
-          <t>107ec83b7b5b4ab8</t>
+          <t>a16c7bca38f7476f</t>
         </is>
       </c>
       <c r="B195" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C195" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T18:00Z</t>
+          <t>2026-08-05T15:00Z</t>
         </is>
       </c>
       <c r="D195" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182204</t>
+          <t>421-2026:182220</t>
         </is>
       </c>
       <c r="E195" s="24" t="inlineStr">
@@ -57326,12 +57422,12 @@
       </c>
       <c r="F195" s="24" t="inlineStr">
         <is>
-          <t>Magda Linette</t>
+          <t>Kayla Cross</t>
         </is>
       </c>
       <c r="G195" s="24" t="inlineStr">
         <is>
-          <t>Iva Jovic</t>
+          <t>Ann Li</t>
         </is>
       </c>
       <c r="H195" s="24" t="inlineStr">
@@ -57360,19 +57456,19 @@
         <v>0.770115</v>
       </c>
       <c r="O195" s="28" t="n">
-        <v>0.661686</v>
+        <v>0.795002</v>
       </c>
       <c r="P195" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q195" s="28" t="n">
-        <v>-0.108429</v>
+        <v>0.024887</v>
       </c>
       <c r="R195" s="26" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="S195" s="29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T195" s="24" t="inlineStr">
         <is>
@@ -57395,7 +57491,7 @@
       <c r="AD195" s="24" t="n"/>
       <c r="AE195" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Magda Linette p=0.338 vs Iva Jovic. Executable ask 0.7700 (aec-wta-ivajov-maglin-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Kayla Cross p=0.205 vs Ann Li. Executable ask 0.7700 (aec-wta-annli-kaycro-2026-08-04).</t>
         </is>
       </c>
       <c r="AF195" s="31" t="inlineStr">
@@ -57436,32 +57532,32 @@
       </c>
       <c r="AP195" s="24" t="inlineStr">
         <is>
-          <t>Magda Linette</t>
+          <t>Kayla Cross</t>
         </is>
       </c>
       <c r="AQ195" s="24" t="inlineStr">
         <is>
-          <t>Magda Linette</t>
+          <t>Kayla Cross</t>
         </is>
       </c>
       <c r="AR195" s="24" t="inlineStr">
         <is>
-          <t>Magda Linette</t>
+          <t>Kayla Cross</t>
         </is>
       </c>
       <c r="AS195" s="24" t="inlineStr">
         <is>
-          <t>Iva Jovic</t>
+          <t>Ann Li</t>
         </is>
       </c>
       <c r="AT195" s="24" t="inlineStr">
         <is>
-          <t>Iva Jovic</t>
+          <t>Ann Li</t>
         </is>
       </c>
       <c r="AU195" s="24" t="inlineStr">
         <is>
-          <t>Iva Jovic</t>
+          <t>Ann Li</t>
         </is>
       </c>
       <c r="AV195" s="24" t="n"/>
@@ -57514,7 +57610,7 @@
       </c>
       <c r="BH195" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:17.250454Z</t>
+          <t>2026-08-05T13:52:38.380096Z</t>
         </is>
       </c>
       <c r="BI195" s="24" t="inlineStr">
@@ -57565,29 +57661,29 @@
       <c r="CR195" s="24" t="n"/>
       <c r="CS195" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="196" ht="36" customHeight="1">
       <c r="A196" s="24" t="inlineStr">
         <is>
-          <t>a18df055a2094241</t>
+          <t>6ddd668cdefb4366</t>
         </is>
       </c>
       <c r="B196" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C196" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T18:00Z</t>
+          <t>2026-08-05T16:30Z</t>
         </is>
       </c>
       <c r="D196" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182208</t>
+          <t>421-2026:182196</t>
         </is>
       </c>
       <c r="E196" s="24" t="inlineStr">
@@ -57597,12 +57693,12 @@
       </c>
       <c r="F196" s="24" t="inlineStr">
         <is>
-          <t>Emma Navarro</t>
+          <t>Magdalena Frech</t>
         </is>
       </c>
       <c r="G196" s="24" t="inlineStr">
         <is>
-          <t>Alina Korneeva</t>
+          <t>Jessica Pegula</t>
         </is>
       </c>
       <c r="H196" s="24" t="inlineStr">
@@ -57612,7 +57708,7 @@
       </c>
       <c r="I196" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J196" s="25" t="n"/>
@@ -57622,28 +57718,28 @@
         </is>
       </c>
       <c r="L196" s="26" t="n">
-        <v>-122</v>
+        <v>-900</v>
       </c>
       <c r="M196" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.111111</v>
       </c>
       <c r="N196" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.9</v>
       </c>
       <c r="O196" s="28" t="n">
-        <v>0.646211</v>
+        <v>0.9137729999999999</v>
       </c>
       <c r="P196" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q196" s="28" t="n">
-        <v>0.096661</v>
+        <v>0.013773</v>
       </c>
       <c r="R196" s="26" t="n">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="S196" s="29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T196" s="24" t="inlineStr">
         <is>
@@ -57666,7 +57762,7 @@
       <c r="AD196" s="24" t="n"/>
       <c r="AE196" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Emma Navarro p=0.646 vs Alina Korneeva. Executable ask 0.5500 (aec-wta-alikor-emmnav-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Magdalena Frech p=0.086 vs Jessica Pegula. Executable ask 0.9000 (aec-wta-jespeg-magfre-2026-08-04).</t>
         </is>
       </c>
       <c r="AF196" s="31" t="inlineStr">
@@ -57684,7 +57780,7 @@
       <c r="AJ196" s="31" t="n"/>
       <c r="AK196" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL196" s="26" t="n">
@@ -57692,47 +57788,47 @@
       </c>
       <c r="AM196" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN196" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO196" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP196" s="24" t="inlineStr">
         <is>
-          <t>Emma Navarro</t>
+          <t>Magdalena Frech</t>
         </is>
       </c>
       <c r="AQ196" s="24" t="inlineStr">
         <is>
-          <t>Emma Navarro</t>
+          <t>Magdalena Frech</t>
         </is>
       </c>
       <c r="AR196" s="24" t="inlineStr">
         <is>
-          <t>Emma Navarro</t>
+          <t>Magdalena Frech</t>
         </is>
       </c>
       <c r="AS196" s="24" t="inlineStr">
         <is>
-          <t>Alina Korneeva</t>
+          <t>Jessica Pegula</t>
         </is>
       </c>
       <c r="AT196" s="24" t="inlineStr">
         <is>
-          <t>Alina Korneeva</t>
+          <t>Jessica Pegula</t>
         </is>
       </c>
       <c r="AU196" s="24" t="inlineStr">
         <is>
-          <t>Alina Korneeva</t>
+          <t>Jessica Pegula</t>
         </is>
       </c>
       <c r="AV196" s="24" t="n"/>
@@ -57785,7 +57881,7 @@
       </c>
       <c r="BH196" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:15.073339Z</t>
+          <t>2026-08-05T13:52:39.841560Z</t>
         </is>
       </c>
       <c r="BI196" s="24" t="inlineStr">
@@ -57795,13 +57891,13 @@
       </c>
       <c r="BJ196" s="25" t="n"/>
       <c r="BK196" s="26" t="n">
-        <v>-122</v>
+        <v>-900</v>
       </c>
       <c r="BL196" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.111111</v>
       </c>
       <c r="BM196" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.9</v>
       </c>
       <c r="BN196" s="28" t="n"/>
       <c r="BO196" s="28" t="n"/>
@@ -57843,22 +57939,22 @@
     <row r="197" ht="36" customHeight="1">
       <c r="A197" s="24" t="inlineStr">
         <is>
-          <t>5377a590652b4ac8</t>
+          <t>39ddf50ddbbd4653</t>
         </is>
       </c>
       <c r="B197" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C197" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T19:30Z</t>
+          <t>2026-08-05T16:30Z</t>
         </is>
       </c>
       <c r="D197" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182178</t>
+          <t>421-2026:182201</t>
         </is>
       </c>
       <c r="E197" s="24" t="inlineStr">
@@ -57868,12 +57964,12 @@
       </c>
       <c r="F197" s="24" t="inlineStr">
         <is>
-          <t>Anna Bondar</t>
+          <t>Belinda Bencic</t>
         </is>
       </c>
       <c r="G197" s="24" t="inlineStr">
         <is>
-          <t>Elise Mertens</t>
+          <t>Sloane Stephens</t>
         </is>
       </c>
       <c r="H197" s="24" t="inlineStr">
@@ -57883,7 +57979,7 @@
       </c>
       <c r="I197" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J197" s="25" t="n"/>
@@ -57893,28 +57989,28 @@
         </is>
       </c>
       <c r="L197" s="26" t="n">
-        <v>-317</v>
+        <v>-733</v>
       </c>
       <c r="M197" s="27" t="n">
-        <v>1.315457</v>
+        <v>1.136426</v>
       </c>
       <c r="N197" s="28" t="n">
-        <v>0.760192</v>
+        <v>0.879952</v>
       </c>
       <c r="O197" s="28" t="n">
-        <v>0.61543</v>
+        <v>0.887489</v>
       </c>
       <c r="P197" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q197" s="28" t="n">
-        <v>-0.144762</v>
+        <v>0.007537</v>
       </c>
       <c r="R197" s="26" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S197" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T197" s="24" t="inlineStr">
         <is>
@@ -57937,7 +58033,7 @@
       <c r="AD197" s="24" t="n"/>
       <c r="AE197" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Anna Bondar p=0.385 vs Elise Mertens. Executable ask 0.7600 (aec-wta-elimer-annbon-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Belinda Bencic p=0.887 vs Sloane Stephens. Executable ask 0.8800 (aec-wta-sloste-belben-2026-08-06).</t>
         </is>
       </c>
       <c r="AF197" s="31" t="inlineStr">
@@ -57978,32 +58074,32 @@
       </c>
       <c r="AP197" s="24" t="inlineStr">
         <is>
-          <t>Anna Bondar</t>
+          <t>Belinda Bencic</t>
         </is>
       </c>
       <c r="AQ197" s="24" t="inlineStr">
         <is>
-          <t>Anna Bondar</t>
+          <t>Belinda Bencic</t>
         </is>
       </c>
       <c r="AR197" s="24" t="inlineStr">
         <is>
-          <t>Anna Bondar</t>
+          <t>Belinda Bencic</t>
         </is>
       </c>
       <c r="AS197" s="24" t="inlineStr">
         <is>
-          <t>Elise Mertens</t>
+          <t>Sloane Stephens</t>
         </is>
       </c>
       <c r="AT197" s="24" t="inlineStr">
         <is>
-          <t>Elise Mertens</t>
+          <t>Sloane Stephens</t>
         </is>
       </c>
       <c r="AU197" s="24" t="inlineStr">
         <is>
-          <t>Elise Mertens</t>
+          <t>Sloane Stephens</t>
         </is>
       </c>
       <c r="AV197" s="24" t="n"/>
@@ -58056,7 +58152,7 @@
       </c>
       <c r="BH197" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:18.350367Z</t>
+          <t>2026-08-05T13:52:41.012065Z</t>
         </is>
       </c>
       <c r="BI197" s="24" t="inlineStr">
@@ -58066,13 +58162,13 @@
       </c>
       <c r="BJ197" s="25" t="n"/>
       <c r="BK197" s="26" t="n">
-        <v>-317</v>
+        <v>-733</v>
       </c>
       <c r="BL197" s="27" t="n">
-        <v>1.315457</v>
+        <v>1.136426</v>
       </c>
       <c r="BM197" s="28" t="n">
-        <v>0.760192</v>
+        <v>0.879952</v>
       </c>
       <c r="BN197" s="28" t="n"/>
       <c r="BO197" s="28" t="n"/>
@@ -58107,29 +58203,29 @@
       <c r="CR197" s="24" t="n"/>
       <c r="CS197" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="198" ht="36" customHeight="1">
       <c r="A198" s="24" t="inlineStr">
         <is>
-          <t>4573e4cbc91a4c92</t>
+          <t>f465d39b412e4847</t>
         </is>
       </c>
       <c r="B198" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C198" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T19:30Z</t>
+          <t>2026-08-05T16:30Z</t>
         </is>
       </c>
       <c r="D198" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182191</t>
+          <t>421-2026:182218</t>
         </is>
       </c>
       <c r="E198" s="24" t="inlineStr">
@@ -58139,12 +58235,12 @@
       </c>
       <c r="F198" s="24" t="inlineStr">
         <is>
-          <t>Zeynep Sonmez</t>
+          <t>Elena Rybakina</t>
         </is>
       </c>
       <c r="G198" s="24" t="inlineStr">
         <is>
-          <t>Maria Sakkari</t>
+          <t>Daria Kasatkina</t>
         </is>
       </c>
       <c r="H198" s="24" t="inlineStr">
@@ -58164,28 +58260,28 @@
         </is>
       </c>
       <c r="L198" s="26" t="n">
-        <v>163</v>
+        <v>-669</v>
       </c>
       <c r="M198" s="27" t="n">
-        <v>2.63</v>
+        <v>1.149477</v>
       </c>
       <c r="N198" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.869961</v>
       </c>
       <c r="O198" s="28" t="n">
-        <v>0.529381</v>
+        <v>0.8561839999999999</v>
       </c>
       <c r="P198" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q198" s="28" t="n">
-        <v>0.149153</v>
+        <v>-0.013777</v>
       </c>
       <c r="R198" s="26" t="n">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="S198" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T198" s="24" t="inlineStr">
         <is>
@@ -58208,7 +58304,7 @@
       <c r="AD198" s="24" t="n"/>
       <c r="AE198" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Zeynep Sonmez p=0.529 vs Maria Sakkari. Executable ask 0.3800 (aec-wta-marsak-zeyson-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Elena Rybakina p=0.856 vs Daria Kasatkina. Executable ask 0.8700 (aec-wta-darkas-eleryb-2026-08-06).</t>
         </is>
       </c>
       <c r="AF198" s="31" t="inlineStr">
@@ -58249,32 +58345,32 @@
       </c>
       <c r="AP198" s="24" t="inlineStr">
         <is>
-          <t>Zeynep Sonmez</t>
+          <t>Elena Rybakina</t>
         </is>
       </c>
       <c r="AQ198" s="24" t="inlineStr">
         <is>
-          <t>Zeynep Sonmez</t>
+          <t>Elena Rybakina</t>
         </is>
       </c>
       <c r="AR198" s="24" t="inlineStr">
         <is>
-          <t>Zeynep Sonmez</t>
+          <t>Elena Rybakina</t>
         </is>
       </c>
       <c r="AS198" s="24" t="inlineStr">
         <is>
-          <t>Maria Sakkari</t>
+          <t>Daria Kasatkina</t>
         </is>
       </c>
       <c r="AT198" s="24" t="inlineStr">
         <is>
-          <t>Maria Sakkari</t>
+          <t>Daria Kasatkina</t>
         </is>
       </c>
       <c r="AU198" s="24" t="inlineStr">
         <is>
-          <t>Maria Sakkari</t>
+          <t>Daria Kasatkina</t>
         </is>
       </c>
       <c r="AV198" s="24" t="n"/>
@@ -58327,7 +58423,7 @@
       </c>
       <c r="BH198" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:18.087842Z</t>
+          <t>2026-08-05T13:52:41.872950Z</t>
         </is>
       </c>
       <c r="BI198" s="24" t="inlineStr">
@@ -58337,13 +58433,13 @@
       </c>
       <c r="BJ198" s="25" t="n"/>
       <c r="BK198" s="26" t="n">
-        <v>163</v>
+        <v>-669</v>
       </c>
       <c r="BL198" s="27" t="n">
-        <v>2.63</v>
+        <v>1.149477</v>
       </c>
       <c r="BM198" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.869961</v>
       </c>
       <c r="BN198" s="28" t="n"/>
       <c r="BO198" s="28" t="n"/>
@@ -58378,29 +58474,29 @@
       <c r="CR198" s="24" t="n"/>
       <c r="CS198" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="199" ht="36" customHeight="1">
       <c r="A199" s="24" t="inlineStr">
         <is>
-          <t>ba9c89d4caf74436</t>
+          <t>c01d22a58c78482c</t>
         </is>
       </c>
       <c r="B199" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C199" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T21:00Z</t>
+          <t>2026-08-05T16:30Z</t>
         </is>
       </c>
       <c r="D199" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182176</t>
+          <t>421-2026:182225</t>
         </is>
       </c>
       <c r="E199" s="24" t="inlineStr">
@@ -58410,12 +58506,12 @@
       </c>
       <c r="F199" s="24" t="inlineStr">
         <is>
-          <t>Naomi Osaka</t>
+          <t>Taylor Townsend</t>
         </is>
       </c>
       <c r="G199" s="24" t="inlineStr">
         <is>
-          <t>Panna Udvardy</t>
+          <t>Marie Bouzkova</t>
         </is>
       </c>
       <c r="H199" s="24" t="inlineStr">
@@ -58425,7 +58521,7 @@
       </c>
       <c r="I199" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J199" s="25" t="n"/>
@@ -58435,28 +58531,28 @@
         </is>
       </c>
       <c r="L199" s="26" t="n">
-        <v>-1011</v>
+        <v>-133</v>
       </c>
       <c r="M199" s="27" t="n">
-        <v>1.098912</v>
+        <v>1.75188</v>
       </c>
       <c r="N199" s="28" t="n">
-        <v>0.909991</v>
+        <v>0.570815</v>
       </c>
       <c r="O199" s="28" t="n">
-        <v>0.728504</v>
+        <v>0.56035</v>
       </c>
       <c r="P199" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q199" s="28" t="n">
-        <v>-0.181487</v>
+        <v>-0.010465</v>
       </c>
       <c r="R199" s="26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S199" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T199" s="24" t="inlineStr">
         <is>
@@ -58479,7 +58575,7 @@
       <c r="AD199" s="24" t="n"/>
       <c r="AE199" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Naomi Osaka p=0.729 vs Panna Udvardy. Executable ask 0.9100 (aec-wta-panudv-naoosa-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Taylor Townsend p=0.440 vs Marie Bouzkova. Executable ask 0.5700 (aec-wta-marbou-taytow-2026-08-06).</t>
         </is>
       </c>
       <c r="AF199" s="31" t="inlineStr">
@@ -58520,32 +58616,32 @@
       </c>
       <c r="AP199" s="24" t="inlineStr">
         <is>
-          <t>Naomi Osaka</t>
+          <t>Taylor Townsend</t>
         </is>
       </c>
       <c r="AQ199" s="24" t="inlineStr">
         <is>
-          <t>Naomi Osaka</t>
+          <t>Taylor Townsend</t>
         </is>
       </c>
       <c r="AR199" s="24" t="inlineStr">
         <is>
-          <t>Naomi Osaka</t>
+          <t>Taylor Townsend</t>
         </is>
       </c>
       <c r="AS199" s="24" t="inlineStr">
         <is>
-          <t>Panna Udvardy</t>
+          <t>Marie Bouzkova</t>
         </is>
       </c>
       <c r="AT199" s="24" t="inlineStr">
         <is>
-          <t>Panna Udvardy</t>
+          <t>Marie Bouzkova</t>
         </is>
       </c>
       <c r="AU199" s="24" t="inlineStr">
         <is>
-          <t>Panna Udvardy</t>
+          <t>Marie Bouzkova</t>
         </is>
       </c>
       <c r="AV199" s="24" t="n"/>
@@ -58598,7 +58694,7 @@
       </c>
       <c r="BH199" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:21.325844Z</t>
+          <t>2026-08-05T13:52:39.163501Z</t>
         </is>
       </c>
       <c r="BI199" s="24" t="inlineStr">
@@ -58608,13 +58704,13 @@
       </c>
       <c r="BJ199" s="25" t="n"/>
       <c r="BK199" s="26" t="n">
-        <v>-1011</v>
+        <v>-133</v>
       </c>
       <c r="BL199" s="27" t="n">
-        <v>1.098912</v>
+        <v>1.75188</v>
       </c>
       <c r="BM199" s="28" t="n">
-        <v>0.909991</v>
+        <v>0.570815</v>
       </c>
       <c r="BN199" s="28" t="n"/>
       <c r="BO199" s="28" t="n"/>
@@ -58656,22 +58752,22 @@
     <row r="200" ht="36" customHeight="1">
       <c r="A200" s="24" t="inlineStr">
         <is>
-          <t>07b02fe2657c42e6</t>
+          <t>1889d8b2c96f4bb3</t>
         </is>
       </c>
       <c r="B200" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C200" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T21:00Z</t>
+          <t>2026-08-05T18:00Z</t>
         </is>
       </c>
       <c r="D200" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182179</t>
+          <t>421-2026:182190</t>
         </is>
       </c>
       <c r="E200" s="24" t="inlineStr">
@@ -58681,12 +58777,12 @@
       </c>
       <c r="F200" s="24" t="inlineStr">
         <is>
-          <t>Maya Joint</t>
+          <t>Coco Gauff</t>
         </is>
       </c>
       <c r="G200" s="24" t="inlineStr">
         <is>
-          <t>Sorana Cirstea</t>
+          <t>Kayla Day</t>
         </is>
       </c>
       <c r="H200" s="24" t="inlineStr">
@@ -58696,7 +58792,7 @@
       </c>
       <c r="I200" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J200" s="25" t="n"/>
@@ -58706,25 +58802,25 @@
         </is>
       </c>
       <c r="L200" s="26" t="n">
-        <v>-335</v>
+        <v>-1011</v>
       </c>
       <c r="M200" s="27" t="n">
-        <v>1.298507</v>
+        <v>1.098912</v>
       </c>
       <c r="N200" s="28" t="n">
-        <v>0.770115</v>
+        <v>0.909991</v>
       </c>
       <c r="O200" s="28" t="n">
-        <v>0.797746</v>
+        <v>0.914779</v>
       </c>
       <c r="P200" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q200" s="28" t="n">
-        <v>0.027631</v>
+        <v>0.004788</v>
       </c>
       <c r="R200" s="26" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="S200" s="29" t="n">
         <v>2</v>
@@ -58750,7 +58846,7 @@
       <c r="AD200" s="24" t="n"/>
       <c r="AE200" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Maya Joint p=0.202 vs Sorana Cirstea. Executable ask 0.7700 (aec-wta-sorcir-mayjoi-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Coco Gauff p=0.915 vs Kayla Day. Executable ask 0.9100 (aec-wta-kayday-cocgau-2026-08-04).</t>
         </is>
       </c>
       <c r="AF200" s="31" t="inlineStr">
@@ -58791,32 +58887,32 @@
       </c>
       <c r="AP200" s="24" t="inlineStr">
         <is>
-          <t>Maya Joint</t>
+          <t>Coco Gauff</t>
         </is>
       </c>
       <c r="AQ200" s="24" t="inlineStr">
         <is>
-          <t>Maya Joint</t>
+          <t>Coco Gauff</t>
         </is>
       </c>
       <c r="AR200" s="24" t="inlineStr">
         <is>
-          <t>Maya Joint</t>
+          <t>Coco Gauff</t>
         </is>
       </c>
       <c r="AS200" s="24" t="inlineStr">
         <is>
-          <t>Sorana Cirstea</t>
+          <t>Kayla Day</t>
         </is>
       </c>
       <c r="AT200" s="24" t="inlineStr">
         <is>
-          <t>Sorana Cirstea</t>
+          <t>Kayla Day</t>
         </is>
       </c>
       <c r="AU200" s="24" t="inlineStr">
         <is>
-          <t>Sorana Cirstea</t>
+          <t>Kayla Day</t>
         </is>
       </c>
       <c r="AV200" s="24" t="n"/>
@@ -58869,7 +58965,7 @@
       </c>
       <c r="BH200" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:19.844141Z</t>
+          <t>2026-08-05T13:52:42.829996Z</t>
         </is>
       </c>
       <c r="BI200" s="24" t="inlineStr">
@@ -58879,13 +58975,13 @@
       </c>
       <c r="BJ200" s="25" t="n"/>
       <c r="BK200" s="26" t="n">
-        <v>-335</v>
+        <v>-1011</v>
       </c>
       <c r="BL200" s="27" t="n">
-        <v>1.298507</v>
+        <v>1.098912</v>
       </c>
       <c r="BM200" s="28" t="n">
-        <v>0.770115</v>
+        <v>0.909991</v>
       </c>
       <c r="BN200" s="28" t="n"/>
       <c r="BO200" s="28" t="n"/>
@@ -58927,22 +59023,22 @@
     <row r="201" ht="36" customHeight="1">
       <c r="A201" s="24" t="inlineStr">
         <is>
-          <t>7f3d0080f41e4f2e</t>
+          <t>b89defaa8aa948a4</t>
         </is>
       </c>
       <c r="B201" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C201" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T21:00Z</t>
+          <t>2026-08-05T18:00Z</t>
         </is>
       </c>
       <c r="D201" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182214</t>
+          <t>421-2026:182192</t>
         </is>
       </c>
       <c r="E201" s="24" t="inlineStr">
@@ -58952,12 +59048,12 @@
       </c>
       <c r="F201" s="24" t="inlineStr">
         <is>
-          <t>Barbora Krejcikova</t>
+          <t>Karolina Pliskova</t>
         </is>
       </c>
       <c r="G201" s="24" t="inlineStr">
         <is>
-          <t>Liudmila Samsonova</t>
+          <t>Mirra Andreeva</t>
         </is>
       </c>
       <c r="H201" s="24" t="inlineStr">
@@ -58967,7 +59063,7 @@
       </c>
       <c r="I201" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J201" s="25" t="n"/>
@@ -58977,25 +59073,25 @@
         </is>
       </c>
       <c r="L201" s="26" t="n">
-        <v>-178</v>
+        <v>-426</v>
       </c>
       <c r="M201" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.234742</v>
       </c>
       <c r="N201" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.809886</v>
       </c>
       <c r="O201" s="28" t="n">
-        <v>0.733479</v>
+        <v>0.753053</v>
       </c>
       <c r="P201" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q201" s="28" t="n">
-        <v>0.093191</v>
+        <v>-0.056833</v>
       </c>
       <c r="R201" s="26" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="S201" s="29" t="n">
         <v>2</v>
@@ -59021,7 +59117,7 @@
       <c r="AD201" s="24" t="n"/>
       <c r="AE201" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Barbora Krejcikova p=0.733 vs Liudmila Samsonova. Executable ask 0.6400 (aec-wta-liusam-barkre-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Karolina Pliskova p=0.247 vs Mirra Andreeva. Executable ask 0.8100 (aec-wta-mirand-karpli-2026-08-04).</t>
         </is>
       </c>
       <c r="AF201" s="31" t="inlineStr">
@@ -59039,7 +59135,7 @@
       <c r="AJ201" s="31" t="n"/>
       <c r="AK201" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL201" s="26" t="n">
@@ -59047,47 +59143,47 @@
       </c>
       <c r="AM201" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN201" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO201" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP201" s="24" t="inlineStr">
         <is>
-          <t>Barbora Krejcikova</t>
+          <t>Karolina Pliskova</t>
         </is>
       </c>
       <c r="AQ201" s="24" t="inlineStr">
         <is>
-          <t>Barbora Krejcikova</t>
+          <t>Karolina Pliskova</t>
         </is>
       </c>
       <c r="AR201" s="24" t="inlineStr">
         <is>
-          <t>Barbora Krejcikova</t>
+          <t>Karolina Pliskova</t>
         </is>
       </c>
       <c r="AS201" s="24" t="inlineStr">
         <is>
-          <t>Liudmila Samsonova</t>
+          <t>Mirra Andreeva</t>
         </is>
       </c>
       <c r="AT201" s="24" t="inlineStr">
         <is>
-          <t>Liudmila Samsonova</t>
+          <t>Mirra Andreeva</t>
         </is>
       </c>
       <c r="AU201" s="24" t="inlineStr">
         <is>
-          <t>Liudmila Samsonova</t>
+          <t>Mirra Andreeva</t>
         </is>
       </c>
       <c r="AV201" s="24" t="n"/>
@@ -59140,7 +59236,7 @@
       </c>
       <c r="BH201" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:19.786889Z</t>
+          <t>2026-08-05T13:52:43.933343Z</t>
         </is>
       </c>
       <c r="BI201" s="24" t="inlineStr">
@@ -59150,13 +59246,13 @@
       </c>
       <c r="BJ201" s="25" t="n"/>
       <c r="BK201" s="26" t="n">
-        <v>-178</v>
+        <v>-426</v>
       </c>
       <c r="BL201" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.234742</v>
       </c>
       <c r="BM201" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.809886</v>
       </c>
       <c r="BN201" s="28" t="n"/>
       <c r="BO201" s="28" t="n"/>
@@ -59191,29 +59287,29 @@
       <c r="CR201" s="24" t="n"/>
       <c r="CS201" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="202" ht="36" customHeight="1">
       <c r="A202" s="24" t="inlineStr">
         <is>
-          <t>63d353c4612d4d70</t>
+          <t>ac0e9183c9b24af2</t>
         </is>
       </c>
       <c r="B202" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C202" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T23:00Z</t>
+          <t>2026-08-05T18:00Z</t>
         </is>
       </c>
       <c r="D202" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182170</t>
+          <t>421-2026:182204</t>
         </is>
       </c>
       <c r="E202" s="24" t="inlineStr">
@@ -59223,12 +59319,12 @@
       </c>
       <c r="F202" s="24" t="inlineStr">
         <is>
-          <t>Leylah Fernandez</t>
+          <t>Magda Linette</t>
         </is>
       </c>
       <c r="G202" s="24" t="inlineStr">
         <is>
-          <t>Renata Zarazua</t>
+          <t>Iva Jovic</t>
         </is>
       </c>
       <c r="H202" s="24" t="inlineStr">
@@ -59238,7 +59334,7 @@
       </c>
       <c r="I202" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J202" s="25" t="n"/>
@@ -59248,28 +59344,28 @@
         </is>
       </c>
       <c r="L202" s="26" t="n">
-        <v>-233</v>
+        <v>-376</v>
       </c>
       <c r="M202" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.265957</v>
       </c>
       <c r="N202" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.789916</v>
       </c>
       <c r="O202" s="28" t="n">
-        <v>0.686095</v>
+        <v>0.661686</v>
       </c>
       <c r="P202" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q202" s="28" t="n">
-        <v>-0.013605</v>
+        <v>-0.12823</v>
       </c>
       <c r="R202" s="26" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="S202" s="29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T202" s="24" t="inlineStr">
         <is>
@@ -59292,7 +59388,7 @@
       <c r="AD202" s="24" t="n"/>
       <c r="AE202" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Leylah Fernandez p=0.686 vs Renata Zarazua. Executable ask 0.7000 (aec-wta-renzar-leyfer-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Magda Linette p=0.338 vs Iva Jovic. Executable ask 0.7900 (aec-wta-ivajov-maglin-2026-08-04).</t>
         </is>
       </c>
       <c r="AF202" s="31" t="inlineStr">
@@ -59333,32 +59429,32 @@
       </c>
       <c r="AP202" s="24" t="inlineStr">
         <is>
-          <t>Leylah Fernandez</t>
+          <t>Magda Linette</t>
         </is>
       </c>
       <c r="AQ202" s="24" t="inlineStr">
         <is>
-          <t>Leylah Fernandez</t>
+          <t>Magda Linette</t>
         </is>
       </c>
       <c r="AR202" s="24" t="inlineStr">
         <is>
-          <t>Leylah Fernandez</t>
+          <t>Magda Linette</t>
         </is>
       </c>
       <c r="AS202" s="24" t="inlineStr">
         <is>
-          <t>Renata Zarazua</t>
+          <t>Iva Jovic</t>
         </is>
       </c>
       <c r="AT202" s="24" t="inlineStr">
         <is>
-          <t>Renata Zarazua</t>
+          <t>Iva Jovic</t>
         </is>
       </c>
       <c r="AU202" s="24" t="inlineStr">
         <is>
-          <t>Renata Zarazua</t>
+          <t>Iva Jovic</t>
         </is>
       </c>
       <c r="AV202" s="24" t="n"/>
@@ -59411,7 +59507,7 @@
       </c>
       <c r="BH202" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:22.562389Z</t>
+          <t>2026-08-05T13:52:43.391817Z</t>
         </is>
       </c>
       <c r="BI202" s="24" t="inlineStr">
@@ -59421,13 +59517,13 @@
       </c>
       <c r="BJ202" s="25" t="n"/>
       <c r="BK202" s="26" t="n">
-        <v>-233</v>
+        <v>-376</v>
       </c>
       <c r="BL202" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.265957</v>
       </c>
       <c r="BM202" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.789916</v>
       </c>
       <c r="BN202" s="28" t="n"/>
       <c r="BO202" s="28" t="n"/>
@@ -59469,22 +59565,22 @@
     <row r="203" ht="36" customHeight="1">
       <c r="A203" s="24" t="inlineStr">
         <is>
-          <t>b30671fb831e4c0d</t>
+          <t>7d0ef94417234e47</t>
         </is>
       </c>
       <c r="B203" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C203" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T00:30Z</t>
+          <t>2026-08-05T18:00Z</t>
         </is>
       </c>
       <c r="D203" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182216</t>
+          <t>421-2026:182208</t>
         </is>
       </c>
       <c r="E203" s="24" t="inlineStr">
@@ -59494,12 +59590,12 @@
       </c>
       <c r="F203" s="24" t="inlineStr">
         <is>
-          <t>Alexandra Eala</t>
+          <t>Emma Navarro</t>
         </is>
       </c>
       <c r="G203" s="24" t="inlineStr">
         <is>
-          <t>Alycia Parks</t>
+          <t>Alina Korneeva</t>
         </is>
       </c>
       <c r="H203" s="24" t="inlineStr">
@@ -59519,28 +59615,28 @@
         </is>
       </c>
       <c r="L203" s="26" t="n">
-        <v>-567</v>
+        <v>-117</v>
       </c>
       <c r="M203" s="27" t="n">
-        <v>1.176367</v>
+        <v>1.854701</v>
       </c>
       <c r="N203" s="28" t="n">
-        <v>0.850075</v>
+        <v>0.539171</v>
       </c>
       <c r="O203" s="28" t="n">
-        <v>0.699863</v>
+        <v>0.646211</v>
       </c>
       <c r="P203" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q203" s="28" t="n">
-        <v>-0.150212</v>
+        <v>0.10704</v>
       </c>
       <c r="R203" s="26" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="S203" s="29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T203" s="24" t="inlineStr">
         <is>
@@ -59563,7 +59659,7 @@
       <c r="AD203" s="24" t="n"/>
       <c r="AE203" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Alexandra Eala p=0.700 vs Alycia Parks. Executable ask 0.8500 (aec-wta-alypar-aleeal-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Emma Navarro p=0.646 vs Alina Korneeva. Executable ask 0.5400 (aec-wta-alikor-emmnav-2026-08-04).</t>
         </is>
       </c>
       <c r="AF203" s="31" t="inlineStr">
@@ -59581,7 +59677,7 @@
       <c r="AJ203" s="31" t="n"/>
       <c r="AK203" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL203" s="26" t="n">
@@ -59589,47 +59685,47 @@
       </c>
       <c r="AM203" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN203" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO203" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP203" s="24" t="inlineStr">
         <is>
-          <t>Alexandra Eala</t>
+          <t>Emma Navarro</t>
         </is>
       </c>
       <c r="AQ203" s="24" t="inlineStr">
         <is>
-          <t>Alexandra Eala</t>
+          <t>Emma Navarro</t>
         </is>
       </c>
       <c r="AR203" s="24" t="inlineStr">
         <is>
-          <t>Alexandra Eala</t>
+          <t>Emma Navarro</t>
         </is>
       </c>
       <c r="AS203" s="24" t="inlineStr">
         <is>
-          <t>Alycia Parks</t>
+          <t>Alina Korneeva</t>
         </is>
       </c>
       <c r="AT203" s="24" t="inlineStr">
         <is>
-          <t>Alycia Parks</t>
+          <t>Alina Korneeva</t>
         </is>
       </c>
       <c r="AU203" s="24" t="inlineStr">
         <is>
-          <t>Alycia Parks</t>
+          <t>Alina Korneeva</t>
         </is>
       </c>
       <c r="AV203" s="24" t="n"/>
@@ -59682,7 +59778,7 @@
       </c>
       <c r="BH203" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:22.894133Z</t>
+          <t>2026-08-05T13:52:42.200980Z</t>
         </is>
       </c>
       <c r="BI203" s="24" t="inlineStr">
@@ -59692,13 +59788,13 @@
       </c>
       <c r="BJ203" s="25" t="n"/>
       <c r="BK203" s="26" t="n">
-        <v>-567</v>
+        <v>-117</v>
       </c>
       <c r="BL203" s="27" t="n">
-        <v>1.176367</v>
+        <v>1.854701</v>
       </c>
       <c r="BM203" s="28" t="n">
-        <v>0.850075</v>
+        <v>0.539171</v>
       </c>
       <c r="BN203" s="28" t="n"/>
       <c r="BO203" s="28" t="n"/>
@@ -59733,29 +59829,29 @@
       <c r="CR203" s="24" t="n"/>
       <c r="CS203" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="204" ht="36" customHeight="1">
       <c r="A204" s="24" t="inlineStr">
         <is>
-          <t>639381b79e134a1a</t>
+          <t>8741461afea9491f</t>
         </is>
       </c>
       <c r="B204" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C204" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T09:00Z</t>
+          <t>2026-08-05T19:30Z</t>
         </is>
       </c>
       <c r="D204" s="24" t="inlineStr">
         <is>
-          <t>961-2026:182103</t>
+          <t>421-2026:182178</t>
         </is>
       </c>
       <c r="E204" s="24" t="inlineStr">
@@ -59765,12 +59861,12 @@
       </c>
       <c r="F204" s="24" t="inlineStr">
         <is>
-          <t>Justina Mikulskyte</t>
+          <t>Anna Bondar</t>
         </is>
       </c>
       <c r="G204" s="24" t="inlineStr">
         <is>
-          <t>Katarzyna Kawa</t>
+          <t>Elise Mertens</t>
         </is>
       </c>
       <c r="H204" s="24" t="inlineStr">
@@ -59790,28 +59886,28 @@
         </is>
       </c>
       <c r="L204" s="26" t="n">
-        <v>-317</v>
+        <v>-257</v>
       </c>
       <c r="M204" s="27" t="n">
-        <v>1.315457</v>
+        <v>1.389105</v>
       </c>
       <c r="N204" s="28" t="n">
-        <v>0.760192</v>
+        <v>0.719888</v>
       </c>
       <c r="O204" s="28" t="n">
-        <v>0.782547</v>
+        <v>0.61543</v>
       </c>
       <c r="P204" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q204" s="28" t="n">
-        <v>0.022355</v>
+        <v>-0.104458</v>
       </c>
       <c r="R204" s="26" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="S204" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T204" s="24" t="inlineStr">
         <is>
@@ -59834,7 +59930,7 @@
       <c r="AD204" s="24" t="n"/>
       <c r="AE204" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Justina Mikulskyte p=0.217 vs Katarzyna Kawa. Executable ask 0.7600 (aec-wta-katkaw-jusmik-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Anna Bondar p=0.385 vs Elise Mertens. Executable ask 0.7200 (aec-wta-elimer-annbon-2026-08-04).</t>
         </is>
       </c>
       <c r="AF204" s="31" t="inlineStr">
@@ -59875,32 +59971,32 @@
       </c>
       <c r="AP204" s="24" t="inlineStr">
         <is>
-          <t>Justina Mikulskyte</t>
+          <t>Anna Bondar</t>
         </is>
       </c>
       <c r="AQ204" s="24" t="inlineStr">
         <is>
-          <t>Justina Mikulskyte</t>
+          <t>Anna Bondar</t>
         </is>
       </c>
       <c r="AR204" s="24" t="inlineStr">
         <is>
-          <t>Justina Mikulskyte</t>
+          <t>Anna Bondar</t>
         </is>
       </c>
       <c r="AS204" s="24" t="inlineStr">
         <is>
-          <t>Katarzyna Kawa</t>
+          <t>Elise Mertens</t>
         </is>
       </c>
       <c r="AT204" s="24" t="inlineStr">
         <is>
-          <t>Katarzyna Kawa</t>
+          <t>Elise Mertens</t>
         </is>
       </c>
       <c r="AU204" s="24" t="inlineStr">
         <is>
-          <t>Katarzyna Kawa</t>
+          <t>Elise Mertens</t>
         </is>
       </c>
       <c r="AV204" s="24" t="n"/>
@@ -59953,7 +60049,7 @@
       </c>
       <c r="BH204" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:10.082069Z</t>
+          <t>2026-08-05T13:52:44.961069Z</t>
         </is>
       </c>
       <c r="BI204" s="24" t="inlineStr">
@@ -59963,13 +60059,13 @@
       </c>
       <c r="BJ204" s="25" t="n"/>
       <c r="BK204" s="26" t="n">
-        <v>-317</v>
+        <v>-257</v>
       </c>
       <c r="BL204" s="27" t="n">
-        <v>1.315457</v>
+        <v>1.389105</v>
       </c>
       <c r="BM204" s="28" t="n">
-        <v>0.760192</v>
+        <v>0.719888</v>
       </c>
       <c r="BN204" s="28" t="n"/>
       <c r="BO204" s="28" t="n"/>
@@ -60004,29 +60100,29 @@
       <c r="CR204" s="24" t="n"/>
       <c r="CS204" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="205" ht="36" customHeight="1">
       <c r="A205" s="24" t="inlineStr">
         <is>
-          <t>0428483b2fae4598</t>
+          <t>85a7a46189474d6e</t>
         </is>
       </c>
       <c r="B205" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C205" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T09:00Z</t>
+          <t>2026-08-05T19:30Z</t>
         </is>
       </c>
       <c r="D205" s="24" t="inlineStr">
         <is>
-          <t>961-2026:182104</t>
+          <t>421-2026:182191</t>
         </is>
       </c>
       <c r="E205" s="24" t="inlineStr">
@@ -60036,12 +60132,12 @@
       </c>
       <c r="F205" s="24" t="inlineStr">
         <is>
-          <t>Aliona Falei</t>
+          <t>Zeynep Sonmez</t>
         </is>
       </c>
       <c r="G205" s="24" t="inlineStr">
         <is>
-          <t>Carol Young Suh Lee</t>
+          <t>Maria Sakkari</t>
         </is>
       </c>
       <c r="H205" s="24" t="inlineStr">
@@ -60051,7 +60147,7 @@
       </c>
       <c r="I205" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J205" s="25" t="n"/>
@@ -60061,28 +60157,28 @@
         </is>
       </c>
       <c r="L205" s="26" t="n">
-        <v>-156</v>
+        <v>156</v>
       </c>
       <c r="M205" s="27" t="n">
-        <v>1.641026</v>
+        <v>2.56</v>
       </c>
       <c r="N205" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.390625</v>
       </c>
       <c r="O205" s="28" t="n">
-        <v>0.589246</v>
+        <v>0.529381</v>
       </c>
       <c r="P205" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q205" s="28" t="n">
-        <v>-0.020129</v>
+        <v>0.138756</v>
       </c>
       <c r="R205" s="26" t="n">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="S205" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T205" s="24" t="inlineStr">
         <is>
@@ -60105,7 +60201,7 @@
       <c r="AD205" s="24" t="n"/>
       <c r="AE205" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Aliona Falei p=0.411 vs Carol Young Suh Lee. Executable ask 0.6100 (aec-wta-carlee-alifal-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Zeynep Sonmez p=0.529 vs Maria Sakkari. Executable ask 0.3900 (aec-wta-marsak-zeyson-2026-08-06).</t>
         </is>
       </c>
       <c r="AF205" s="31" t="inlineStr">
@@ -60146,32 +60242,32 @@
       </c>
       <c r="AP205" s="24" t="inlineStr">
         <is>
-          <t>Aliona Falei</t>
+          <t>Zeynep Sonmez</t>
         </is>
       </c>
       <c r="AQ205" s="24" t="inlineStr">
         <is>
-          <t>Aliona Falei</t>
+          <t>Zeynep Sonmez</t>
         </is>
       </c>
       <c r="AR205" s="24" t="inlineStr">
         <is>
-          <t>Aliona Falei</t>
+          <t>Zeynep Sonmez</t>
         </is>
       </c>
       <c r="AS205" s="24" t="inlineStr">
         <is>
-          <t>Carol Young Suh Lee</t>
+          <t>Maria Sakkari</t>
         </is>
       </c>
       <c r="AT205" s="24" t="inlineStr">
         <is>
-          <t>Carol Young Suh Lee</t>
+          <t>Maria Sakkari</t>
         </is>
       </c>
       <c r="AU205" s="24" t="inlineStr">
         <is>
-          <t>Carol Young Suh Lee</t>
+          <t>Maria Sakkari</t>
         </is>
       </c>
       <c r="AV205" s="24" t="n"/>
@@ -60224,7 +60320,7 @@
       </c>
       <c r="BH205" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:10.066030Z</t>
+          <t>2026-08-05T13:52:44.641647Z</t>
         </is>
       </c>
       <c r="BI205" s="24" t="inlineStr">
@@ -60234,13 +60330,13 @@
       </c>
       <c r="BJ205" s="25" t="n"/>
       <c r="BK205" s="26" t="n">
-        <v>-156</v>
+        <v>156</v>
       </c>
       <c r="BL205" s="27" t="n">
-        <v>1.641026</v>
+        <v>2.56</v>
       </c>
       <c r="BM205" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.390625</v>
       </c>
       <c r="BN205" s="28" t="n"/>
       <c r="BO205" s="28" t="n"/>
@@ -60275,29 +60371,29 @@
       <c r="CR205" s="24" t="n"/>
       <c r="CS205" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="206" ht="36" customHeight="1">
       <c r="A206" s="24" t="inlineStr">
         <is>
-          <t>db3e3391389e499e</t>
+          <t>e963b8e997dc4d04</t>
         </is>
       </c>
       <c r="B206" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C206" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T10:30Z</t>
+          <t>2026-08-05T21:00Z</t>
         </is>
       </c>
       <c r="D206" s="24" t="inlineStr">
         <is>
-          <t>961-2026:182101</t>
+          <t>421-2026:182176</t>
         </is>
       </c>
       <c r="E206" s="24" t="inlineStr">
@@ -60307,12 +60403,12 @@
       </c>
       <c r="F206" s="24" t="inlineStr">
         <is>
-          <t>Ella Seidel</t>
+          <t>Naomi Osaka</t>
         </is>
       </c>
       <c r="G206" s="24" t="inlineStr">
         <is>
-          <t>Gabriela Knutson</t>
+          <t>Panna Udvardy</t>
         </is>
       </c>
       <c r="H206" s="24" t="inlineStr">
@@ -60322,7 +60418,7 @@
       </c>
       <c r="I206" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J206" s="25" t="n"/>
@@ -60332,28 +60428,28 @@
         </is>
       </c>
       <c r="L206" s="26" t="n">
-        <v>186</v>
+        <v>-1150</v>
       </c>
       <c r="M206" s="27" t="n">
-        <v>2.86</v>
+        <v>1.086957</v>
       </c>
       <c r="N206" s="28" t="n">
-        <v>0.34965</v>
+        <v>0.92</v>
       </c>
       <c r="O206" s="28" t="n">
-        <v>0.518196</v>
+        <v>0.728504</v>
       </c>
       <c r="P206" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q206" s="28" t="n">
-        <v>0.168546</v>
+        <v>-0.191496</v>
       </c>
       <c r="R206" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S206" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T206" s="24" t="inlineStr">
         <is>
@@ -60376,7 +60472,7 @@
       <c r="AD206" s="24" t="n"/>
       <c r="AE206" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Ella Seidel p=0.482 vs Gabriela Knutson. Executable ask 0.3500 (aec-wta-gabknu-ellsei-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Naomi Osaka p=0.729 vs Panna Udvardy. Executable ask 0.9200 (aec-wta-panudv-naoosa-2026-08-06).</t>
         </is>
       </c>
       <c r="AF206" s="31" t="inlineStr">
@@ -60417,32 +60513,32 @@
       </c>
       <c r="AP206" s="24" t="inlineStr">
         <is>
-          <t>Ella Seidel</t>
+          <t>Naomi Osaka</t>
         </is>
       </c>
       <c r="AQ206" s="24" t="inlineStr">
         <is>
-          <t>Ella Seidel</t>
+          <t>Naomi Osaka</t>
         </is>
       </c>
       <c r="AR206" s="24" t="inlineStr">
         <is>
-          <t>Ella Seidel</t>
+          <t>Naomi Osaka</t>
         </is>
       </c>
       <c r="AS206" s="24" t="inlineStr">
         <is>
-          <t>Gabriela Knutson</t>
+          <t>Panna Udvardy</t>
         </is>
       </c>
       <c r="AT206" s="24" t="inlineStr">
         <is>
-          <t>Gabriela Knutson</t>
+          <t>Panna Udvardy</t>
         </is>
       </c>
       <c r="AU206" s="24" t="inlineStr">
         <is>
-          <t>Gabriela Knutson</t>
+          <t>Panna Udvardy</t>
         </is>
       </c>
       <c r="AV206" s="24" t="n"/>
@@ -60495,7 +60591,7 @@
       </c>
       <c r="BH206" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:10.124922Z</t>
+          <t>2026-08-05T13:52:47.274775Z</t>
         </is>
       </c>
       <c r="BI206" s="24" t="inlineStr">
@@ -60505,13 +60601,13 @@
       </c>
       <c r="BJ206" s="25" t="n"/>
       <c r="BK206" s="26" t="n">
-        <v>186</v>
+        <v>-1150</v>
       </c>
       <c r="BL206" s="27" t="n">
-        <v>2.86</v>
+        <v>1.086957</v>
       </c>
       <c r="BM206" s="28" t="n">
-        <v>0.34965</v>
+        <v>0.92</v>
       </c>
       <c r="BN206" s="28" t="n"/>
       <c r="BO206" s="28" t="n"/>
@@ -60546,29 +60642,29 @@
       <c r="CR206" s="24" t="n"/>
       <c r="CS206" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="207" ht="36" customHeight="1">
       <c r="A207" s="24" t="inlineStr">
         <is>
-          <t>7e97999756334cef</t>
+          <t>9e543d88f56e46b2</t>
         </is>
       </c>
       <c r="B207" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C207" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T10:30Z</t>
+          <t>2026-08-05T21:00Z</t>
         </is>
       </c>
       <c r="D207" s="24" t="inlineStr">
         <is>
-          <t>961-2026:182098</t>
+          <t>421-2026:182179</t>
         </is>
       </c>
       <c r="E207" s="24" t="inlineStr">
@@ -60578,12 +60674,12 @@
       </c>
       <c r="F207" s="24" t="inlineStr">
         <is>
-          <t>Mona Barthel</t>
+          <t>Maya Joint</t>
         </is>
       </c>
       <c r="G207" s="24" t="inlineStr">
         <is>
-          <t>Martyna Kubka</t>
+          <t>Sorana Cirstea</t>
         </is>
       </c>
       <c r="H207" s="24" t="inlineStr">
@@ -60593,7 +60689,7 @@
       </c>
       <c r="I207" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J207" s="25" t="n"/>
@@ -60603,28 +60699,28 @@
         </is>
       </c>
       <c r="L207" s="26" t="n">
-        <v>156</v>
+        <v>-270</v>
       </c>
       <c r="M207" s="27" t="n">
-        <v>2.56</v>
+        <v>1.37037</v>
       </c>
       <c r="N207" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.72973</v>
       </c>
       <c r="O207" s="28" t="n">
-        <v>0.5849800000000001</v>
+        <v>0.797746</v>
       </c>
       <c r="P207" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q207" s="28" t="n">
-        <v>0.194355</v>
+        <v>0.06801599999999999</v>
       </c>
       <c r="R207" s="26" t="n">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="S207" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T207" s="24" t="inlineStr">
         <is>
@@ -60647,7 +60743,7 @@
       <c r="AD207" s="24" t="n"/>
       <c r="AE207" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Mona Barthel p=0.585 vs Martyna Kubka. Executable ask 0.3900 (aec-wta-markub-monbar-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Maya Joint p=0.202 vs Sorana Cirstea. Executable ask 0.7300 (aec-wta-sorcir-mayjoi-2026-08-04).</t>
         </is>
       </c>
       <c r="AF207" s="31" t="inlineStr">
@@ -60688,32 +60784,32 @@
       </c>
       <c r="AP207" s="24" t="inlineStr">
         <is>
-          <t>Mona Barthel</t>
+          <t>Maya Joint</t>
         </is>
       </c>
       <c r="AQ207" s="24" t="inlineStr">
         <is>
-          <t>Mona Barthel</t>
+          <t>Maya Joint</t>
         </is>
       </c>
       <c r="AR207" s="24" t="inlineStr">
         <is>
-          <t>Mona Barthel</t>
+          <t>Maya Joint</t>
         </is>
       </c>
       <c r="AS207" s="24" t="inlineStr">
         <is>
-          <t>Martyna Kubka</t>
+          <t>Sorana Cirstea</t>
         </is>
       </c>
       <c r="AT207" s="24" t="inlineStr">
         <is>
-          <t>Martyna Kubka</t>
+          <t>Sorana Cirstea</t>
         </is>
       </c>
       <c r="AU207" s="24" t="inlineStr">
         <is>
-          <t>Martyna Kubka</t>
+          <t>Sorana Cirstea</t>
         </is>
       </c>
       <c r="AV207" s="24" t="n"/>
@@ -60766,7 +60862,7 @@
       </c>
       <c r="BH207" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:10.279442Z</t>
+          <t>2026-08-05T13:52:46.461127Z</t>
         </is>
       </c>
       <c r="BI207" s="24" t="inlineStr">
@@ -60776,13 +60872,13 @@
       </c>
       <c r="BJ207" s="25" t="n"/>
       <c r="BK207" s="26" t="n">
-        <v>156</v>
+        <v>-270</v>
       </c>
       <c r="BL207" s="27" t="n">
-        <v>2.56</v>
+        <v>1.37037</v>
       </c>
       <c r="BM207" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.72973</v>
       </c>
       <c r="BN207" s="28" t="n"/>
       <c r="BO207" s="28" t="n"/>
@@ -60824,22 +60920,22 @@
     <row r="208" ht="36" customHeight="1">
       <c r="A208" s="24" t="inlineStr">
         <is>
-          <t>2d3f1b22f36b4ed1</t>
+          <t>d22b9f7c8c9b46ab</t>
         </is>
       </c>
       <c r="B208" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C208" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T10:30Z</t>
+          <t>2026-08-05T21:00Z</t>
         </is>
       </c>
       <c r="D208" s="24" t="inlineStr">
         <is>
-          <t>961-2026:182102</t>
+          <t>421-2026:182214</t>
         </is>
       </c>
       <c r="E208" s="24" t="inlineStr">
@@ -60849,12 +60945,12 @@
       </c>
       <c r="F208" s="24" t="inlineStr">
         <is>
-          <t>Yuan Yue</t>
+          <t>Barbora Krejcikova</t>
         </is>
       </c>
       <c r="G208" s="24" t="inlineStr">
         <is>
-          <t>Elizara Yaneva</t>
+          <t>Liudmila Samsonova</t>
         </is>
       </c>
       <c r="H208" s="24" t="inlineStr">
@@ -60883,19 +60979,19 @@
         <v>0.590164</v>
       </c>
       <c r="O208" s="28" t="n">
-        <v>0.549241</v>
+        <v>0.733479</v>
       </c>
       <c r="P208" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q208" s="28" t="n">
-        <v>-0.040923</v>
+        <v>0.143315</v>
       </c>
       <c r="R208" s="26" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="S208" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T208" s="24" t="inlineStr">
         <is>
@@ -60918,7 +61014,7 @@
       <c r="AD208" s="24" t="n"/>
       <c r="AE208" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Yuan Yue p=0.549 vs Elizara Yaneva. Executable ask 0.5900 (aec-wta-eliyan-yueyua-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Barbora Krejcikova p=0.733 vs Liudmila Samsonova. Executable ask 0.5900 (aec-wta-liusam-barkre-2026-08-06).</t>
         </is>
       </c>
       <c r="AF208" s="31" t="inlineStr">
@@ -60936,7 +61032,7 @@
       <c r="AJ208" s="31" t="n"/>
       <c r="AK208" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL208" s="26" t="n">
@@ -60944,47 +61040,47 @@
       </c>
       <c r="AM208" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN208" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO208" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP208" s="24" t="inlineStr">
         <is>
-          <t>Yuan Yue</t>
+          <t>Barbora Krejcikova</t>
         </is>
       </c>
       <c r="AQ208" s="24" t="inlineStr">
         <is>
-          <t>Yuan Yue</t>
+          <t>Barbora Krejcikova</t>
         </is>
       </c>
       <c r="AR208" s="24" t="inlineStr">
         <is>
-          <t>Yuan Yue</t>
+          <t>Barbora Krejcikova</t>
         </is>
       </c>
       <c r="AS208" s="24" t="inlineStr">
         <is>
-          <t>Elizara Yaneva</t>
+          <t>Liudmila Samsonova</t>
         </is>
       </c>
       <c r="AT208" s="24" t="inlineStr">
         <is>
-          <t>Elizara Yaneva</t>
+          <t>Liudmila Samsonova</t>
         </is>
       </c>
       <c r="AU208" s="24" t="inlineStr">
         <is>
-          <t>Elizara Yaneva</t>
+          <t>Liudmila Samsonova</t>
         </is>
       </c>
       <c r="AV208" s="24" t="n"/>
@@ -61037,7 +61133,7 @@
       </c>
       <c r="BH208" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:10.301877Z</t>
+          <t>2026-08-05T13:52:45.892436Z</t>
         </is>
       </c>
       <c r="BI208" s="24" t="inlineStr">
@@ -61088,29 +61184,29 @@
       <c r="CR208" s="24" t="n"/>
       <c r="CS208" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="209" ht="36" customHeight="1">
       <c r="A209" s="24" t="inlineStr">
         <is>
-          <t>9c5d8619c74348d8</t>
+          <t>093aa60ca2694bb8</t>
         </is>
       </c>
       <c r="B209" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C209" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T12:00Z</t>
+          <t>2026-08-05T23:00Z</t>
         </is>
       </c>
       <c r="D209" s="24" t="inlineStr">
         <is>
-          <t>961-2026:182099</t>
+          <t>421-2026:182170</t>
         </is>
       </c>
       <c r="E209" s="24" t="inlineStr">
@@ -61120,12 +61216,12 @@
       </c>
       <c r="F209" s="24" t="inlineStr">
         <is>
-          <t>Noma Noha Akugue</t>
+          <t>Leylah Fernandez</t>
         </is>
       </c>
       <c r="G209" s="24" t="inlineStr">
         <is>
-          <t>Weronika Falkowska</t>
+          <t>Renata Zarazua</t>
         </is>
       </c>
       <c r="H209" s="24" t="inlineStr">
@@ -61135,7 +61231,7 @@
       </c>
       <c r="I209" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J209" s="25" t="n"/>
@@ -61145,28 +61241,28 @@
         </is>
       </c>
       <c r="L209" s="26" t="n">
-        <v>156</v>
+        <v>-245</v>
       </c>
       <c r="M209" s="27" t="n">
-        <v>2.56</v>
+        <v>1.408163</v>
       </c>
       <c r="N209" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.710145</v>
       </c>
       <c r="O209" s="28" t="n">
-        <v>0.513857</v>
+        <v>0.686095</v>
       </c>
       <c r="P209" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q209" s="28" t="n">
-        <v>0.123232</v>
+        <v>-0.02405</v>
       </c>
       <c r="R209" s="26" t="n">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="S209" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T209" s="24" t="inlineStr">
         <is>
@@ -61189,7 +61285,7 @@
       <c r="AD209" s="24" t="n"/>
       <c r="AE209" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Noma Noha Akugue p=0.486 vs Weronika Falkowska. Executable ask 0.3900 (aec-wta-werfal-nomaku-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Leylah Fernandez p=0.686 vs Renata Zarazua. Executable ask 0.7100 (aec-wta-renzar-leyfer-2026-08-05).</t>
         </is>
       </c>
       <c r="AF209" s="31" t="inlineStr">
@@ -61230,32 +61326,32 @@
       </c>
       <c r="AP209" s="24" t="inlineStr">
         <is>
-          <t>Noma Noha Akugue</t>
+          <t>Leylah Fernandez</t>
         </is>
       </c>
       <c r="AQ209" s="24" t="inlineStr">
         <is>
-          <t>Noma Noha Akugue</t>
+          <t>Leylah Fernandez</t>
         </is>
       </c>
       <c r="AR209" s="24" t="inlineStr">
         <is>
-          <t>Noma Noha Akugue</t>
+          <t>Leylah Fernandez</t>
         </is>
       </c>
       <c r="AS209" s="24" t="inlineStr">
         <is>
-          <t>Weronika Falkowska</t>
+          <t>Renata Zarazua</t>
         </is>
       </c>
       <c r="AT209" s="24" t="inlineStr">
         <is>
-          <t>Weronika Falkowska</t>
+          <t>Renata Zarazua</t>
         </is>
       </c>
       <c r="AU209" s="24" t="inlineStr">
         <is>
-          <t>Weronika Falkowska</t>
+          <t>Renata Zarazua</t>
         </is>
       </c>
       <c r="AV209" s="24" t="n"/>
@@ -61308,7 +61404,7 @@
       </c>
       <c r="BH209" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:10.333050Z</t>
+          <t>2026-08-05T13:52:48.602839Z</t>
         </is>
       </c>
       <c r="BI209" s="24" t="inlineStr">
@@ -61318,13 +61414,13 @@
       </c>
       <c r="BJ209" s="25" t="n"/>
       <c r="BK209" s="26" t="n">
-        <v>156</v>
+        <v>-245</v>
       </c>
       <c r="BL209" s="27" t="n">
-        <v>2.56</v>
+        <v>1.408163</v>
       </c>
       <c r="BM209" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.710145</v>
       </c>
       <c r="BN209" s="28" t="n"/>
       <c r="BO209" s="28" t="n"/>
@@ -61359,29 +61455,29 @@
       <c r="CR209" s="24" t="n"/>
       <c r="CS209" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="210" ht="36" customHeight="1">
       <c r="A210" s="24" t="inlineStr">
         <is>
-          <t>095453c3a20a441e</t>
+          <t>88158a0472534199</t>
         </is>
       </c>
       <c r="B210" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C210" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T12:00Z</t>
+          <t>2026-08-06T00:30Z</t>
         </is>
       </c>
       <c r="D210" s="24" t="inlineStr">
         <is>
-          <t>961-2026:182097</t>
+          <t>421-2026:182216</t>
         </is>
       </c>
       <c r="E210" s="24" t="inlineStr">
@@ -61391,12 +61487,12 @@
       </c>
       <c r="F210" s="24" t="inlineStr">
         <is>
-          <t>Veronika Podrez</t>
+          <t>Alexandra Eala</t>
         </is>
       </c>
       <c r="G210" s="24" t="inlineStr">
         <is>
-          <t>Susan Bandecchi</t>
+          <t>Alycia Parks</t>
         </is>
       </c>
       <c r="H210" s="24" t="inlineStr">
@@ -61416,25 +61512,25 @@
         </is>
       </c>
       <c r="L210" s="26" t="n">
-        <v>-108</v>
+        <v>-456</v>
       </c>
       <c r="M210" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.219298</v>
       </c>
       <c r="N210" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.820144</v>
       </c>
       <c r="O210" s="28" t="n">
-        <v>0.684504</v>
+        <v>0.699863</v>
       </c>
       <c r="P210" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q210" s="28" t="n">
-        <v>0.165273</v>
+        <v>-0.120281</v>
       </c>
       <c r="R210" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S210" s="29" t="n">
         <v>2</v>
@@ -61460,7 +61556,7 @@
       <c r="AD210" s="24" t="n"/>
       <c r="AE210" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Veronika Podrez p=0.685 vs Susan Bandecchi. Executable ask 0.5200 (aec-wta-susban-verpod-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Alexandra Eala p=0.700 vs Alycia Parks. Executable ask 0.8200 (aec-wta-alypar-aleeal-2026-08-04).</t>
         </is>
       </c>
       <c r="AF210" s="31" t="inlineStr">
@@ -61478,7 +61574,7 @@
       <c r="AJ210" s="31" t="n"/>
       <c r="AK210" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL210" s="26" t="n">
@@ -61486,47 +61582,47 @@
       </c>
       <c r="AM210" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN210" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO210" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP210" s="24" t="inlineStr">
         <is>
-          <t>Veronika Podrez</t>
+          <t>Alexandra Eala</t>
         </is>
       </c>
       <c r="AQ210" s="24" t="inlineStr">
         <is>
-          <t>Veronika Podrez</t>
+          <t>Alexandra Eala</t>
         </is>
       </c>
       <c r="AR210" s="24" t="inlineStr">
         <is>
-          <t>Veronika Podrez</t>
+          <t>Alexandra Eala</t>
         </is>
       </c>
       <c r="AS210" s="24" t="inlineStr">
         <is>
-          <t>Susan Bandecchi</t>
+          <t>Alycia Parks</t>
         </is>
       </c>
       <c r="AT210" s="24" t="inlineStr">
         <is>
-          <t>Susan Bandecchi</t>
+          <t>Alycia Parks</t>
         </is>
       </c>
       <c r="AU210" s="24" t="inlineStr">
         <is>
-          <t>Susan Bandecchi</t>
+          <t>Alycia Parks</t>
         </is>
       </c>
       <c r="AV210" s="24" t="n"/>
@@ -61579,7 +61675,7 @@
       </c>
       <c r="BH210" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:10.339946Z</t>
+          <t>2026-08-05T13:52:49.129181Z</t>
         </is>
       </c>
       <c r="BI210" s="24" t="inlineStr">
@@ -61589,13 +61685,13 @@
       </c>
       <c r="BJ210" s="25" t="n"/>
       <c r="BK210" s="26" t="n">
-        <v>-108</v>
+        <v>-456</v>
       </c>
       <c r="BL210" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.219298</v>
       </c>
       <c r="BM210" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.820144</v>
       </c>
       <c r="BN210" s="28" t="n"/>
       <c r="BO210" s="28" t="n"/>
@@ -61630,29 +61726,29 @@
       <c r="CR210" s="24" t="n"/>
       <c r="CS210" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="211" ht="36" customHeight="1">
       <c r="A211" s="24" t="inlineStr">
         <is>
-          <t>9e2cab20b3a746a6</t>
+          <t>2811cb0a91b94e15</t>
         </is>
       </c>
       <c r="B211" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C211" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T14:30Z</t>
+          <t>2026-08-05T15:00Z</t>
         </is>
       </c>
       <c r="D211" s="24" t="inlineStr">
         <is>
-          <t>961-2026:182100</t>
+          <t>421-2026:181726</t>
         </is>
       </c>
       <c r="E211" s="24" t="inlineStr">
@@ -61662,12 +61758,12 @@
       </c>
       <c r="F211" s="24" t="inlineStr">
         <is>
-          <t>Zuzanna Pawlikowska</t>
+          <t>Sebastian Baez</t>
         </is>
       </c>
       <c r="G211" s="24" t="inlineStr">
         <is>
-          <t>Vendula Valdmannova</t>
+          <t>Zizou Bergs</t>
         </is>
       </c>
       <c r="H211" s="24" t="inlineStr">
@@ -61687,22 +61783,22 @@
         </is>
       </c>
       <c r="L211" s="26" t="n">
-        <v>-669</v>
+        <v>-144</v>
       </c>
       <c r="M211" s="27" t="n">
-        <v>1.149477</v>
+        <v>1.694444</v>
       </c>
       <c r="N211" s="28" t="n">
-        <v>0.869961</v>
+        <v>0.590164</v>
       </c>
       <c r="O211" s="28" t="n">
-        <v>0.557355</v>
+        <v>0.52297</v>
       </c>
       <c r="P211" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q211" s="28" t="n">
-        <v>-0.312606</v>
+        <v>-0.067194</v>
       </c>
       <c r="R211" s="26" t="n">
         <v>0</v>
@@ -61731,7 +61827,7 @@
       <c r="AD211" s="24" t="n"/>
       <c r="AE211" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Zuzanna Pawlikowska p=0.443 vs Vendula Valdmannova. Executable ask 0.8700 (aec-wta-venval-zuzpaw-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Sebastian Baez p=0.477 vs Zizou Bergs. Executable ask 0.5900 (aec-atp-zizber-sebbae-2026-08-06).</t>
         </is>
       </c>
       <c r="AF211" s="31" t="inlineStr">
@@ -61767,37 +61863,37 @@
       </c>
       <c r="AO211" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP211" s="24" t="inlineStr">
         <is>
-          <t>Zuzanna Pawlikowska</t>
+          <t>Sebastian Baez</t>
         </is>
       </c>
       <c r="AQ211" s="24" t="inlineStr">
         <is>
-          <t>Zuzanna Pawlikowska</t>
+          <t>Sebastian Baez</t>
         </is>
       </c>
       <c r="AR211" s="24" t="inlineStr">
         <is>
-          <t>Zuzanna Pawlikowska</t>
+          <t>Sebastian Baez</t>
         </is>
       </c>
       <c r="AS211" s="24" t="inlineStr">
         <is>
-          <t>Vendula Valdmannova</t>
+          <t>Zizou Bergs</t>
         </is>
       </c>
       <c r="AT211" s="24" t="inlineStr">
         <is>
-          <t>Vendula Valdmannova</t>
+          <t>Zizou Bergs</t>
         </is>
       </c>
       <c r="AU211" s="24" t="inlineStr">
         <is>
-          <t>Vendula Valdmannova</t>
+          <t>Zizou Bergs</t>
         </is>
       </c>
       <c r="AV211" s="24" t="n"/>
@@ -61850,7 +61946,7 @@
       </c>
       <c r="BH211" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:10.144456Z</t>
+          <t>2026-08-05T13:52:51.067876Z</t>
         </is>
       </c>
       <c r="BI211" s="24" t="inlineStr">
@@ -61860,13 +61956,13 @@
       </c>
       <c r="BJ211" s="25" t="n"/>
       <c r="BK211" s="26" t="n">
-        <v>-669</v>
+        <v>-144</v>
       </c>
       <c r="BL211" s="27" t="n">
-        <v>1.149477</v>
+        <v>1.694444</v>
       </c>
       <c r="BM211" s="28" t="n">
-        <v>0.869961</v>
+        <v>0.590164</v>
       </c>
       <c r="BN211" s="28" t="n"/>
       <c r="BO211" s="28" t="n"/>
@@ -61908,12 +62004,12 @@
     <row r="212" ht="36" customHeight="1">
       <c r="A212" s="24" t="inlineStr">
         <is>
-          <t>322d2ef952df4f82</t>
+          <t>06ce4b5381084b0a</t>
         </is>
       </c>
       <c r="B212" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C212" s="24" t="inlineStr">
@@ -61923,7 +62019,7 @@
       </c>
       <c r="D212" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181726</t>
+          <t>421-2026:181727</t>
         </is>
       </c>
       <c r="E212" s="24" t="inlineStr">
@@ -61933,12 +62029,12 @@
       </c>
       <c r="F212" s="24" t="inlineStr">
         <is>
-          <t>Sebastian Baez</t>
+          <t>Joao Fonseca</t>
         </is>
       </c>
       <c r="G212" s="24" t="inlineStr">
         <is>
-          <t>Zizou Bergs</t>
+          <t>Stefanos Tsitsipas</t>
         </is>
       </c>
       <c r="H212" s="24" t="inlineStr">
@@ -61948,7 +62044,7 @@
       </c>
       <c r="I212" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J212" s="25" t="n"/>
@@ -61958,28 +62054,28 @@
         </is>
       </c>
       <c r="L212" s="26" t="n">
-        <v>-163</v>
+        <v>-150</v>
       </c>
       <c r="M212" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.666667</v>
       </c>
       <c r="N212" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.6</v>
       </c>
       <c r="O212" s="28" t="n">
-        <v>0.52297</v>
+        <v>0.629315</v>
       </c>
       <c r="P212" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q212" s="28" t="n">
-        <v>-0.096802</v>
+        <v>0.029315</v>
       </c>
       <c r="R212" s="26" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="S212" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T212" s="24" t="inlineStr">
         <is>
@@ -62002,7 +62098,7 @@
       <c r="AD212" s="24" t="n"/>
       <c r="AE212" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Sebastian Baez p=0.477 vs Zizou Bergs. Executable ask 0.6200 (aec-atp-zizber-sebbae-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Joao Fonseca p=0.629 vs Stefanos Tsitsipas. Executable ask 0.6000 (aec-atp-stetsi-joafon-2026-08-05).</t>
         </is>
       </c>
       <c r="AF212" s="31" t="inlineStr">
@@ -62043,32 +62139,32 @@
       </c>
       <c r="AP212" s="24" t="inlineStr">
         <is>
-          <t>Sebastian Baez</t>
+          <t>Joao Fonseca</t>
         </is>
       </c>
       <c r="AQ212" s="24" t="inlineStr">
         <is>
-          <t>Sebastian Baez</t>
+          <t>Joao Fonseca</t>
         </is>
       </c>
       <c r="AR212" s="24" t="inlineStr">
         <is>
-          <t>Sebastian Baez</t>
+          <t>Joao Fonseca</t>
         </is>
       </c>
       <c r="AS212" s="24" t="inlineStr">
         <is>
-          <t>Zizou Bergs</t>
+          <t>Stefanos Tsitsipas</t>
         </is>
       </c>
       <c r="AT212" s="24" t="inlineStr">
         <is>
-          <t>Zizou Bergs</t>
+          <t>Stefanos Tsitsipas</t>
         </is>
       </c>
       <c r="AU212" s="24" t="inlineStr">
         <is>
-          <t>Zizou Bergs</t>
+          <t>Stefanos Tsitsipas</t>
         </is>
       </c>
       <c r="AV212" s="24" t="n"/>
@@ -62121,7 +62217,7 @@
       </c>
       <c r="BH212" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:24.697166Z</t>
+          <t>2026-08-05T13:52:53.241498Z</t>
         </is>
       </c>
       <c r="BI212" s="24" t="inlineStr">
@@ -62131,13 +62227,13 @@
       </c>
       <c r="BJ212" s="25" t="n"/>
       <c r="BK212" s="26" t="n">
-        <v>-163</v>
+        <v>-150</v>
       </c>
       <c r="BL212" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.666667</v>
       </c>
       <c r="BM212" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.6</v>
       </c>
       <c r="BN212" s="28" t="n"/>
       <c r="BO212" s="28" t="n"/>
@@ -62172,19 +62268,19 @@
       <c r="CR212" s="24" t="n"/>
       <c r="CS212" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="213" ht="36" customHeight="1">
       <c r="A213" s="24" t="inlineStr">
         <is>
-          <t>89904735d0104fa7</t>
+          <t>a4438889fb85473c</t>
         </is>
       </c>
       <c r="B213" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C213" s="24" t="inlineStr">
@@ -62194,7 +62290,7 @@
       </c>
       <c r="D213" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181727</t>
+          <t>421-2026:181747</t>
         </is>
       </c>
       <c r="E213" s="24" t="inlineStr">
@@ -62204,12 +62300,12 @@
       </c>
       <c r="F213" s="24" t="inlineStr">
         <is>
-          <t>Joao Fonseca</t>
+          <t>Lorenzo Musetti</t>
         </is>
       </c>
       <c r="G213" s="24" t="inlineStr">
         <is>
-          <t>Stefanos Tsitsipas</t>
+          <t>Nicolas Mejia</t>
         </is>
       </c>
       <c r="H213" s="24" t="inlineStr">
@@ -62229,28 +62325,28 @@
         </is>
       </c>
       <c r="L213" s="26" t="n">
-        <v>-133</v>
+        <v>-669</v>
       </c>
       <c r="M213" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.149477</v>
       </c>
       <c r="N213" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.869961</v>
       </c>
       <c r="O213" s="28" t="n">
-        <v>0.629315</v>
+        <v>0.855919</v>
       </c>
       <c r="P213" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q213" s="28" t="n">
-        <v>0.0585</v>
+        <v>-0.014042</v>
       </c>
       <c r="R213" s="26" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="S213" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T213" s="24" t="inlineStr">
         <is>
@@ -62273,7 +62369,7 @@
       <c r="AD213" s="24" t="n"/>
       <c r="AE213" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Joao Fonseca p=0.629 vs Stefanos Tsitsipas. Executable ask 0.5700 (aec-atp-stetsi-joafon-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Lorenzo Musetti p=0.856 vs Nicolas Mejia. Executable ask 0.8700 (aec-atp-nicmej-lormus-2026-08-04).</t>
         </is>
       </c>
       <c r="AF213" s="31" t="inlineStr">
@@ -62291,7 +62387,7 @@
       <c r="AJ213" s="31" t="n"/>
       <c r="AK213" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL213" s="26" t="n">
@@ -62299,47 +62395,47 @@
       </c>
       <c r="AM213" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN213" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO213" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP213" s="24" t="inlineStr">
         <is>
-          <t>Joao Fonseca</t>
+          <t>Lorenzo Musetti</t>
         </is>
       </c>
       <c r="AQ213" s="24" t="inlineStr">
         <is>
-          <t>Joao Fonseca</t>
+          <t>Lorenzo Musetti</t>
         </is>
       </c>
       <c r="AR213" s="24" t="inlineStr">
         <is>
-          <t>Joao Fonseca</t>
+          <t>Lorenzo Musetti</t>
         </is>
       </c>
       <c r="AS213" s="24" t="inlineStr">
         <is>
-          <t>Stefanos Tsitsipas</t>
+          <t>Nicolas Mejia</t>
         </is>
       </c>
       <c r="AT213" s="24" t="inlineStr">
         <is>
-          <t>Stefanos Tsitsipas</t>
+          <t>Nicolas Mejia</t>
         </is>
       </c>
       <c r="AU213" s="24" t="inlineStr">
         <is>
-          <t>Stefanos Tsitsipas</t>
+          <t>Nicolas Mejia</t>
         </is>
       </c>
       <c r="AV213" s="24" t="n"/>
@@ -62392,7 +62488,7 @@
       </c>
       <c r="BH213" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:29.605345Z</t>
+          <t>2026-08-05T13:52:49.651695Z</t>
         </is>
       </c>
       <c r="BI213" s="24" t="inlineStr">
@@ -62402,13 +62498,13 @@
       </c>
       <c r="BJ213" s="25" t="n"/>
       <c r="BK213" s="26" t="n">
-        <v>-133</v>
+        <v>-669</v>
       </c>
       <c r="BL213" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.149477</v>
       </c>
       <c r="BM213" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.869961</v>
       </c>
       <c r="BN213" s="28" t="n"/>
       <c r="BO213" s="28" t="n"/>
@@ -62443,19 +62539,19 @@
       <c r="CR213" s="24" t="n"/>
       <c r="CS213" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="214" ht="36" customHeight="1">
       <c r="A214" s="24" t="inlineStr">
         <is>
-          <t>f8db030794bc45c9</t>
+          <t>6f49f42d5b724416</t>
         </is>
       </c>
       <c r="B214" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C214" s="24" t="inlineStr">
@@ -62465,7 +62561,7 @@
       </c>
       <c r="D214" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181747</t>
+          <t>421-2026:181760</t>
         </is>
       </c>
       <c r="E214" s="24" t="inlineStr">
@@ -62475,12 +62571,12 @@
       </c>
       <c r="F214" s="24" t="inlineStr">
         <is>
-          <t>Lorenzo Musetti</t>
+          <t>Mariano Navone</t>
         </is>
       </c>
       <c r="G214" s="24" t="inlineStr">
         <is>
-          <t>Nicolas Mejia</t>
+          <t>Valentin Vacherot</t>
         </is>
       </c>
       <c r="H214" s="24" t="inlineStr">
@@ -62490,7 +62586,7 @@
       </c>
       <c r="I214" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J214" s="25" t="n"/>
@@ -62500,28 +62596,28 @@
         </is>
       </c>
       <c r="L214" s="26" t="n">
-        <v>-809</v>
+        <v>-156</v>
       </c>
       <c r="M214" s="27" t="n">
-        <v>1.123609</v>
+        <v>1.641026</v>
       </c>
       <c r="N214" s="28" t="n">
-        <v>0.889989</v>
+        <v>0.609375</v>
       </c>
       <c r="O214" s="28" t="n">
-        <v>0.855919</v>
+        <v>0.642108</v>
       </c>
       <c r="P214" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q214" s="28" t="n">
-        <v>-0.03407</v>
+        <v>0.032733</v>
       </c>
       <c r="R214" s="26" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="S214" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T214" s="24" t="inlineStr">
         <is>
@@ -62544,7 +62640,7 @@
       <c r="AD214" s="24" t="n"/>
       <c r="AE214" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Lorenzo Musetti p=0.856 vs Nicolas Mejia. Executable ask 0.8900 (aec-atp-nicmej-lormus-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Mariano Navone p=0.358 vs Valentin Vacherot. Executable ask 0.6100 (aec-atp-valvac-marnav-2026-08-04).</t>
         </is>
       </c>
       <c r="AF214" s="31" t="inlineStr">
@@ -62585,32 +62681,32 @@
       </c>
       <c r="AP214" s="24" t="inlineStr">
         <is>
-          <t>Lorenzo Musetti</t>
+          <t>Mariano Navone</t>
         </is>
       </c>
       <c r="AQ214" s="24" t="inlineStr">
         <is>
-          <t>Lorenzo Musetti</t>
+          <t>Mariano Navone</t>
         </is>
       </c>
       <c r="AR214" s="24" t="inlineStr">
         <is>
-          <t>Lorenzo Musetti</t>
+          <t>Mariano Navone</t>
         </is>
       </c>
       <c r="AS214" s="24" t="inlineStr">
         <is>
-          <t>Nicolas Mejia</t>
+          <t>Valentin Vacherot</t>
         </is>
       </c>
       <c r="AT214" s="24" t="inlineStr">
         <is>
-          <t>Nicolas Mejia</t>
+          <t>Valentin Vacherot</t>
         </is>
       </c>
       <c r="AU214" s="24" t="inlineStr">
         <is>
-          <t>Nicolas Mejia</t>
+          <t>Valentin Vacherot</t>
         </is>
       </c>
       <c r="AV214" s="24" t="n"/>
@@ -62663,7 +62759,7 @@
       </c>
       <c r="BH214" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:26.818383Z</t>
+          <t>2026-08-05T13:52:50.187567Z</t>
         </is>
       </c>
       <c r="BI214" s="24" t="inlineStr">
@@ -62673,13 +62769,13 @@
       </c>
       <c r="BJ214" s="25" t="n"/>
       <c r="BK214" s="26" t="n">
-        <v>-809</v>
+        <v>-156</v>
       </c>
       <c r="BL214" s="27" t="n">
-        <v>1.123609</v>
+        <v>1.641026</v>
       </c>
       <c r="BM214" s="28" t="n">
-        <v>0.889989</v>
+        <v>0.609375</v>
       </c>
       <c r="BN214" s="28" t="n"/>
       <c r="BO214" s="28" t="n"/>
@@ -62714,29 +62810,29 @@
       <c r="CR214" s="24" t="n"/>
       <c r="CS214" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="215" ht="36" customHeight="1">
       <c r="A215" s="24" t="inlineStr">
         <is>
-          <t>e872318348314bac</t>
+          <t>6fbba5bf31bc4f32</t>
         </is>
       </c>
       <c r="B215" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C215" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T15:00Z</t>
+          <t>2026-08-05T16:30Z</t>
         </is>
       </c>
       <c r="D215" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181760</t>
+          <t>421-2026:181724</t>
         </is>
       </c>
       <c r="E215" s="24" t="inlineStr">
@@ -62746,12 +62842,12 @@
       </c>
       <c r="F215" s="24" t="inlineStr">
         <is>
-          <t>Mariano Navone</t>
+          <t>Juan Manuel Cerundolo</t>
         </is>
       </c>
       <c r="G215" s="24" t="inlineStr">
         <is>
-          <t>Valentin Vacherot</t>
+          <t>Casper Ruud</t>
         </is>
       </c>
       <c r="H215" s="24" t="inlineStr">
@@ -62771,28 +62867,28 @@
         </is>
       </c>
       <c r="L215" s="26" t="n">
-        <v>-178</v>
+        <v>-245</v>
       </c>
       <c r="M215" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.408163</v>
       </c>
       <c r="N215" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.710145</v>
       </c>
       <c r="O215" s="28" t="n">
-        <v>0.642108</v>
+        <v>0.735828</v>
       </c>
       <c r="P215" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q215" s="28" t="n">
-        <v>0.00182</v>
+        <v>0.025683</v>
       </c>
       <c r="R215" s="26" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="S215" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T215" s="24" t="inlineStr">
         <is>
@@ -62815,7 +62911,7 @@
       <c r="AD215" s="24" t="n"/>
       <c r="AE215" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Mariano Navone p=0.358 vs Valentin Vacherot. Executable ask 0.6400 (aec-atp-valvac-marnav-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Juan Manuel Cerundolo p=0.264 vs Casper Ruud. Executable ask 0.7100 (aec-atp-casruu-juacer-2026-08-06).</t>
         </is>
       </c>
       <c r="AF215" s="31" t="inlineStr">
@@ -62856,32 +62952,32 @@
       </c>
       <c r="AP215" s="24" t="inlineStr">
         <is>
-          <t>Mariano Navone</t>
+          <t>Juan Manuel Cerundolo</t>
         </is>
       </c>
       <c r="AQ215" s="24" t="inlineStr">
         <is>
-          <t>Mariano Navone</t>
+          <t>Juan Manuel Cerundolo</t>
         </is>
       </c>
       <c r="AR215" s="24" t="inlineStr">
         <is>
-          <t>Mariano Navone</t>
+          <t>Juan Manuel Cerundolo</t>
         </is>
       </c>
       <c r="AS215" s="24" t="inlineStr">
         <is>
-          <t>Valentin Vacherot</t>
+          <t>Casper Ruud</t>
         </is>
       </c>
       <c r="AT215" s="24" t="inlineStr">
         <is>
-          <t>Valentin Vacherot</t>
+          <t>Casper Ruud</t>
         </is>
       </c>
       <c r="AU215" s="24" t="inlineStr">
         <is>
-          <t>Valentin Vacherot</t>
+          <t>Casper Ruud</t>
         </is>
       </c>
       <c r="AV215" s="24" t="n"/>
@@ -62934,7 +63030,7 @@
       </c>
       <c r="BH215" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:25.594765Z</t>
+          <t>2026-08-05T13:52:53.800312Z</t>
         </is>
       </c>
       <c r="BI215" s="24" t="inlineStr">
@@ -62944,13 +63040,13 @@
       </c>
       <c r="BJ215" s="25" t="n"/>
       <c r="BK215" s="26" t="n">
-        <v>-178</v>
+        <v>-245</v>
       </c>
       <c r="BL215" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.408163</v>
       </c>
       <c r="BM215" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.710145</v>
       </c>
       <c r="BN215" s="28" t="n"/>
       <c r="BO215" s="28" t="n"/>
@@ -62992,12 +63088,12 @@
     <row r="216" ht="36" customHeight="1">
       <c r="A216" s="24" t="inlineStr">
         <is>
-          <t>d403b0bb55d74b0b</t>
+          <t>df1b39de672f43dc</t>
         </is>
       </c>
       <c r="B216" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C216" s="24" t="inlineStr">
@@ -63007,7 +63103,7 @@
       </c>
       <c r="D216" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181724</t>
+          <t>421-2026:181732</t>
         </is>
       </c>
       <c r="E216" s="24" t="inlineStr">
@@ -63017,12 +63113,12 @@
       </c>
       <c r="F216" s="24" t="inlineStr">
         <is>
-          <t>Juan Manuel Cerundolo</t>
+          <t>Cameron Norrie</t>
         </is>
       </c>
       <c r="G216" s="24" t="inlineStr">
         <is>
-          <t>Casper Ruud</t>
+          <t>Ignacio Buse</t>
         </is>
       </c>
       <c r="H216" s="24" t="inlineStr">
@@ -63032,7 +63128,7 @@
       </c>
       <c r="I216" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J216" s="25" t="n"/>
@@ -63042,28 +63138,28 @@
         </is>
       </c>
       <c r="L216" s="26" t="n">
-        <v>-257</v>
+        <v>-223</v>
       </c>
       <c r="M216" s="27" t="n">
-        <v>1.389105</v>
+        <v>1.44843</v>
       </c>
       <c r="N216" s="28" t="n">
-        <v>0.719888</v>
+        <v>0.690402</v>
       </c>
       <c r="O216" s="28" t="n">
-        <v>0.735828</v>
+        <v>0.555985</v>
       </c>
       <c r="P216" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q216" s="28" t="n">
-        <v>0.01594</v>
+        <v>-0.134417</v>
       </c>
       <c r="R216" s="26" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S216" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T216" s="24" t="inlineStr">
         <is>
@@ -63086,7 +63182,7 @@
       <c r="AD216" s="24" t="n"/>
       <c r="AE216" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Juan Manuel Cerundolo p=0.264 vs Casper Ruud. Executable ask 0.7200 (aec-atp-casruu-juacer-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Cameron Norrie p=0.556 vs Ignacio Buse. Executable ask 0.6900 (aec-atp-ignbus-camnor-2026-08-05).</t>
         </is>
       </c>
       <c r="AF216" s="31" t="inlineStr">
@@ -63127,32 +63223,32 @@
       </c>
       <c r="AP216" s="24" t="inlineStr">
         <is>
-          <t>Juan Manuel Cerundolo</t>
+          <t>Cameron Norrie</t>
         </is>
       </c>
       <c r="AQ216" s="24" t="inlineStr">
         <is>
-          <t>Juan Manuel Cerundolo</t>
+          <t>Cameron Norrie</t>
         </is>
       </c>
       <c r="AR216" s="24" t="inlineStr">
         <is>
-          <t>Juan Manuel Cerundolo</t>
+          <t>Cameron Norrie</t>
         </is>
       </c>
       <c r="AS216" s="24" t="inlineStr">
         <is>
-          <t>Casper Ruud</t>
+          <t>Ignacio Buse</t>
         </is>
       </c>
       <c r="AT216" s="24" t="inlineStr">
         <is>
-          <t>Casper Ruud</t>
+          <t>Ignacio Buse</t>
         </is>
       </c>
       <c r="AU216" s="24" t="inlineStr">
         <is>
-          <t>Casper Ruud</t>
+          <t>Ignacio Buse</t>
         </is>
       </c>
       <c r="AV216" s="24" t="n"/>
@@ -63205,7 +63301,7 @@
       </c>
       <c r="BH216" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:30.988159Z</t>
+          <t>2026-08-05T13:52:55.689355Z</t>
         </is>
       </c>
       <c r="BI216" s="24" t="inlineStr">
@@ -63215,13 +63311,13 @@
       </c>
       <c r="BJ216" s="25" t="n"/>
       <c r="BK216" s="26" t="n">
-        <v>-257</v>
+        <v>-223</v>
       </c>
       <c r="BL216" s="27" t="n">
-        <v>1.389105</v>
+        <v>1.44843</v>
       </c>
       <c r="BM216" s="28" t="n">
-        <v>0.719888</v>
+        <v>0.690402</v>
       </c>
       <c r="BN216" s="28" t="n"/>
       <c r="BO216" s="28" t="n"/>
@@ -63256,19 +63352,19 @@
       <c r="CR216" s="24" t="n"/>
       <c r="CS216" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="217" ht="36" customHeight="1">
       <c r="A217" s="24" t="inlineStr">
         <is>
-          <t>6c096f6cc3314c23</t>
+          <t>8f935c82cbf44be9</t>
         </is>
       </c>
       <c r="B217" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C217" s="24" t="inlineStr">
@@ -63278,7 +63374,7 @@
       </c>
       <c r="D217" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181732</t>
+          <t>421-2026:181752</t>
         </is>
       </c>
       <c r="E217" s="24" t="inlineStr">
@@ -63288,12 +63384,12 @@
       </c>
       <c r="F217" s="24" t="inlineStr">
         <is>
-          <t>Cameron Norrie</t>
+          <t>Arthur Rinderknech</t>
         </is>
       </c>
       <c r="G217" s="24" t="inlineStr">
         <is>
-          <t>Ignacio Buse</t>
+          <t>Miomir Kecmanovic</t>
         </is>
       </c>
       <c r="H217" s="24" t="inlineStr">
@@ -63313,28 +63409,28 @@
         </is>
       </c>
       <c r="L217" s="26" t="n">
-        <v>-194</v>
+        <v>104</v>
       </c>
       <c r="M217" s="27" t="n">
-        <v>1.515464</v>
+        <v>2.04</v>
       </c>
       <c r="N217" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.490196</v>
       </c>
       <c r="O217" s="28" t="n">
-        <v>0.555985</v>
+        <v>0.5960220000000001</v>
       </c>
       <c r="P217" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q217" s="28" t="n">
-        <v>-0.103879</v>
+        <v>0.105826</v>
       </c>
       <c r="R217" s="26" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="S217" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T217" s="24" t="inlineStr">
         <is>
@@ -63357,7 +63453,7 @@
       <c r="AD217" s="24" t="n"/>
       <c r="AE217" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Cameron Norrie p=0.556 vs Ignacio Buse. Executable ask 0.6600 (aec-atp-ignbus-camnor-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Arthur Rinderknech p=0.596 vs Miomir Kecmanovic. Executable ask 0.4900 (aec-atp-miokec-artrin-2026-08-05).</t>
         </is>
       </c>
       <c r="AF217" s="31" t="inlineStr">
@@ -63375,7 +63471,7 @@
       <c r="AJ217" s="31" t="n"/>
       <c r="AK217" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL217" s="26" t="n">
@@ -63383,47 +63479,47 @@
       </c>
       <c r="AM217" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN217" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO217" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP217" s="24" t="inlineStr">
         <is>
-          <t>Cameron Norrie</t>
+          <t>Arthur Rinderknech</t>
         </is>
       </c>
       <c r="AQ217" s="24" t="inlineStr">
         <is>
-          <t>Cameron Norrie</t>
+          <t>Arthur Rinderknech</t>
         </is>
       </c>
       <c r="AR217" s="24" t="inlineStr">
         <is>
-          <t>Cameron Norrie</t>
+          <t>Arthur Rinderknech</t>
         </is>
       </c>
       <c r="AS217" s="24" t="inlineStr">
         <is>
-          <t>Ignacio Buse</t>
+          <t>Miomir Kecmanovic</t>
         </is>
       </c>
       <c r="AT217" s="24" t="inlineStr">
         <is>
-          <t>Ignacio Buse</t>
+          <t>Miomir Kecmanovic</t>
         </is>
       </c>
       <c r="AU217" s="24" t="inlineStr">
         <is>
-          <t>Ignacio Buse</t>
+          <t>Miomir Kecmanovic</t>
         </is>
       </c>
       <c r="AV217" s="24" t="n"/>
@@ -63476,7 +63572,7 @@
       </c>
       <c r="BH217" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:31.743878Z</t>
+          <t>2026-08-05T13:52:54.747914Z</t>
         </is>
       </c>
       <c r="BI217" s="24" t="inlineStr">
@@ -63486,13 +63582,13 @@
       </c>
       <c r="BJ217" s="25" t="n"/>
       <c r="BK217" s="26" t="n">
-        <v>-194</v>
+        <v>104</v>
       </c>
       <c r="BL217" s="27" t="n">
-        <v>1.515464</v>
+        <v>2.04</v>
       </c>
       <c r="BM217" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.490196</v>
       </c>
       <c r="BN217" s="28" t="n"/>
       <c r="BO217" s="28" t="n"/>
@@ -63527,19 +63623,19 @@
       <c r="CR217" s="24" t="n"/>
       <c r="CS217" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="218" ht="36" customHeight="1">
       <c r="A218" s="24" t="inlineStr">
         <is>
-          <t>27c7bb13584f4d97</t>
+          <t>65d319e932d34bc7</t>
         </is>
       </c>
       <c r="B218" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C218" s="24" t="inlineStr">
@@ -63549,7 +63645,7 @@
       </c>
       <c r="D218" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181752</t>
+          <t>421-2026:181762</t>
         </is>
       </c>
       <c r="E218" s="24" t="inlineStr">
@@ -63559,12 +63655,12 @@
       </c>
       <c r="F218" s="24" t="inlineStr">
         <is>
-          <t>Arthur Rinderknech</t>
+          <t>Arthur Fils</t>
         </is>
       </c>
       <c r="G218" s="24" t="inlineStr">
         <is>
-          <t>Miomir Kecmanovic</t>
+          <t>Zachary Svajda</t>
         </is>
       </c>
       <c r="H218" s="24" t="inlineStr">
@@ -63584,28 +63680,28 @@
         </is>
       </c>
       <c r="L218" s="26" t="n">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="M218" s="27" t="n">
-        <v>2</v>
+        <v>1.333333</v>
       </c>
       <c r="N218" s="28" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="O218" s="28" t="n">
-        <v>0.5960220000000001</v>
+        <v>0.781423</v>
       </c>
       <c r="P218" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q218" s="28" t="n">
-        <v>0.096022</v>
+        <v>0.031423</v>
       </c>
       <c r="R218" s="26" t="n">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="S218" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T218" s="24" t="inlineStr">
         <is>
@@ -63628,7 +63724,7 @@
       <c r="AD218" s="24" t="n"/>
       <c r="AE218" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Arthur Rinderknech p=0.596 vs Miomir Kecmanovic. Executable ask 0.5000 (aec-atp-miokec-artrin-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Arthur Fils p=0.781 vs Zachary Svajda. Executable ask 0.7500 (aec-atp-zacsva-artfil-2026-08-06).</t>
         </is>
       </c>
       <c r="AF218" s="31" t="inlineStr">
@@ -63646,7 +63742,7 @@
       <c r="AJ218" s="31" t="n"/>
       <c r="AK218" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL218" s="26" t="n">
@@ -63654,47 +63750,47 @@
       </c>
       <c r="AM218" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN218" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO218" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP218" s="24" t="inlineStr">
         <is>
-          <t>Arthur Rinderknech</t>
+          <t>Arthur Fils</t>
         </is>
       </c>
       <c r="AQ218" s="24" t="inlineStr">
         <is>
-          <t>Arthur Rinderknech</t>
+          <t>Arthur Fils</t>
         </is>
       </c>
       <c r="AR218" s="24" t="inlineStr">
         <is>
-          <t>Arthur Rinderknech</t>
+          <t>Arthur Fils</t>
         </is>
       </c>
       <c r="AS218" s="24" t="inlineStr">
         <is>
-          <t>Miomir Kecmanovic</t>
+          <t>Zachary Svajda</t>
         </is>
       </c>
       <c r="AT218" s="24" t="inlineStr">
         <is>
-          <t>Miomir Kecmanovic</t>
+          <t>Zachary Svajda</t>
         </is>
       </c>
       <c r="AU218" s="24" t="inlineStr">
         <is>
-          <t>Miomir Kecmanovic</t>
+          <t>Zachary Svajda</t>
         </is>
       </c>
       <c r="AV218" s="24" t="n"/>
@@ -63747,7 +63843,7 @@
       </c>
       <c r="BH218" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:30.228623Z</t>
+          <t>2026-08-05T13:52:56.392048Z</t>
         </is>
       </c>
       <c r="BI218" s="24" t="inlineStr">
@@ -63757,13 +63853,13 @@
       </c>
       <c r="BJ218" s="25" t="n"/>
       <c r="BK218" s="26" t="n">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="BL218" s="27" t="n">
-        <v>2</v>
+        <v>1.333333</v>
       </c>
       <c r="BM218" s="28" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="BN218" s="28" t="n"/>
       <c r="BO218" s="28" t="n"/>
@@ -63805,12 +63901,12 @@
     <row r="219" ht="36" customHeight="1">
       <c r="A219" s="24" t="inlineStr">
         <is>
-          <t>312dfa1e69714149</t>
+          <t>d1a68a02d83f47ba</t>
         </is>
       </c>
       <c r="B219" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C219" s="24" t="inlineStr">
@@ -63820,7 +63916,7 @@
       </c>
       <c r="D219" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181762</t>
+          <t>421-2026:181765</t>
         </is>
       </c>
       <c r="E219" s="24" t="inlineStr">
@@ -63830,12 +63926,12 @@
       </c>
       <c r="F219" s="24" t="inlineStr">
         <is>
-          <t>Arthur Fils</t>
+          <t>Ben Shelton</t>
         </is>
       </c>
       <c r="G219" s="24" t="inlineStr">
         <is>
-          <t>Zachary Svajda</t>
+          <t>Jenson Brooksby</t>
         </is>
       </c>
       <c r="H219" s="24" t="inlineStr">
@@ -63864,16 +63960,16 @@
         <v>0.75</v>
       </c>
       <c r="O219" s="28" t="n">
-        <v>0.781423</v>
+        <v>0.814392</v>
       </c>
       <c r="P219" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q219" s="28" t="n">
-        <v>0.031423</v>
+        <v>0.064392</v>
       </c>
       <c r="R219" s="26" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="S219" s="29" t="n">
         <v>2</v>
@@ -63899,7 +63995,7 @@
       <c r="AD219" s="24" t="n"/>
       <c r="AE219" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Arthur Fils p=0.781 vs Zachary Svajda. Executable ask 0.7500 (aec-atp-zacsva-artfil-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Ben Shelton p=0.814 vs Jenson Brooksby. Executable ask 0.7500 (aec-atp-jenbro-benshe-2026-08-06).</t>
         </is>
       </c>
       <c r="AF219" s="31" t="inlineStr">
@@ -63917,7 +64013,7 @@
       <c r="AJ219" s="31" t="n"/>
       <c r="AK219" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL219" s="26" t="n">
@@ -63925,47 +64021,47 @@
       </c>
       <c r="AM219" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN219" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO219" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP219" s="24" t="inlineStr">
         <is>
-          <t>Arthur Fils</t>
+          <t>Ben Shelton</t>
         </is>
       </c>
       <c r="AQ219" s="24" t="inlineStr">
         <is>
-          <t>Arthur Fils</t>
+          <t>Ben Shelton</t>
         </is>
       </c>
       <c r="AR219" s="24" t="inlineStr">
         <is>
-          <t>Arthur Fils</t>
+          <t>Ben Shelton</t>
         </is>
       </c>
       <c r="AS219" s="24" t="inlineStr">
         <is>
-          <t>Zachary Svajda</t>
+          <t>Jenson Brooksby</t>
         </is>
       </c>
       <c r="AT219" s="24" t="inlineStr">
         <is>
-          <t>Zachary Svajda</t>
+          <t>Jenson Brooksby</t>
         </is>
       </c>
       <c r="AU219" s="24" t="inlineStr">
         <is>
-          <t>Zachary Svajda</t>
+          <t>Jenson Brooksby</t>
         </is>
       </c>
       <c r="AV219" s="24" t="n"/>
@@ -64018,7 +64114,7 @@
       </c>
       <c r="BH219" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:33.623075Z</t>
+          <t>2026-08-05T13:52:57.128543Z</t>
         </is>
       </c>
       <c r="BI219" s="24" t="inlineStr">
@@ -64076,22 +64172,22 @@
     <row r="220" ht="36" customHeight="1">
       <c r="A220" s="24" t="inlineStr">
         <is>
-          <t>d32dcf2b9d644d8f</t>
+          <t>7c401d6233bc4cc2</t>
         </is>
       </c>
       <c r="B220" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C220" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T16:30Z</t>
+          <t>2026-08-05T18:00Z</t>
         </is>
       </c>
       <c r="D220" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181765</t>
+          <t>421-2026:181729</t>
         </is>
       </c>
       <c r="E220" s="24" t="inlineStr">
@@ -64101,12 +64197,12 @@
       </c>
       <c r="F220" s="24" t="inlineStr">
         <is>
-          <t>Ben Shelton</t>
+          <t>Alexei Popyrin</t>
         </is>
       </c>
       <c r="G220" s="24" t="inlineStr">
         <is>
-          <t>Jenson Brooksby</t>
+          <t>Raphael Collignon</t>
         </is>
       </c>
       <c r="H220" s="24" t="inlineStr">
@@ -64116,7 +64212,7 @@
       </c>
       <c r="I220" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J220" s="25" t="n"/>
@@ -64126,28 +64222,28 @@
         </is>
       </c>
       <c r="L220" s="26" t="n">
-        <v>-355</v>
+        <v>-163</v>
       </c>
       <c r="M220" s="27" t="n">
-        <v>1.28169</v>
+        <v>1.613497</v>
       </c>
       <c r="N220" s="28" t="n">
-        <v>0.78022</v>
+        <v>0.619772</v>
       </c>
       <c r="O220" s="28" t="n">
-        <v>0.814392</v>
+        <v>0.57423</v>
       </c>
       <c r="P220" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q220" s="28" t="n">
-        <v>0.034172</v>
+        <v>-0.045542</v>
       </c>
       <c r="R220" s="26" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="S220" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T220" s="24" t="inlineStr">
         <is>
@@ -64170,7 +64266,7 @@
       <c r="AD220" s="24" t="n"/>
       <c r="AE220" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Ben Shelton p=0.814 vs Jenson Brooksby. Executable ask 0.7800 (aec-atp-jenbro-benshe-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Alexei Popyrin p=0.426 vs Raphael Collignon. Executable ask 0.6200 (aec-atp-rapcol-alepop-2026-08-05).</t>
         </is>
       </c>
       <c r="AF220" s="31" t="inlineStr">
@@ -64211,32 +64307,32 @@
       </c>
       <c r="AP220" s="24" t="inlineStr">
         <is>
-          <t>Ben Shelton</t>
+          <t>Alexei Popyrin</t>
         </is>
       </c>
       <c r="AQ220" s="24" t="inlineStr">
         <is>
-          <t>Ben Shelton</t>
+          <t>Alexei Popyrin</t>
         </is>
       </c>
       <c r="AR220" s="24" t="inlineStr">
         <is>
-          <t>Ben Shelton</t>
+          <t>Alexei Popyrin</t>
         </is>
       </c>
       <c r="AS220" s="24" t="inlineStr">
         <is>
-          <t>Jenson Brooksby</t>
+          <t>Raphael Collignon</t>
         </is>
       </c>
       <c r="AT220" s="24" t="inlineStr">
         <is>
-          <t>Jenson Brooksby</t>
+          <t>Raphael Collignon</t>
         </is>
       </c>
       <c r="AU220" s="24" t="inlineStr">
         <is>
-          <t>Jenson Brooksby</t>
+          <t>Raphael Collignon</t>
         </is>
       </c>
       <c r="AV220" s="24" t="n"/>
@@ -64289,7 +64385,7 @@
       </c>
       <c r="BH220" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:32.617133Z</t>
+          <t>2026-08-05T13:52:59.259154Z</t>
         </is>
       </c>
       <c r="BI220" s="24" t="inlineStr">
@@ -64299,13 +64395,13 @@
       </c>
       <c r="BJ220" s="25" t="n"/>
       <c r="BK220" s="26" t="n">
-        <v>-355</v>
+        <v>-163</v>
       </c>
       <c r="BL220" s="27" t="n">
-        <v>1.28169</v>
+        <v>1.613497</v>
       </c>
       <c r="BM220" s="28" t="n">
-        <v>0.78022</v>
+        <v>0.619772</v>
       </c>
       <c r="BN220" s="28" t="n"/>
       <c r="BO220" s="28" t="n"/>
@@ -64340,19 +64436,19 @@
       <c r="CR220" s="24" t="n"/>
       <c r="CS220" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="221" ht="36" customHeight="1">
       <c r="A221" s="24" t="inlineStr">
         <is>
-          <t>d504a64bd6174b3a</t>
+          <t>d1c2c19861b34a70</t>
         </is>
       </c>
       <c r="B221" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C221" s="24" t="inlineStr">
@@ -64362,7 +64458,7 @@
       </c>
       <c r="D221" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181729</t>
+          <t>421-2026:181735</t>
         </is>
       </c>
       <c r="E221" s="24" t="inlineStr">
@@ -64372,12 +64468,12 @@
       </c>
       <c r="F221" s="24" t="inlineStr">
         <is>
-          <t>Alexei Popyrin</t>
+          <t>Taylor Fritz</t>
         </is>
       </c>
       <c r="G221" s="24" t="inlineStr">
         <is>
-          <t>Raphael Collignon</t>
+          <t>Thiago Agustin Tirante</t>
         </is>
       </c>
       <c r="H221" s="24" t="inlineStr">
@@ -64387,7 +64483,7 @@
       </c>
       <c r="I221" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J221" s="25" t="n"/>
@@ -64397,28 +64493,28 @@
         </is>
       </c>
       <c r="L221" s="26" t="n">
-        <v>-178</v>
+        <v>-525</v>
       </c>
       <c r="M221" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.190476</v>
       </c>
       <c r="N221" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.84</v>
       </c>
       <c r="O221" s="28" t="n">
-        <v>0.57423</v>
+        <v>0.744005</v>
       </c>
       <c r="P221" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q221" s="28" t="n">
-        <v>-0.06605800000000001</v>
+        <v>-0.095995</v>
       </c>
       <c r="R221" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S221" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T221" s="24" t="inlineStr">
         <is>
@@ -64441,7 +64537,7 @@
       <c r="AD221" s="24" t="n"/>
       <c r="AE221" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Alexei Popyrin p=0.426 vs Raphael Collignon. Executable ask 0.6400 (aec-atp-rapcol-alepop-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Taylor Fritz p=0.744 vs Thiago Agustin Tirante. Executable ask 0.8400 (aec-atp-thitir-tayfri-2026-08-05).</t>
         </is>
       </c>
       <c r="AF221" s="31" t="inlineStr">
@@ -64482,32 +64578,32 @@
       </c>
       <c r="AP221" s="24" t="inlineStr">
         <is>
-          <t>Alexei Popyrin</t>
+          <t>Taylor Fritz</t>
         </is>
       </c>
       <c r="AQ221" s="24" t="inlineStr">
         <is>
-          <t>Alexei Popyrin</t>
+          <t>Taylor Fritz</t>
         </is>
       </c>
       <c r="AR221" s="24" t="inlineStr">
         <is>
-          <t>Alexei Popyrin</t>
+          <t>Taylor Fritz</t>
         </is>
       </c>
       <c r="AS221" s="24" t="inlineStr">
         <is>
-          <t>Raphael Collignon</t>
+          <t>Thiago Agustin Tirante</t>
         </is>
       </c>
       <c r="AT221" s="24" t="inlineStr">
         <is>
-          <t>Raphael Collignon</t>
+          <t>Thiago Agustin Tirante</t>
         </is>
       </c>
       <c r="AU221" s="24" t="inlineStr">
         <is>
-          <t>Raphael Collignon</t>
+          <t>Thiago Agustin Tirante</t>
         </is>
       </c>
       <c r="AV221" s="24" t="n"/>
@@ -64560,7 +64656,7 @@
       </c>
       <c r="BH221" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:35.776227Z</t>
+          <t>2026-08-05T13:52:57.882845Z</t>
         </is>
       </c>
       <c r="BI221" s="24" t="inlineStr">
@@ -64570,13 +64666,13 @@
       </c>
       <c r="BJ221" s="25" t="n"/>
       <c r="BK221" s="26" t="n">
-        <v>-178</v>
+        <v>-525</v>
       </c>
       <c r="BL221" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.190476</v>
       </c>
       <c r="BM221" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.84</v>
       </c>
       <c r="BN221" s="28" t="n"/>
       <c r="BO221" s="28" t="n"/>
@@ -64618,12 +64714,12 @@
     <row r="222" ht="36" customHeight="1">
       <c r="A222" s="24" t="inlineStr">
         <is>
-          <t>4890a2553285485e</t>
+          <t>ae87c3e4586a400e</t>
         </is>
       </c>
       <c r="B222" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C222" s="24" t="inlineStr">
@@ -64633,7 +64729,7 @@
       </c>
       <c r="D222" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181735</t>
+          <t>421-2026:181743</t>
         </is>
       </c>
       <c r="E222" s="24" t="inlineStr">
@@ -64643,12 +64739,12 @@
       </c>
       <c r="F222" s="24" t="inlineStr">
         <is>
-          <t>Taylor Fritz</t>
+          <t>Alejandro Tabilo</t>
         </is>
       </c>
       <c r="G222" s="24" t="inlineStr">
         <is>
-          <t>Thiago Agustin Tirante</t>
+          <t>Hubert Hurkacz</t>
         </is>
       </c>
       <c r="H222" s="24" t="inlineStr">
@@ -64668,28 +64764,28 @@
         </is>
       </c>
       <c r="L222" s="26" t="n">
-        <v>-614</v>
+        <v>138</v>
       </c>
       <c r="M222" s="27" t="n">
-        <v>1.162866</v>
+        <v>2.38</v>
       </c>
       <c r="N222" s="28" t="n">
-        <v>0.859944</v>
+        <v>0.420168</v>
       </c>
       <c r="O222" s="28" t="n">
-        <v>0.744005</v>
+        <v>0.584869</v>
       </c>
       <c r="P222" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q222" s="28" t="n">
-        <v>-0.115939</v>
+        <v>0.164701</v>
       </c>
       <c r="R222" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S222" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T222" s="24" t="inlineStr">
         <is>
@@ -64712,7 +64808,7 @@
       <c r="AD222" s="24" t="n"/>
       <c r="AE222" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Taylor Fritz p=0.744 vs Thiago Agustin Tirante. Executable ask 0.8600 (aec-atp-thitir-tayfri-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Alejandro Tabilo p=0.585 vs Hubert Hurkacz. Executable ask 0.4200 (aec-atp-hubhur-aletab-2026-08-06).</t>
         </is>
       </c>
       <c r="AF222" s="31" t="inlineStr">
@@ -64730,7 +64826,7 @@
       <c r="AJ222" s="31" t="n"/>
       <c r="AK222" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL222" s="26" t="n">
@@ -64738,47 +64834,47 @@
       </c>
       <c r="AM222" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN222" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO222" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP222" s="24" t="inlineStr">
         <is>
-          <t>Taylor Fritz</t>
+          <t>Alejandro Tabilo</t>
         </is>
       </c>
       <c r="AQ222" s="24" t="inlineStr">
         <is>
-          <t>Taylor Fritz</t>
+          <t>Alejandro Tabilo</t>
         </is>
       </c>
       <c r="AR222" s="24" t="inlineStr">
         <is>
-          <t>Taylor Fritz</t>
+          <t>Alejandro Tabilo</t>
         </is>
       </c>
       <c r="AS222" s="24" t="inlineStr">
         <is>
-          <t>Thiago Agustin Tirante</t>
+          <t>Hubert Hurkacz</t>
         </is>
       </c>
       <c r="AT222" s="24" t="inlineStr">
         <is>
-          <t>Thiago Agustin Tirante</t>
+          <t>Hubert Hurkacz</t>
         </is>
       </c>
       <c r="AU222" s="24" t="inlineStr">
         <is>
-          <t>Thiago Agustin Tirante</t>
+          <t>Hubert Hurkacz</t>
         </is>
       </c>
       <c r="AV222" s="24" t="n"/>
@@ -64831,7 +64927,7 @@
       </c>
       <c r="BH222" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:36.860956Z</t>
+          <t>2026-08-05T13:53:00.150232Z</t>
         </is>
       </c>
       <c r="BI222" s="24" t="inlineStr">
@@ -64841,13 +64937,13 @@
       </c>
       <c r="BJ222" s="25" t="n"/>
       <c r="BK222" s="26" t="n">
-        <v>-614</v>
+        <v>138</v>
       </c>
       <c r="BL222" s="27" t="n">
-        <v>1.162866</v>
+        <v>2.38</v>
       </c>
       <c r="BM222" s="28" t="n">
-        <v>0.859944</v>
+        <v>0.420168</v>
       </c>
       <c r="BN222" s="28" t="n"/>
       <c r="BO222" s="28" t="n"/>
@@ -64882,19 +64978,19 @@
       <c r="CR222" s="24" t="n"/>
       <c r="CS222" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="223" ht="36" customHeight="1">
       <c r="A223" s="24" t="inlineStr">
         <is>
-          <t>b436f00b7ed040d7</t>
+          <t>a0a80605271446cb</t>
         </is>
       </c>
       <c r="B223" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C223" s="24" t="inlineStr">
@@ -64904,7 +65000,7 @@
       </c>
       <c r="D223" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181743</t>
+          <t>421-2026:181749</t>
         </is>
       </c>
       <c r="E223" s="24" t="inlineStr">
@@ -64914,12 +65010,12 @@
       </c>
       <c r="F223" s="24" t="inlineStr">
         <is>
-          <t>Alejandro Tabilo</t>
+          <t>Corentin Moutet</t>
         </is>
       </c>
       <c r="G223" s="24" t="inlineStr">
         <is>
-          <t>Hubert Hurkacz</t>
+          <t>Rafael Jodar</t>
         </is>
       </c>
       <c r="H223" s="24" t="inlineStr">
@@ -64929,7 +65025,7 @@
       </c>
       <c r="I223" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J223" s="25" t="n"/>
@@ -64939,28 +65035,28 @@
         </is>
       </c>
       <c r="L223" s="26" t="n">
-        <v>150</v>
+        <v>-285</v>
       </c>
       <c r="M223" s="27" t="n">
-        <v>2.5</v>
+        <v>1.350877</v>
       </c>
       <c r="N223" s="28" t="n">
-        <v>0.4</v>
+        <v>0.74026</v>
       </c>
       <c r="O223" s="28" t="n">
-        <v>0.584869</v>
+        <v>0.707792</v>
       </c>
       <c r="P223" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q223" s="28" t="n">
-        <v>0.184869</v>
+        <v>-0.032468</v>
       </c>
       <c r="R223" s="26" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="S223" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T223" s="24" t="inlineStr">
         <is>
@@ -64983,7 +65079,7 @@
       <c r="AD223" s="24" t="n"/>
       <c r="AE223" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Alejandro Tabilo p=0.585 vs Hubert Hurkacz. Executable ask 0.4000 (aec-atp-hubhur-aletab-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Corentin Moutet p=0.292 vs Rafael Jodar. Executable ask 0.7400 (aec-atp-rafjod-cormou-2026-08-06).</t>
         </is>
       </c>
       <c r="AF223" s="31" t="inlineStr">
@@ -65001,7 +65097,7 @@
       <c r="AJ223" s="31" t="n"/>
       <c r="AK223" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL223" s="26" t="n">
@@ -65009,47 +65105,47 @@
       </c>
       <c r="AM223" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN223" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO223" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP223" s="24" t="inlineStr">
         <is>
-          <t>Alejandro Tabilo</t>
+          <t>Corentin Moutet</t>
         </is>
       </c>
       <c r="AQ223" s="24" t="inlineStr">
         <is>
-          <t>Alejandro Tabilo</t>
+          <t>Corentin Moutet</t>
         </is>
       </c>
       <c r="AR223" s="24" t="inlineStr">
         <is>
-          <t>Alejandro Tabilo</t>
+          <t>Corentin Moutet</t>
         </is>
       </c>
       <c r="AS223" s="24" t="inlineStr">
         <is>
-          <t>Hubert Hurkacz</t>
+          <t>Rafael Jodar</t>
         </is>
       </c>
       <c r="AT223" s="24" t="inlineStr">
         <is>
-          <t>Hubert Hurkacz</t>
+          <t>Rafael Jodar</t>
         </is>
       </c>
       <c r="AU223" s="24" t="inlineStr">
         <is>
-          <t>Hubert Hurkacz</t>
+          <t>Rafael Jodar</t>
         </is>
       </c>
       <c r="AV223" s="24" t="n"/>
@@ -65102,7 +65198,7 @@
       </c>
       <c r="BH223" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:34.393571Z</t>
+          <t>2026-08-05T13:52:58.279777Z</t>
         </is>
       </c>
       <c r="BI223" s="24" t="inlineStr">
@@ -65112,13 +65208,13 @@
       </c>
       <c r="BJ223" s="25" t="n"/>
       <c r="BK223" s="26" t="n">
-        <v>150</v>
+        <v>-285</v>
       </c>
       <c r="BL223" s="27" t="n">
-        <v>2.5</v>
+        <v>1.350877</v>
       </c>
       <c r="BM223" s="28" t="n">
-        <v>0.4</v>
+        <v>0.74026</v>
       </c>
       <c r="BN223" s="28" t="n"/>
       <c r="BO223" s="28" t="n"/>
@@ -65153,19 +65249,19 @@
       <c r="CR223" s="24" t="n"/>
       <c r="CS223" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="224" ht="36" customHeight="1">
       <c r="A224" s="24" t="inlineStr">
         <is>
-          <t>9ef0e1c9a5cf4237</t>
+          <t>d05b8c0a715b4ecd</t>
         </is>
       </c>
       <c r="B224" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C224" s="24" t="inlineStr">
@@ -65175,7 +65271,7 @@
       </c>
       <c r="D224" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181749</t>
+          <t>421-2026:181750</t>
         </is>
       </c>
       <c r="E224" s="24" t="inlineStr">
@@ -65185,12 +65281,12 @@
       </c>
       <c r="F224" s="24" t="inlineStr">
         <is>
-          <t>Corentin Moutet</t>
+          <t>Tallon Griekspoor</t>
         </is>
       </c>
       <c r="G224" s="24" t="inlineStr">
         <is>
-          <t>Rafael Jodar</t>
+          <t>Alexander Zverev</t>
         </is>
       </c>
       <c r="H224" s="24" t="inlineStr">
@@ -65210,25 +65306,25 @@
         </is>
       </c>
       <c r="L224" s="26" t="n">
-        <v>-285</v>
+        <v>-1011</v>
       </c>
       <c r="M224" s="27" t="n">
-        <v>1.350877</v>
+        <v>1.098912</v>
       </c>
       <c r="N224" s="28" t="n">
-        <v>0.74026</v>
+        <v>0.909991</v>
       </c>
       <c r="O224" s="28" t="n">
-        <v>0.707792</v>
+        <v>0.873265</v>
       </c>
       <c r="P224" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q224" s="28" t="n">
-        <v>-0.032468</v>
+        <v>-0.036726</v>
       </c>
       <c r="R224" s="26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S224" s="29" t="n">
         <v>2</v>
@@ -65254,7 +65350,7 @@
       <c r="AD224" s="24" t="n"/>
       <c r="AE224" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Corentin Moutet p=0.292 vs Rafael Jodar. Executable ask 0.7400 (aec-atp-rafjod-cormou-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Tallon Griekspoor p=0.127 vs Alexander Zverev. Executable ask 0.9100 (aec-atp-alezve-talgri-2026-08-06).</t>
         </is>
       </c>
       <c r="AF224" s="31" t="inlineStr">
@@ -65295,32 +65391,32 @@
       </c>
       <c r="AP224" s="24" t="inlineStr">
         <is>
-          <t>Corentin Moutet</t>
+          <t>Tallon Griekspoor</t>
         </is>
       </c>
       <c r="AQ224" s="24" t="inlineStr">
         <is>
-          <t>Corentin Moutet</t>
+          <t>Tallon Griekspoor</t>
         </is>
       </c>
       <c r="AR224" s="24" t="inlineStr">
         <is>
-          <t>Corentin Moutet</t>
+          <t>Tallon Griekspoor</t>
         </is>
       </c>
       <c r="AS224" s="24" t="inlineStr">
         <is>
-          <t>Rafael Jodar</t>
+          <t>Alexander Zverev</t>
         </is>
       </c>
       <c r="AT224" s="24" t="inlineStr">
         <is>
-          <t>Rafael Jodar</t>
+          <t>Alexander Zverev</t>
         </is>
       </c>
       <c r="AU224" s="24" t="inlineStr">
         <is>
-          <t>Rafael Jodar</t>
+          <t>Alexander Zverev</t>
         </is>
       </c>
       <c r="AV224" s="24" t="n"/>
@@ -65373,7 +65469,7 @@
       </c>
       <c r="BH224" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:34.875536Z</t>
+          <t>2026-08-05T13:52:58.722373Z</t>
         </is>
       </c>
       <c r="BI224" s="24" t="inlineStr">
@@ -65383,13 +65479,13 @@
       </c>
       <c r="BJ224" s="25" t="n"/>
       <c r="BK224" s="26" t="n">
-        <v>-285</v>
+        <v>-1011</v>
       </c>
       <c r="BL224" s="27" t="n">
-        <v>1.350877</v>
+        <v>1.098912</v>
       </c>
       <c r="BM224" s="28" t="n">
-        <v>0.74026</v>
+        <v>0.909991</v>
       </c>
       <c r="BN224" s="28" t="n"/>
       <c r="BO224" s="28" t="n"/>
@@ -65431,22 +65527,22 @@
     <row r="225" ht="36" customHeight="1">
       <c r="A225" s="24" t="inlineStr">
         <is>
-          <t>2ae10845562b465c</t>
+          <t>533fa955ee3a4d7c</t>
         </is>
       </c>
       <c r="B225" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C225" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T18:00Z</t>
+          <t>2026-08-05T19:30Z</t>
         </is>
       </c>
       <c r="D225" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181750</t>
+          <t>421-2026:181741</t>
         </is>
       </c>
       <c r="E225" s="24" t="inlineStr">
@@ -65456,12 +65552,12 @@
       </c>
       <c r="F225" s="24" t="inlineStr">
         <is>
-          <t>Tallon Griekspoor</t>
+          <t>Terence Atmane</t>
         </is>
       </c>
       <c r="G225" s="24" t="inlineStr">
         <is>
-          <t>Alexander Zverev</t>
+          <t>Karen Khachanov</t>
         </is>
       </c>
       <c r="H225" s="24" t="inlineStr">
@@ -65481,28 +65577,28 @@
         </is>
       </c>
       <c r="L225" s="26" t="n">
-        <v>-1011</v>
+        <v>-133</v>
       </c>
       <c r="M225" s="27" t="n">
-        <v>1.098912</v>
+        <v>1.75188</v>
       </c>
       <c r="N225" s="28" t="n">
-        <v>0.909991</v>
+        <v>0.570815</v>
       </c>
       <c r="O225" s="28" t="n">
-        <v>0.873265</v>
+        <v>0.596987</v>
       </c>
       <c r="P225" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q225" s="28" t="n">
-        <v>-0.036726</v>
+        <v>0.026172</v>
       </c>
       <c r="R225" s="26" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="S225" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T225" s="24" t="inlineStr">
         <is>
@@ -65525,7 +65621,7 @@
       <c r="AD225" s="24" t="n"/>
       <c r="AE225" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Tallon Griekspoor p=0.127 vs Alexander Zverev. Executable ask 0.9100 (aec-atp-alezve-talgri-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Terence Atmane p=0.403 vs Karen Khachanov. Executable ask 0.5700 (aec-atp-karkha-teratm-2026-08-06).</t>
         </is>
       </c>
       <c r="AF225" s="31" t="inlineStr">
@@ -65566,32 +65662,32 @@
       </c>
       <c r="AP225" s="24" t="inlineStr">
         <is>
-          <t>Tallon Griekspoor</t>
+          <t>Terence Atmane</t>
         </is>
       </c>
       <c r="AQ225" s="24" t="inlineStr">
         <is>
-          <t>Tallon Griekspoor</t>
+          <t>Terence Atmane</t>
         </is>
       </c>
       <c r="AR225" s="24" t="inlineStr">
         <is>
-          <t>Tallon Griekspoor</t>
+          <t>Terence Atmane</t>
         </is>
       </c>
       <c r="AS225" s="24" t="inlineStr">
         <is>
-          <t>Alexander Zverev</t>
+          <t>Karen Khachanov</t>
         </is>
       </c>
       <c r="AT225" s="24" t="inlineStr">
         <is>
-          <t>Alexander Zverev</t>
+          <t>Karen Khachanov</t>
         </is>
       </c>
       <c r="AU225" s="24" t="inlineStr">
         <is>
-          <t>Alexander Zverev</t>
+          <t>Karen Khachanov</t>
         </is>
       </c>
       <c r="AV225" s="24" t="n"/>
@@ -65644,7 +65740,7 @@
       </c>
       <c r="BH225" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:37.236117Z</t>
+          <t>2026-08-05T13:53:00.889659Z</t>
         </is>
       </c>
       <c r="BI225" s="24" t="inlineStr">
@@ -65654,13 +65750,13 @@
       </c>
       <c r="BJ225" s="25" t="n"/>
       <c r="BK225" s="26" t="n">
-        <v>-1011</v>
+        <v>-133</v>
       </c>
       <c r="BL225" s="27" t="n">
-        <v>1.098912</v>
+        <v>1.75188</v>
       </c>
       <c r="BM225" s="28" t="n">
-        <v>0.909991</v>
+        <v>0.570815</v>
       </c>
       <c r="BN225" s="28" t="n"/>
       <c r="BO225" s="28" t="n"/>
@@ -65695,19 +65791,19 @@
       <c r="CR225" s="24" t="n"/>
       <c r="CS225" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="226" ht="36" customHeight="1">
       <c r="A226" s="24" t="inlineStr">
         <is>
-          <t>28c64cab10954dea</t>
+          <t>6a911424e16e4365</t>
         </is>
       </c>
       <c r="B226" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C226" s="24" t="inlineStr">
@@ -65717,7 +65813,7 @@
       </c>
       <c r="D226" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181741</t>
+          <t>421-2026:181746</t>
         </is>
       </c>
       <c r="E226" s="24" t="inlineStr">
@@ -65727,12 +65823,12 @@
       </c>
       <c r="F226" s="24" t="inlineStr">
         <is>
-          <t>Terence Atmane</t>
+          <t>Matteo Arnaldi</t>
         </is>
       </c>
       <c r="G226" s="24" t="inlineStr">
         <is>
-          <t>Karen Khachanov</t>
+          <t>Fabian Marozsan</t>
         </is>
       </c>
       <c r="H226" s="24" t="inlineStr">
@@ -65752,25 +65848,25 @@
         </is>
       </c>
       <c r="L226" s="26" t="n">
-        <v>-150</v>
+        <v>-133</v>
       </c>
       <c r="M226" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.75188</v>
       </c>
       <c r="N226" s="28" t="n">
-        <v>0.6</v>
+        <v>0.570815</v>
       </c>
       <c r="O226" s="28" t="n">
-        <v>0.596987</v>
+        <v>0.605216</v>
       </c>
       <c r="P226" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q226" s="28" t="n">
-        <v>-0.003013</v>
+        <v>0.034401</v>
       </c>
       <c r="R226" s="26" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="S226" s="29" t="n">
         <v>1.25</v>
@@ -65796,7 +65892,7 @@
       <c r="AD226" s="24" t="n"/>
       <c r="AE226" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Terence Atmane p=0.403 vs Karen Khachanov. Executable ask 0.6000 (aec-atp-karkha-teratm-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Matteo Arnaldi p=0.395 vs Fabian Marozsan. Executable ask 0.5700 (aec-atp-fabmar-matarn-2026-08-05).</t>
         </is>
       </c>
       <c r="AF226" s="31" t="inlineStr">
@@ -65837,32 +65933,32 @@
       </c>
       <c r="AP226" s="24" t="inlineStr">
         <is>
-          <t>Terence Atmane</t>
+          <t>Matteo Arnaldi</t>
         </is>
       </c>
       <c r="AQ226" s="24" t="inlineStr">
         <is>
-          <t>Terence Atmane</t>
+          <t>Matteo Arnaldi</t>
         </is>
       </c>
       <c r="AR226" s="24" t="inlineStr">
         <is>
-          <t>Terence Atmane</t>
+          <t>Matteo Arnaldi</t>
         </is>
       </c>
       <c r="AS226" s="24" t="inlineStr">
         <is>
-          <t>Karen Khachanov</t>
+          <t>Fabian Marozsan</t>
         </is>
       </c>
       <c r="AT226" s="24" t="inlineStr">
         <is>
-          <t>Karen Khachanov</t>
+          <t>Fabian Marozsan</t>
         </is>
       </c>
       <c r="AU226" s="24" t="inlineStr">
         <is>
-          <t>Karen Khachanov</t>
+          <t>Fabian Marozsan</t>
         </is>
       </c>
       <c r="AV226" s="24" t="n"/>
@@ -65915,7 +66011,7 @@
       </c>
       <c r="BH226" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:37.920386Z</t>
+          <t>2026-08-05T13:53:02.385177Z</t>
         </is>
       </c>
       <c r="BI226" s="24" t="inlineStr">
@@ -65925,13 +66021,13 @@
       </c>
       <c r="BJ226" s="25" t="n"/>
       <c r="BK226" s="26" t="n">
-        <v>-150</v>
+        <v>-133</v>
       </c>
       <c r="BL226" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.75188</v>
       </c>
       <c r="BM226" s="28" t="n">
-        <v>0.6</v>
+        <v>0.570815</v>
       </c>
       <c r="BN226" s="28" t="n"/>
       <c r="BO226" s="28" t="n"/>
@@ -65966,19 +66062,19 @@
       <c r="CR226" s="24" t="n"/>
       <c r="CS226" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="227" ht="36" customHeight="1">
       <c r="A227" s="24" t="inlineStr">
         <is>
-          <t>009b032ba67b45cf</t>
+          <t>1d46255c47604bcc</t>
         </is>
       </c>
       <c r="B227" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C227" s="24" t="inlineStr">
@@ -65988,7 +66084,7 @@
       </c>
       <c r="D227" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181746</t>
+          <t>421-2026:181753</t>
         </is>
       </c>
       <c r="E227" s="24" t="inlineStr">
@@ -65998,12 +66094,12 @@
       </c>
       <c r="F227" s="24" t="inlineStr">
         <is>
-          <t>Matteo Arnaldi</t>
+          <t>Francisco Cerundolo</t>
         </is>
       </c>
       <c r="G227" s="24" t="inlineStr">
         <is>
-          <t>Fabian Marozsan</t>
+          <t>Alex Michelsen</t>
         </is>
       </c>
       <c r="H227" s="24" t="inlineStr">
@@ -66013,7 +66109,7 @@
       </c>
       <c r="I227" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J227" s="25" t="n"/>
@@ -66023,28 +66119,28 @@
         </is>
       </c>
       <c r="L227" s="26" t="n">
-        <v>-163</v>
+        <v>150</v>
       </c>
       <c r="M227" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.5</v>
       </c>
       <c r="N227" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.4</v>
       </c>
       <c r="O227" s="28" t="n">
-        <v>0.605216</v>
+        <v>0.657899</v>
       </c>
       <c r="P227" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q227" s="28" t="n">
-        <v>-0.014556</v>
+        <v>0.257899</v>
       </c>
       <c r="R227" s="26" t="n">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="S227" s="29" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="T227" s="24" t="inlineStr">
         <is>
@@ -66067,7 +66163,7 @@
       <c r="AD227" s="24" t="n"/>
       <c r="AE227" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Matteo Arnaldi p=0.395 vs Fabian Marozsan. Executable ask 0.6200 (aec-atp-fabmar-matarn-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Francisco Cerundolo p=0.658 vs Alex Michelsen. Executable ask 0.4000 (aec-atp-alemic-fracer-2026-08-06).</t>
         </is>
       </c>
       <c r="AF227" s="31" t="inlineStr">
@@ -66085,7 +66181,7 @@
       <c r="AJ227" s="31" t="n"/>
       <c r="AK227" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL227" s="26" t="n">
@@ -66093,47 +66189,47 @@
       </c>
       <c r="AM227" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN227" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO227" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP227" s="24" t="inlineStr">
         <is>
-          <t>Matteo Arnaldi</t>
+          <t>Francisco Cerundolo</t>
         </is>
       </c>
       <c r="AQ227" s="24" t="inlineStr">
         <is>
-          <t>Matteo Arnaldi</t>
+          <t>Francisco Cerundolo</t>
         </is>
       </c>
       <c r="AR227" s="24" t="inlineStr">
         <is>
-          <t>Matteo Arnaldi</t>
+          <t>Francisco Cerundolo</t>
         </is>
       </c>
       <c r="AS227" s="24" t="inlineStr">
         <is>
-          <t>Fabian Marozsan</t>
+          <t>Alex Michelsen</t>
         </is>
       </c>
       <c r="AT227" s="24" t="inlineStr">
         <is>
-          <t>Fabian Marozsan</t>
+          <t>Alex Michelsen</t>
         </is>
       </c>
       <c r="AU227" s="24" t="inlineStr">
         <is>
-          <t>Fabian Marozsan</t>
+          <t>Alex Michelsen</t>
         </is>
       </c>
       <c r="AV227" s="24" t="n"/>
@@ -66186,7 +66282,7 @@
       </c>
       <c r="BH227" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:38.565853Z</t>
+          <t>2026-08-05T13:53:01.869933Z</t>
         </is>
       </c>
       <c r="BI227" s="24" t="inlineStr">
@@ -66196,13 +66292,13 @@
       </c>
       <c r="BJ227" s="25" t="n"/>
       <c r="BK227" s="26" t="n">
-        <v>-163</v>
+        <v>150</v>
       </c>
       <c r="BL227" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.5</v>
       </c>
       <c r="BM227" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.4</v>
       </c>
       <c r="BN227" s="28" t="n"/>
       <c r="BO227" s="28" t="n"/>
@@ -66237,29 +66333,29 @@
       <c r="CR227" s="24" t="n"/>
       <c r="CS227" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="228" ht="36" customHeight="1">
       <c r="A228" s="24" t="inlineStr">
         <is>
-          <t>d4b169740ac44c87</t>
+          <t>d1f202cb1bcb4878</t>
         </is>
       </c>
       <c r="B228" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C228" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T19:30Z</t>
+          <t>2026-08-05T21:00Z</t>
         </is>
       </c>
       <c r="D228" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181753</t>
+          <t>421-2026:181719</t>
         </is>
       </c>
       <c r="E228" s="24" t="inlineStr">
@@ -66269,12 +66365,12 @@
       </c>
       <c r="F228" s="24" t="inlineStr">
         <is>
-          <t>Francisco Cerundolo</t>
+          <t>Jakub Mensik</t>
         </is>
       </c>
       <c r="G228" s="24" t="inlineStr">
         <is>
-          <t>Alex Michelsen</t>
+          <t>Jacob Fearnley</t>
         </is>
       </c>
       <c r="H228" s="24" t="inlineStr">
@@ -66294,28 +66390,28 @@
         </is>
       </c>
       <c r="L228" s="26" t="n">
-        <v>150</v>
+        <v>-223</v>
       </c>
       <c r="M228" s="27" t="n">
-        <v>2.5</v>
+        <v>1.44843</v>
       </c>
       <c r="N228" s="28" t="n">
-        <v>0.4</v>
+        <v>0.690402</v>
       </c>
       <c r="O228" s="28" t="n">
-        <v>0.657899</v>
+        <v>0.742792</v>
       </c>
       <c r="P228" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q228" s="28" t="n">
-        <v>0.257899</v>
+        <v>0.05239</v>
       </c>
       <c r="R228" s="26" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="S228" s="29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T228" s="24" t="inlineStr">
         <is>
@@ -66338,7 +66434,7 @@
       <c r="AD228" s="24" t="n"/>
       <c r="AE228" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Francisco Cerundolo p=0.658 vs Alex Michelsen. Executable ask 0.4000 (aec-atp-alemic-fracer-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Jakub Mensik p=0.743 vs Jacob Fearnley. Executable ask 0.6900 (aec-atp-jacfea-jakmen-2026-08-05).</t>
         </is>
       </c>
       <c r="AF228" s="31" t="inlineStr">
@@ -66379,32 +66475,32 @@
       </c>
       <c r="AP228" s="24" t="inlineStr">
         <is>
-          <t>Francisco Cerundolo</t>
+          <t>Jakub Mensik</t>
         </is>
       </c>
       <c r="AQ228" s="24" t="inlineStr">
         <is>
-          <t>Francisco Cerundolo</t>
+          <t>Jakub Mensik</t>
         </is>
       </c>
       <c r="AR228" s="24" t="inlineStr">
         <is>
-          <t>Francisco Cerundolo</t>
+          <t>Jakub Mensik</t>
         </is>
       </c>
       <c r="AS228" s="24" t="inlineStr">
         <is>
-          <t>Alex Michelsen</t>
+          <t>Jacob Fearnley</t>
         </is>
       </c>
       <c r="AT228" s="24" t="inlineStr">
         <is>
-          <t>Alex Michelsen</t>
+          <t>Jacob Fearnley</t>
         </is>
       </c>
       <c r="AU228" s="24" t="inlineStr">
         <is>
-          <t>Alex Michelsen</t>
+          <t>Jacob Fearnley</t>
         </is>
       </c>
       <c r="AV228" s="24" t="n"/>
@@ -66457,7 +66553,7 @@
       </c>
       <c r="BH228" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:39.206890Z</t>
+          <t>2026-08-05T13:53:03.385419Z</t>
         </is>
       </c>
       <c r="BI228" s="24" t="inlineStr">
@@ -66467,13 +66563,13 @@
       </c>
       <c r="BJ228" s="25" t="n"/>
       <c r="BK228" s="26" t="n">
-        <v>150</v>
+        <v>-223</v>
       </c>
       <c r="BL228" s="27" t="n">
-        <v>2.5</v>
+        <v>1.44843</v>
       </c>
       <c r="BM228" s="28" t="n">
-        <v>0.4</v>
+        <v>0.690402</v>
       </c>
       <c r="BN228" s="28" t="n"/>
       <c r="BO228" s="28" t="n"/>
@@ -66515,12 +66611,12 @@
     <row r="229" ht="36" customHeight="1">
       <c r="A229" s="24" t="inlineStr">
         <is>
-          <t>4a915a49c32e4a37</t>
+          <t>f1ade9f253b64dd8</t>
         </is>
       </c>
       <c r="B229" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C229" s="24" t="inlineStr">
@@ -66530,7 +66626,7 @@
       </c>
       <c r="D229" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181719</t>
+          <t>421-2026:181755</t>
         </is>
       </c>
       <c r="E229" s="24" t="inlineStr">
@@ -66540,12 +66636,12 @@
       </c>
       <c r="F229" s="24" t="inlineStr">
         <is>
-          <t>Jakub Mensik</t>
+          <t>Daniel Merida</t>
         </is>
       </c>
       <c r="G229" s="24" t="inlineStr">
         <is>
-          <t>Jacob Fearnley</t>
+          <t>Ugo Humbert</t>
         </is>
       </c>
       <c r="H229" s="24" t="inlineStr">
@@ -66555,7 +66651,7 @@
       </c>
       <c r="I229" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J229" s="25" t="n"/>
@@ -66565,28 +66661,28 @@
         </is>
       </c>
       <c r="L229" s="26" t="n">
-        <v>-257</v>
+        <v>-223</v>
       </c>
       <c r="M229" s="27" t="n">
-        <v>1.389105</v>
+        <v>1.44843</v>
       </c>
       <c r="N229" s="28" t="n">
-        <v>0.719888</v>
+        <v>0.690402</v>
       </c>
       <c r="O229" s="28" t="n">
-        <v>0.742792</v>
+        <v>0.601922</v>
       </c>
       <c r="P229" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q229" s="28" t="n">
-        <v>0.022904</v>
+        <v>-0.08848</v>
       </c>
       <c r="R229" s="26" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="S229" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T229" s="24" t="inlineStr">
         <is>
@@ -66609,7 +66705,7 @@
       <c r="AD229" s="24" t="n"/>
       <c r="AE229" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Jakub Mensik p=0.743 vs Jacob Fearnley. Executable ask 0.7200 (aec-atp-jacfea-jakmen-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Daniel Merida p=0.398 vs Ugo Humbert. Executable ask 0.6900 (aec-atp-ugohum-danagu-2026-08-06).</t>
         </is>
       </c>
       <c r="AF229" s="31" t="inlineStr">
@@ -66650,32 +66746,32 @@
       </c>
       <c r="AP229" s="24" t="inlineStr">
         <is>
-          <t>Jakub Mensik</t>
+          <t>Daniel Merida</t>
         </is>
       </c>
       <c r="AQ229" s="24" t="inlineStr">
         <is>
-          <t>Jakub Mensik</t>
+          <t>Daniel Merida</t>
         </is>
       </c>
       <c r="AR229" s="24" t="inlineStr">
         <is>
-          <t>Jakub Mensik</t>
+          <t>Daniel Merida</t>
         </is>
       </c>
       <c r="AS229" s="24" t="inlineStr">
         <is>
-          <t>Jacob Fearnley</t>
+          <t>Ugo Humbert</t>
         </is>
       </c>
       <c r="AT229" s="24" t="inlineStr">
         <is>
-          <t>Jacob Fearnley</t>
+          <t>Ugo Humbert</t>
         </is>
       </c>
       <c r="AU229" s="24" t="inlineStr">
         <is>
-          <t>Jacob Fearnley</t>
+          <t>Ugo Humbert</t>
         </is>
       </c>
       <c r="AV229" s="24" t="n"/>
@@ -66728,7 +66824,7 @@
       </c>
       <c r="BH229" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:40.271203Z</t>
+          <t>2026-08-05T13:53:03.927987Z</t>
         </is>
       </c>
       <c r="BI229" s="24" t="inlineStr">
@@ -66738,13 +66834,13 @@
       </c>
       <c r="BJ229" s="25" t="n"/>
       <c r="BK229" s="26" t="n">
-        <v>-257</v>
+        <v>-223</v>
       </c>
       <c r="BL229" s="27" t="n">
-        <v>1.389105</v>
+        <v>1.44843</v>
       </c>
       <c r="BM229" s="28" t="n">
-        <v>0.719888</v>
+        <v>0.690402</v>
       </c>
       <c r="BN229" s="28" t="n"/>
       <c r="BO229" s="28" t="n"/>
@@ -66779,29 +66875,29 @@
       <c r="CR229" s="24" t="n"/>
       <c r="CS229" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="230" ht="36" customHeight="1">
       <c r="A230" s="24" t="inlineStr">
         <is>
-          <t>d443095426d44eda</t>
+          <t>be6a07c3603b40b4</t>
         </is>
       </c>
       <c r="B230" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C230" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T21:00Z</t>
+          <t>2026-08-05T22:00Z</t>
         </is>
       </c>
       <c r="D230" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181755</t>
+          <t>421-2026:181733</t>
         </is>
       </c>
       <c r="E230" s="24" t="inlineStr">
@@ -66811,12 +66907,12 @@
       </c>
       <c r="F230" s="24" t="inlineStr">
         <is>
-          <t>Daniel Merida</t>
+          <t>Botic Van De Zandschulp</t>
         </is>
       </c>
       <c r="G230" s="24" t="inlineStr">
         <is>
-          <t>Ugo Humbert</t>
+          <t>Daniil Medvedev</t>
         </is>
       </c>
       <c r="H230" s="24" t="inlineStr">
@@ -66836,28 +66932,28 @@
         </is>
       </c>
       <c r="L230" s="26" t="n">
-        <v>-285</v>
+        <v>-300</v>
       </c>
       <c r="M230" s="27" t="n">
-        <v>1.350877</v>
+        <v>1.333333</v>
       </c>
       <c r="N230" s="28" t="n">
-        <v>0.74026</v>
+        <v>0.75</v>
       </c>
       <c r="O230" s="28" t="n">
-        <v>0.601922</v>
+        <v>0.8122509999999999</v>
       </c>
       <c r="P230" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q230" s="28" t="n">
-        <v>-0.138338</v>
+        <v>0.062251</v>
       </c>
       <c r="R230" s="26" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="S230" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T230" s="24" t="inlineStr">
         <is>
@@ -66880,7 +66976,7 @@
       <c r="AD230" s="24" t="n"/>
       <c r="AE230" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Daniel Merida p=0.398 vs Ugo Humbert. Executable ask 0.7400 (aec-atp-ugohum-danagu-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Botic Van De Zandschulp p=0.188 vs Daniil Medvedev. Executable ask 0.7500 (aec-atp-danmed-botzan-2026-08-06).</t>
         </is>
       </c>
       <c r="AF230" s="31" t="inlineStr">
@@ -66898,7 +66994,7 @@
       <c r="AJ230" s="31" t="n"/>
       <c r="AK230" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL230" s="26" t="n">
@@ -66906,47 +67002,47 @@
       </c>
       <c r="AM230" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN230" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO230" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP230" s="24" t="inlineStr">
         <is>
-          <t>Daniel Merida</t>
+          <t>Botic Van De Zandschulp</t>
         </is>
       </c>
       <c r="AQ230" s="24" t="inlineStr">
         <is>
-          <t>Daniel Merida</t>
+          <t>Botic Van De Zandschulp</t>
         </is>
       </c>
       <c r="AR230" s="24" t="inlineStr">
         <is>
-          <t>Daniel Merida</t>
+          <t>Botic Van De Zandschulp</t>
         </is>
       </c>
       <c r="AS230" s="24" t="inlineStr">
         <is>
-          <t>Ugo Humbert</t>
+          <t>Daniil Medvedev</t>
         </is>
       </c>
       <c r="AT230" s="24" t="inlineStr">
         <is>
-          <t>Ugo Humbert</t>
+          <t>Daniil Medvedev</t>
         </is>
       </c>
       <c r="AU230" s="24" t="inlineStr">
         <is>
-          <t>Ugo Humbert</t>
+          <t>Daniil Medvedev</t>
         </is>
       </c>
       <c r="AV230" s="24" t="n"/>
@@ -66999,7 +67095,7 @@
       </c>
       <c r="BH230" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:41.277534Z</t>
+          <t>2026-08-05T13:53:04.877388Z</t>
         </is>
       </c>
       <c r="BI230" s="24" t="inlineStr">
@@ -67009,13 +67105,13 @@
       </c>
       <c r="BJ230" s="25" t="n"/>
       <c r="BK230" s="26" t="n">
-        <v>-285</v>
+        <v>-300</v>
       </c>
       <c r="BL230" s="27" t="n">
-        <v>1.350877</v>
+        <v>1.333333</v>
       </c>
       <c r="BM230" s="28" t="n">
-        <v>0.74026</v>
+        <v>0.75</v>
       </c>
       <c r="BN230" s="28" t="n"/>
       <c r="BO230" s="28" t="n"/>
@@ -67050,29 +67146,29 @@
       <c r="CR230" s="24" t="n"/>
       <c r="CS230" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="231" ht="36" customHeight="1">
       <c r="A231" s="24" t="inlineStr">
         <is>
-          <t>d6c591707d94465f</t>
+          <t>ce4cbf523a13445e</t>
         </is>
       </c>
       <c r="B231" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C231" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T22:00Z</t>
+          <t>2026-08-05T23:00Z</t>
         </is>
       </c>
       <c r="D231" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181733</t>
+          <t>421-2026:181757</t>
         </is>
       </c>
       <c r="E231" s="24" t="inlineStr">
@@ -67082,12 +67178,12 @@
       </c>
       <c r="F231" s="24" t="inlineStr">
         <is>
-          <t>Botic Van De Zandschulp</t>
+          <t>Felix Auger-Aliassime</t>
         </is>
       </c>
       <c r="G231" s="24" t="inlineStr">
         <is>
-          <t>Daniil Medvedev</t>
+          <t>Titouan Droguet</t>
         </is>
       </c>
       <c r="H231" s="24" t="inlineStr">
@@ -67097,7 +67193,7 @@
       </c>
       <c r="I231" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J231" s="25" t="n"/>
@@ -67107,25 +67203,25 @@
         </is>
       </c>
       <c r="L231" s="26" t="n">
-        <v>-270</v>
+        <v>-400</v>
       </c>
       <c r="M231" s="27" t="n">
-        <v>1.37037</v>
+        <v>1.25</v>
       </c>
       <c r="N231" s="28" t="n">
-        <v>0.72973</v>
+        <v>0.8</v>
       </c>
       <c r="O231" s="28" t="n">
-        <v>0.8122509999999999</v>
+        <v>0.793621</v>
       </c>
       <c r="P231" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q231" s="28" t="n">
-        <v>0.082521</v>
+        <v>-0.006379</v>
       </c>
       <c r="R231" s="26" t="n">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="S231" s="29" t="n">
         <v>2</v>
@@ -67151,7 +67247,7 @@
       <c r="AD231" s="24" t="n"/>
       <c r="AE231" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Botic Van De Zandschulp p=0.188 vs Daniil Medvedev. Executable ask 0.7300 (aec-atp-danmed-botzan-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Felix Auger-Aliassime p=0.794 vs Titouan Droguet. Executable ask 0.8000 (aec-atp-titdro-felaug-2026-08-04).</t>
         </is>
       </c>
       <c r="AF231" s="31" t="inlineStr">
@@ -67169,7 +67265,7 @@
       <c r="AJ231" s="31" t="n"/>
       <c r="AK231" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL231" s="26" t="n">
@@ -67177,47 +67273,47 @@
       </c>
       <c r="AM231" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN231" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO231" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP231" s="24" t="inlineStr">
         <is>
-          <t>Botic Van De Zandschulp</t>
+          <t>Felix Auger-Aliassime</t>
         </is>
       </c>
       <c r="AQ231" s="24" t="inlineStr">
         <is>
-          <t>Botic Van De Zandschulp</t>
+          <t>Felix Auger-Aliassime</t>
         </is>
       </c>
       <c r="AR231" s="24" t="inlineStr">
         <is>
-          <t>Botic Van De Zandschulp</t>
+          <t>Felix Auger-Aliassime</t>
         </is>
       </c>
       <c r="AS231" s="24" t="inlineStr">
         <is>
-          <t>Daniil Medvedev</t>
+          <t>Titouan Droguet</t>
         </is>
       </c>
       <c r="AT231" s="24" t="inlineStr">
         <is>
-          <t>Daniil Medvedev</t>
+          <t>Titouan Droguet</t>
         </is>
       </c>
       <c r="AU231" s="24" t="inlineStr">
         <is>
-          <t>Daniil Medvedev</t>
+          <t>Titouan Droguet</t>
         </is>
       </c>
       <c r="AV231" s="24" t="n"/>
@@ -67270,7 +67366,7 @@
       </c>
       <c r="BH231" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:42.085885Z</t>
+          <t>2026-08-05T13:53:05.620959Z</t>
         </is>
       </c>
       <c r="BI231" s="24" t="inlineStr">
@@ -67280,13 +67376,13 @@
       </c>
       <c r="BJ231" s="25" t="n"/>
       <c r="BK231" s="26" t="n">
-        <v>-270</v>
+        <v>-400</v>
       </c>
       <c r="BL231" s="27" t="n">
-        <v>1.37037</v>
+        <v>1.25</v>
       </c>
       <c r="BM231" s="28" t="n">
-        <v>0.72973</v>
+        <v>0.8</v>
       </c>
       <c r="BN231" s="28" t="n"/>
       <c r="BO231" s="28" t="n"/>
@@ -67321,29 +67417,29 @@
       <c r="CR231" s="24" t="n"/>
       <c r="CS231" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="232" ht="36" customHeight="1">
       <c r="A232" s="24" t="inlineStr">
         <is>
-          <t>d57b1d42fc71481b</t>
+          <t>d53603e490024db2</t>
         </is>
       </c>
       <c r="B232" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C232" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T23:00Z</t>
+          <t>2026-08-05T23:30Z</t>
         </is>
       </c>
       <c r="D232" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181757</t>
+          <t>421-2026:181731</t>
         </is>
       </c>
       <c r="E232" s="24" t="inlineStr">
@@ -67353,12 +67449,12 @@
       </c>
       <c r="F232" s="24" t="inlineStr">
         <is>
-          <t>Felix Auger-Aliassime</t>
+          <t>Tommy Paul</t>
         </is>
       </c>
       <c r="G232" s="24" t="inlineStr">
         <is>
-          <t>Titouan Droguet</t>
+          <t>Valentin Royer</t>
         </is>
       </c>
       <c r="H232" s="24" t="inlineStr">
@@ -67378,25 +67474,25 @@
         </is>
       </c>
       <c r="L232" s="26" t="n">
-        <v>-426</v>
+        <v>-488</v>
       </c>
       <c r="M232" s="27" t="n">
-        <v>1.234742</v>
+        <v>1.204918</v>
       </c>
       <c r="N232" s="28" t="n">
-        <v>0.809886</v>
+        <v>0.829932</v>
       </c>
       <c r="O232" s="28" t="n">
-        <v>0.793621</v>
+        <v>0.855695</v>
       </c>
       <c r="P232" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q232" s="28" t="n">
-        <v>-0.016265</v>
+        <v>0.025763</v>
       </c>
       <c r="R232" s="26" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="S232" s="29" t="n">
         <v>2</v>
@@ -67422,7 +67518,7 @@
       <c r="AD232" s="24" t="n"/>
       <c r="AE232" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Felix Auger-Aliassime p=0.794 vs Titouan Droguet. Executable ask 0.8100 (aec-atp-titdro-felaug-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Tommy Paul p=0.856 vs Valentin Royer. Executable ask 0.8300 (aec-atp-valroy-tompau-2026-08-05).</t>
         </is>
       </c>
       <c r="AF232" s="31" t="inlineStr">
@@ -67463,32 +67559,32 @@
       </c>
       <c r="AP232" s="24" t="inlineStr">
         <is>
-          <t>Felix Auger-Aliassime</t>
+          <t>Tommy Paul</t>
         </is>
       </c>
       <c r="AQ232" s="24" t="inlineStr">
         <is>
-          <t>Felix Auger-Aliassime</t>
+          <t>Tommy Paul</t>
         </is>
       </c>
       <c r="AR232" s="24" t="inlineStr">
         <is>
-          <t>Felix Auger-Aliassime</t>
+          <t>Tommy Paul</t>
         </is>
       </c>
       <c r="AS232" s="24" t="inlineStr">
         <is>
-          <t>Titouan Droguet</t>
+          <t>Valentin Royer</t>
         </is>
       </c>
       <c r="AT232" s="24" t="inlineStr">
         <is>
-          <t>Titouan Droguet</t>
+          <t>Valentin Royer</t>
         </is>
       </c>
       <c r="AU232" s="24" t="inlineStr">
         <is>
-          <t>Titouan Droguet</t>
+          <t>Valentin Royer</t>
         </is>
       </c>
       <c r="AV232" s="24" t="n"/>
@@ -67541,7 +67637,7 @@
       </c>
       <c r="BH232" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:42.843341Z</t>
+          <t>2026-08-05T13:53:06.160349Z</t>
         </is>
       </c>
       <c r="BI232" s="24" t="inlineStr">
@@ -67551,13 +67647,13 @@
       </c>
       <c r="BJ232" s="25" t="n"/>
       <c r="BK232" s="26" t="n">
-        <v>-426</v>
+        <v>-488</v>
       </c>
       <c r="BL232" s="27" t="n">
-        <v>1.234742</v>
+        <v>1.204918</v>
       </c>
       <c r="BM232" s="28" t="n">
-        <v>0.809886</v>
+        <v>0.829932</v>
       </c>
       <c r="BN232" s="28" t="n"/>
       <c r="BO232" s="28" t="n"/>
@@ -67592,29 +67688,29 @@
       <c r="CR232" s="24" t="n"/>
       <c r="CS232" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="233" ht="36" customHeight="1">
       <c r="A233" s="24" t="inlineStr">
         <is>
-          <t>421b8457038f47d8</t>
+          <t>c32c11b1702d4012</t>
         </is>
       </c>
       <c r="B233" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C233" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T23:30Z</t>
+          <t>2026-08-06T00:30Z</t>
         </is>
       </c>
       <c r="D233" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181731</t>
+          <t>421-2026:181761</t>
         </is>
       </c>
       <c r="E233" s="24" t="inlineStr">
@@ -67624,12 +67720,12 @@
       </c>
       <c r="F233" s="24" t="inlineStr">
         <is>
-          <t>Tommy Paul</t>
+          <t>Gael Monfils</t>
         </is>
       </c>
       <c r="G233" s="24" t="inlineStr">
         <is>
-          <t>Valentin Royer</t>
+          <t>Learner Tien</t>
         </is>
       </c>
       <c r="H233" s="24" t="inlineStr">
@@ -67639,7 +67735,7 @@
       </c>
       <c r="I233" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J233" s="25" t="n"/>
@@ -67649,25 +67745,25 @@
         </is>
       </c>
       <c r="L233" s="26" t="n">
-        <v>-426</v>
+        <v>-270</v>
       </c>
       <c r="M233" s="27" t="n">
-        <v>1.234742</v>
+        <v>1.37037</v>
       </c>
       <c r="N233" s="28" t="n">
-        <v>0.809886</v>
+        <v>0.72973</v>
       </c>
       <c r="O233" s="28" t="n">
-        <v>0.855695</v>
+        <v>0.768099</v>
       </c>
       <c r="P233" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q233" s="28" t="n">
-        <v>0.045809</v>
+        <v>0.038369</v>
       </c>
       <c r="R233" s="26" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="S233" s="29" t="n">
         <v>2</v>
@@ -67693,7 +67789,7 @@
       <c r="AD233" s="24" t="n"/>
       <c r="AE233" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Tommy Paul p=0.856 vs Valentin Royer. Executable ask 0.8100 (aec-atp-valroy-tompau-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Gael Monfils p=0.232 vs Learner Tien. Executable ask 0.7300 (aec-atp-leatie-gaemon-2026-08-05).</t>
         </is>
       </c>
       <c r="AF233" s="31" t="inlineStr">
@@ -67734,32 +67830,32 @@
       </c>
       <c r="AP233" s="24" t="inlineStr">
         <is>
-          <t>Tommy Paul</t>
+          <t>Gael Monfils</t>
         </is>
       </c>
       <c r="AQ233" s="24" t="inlineStr">
         <is>
-          <t>Tommy Paul</t>
+          <t>Gael Monfils</t>
         </is>
       </c>
       <c r="AR233" s="24" t="inlineStr">
         <is>
-          <t>Tommy Paul</t>
+          <t>Gael Monfils</t>
         </is>
       </c>
       <c r="AS233" s="24" t="inlineStr">
         <is>
-          <t>Valentin Royer</t>
+          <t>Learner Tien</t>
         </is>
       </c>
       <c r="AT233" s="24" t="inlineStr">
         <is>
-          <t>Valentin Royer</t>
+          <t>Learner Tien</t>
         </is>
       </c>
       <c r="AU233" s="24" t="inlineStr">
         <is>
-          <t>Valentin Royer</t>
+          <t>Learner Tien</t>
         </is>
       </c>
       <c r="AV233" s="24" t="n"/>
@@ -67812,7 +67908,7 @@
       </c>
       <c r="BH233" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:43.926469Z</t>
+          <t>2026-08-05T13:53:06.574351Z</t>
         </is>
       </c>
       <c r="BI233" s="24" t="inlineStr">
@@ -67822,13 +67918,13 @@
       </c>
       <c r="BJ233" s="25" t="n"/>
       <c r="BK233" s="26" t="n">
-        <v>-426</v>
+        <v>-270</v>
       </c>
       <c r="BL233" s="27" t="n">
-        <v>1.234742</v>
+        <v>1.37037</v>
       </c>
       <c r="BM233" s="28" t="n">
-        <v>0.809886</v>
+        <v>0.72973</v>
       </c>
       <c r="BN233" s="28" t="n"/>
       <c r="BO233" s="28" t="n"/>
@@ -67867,277 +67963,6 @@
         </is>
       </c>
     </row>
-    <row r="234" ht="36" customHeight="1">
-      <c r="A234" s="24" t="inlineStr">
-        <is>
-          <t>974b6458e56e43a0</t>
-        </is>
-      </c>
-      <c r="B234" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
-        </is>
-      </c>
-      <c r="C234" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-06T00:30Z</t>
-        </is>
-      </c>
-      <c r="D234" s="24" t="inlineStr">
-        <is>
-          <t>421-2026:181761</t>
-        </is>
-      </c>
-      <c r="E234" s="24" t="inlineStr">
-        <is>
-          <t>TENNIS</t>
-        </is>
-      </c>
-      <c r="F234" s="24" t="inlineStr">
-        <is>
-          <t>Gael Monfils</t>
-        </is>
-      </c>
-      <c r="G234" s="24" t="inlineStr">
-        <is>
-          <t>Learner Tien</t>
-        </is>
-      </c>
-      <c r="H234" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I234" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J234" s="25" t="n"/>
-      <c r="K234" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L234" s="26" t="n">
-        <v>-270</v>
-      </c>
-      <c r="M234" s="27" t="n">
-        <v>1.37037</v>
-      </c>
-      <c r="N234" s="28" t="n">
-        <v>0.72973</v>
-      </c>
-      <c r="O234" s="28" t="n">
-        <v>0.768099</v>
-      </c>
-      <c r="P234" s="28" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Q234" s="28" t="n">
-        <v>0.038369</v>
-      </c>
-      <c r="R234" s="26" t="n">
-        <v>39</v>
-      </c>
-      <c r="S234" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T234" s="24" t="inlineStr">
-        <is>
-          <t>tennis-surface-elo-v1</t>
-        </is>
-      </c>
-      <c r="U234" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V234" s="24" t="n"/>
-      <c r="W234" s="26" t="n"/>
-      <c r="X234" s="26" t="n"/>
-      <c r="Y234" s="25" t="n"/>
-      <c r="Z234" s="26" t="n"/>
-      <c r="AA234" s="28" t="n"/>
-      <c r="AB234" s="28" t="n"/>
-      <c r="AC234" s="30" t="n"/>
-      <c r="AD234" s="24" t="n"/>
-      <c r="AE234" s="31" t="inlineStr">
-        <is>
-          <t>Surface-blended Elo on Hard: Gael Monfils p=0.232 vs Learner Tien. Executable ask 0.7300 (aec-atp-leatie-gaemon-2026-08-05).</t>
-        </is>
-      </c>
-      <c r="AF234" s="31" t="inlineStr">
-        <is>
-          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
-        </is>
-      </c>
-      <c r="AG234" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH234" s="24" t="n"/>
-      <c r="AI234" s="31" t="n"/>
-      <c r="AJ234" s="31" t="n"/>
-      <c r="AK234" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL234" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM234" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN234" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO234" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP234" s="24" t="inlineStr">
-        <is>
-          <t>Gael Monfils</t>
-        </is>
-      </c>
-      <c r="AQ234" s="24" t="inlineStr">
-        <is>
-          <t>Gael Monfils</t>
-        </is>
-      </c>
-      <c r="AR234" s="24" t="inlineStr">
-        <is>
-          <t>Gael Monfils</t>
-        </is>
-      </c>
-      <c r="AS234" s="24" t="inlineStr">
-        <is>
-          <t>Learner Tien</t>
-        </is>
-      </c>
-      <c r="AT234" s="24" t="inlineStr">
-        <is>
-          <t>Learner Tien</t>
-        </is>
-      </c>
-      <c r="AU234" s="24" t="inlineStr">
-        <is>
-          <t>Learner Tien</t>
-        </is>
-      </c>
-      <c r="AV234" s="24" t="n"/>
-      <c r="AW234" s="24" t="n"/>
-      <c r="AX234" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY234" s="24" t="n"/>
-      <c r="AZ234" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA234" s="24" t="inlineStr">
-        <is>
-          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
-        </is>
-      </c>
-      <c r="BB234" s="24" t="inlineStr">
-        <is>
-          <t>surface_blended_elo</t>
-        </is>
-      </c>
-      <c r="BC234" s="24" t="inlineStr">
-        <is>
-          <t>tennis-surface-elo-v1</t>
-        </is>
-      </c>
-      <c r="BD234" s="24" t="inlineStr">
-        <is>
-          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
-        </is>
-      </c>
-      <c r="BE234" s="24" t="inlineStr">
-        <is>
-          <t>tennis-surface-elo-v1</t>
-        </is>
-      </c>
-      <c r="BF234" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG234" s="24" t="inlineStr">
-        <is>
-          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
-        </is>
-      </c>
-      <c r="BH234" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T04:34:44.249516Z</t>
-        </is>
-      </c>
-      <c r="BI234" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ234" s="25" t="n"/>
-      <c r="BK234" s="26" t="n">
-        <v>-270</v>
-      </c>
-      <c r="BL234" s="27" t="n">
-        <v>1.37037</v>
-      </c>
-      <c r="BM234" s="28" t="n">
-        <v>0.72973</v>
-      </c>
-      <c r="BN234" s="28" t="n"/>
-      <c r="BO234" s="28" t="n"/>
-      <c r="BP234" s="25" t="n"/>
-      <c r="BQ234" s="27" t="n"/>
-      <c r="BR234" s="28" t="n"/>
-      <c r="BS234" s="28" t="n"/>
-      <c r="BT234" s="28" t="n"/>
-      <c r="BU234" s="25" t="n"/>
-      <c r="BV234" s="29" t="n"/>
-      <c r="BW234" s="24" t="n"/>
-      <c r="BX234" s="30" t="n"/>
-      <c r="BY234" s="27" t="n"/>
-      <c r="BZ234" s="24" t="n"/>
-      <c r="CA234" s="31" t="n"/>
-      <c r="CB234" s="24" t="n"/>
-      <c r="CC234" s="24" t="n"/>
-      <c r="CD234" s="24" t="n"/>
-      <c r="CE234" s="24" t="n"/>
-      <c r="CF234" s="24" t="n"/>
-      <c r="CG234" s="24" t="n"/>
-      <c r="CH234" s="24" t="n"/>
-      <c r="CI234" s="24" t="n"/>
-      <c r="CJ234" s="24" t="n"/>
-      <c r="CK234" s="24" t="n"/>
-      <c r="CL234" s="24" t="n"/>
-      <c r="CM234" s="24" t="n"/>
-      <c r="CN234" s="24" t="n"/>
-      <c r="CO234" s="24" t="n"/>
-      <c r="CP234" s="24" t="n"/>
-      <c r="CQ234" s="24" t="n"/>
-      <c r="CR234" s="24" t="n"/>
-      <c r="CS234" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/flat/tennis.xlsx
+++ b/data/flat/tennis.xlsx
@@ -71404,18 +71404,38 @@
       </c>
       <c r="U242" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V242" s="24" t="n"/>
-      <c r="W242" s="26" t="n"/>
-      <c r="X242" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V242" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W242" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X242" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y242" s="25" t="n"/>
-      <c r="Z242" s="26" t="n"/>
-      <c r="AA242" s="28" t="n"/>
-      <c r="AB242" s="28" t="n"/>
-      <c r="AC242" s="30" t="n"/>
-      <c r="AD242" s="24" t="n"/>
+      <c r="Z242" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="AA242" s="28" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AB242" s="28" t="n">
+        <v>0.000136</v>
+      </c>
+      <c r="AC242" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD242" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:25:54.678627Z</t>
+        </is>
+      </c>
       <c r="AE242" s="31" t="inlineStr">
         <is>
           <t>Surface-blended Elo on Hard: Alina Korneeva p=0.264 vs Iva Jovic. Executable ask 0.6600 (aec-wta-ivajov-alikor-2026-08-08).</t>
@@ -71428,7 +71448,7 @@
       </c>
       <c r="AG242" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH242" s="24" t="n"/>
@@ -71558,8 +71578,12 @@
       <c r="BN242" s="28" t="n"/>
       <c r="BO242" s="28" t="n"/>
       <c r="BP242" s="25" t="n"/>
-      <c r="BQ242" s="27" t="n"/>
-      <c r="BR242" s="28" t="n"/>
+      <c r="BQ242" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BR242" s="28" t="n">
+        <v>0.66</v>
+      </c>
       <c r="BS242" s="28" t="n"/>
       <c r="BT242" s="28" t="n"/>
       <c r="BU242" s="25" t="n"/>
@@ -71675,18 +71699,38 @@
       </c>
       <c r="U243" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V243" s="24" t="n"/>
-      <c r="W243" s="26" t="n"/>
-      <c r="X243" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V243" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W243" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X243" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y243" s="25" t="n"/>
-      <c r="Z243" s="26" t="n"/>
-      <c r="AA243" s="28" t="n"/>
-      <c r="AB243" s="28" t="n"/>
-      <c r="AC243" s="30" t="n"/>
-      <c r="AD243" s="24" t="n"/>
+      <c r="Z243" s="26" t="n">
+        <v>-525</v>
+      </c>
+      <c r="AA243" s="28" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AB243" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC243" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD243" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:25:57.376319Z</t>
+        </is>
+      </c>
       <c r="AE243" s="31" t="inlineStr">
         <is>
           <t>Surface-blended Elo on Hard: Elena Rybakina p=0.871 vs Ann Li. Executable ask 0.8400 (aec-wta-annli-eleryb-2026-08-06).</t>
@@ -71829,8 +71873,12 @@
       <c r="BN243" s="28" t="n"/>
       <c r="BO243" s="28" t="n"/>
       <c r="BP243" s="25" t="n"/>
-      <c r="BQ243" s="27" t="n"/>
-      <c r="BR243" s="28" t="n"/>
+      <c r="BQ243" s="27" t="n">
+        <v>1.190476</v>
+      </c>
+      <c r="BR243" s="28" t="n">
+        <v>0.84</v>
+      </c>
       <c r="BS243" s="28" t="n"/>
       <c r="BT243" s="28" t="n"/>
       <c r="BU243" s="25" t="n"/>
@@ -72137,7 +72185,7 @@
     <row r="245" ht="36" customHeight="1">
       <c r="A245" s="24" t="inlineStr">
         <is>
-          <t>415b6ad452a34521</t>
+          <t>d775004207ca4eb4</t>
         </is>
       </c>
       <c r="B245" s="24" t="inlineStr">
@@ -72147,12 +72195,12 @@
       </c>
       <c r="C245" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T19:00Z</t>
+          <t>2026-08-07T16:30Z</t>
         </is>
       </c>
       <c r="D245" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182209</t>
+          <t>421-2026:181725</t>
         </is>
       </c>
       <c r="E245" s="24" t="inlineStr">
@@ -72162,12 +72210,12 @@
       </c>
       <c r="F245" s="24" t="inlineStr">
         <is>
-          <t>Liudmila Samsonova</t>
+          <t>Matteo Arnaldi</t>
         </is>
       </c>
       <c r="G245" s="24" t="inlineStr">
         <is>
-          <t>Maya Joint</t>
+          <t>Tallon Griekspoor</t>
         </is>
       </c>
       <c r="H245" s="24" t="inlineStr">
@@ -72177,7 +72225,7 @@
       </c>
       <c r="I245" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J245" s="25" t="n"/>
@@ -72187,22 +72235,22 @@
         </is>
       </c>
       <c r="L245" s="26" t="n">
-        <v>-245</v>
+        <v>-194</v>
       </c>
       <c r="M245" s="27" t="n">
-        <v>1.408163</v>
+        <v>1.515464</v>
       </c>
       <c r="N245" s="28" t="n">
-        <v>0.710145</v>
+        <v>0.659864</v>
       </c>
       <c r="O245" s="28" t="n">
-        <v>0.502257</v>
+        <v>0.577767</v>
       </c>
       <c r="P245" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q245" s="28" t="n">
-        <v>-0.207888</v>
+        <v>-0.082097</v>
       </c>
       <c r="R245" s="26" t="n">
         <v>0</v>
@@ -72231,7 +72279,7 @@
       <c r="AD245" s="24" t="n"/>
       <c r="AE245" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Liudmila Samsonova p=0.502 vs Maya Joint. Executable ask 0.7100 (aec-wta-mayjoi-liusam-2026-08-07).</t>
+          <t>Surface-blended Elo on Hard: Matteo Arnaldi p=0.422 vs Tallon Griekspoor. Executable ask 0.6600 (aec-atp-talgri-matarn-2026-08-06).</t>
         </is>
       </c>
       <c r="AF245" s="31" t="inlineStr">
@@ -72272,32 +72320,32 @@
       </c>
       <c r="AP245" s="24" t="inlineStr">
         <is>
-          <t>Liudmila Samsonova</t>
+          <t>Matteo Arnaldi</t>
         </is>
       </c>
       <c r="AQ245" s="24" t="inlineStr">
         <is>
-          <t>Liudmila Samsonova</t>
+          <t>Matteo Arnaldi</t>
         </is>
       </c>
       <c r="AR245" s="24" t="inlineStr">
         <is>
-          <t>Liudmila Samsonova</t>
+          <t>Matteo Arnaldi</t>
         </is>
       </c>
       <c r="AS245" s="24" t="inlineStr">
         <is>
-          <t>Maya Joint</t>
+          <t>Tallon Griekspoor</t>
         </is>
       </c>
       <c r="AT245" s="24" t="inlineStr">
         <is>
-          <t>Maya Joint</t>
+          <t>Tallon Griekspoor</t>
         </is>
       </c>
       <c r="AU245" s="24" t="inlineStr">
         <is>
-          <t>Maya Joint</t>
+          <t>Tallon Griekspoor</t>
         </is>
       </c>
       <c r="AV245" s="24" t="n"/>
@@ -72350,7 +72398,7 @@
       </c>
       <c r="BH245" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:46.473302Z</t>
+          <t>2026-08-07T15:20:50.125037Z</t>
         </is>
       </c>
       <c r="BI245" s="24" t="inlineStr">
@@ -72360,13 +72408,13 @@
       </c>
       <c r="BJ245" s="25" t="n"/>
       <c r="BK245" s="26" t="n">
-        <v>-245</v>
+        <v>-194</v>
       </c>
       <c r="BL245" s="27" t="n">
-        <v>1.408163</v>
+        <v>1.515464</v>
       </c>
       <c r="BM245" s="28" t="n">
-        <v>0.710145</v>
+        <v>0.659864</v>
       </c>
       <c r="BN245" s="28" t="n"/>
       <c r="BO245" s="28" t="n"/>
@@ -72408,7 +72456,7 @@
     <row r="246" ht="36" customHeight="1">
       <c r="A246" s="24" t="inlineStr">
         <is>
-          <t>e31f7ca6e24a4cd0</t>
+          <t>b21dcf0589eb4d96</t>
         </is>
       </c>
       <c r="B246" s="24" t="inlineStr">
@@ -72418,12 +72466,12 @@
       </c>
       <c r="C246" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T21:00Z</t>
+          <t>2026-08-07T16:30Z</t>
         </is>
       </c>
       <c r="D246" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182205</t>
+          <t>421-2026:181728</t>
         </is>
       </c>
       <c r="E246" s="24" t="inlineStr">
@@ -72433,12 +72481,12 @@
       </c>
       <c r="F246" s="24" t="inlineStr">
         <is>
-          <t>Naomi Osaka</t>
+          <t>Alex Michelsen</t>
         </is>
       </c>
       <c r="G246" s="24" t="inlineStr">
         <is>
-          <t>Elise Mertens</t>
+          <t>Daniel Merida</t>
         </is>
       </c>
       <c r="H246" s="24" t="inlineStr">
@@ -72458,22 +72506,22 @@
         </is>
       </c>
       <c r="L246" s="26" t="n">
-        <v>-213</v>
+        <v>-257</v>
       </c>
       <c r="M246" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.389105</v>
       </c>
       <c r="N246" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.719888</v>
       </c>
       <c r="O246" s="28" t="n">
-        <v>0.633161</v>
+        <v>0.555003</v>
       </c>
       <c r="P246" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q246" s="28" t="n">
-        <v>-0.04735</v>
+        <v>-0.164885</v>
       </c>
       <c r="R246" s="26" t="n">
         <v>0</v>
@@ -72502,7 +72550,7 @@
       <c r="AD246" s="24" t="n"/>
       <c r="AE246" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Naomi Osaka p=0.633 vs Elise Mertens. Executable ask 0.6800 (aec-wta-elimer-naoosa-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Alex Michelsen p=0.555 vs Daniel Merida. Executable ask 0.7200 (aec-atp-danagu-alemic-2026-08-07).</t>
         </is>
       </c>
       <c r="AF246" s="31" t="inlineStr">
@@ -72543,32 +72591,32 @@
       </c>
       <c r="AP246" s="24" t="inlineStr">
         <is>
-          <t>Naomi Osaka</t>
+          <t>Alex Michelsen</t>
         </is>
       </c>
       <c r="AQ246" s="24" t="inlineStr">
         <is>
-          <t>Naomi Osaka</t>
+          <t>Alex Michelsen</t>
         </is>
       </c>
       <c r="AR246" s="24" t="inlineStr">
         <is>
-          <t>Naomi Osaka</t>
+          <t>Alex Michelsen</t>
         </is>
       </c>
       <c r="AS246" s="24" t="inlineStr">
         <is>
-          <t>Elise Mertens</t>
+          <t>Daniel Merida</t>
         </is>
       </c>
       <c r="AT246" s="24" t="inlineStr">
         <is>
-          <t>Elise Mertens</t>
+          <t>Daniel Merida</t>
         </is>
       </c>
       <c r="AU246" s="24" t="inlineStr">
         <is>
-          <t>Elise Mertens</t>
+          <t>Daniel Merida</t>
         </is>
       </c>
       <c r="AV246" s="24" t="n"/>
@@ -72621,7 +72669,7 @@
       </c>
       <c r="BH246" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:46.808324Z</t>
+          <t>2026-08-07T15:20:51.879770Z</t>
         </is>
       </c>
       <c r="BI246" s="24" t="inlineStr">
@@ -72631,13 +72679,13 @@
       </c>
       <c r="BJ246" s="25" t="n"/>
       <c r="BK246" s="26" t="n">
-        <v>-213</v>
+        <v>-257</v>
       </c>
       <c r="BL246" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.389105</v>
       </c>
       <c r="BM246" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.719888</v>
       </c>
       <c r="BN246" s="28" t="n"/>
       <c r="BO246" s="28" t="n"/>
@@ -72679,7 +72727,7 @@
     <row r="247" ht="36" customHeight="1">
       <c r="A247" s="24" t="inlineStr">
         <is>
-          <t>caa9661502a243e0</t>
+          <t>41de4fbbaf384439</t>
         </is>
       </c>
       <c r="B247" s="24" t="inlineStr">
@@ -72689,12 +72737,12 @@
       </c>
       <c r="C247" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T22:30Z</t>
+          <t>2026-08-07T18:00Z</t>
         </is>
       </c>
       <c r="D247" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182212</t>
+          <t>421-2026:181754</t>
         </is>
       </c>
       <c r="E247" s="24" t="inlineStr">
@@ -72704,12 +72752,12 @@
       </c>
       <c r="F247" s="24" t="inlineStr">
         <is>
-          <t>Belinda Bencic</t>
+          <t>Ben Shelton</t>
         </is>
       </c>
       <c r="G247" s="24" t="inlineStr">
         <is>
-          <t>Taylor Townsend</t>
+          <t>Zizou Bergs</t>
         </is>
       </c>
       <c r="H247" s="24" t="inlineStr">
@@ -72738,16 +72786,16 @@
         <v>0.72973</v>
       </c>
       <c r="O247" s="28" t="n">
-        <v>0.67718</v>
+        <v>0.76591</v>
       </c>
       <c r="P247" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q247" s="28" t="n">
-        <v>-0.05255</v>
+        <v>0.03618</v>
       </c>
       <c r="R247" s="26" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="S247" s="29" t="n">
         <v>0</v>
@@ -72773,7 +72821,7 @@
       <c r="AD247" s="24" t="n"/>
       <c r="AE247" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Belinda Bencic p=0.677 vs Taylor Townsend. Executable ask 0.7300 (aec-wta-taytow-belben-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Ben Shelton p=0.766 vs Zizou Bergs. Executable ask 0.7300 (aec-atp-zizber-benshe-2026-08-07).</t>
         </is>
       </c>
       <c r="AF247" s="31" t="inlineStr">
@@ -72814,32 +72862,32 @@
       </c>
       <c r="AP247" s="24" t="inlineStr">
         <is>
-          <t>Belinda Bencic</t>
+          <t>Ben Shelton</t>
         </is>
       </c>
       <c r="AQ247" s="24" t="inlineStr">
         <is>
-          <t>Belinda Bencic</t>
+          <t>Ben Shelton</t>
         </is>
       </c>
       <c r="AR247" s="24" t="inlineStr">
         <is>
-          <t>Belinda Bencic</t>
+          <t>Ben Shelton</t>
         </is>
       </c>
       <c r="AS247" s="24" t="inlineStr">
         <is>
-          <t>Taylor Townsend</t>
+          <t>Zizou Bergs</t>
         </is>
       </c>
       <c r="AT247" s="24" t="inlineStr">
         <is>
-          <t>Taylor Townsend</t>
+          <t>Zizou Bergs</t>
         </is>
       </c>
       <c r="AU247" s="24" t="inlineStr">
         <is>
-          <t>Taylor Townsend</t>
+          <t>Zizou Bergs</t>
         </is>
       </c>
       <c r="AV247" s="24" t="n"/>
@@ -72892,7 +72940,7 @@
       </c>
       <c r="BH247" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:43.289813Z</t>
+          <t>2026-08-07T15:20:53.852912Z</t>
         </is>
       </c>
       <c r="BI247" s="24" t="inlineStr">
@@ -72943,14 +72991,14 @@
       <c r="CR247" s="24" t="n"/>
       <c r="CS247" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="248" ht="36" customHeight="1">
       <c r="A248" s="24" t="inlineStr">
         <is>
-          <t>7926701a054c44a4</t>
+          <t>050eb285078c4188</t>
         </is>
       </c>
       <c r="B248" s="24" t="inlineStr">
@@ -72960,12 +73008,12 @@
       </c>
       <c r="C248" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T23:00Z</t>
+          <t>2026-08-07T18:00Z</t>
         </is>
       </c>
       <c r="D248" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182222</t>
+          <t>421-2026:181771</t>
         </is>
       </c>
       <c r="E248" s="24" t="inlineStr">
@@ -72975,12 +73023,12 @@
       </c>
       <c r="F248" s="24" t="inlineStr">
         <is>
-          <t>Coco Gauff</t>
+          <t>Hubert Hurkacz</t>
         </is>
       </c>
       <c r="G248" s="24" t="inlineStr">
         <is>
-          <t>Maria Sakkari</t>
+          <t>Botic Van De Zandschulp</t>
         </is>
       </c>
       <c r="H248" s="24" t="inlineStr">
@@ -72990,7 +73038,7 @@
       </c>
       <c r="I248" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J248" s="25" t="n"/>
@@ -73000,28 +73048,28 @@
         </is>
       </c>
       <c r="L248" s="26" t="n">
-        <v>-355</v>
+        <v>186</v>
       </c>
       <c r="M248" s="27" t="n">
-        <v>1.28169</v>
+        <v>2.86</v>
       </c>
       <c r="N248" s="28" t="n">
-        <v>0.78022</v>
+        <v>0.34965</v>
       </c>
       <c r="O248" s="28" t="n">
-        <v>0.801053</v>
+        <v>0.505166</v>
       </c>
       <c r="P248" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q248" s="28" t="n">
-        <v>0.020833</v>
+        <v>0.155516</v>
       </c>
       <c r="R248" s="26" t="n">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="S248" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T248" s="24" t="inlineStr">
         <is>
@@ -73044,7 +73092,7 @@
       <c r="AD248" s="24" t="n"/>
       <c r="AE248" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Coco Gauff p=0.801 vs Maria Sakkari. Executable ask 0.7800 (aec-wta-marsak-cocgau-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Hubert Hurkacz p=0.495 vs Botic Van De Zandschulp. Executable ask 0.3500 (aec-atp-botzan-hubhur-2026-08-07).</t>
         </is>
       </c>
       <c r="AF248" s="31" t="inlineStr">
@@ -73080,37 +73128,37 @@
       </c>
       <c r="AO248" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_WINNER_OVERVALUED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP248" s="24" t="inlineStr">
         <is>
-          <t>Coco Gauff</t>
+          <t>Hubert Hurkacz</t>
         </is>
       </c>
       <c r="AQ248" s="24" t="inlineStr">
         <is>
-          <t>Coco Gauff</t>
+          <t>Hubert Hurkacz</t>
         </is>
       </c>
       <c r="AR248" s="24" t="inlineStr">
         <is>
-          <t>Coco Gauff</t>
+          <t>Hubert Hurkacz</t>
         </is>
       </c>
       <c r="AS248" s="24" t="inlineStr">
         <is>
-          <t>Maria Sakkari</t>
+          <t>Botic Van De Zandschulp</t>
         </is>
       </c>
       <c r="AT248" s="24" t="inlineStr">
         <is>
-          <t>Maria Sakkari</t>
+          <t>Botic Van De Zandschulp</t>
         </is>
       </c>
       <c r="AU248" s="24" t="inlineStr">
         <is>
-          <t>Maria Sakkari</t>
+          <t>Botic Van De Zandschulp</t>
         </is>
       </c>
       <c r="AV248" s="24" t="n"/>
@@ -73163,7 +73211,7 @@
       </c>
       <c r="BH248" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:48.128859Z</t>
+          <t>2026-08-07T15:20:52.687497Z</t>
         </is>
       </c>
       <c r="BI248" s="24" t="inlineStr">
@@ -73173,13 +73221,13 @@
       </c>
       <c r="BJ248" s="25" t="n"/>
       <c r="BK248" s="26" t="n">
-        <v>-355</v>
+        <v>186</v>
       </c>
       <c r="BL248" s="27" t="n">
-        <v>1.28169</v>
+        <v>2.86</v>
       </c>
       <c r="BM248" s="28" t="n">
-        <v>0.78022</v>
+        <v>0.34965</v>
       </c>
       <c r="BN248" s="28" t="n"/>
       <c r="BO248" s="28" t="n"/>
@@ -73221,22 +73269,22 @@
     <row r="249" ht="36" customHeight="1">
       <c r="A249" s="24" t="inlineStr">
         <is>
-          <t>d775004207ca4eb4</t>
+          <t>49ecba67b09a4c9c</t>
         </is>
       </c>
       <c r="B249" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:22:21.644116Z</t>
+          <t>2026-08-07T18:29:30.567007Z</t>
         </is>
       </c>
       <c r="C249" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T16:30Z</t>
+          <t>2026-08-07T19:00Z</t>
         </is>
       </c>
       <c r="D249" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181725</t>
+          <t>421-2026:182209</t>
         </is>
       </c>
       <c r="E249" s="24" t="inlineStr">
@@ -73246,12 +73294,12 @@
       </c>
       <c r="F249" s="24" t="inlineStr">
         <is>
-          <t>Matteo Arnaldi</t>
+          <t>Liudmila Samsonova</t>
         </is>
       </c>
       <c r="G249" s="24" t="inlineStr">
         <is>
-          <t>Tallon Griekspoor</t>
+          <t>Maya Joint</t>
         </is>
       </c>
       <c r="H249" s="24" t="inlineStr">
@@ -73261,7 +73309,7 @@
       </c>
       <c r="I249" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J249" s="25" t="n"/>
@@ -73271,22 +73319,22 @@
         </is>
       </c>
       <c r="L249" s="26" t="n">
-        <v>-194</v>
+        <v>-257</v>
       </c>
       <c r="M249" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.389105</v>
       </c>
       <c r="N249" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.719888</v>
       </c>
       <c r="O249" s="28" t="n">
-        <v>0.577767</v>
+        <v>0.502257</v>
       </c>
       <c r="P249" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q249" s="28" t="n">
-        <v>-0.082097</v>
+        <v>-0.217631</v>
       </c>
       <c r="R249" s="26" t="n">
         <v>0</v>
@@ -73315,7 +73363,7 @@
       <c r="AD249" s="24" t="n"/>
       <c r="AE249" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Matteo Arnaldi p=0.422 vs Tallon Griekspoor. Executable ask 0.6600 (aec-atp-talgri-matarn-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Liudmila Samsonova p=0.502 vs Maya Joint. Executable ask 0.7200 (aec-wta-mayjoi-liusam-2026-08-07).</t>
         </is>
       </c>
       <c r="AF249" s="31" t="inlineStr">
@@ -73356,32 +73404,32 @@
       </c>
       <c r="AP249" s="24" t="inlineStr">
         <is>
-          <t>Matteo Arnaldi</t>
+          <t>Liudmila Samsonova</t>
         </is>
       </c>
       <c r="AQ249" s="24" t="inlineStr">
         <is>
-          <t>Matteo Arnaldi</t>
+          <t>Liudmila Samsonova</t>
         </is>
       </c>
       <c r="AR249" s="24" t="inlineStr">
         <is>
-          <t>Matteo Arnaldi</t>
+          <t>Liudmila Samsonova</t>
         </is>
       </c>
       <c r="AS249" s="24" t="inlineStr">
         <is>
-          <t>Tallon Griekspoor</t>
+          <t>Maya Joint</t>
         </is>
       </c>
       <c r="AT249" s="24" t="inlineStr">
         <is>
-          <t>Tallon Griekspoor</t>
+          <t>Maya Joint</t>
         </is>
       </c>
       <c r="AU249" s="24" t="inlineStr">
         <is>
-          <t>Tallon Griekspoor</t>
+          <t>Maya Joint</t>
         </is>
       </c>
       <c r="AV249" s="24" t="n"/>
@@ -73434,7 +73482,7 @@
       </c>
       <c r="BH249" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:50.125037Z</t>
+          <t>2026-08-07T18:28:08.001910Z</t>
         </is>
       </c>
       <c r="BI249" s="24" t="inlineStr">
@@ -73444,13 +73492,13 @@
       </c>
       <c r="BJ249" s="25" t="n"/>
       <c r="BK249" s="26" t="n">
-        <v>-194</v>
+        <v>-257</v>
       </c>
       <c r="BL249" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.389105</v>
       </c>
       <c r="BM249" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.719888</v>
       </c>
       <c r="BN249" s="28" t="n"/>
       <c r="BO249" s="28" t="n"/>
@@ -73492,22 +73540,22 @@
     <row r="250" ht="36" customHeight="1">
       <c r="A250" s="24" t="inlineStr">
         <is>
-          <t>b21dcf0589eb4d96</t>
+          <t>6e962dd1d9bb499f</t>
         </is>
       </c>
       <c r="B250" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:22:21.644116Z</t>
+          <t>2026-08-07T18:29:30.567007Z</t>
         </is>
       </c>
       <c r="C250" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T16:30Z</t>
+          <t>2026-08-07T21:00Z</t>
         </is>
       </c>
       <c r="D250" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181728</t>
+          <t>421-2026:182205</t>
         </is>
       </c>
       <c r="E250" s="24" t="inlineStr">
@@ -73517,12 +73565,12 @@
       </c>
       <c r="F250" s="24" t="inlineStr">
         <is>
-          <t>Alex Michelsen</t>
+          <t>Naomi Osaka</t>
         </is>
       </c>
       <c r="G250" s="24" t="inlineStr">
         <is>
-          <t>Daniel Merida</t>
+          <t>Elise Mertens</t>
         </is>
       </c>
       <c r="H250" s="24" t="inlineStr">
@@ -73542,22 +73590,22 @@
         </is>
       </c>
       <c r="L250" s="26" t="n">
-        <v>-257</v>
+        <v>-223</v>
       </c>
       <c r="M250" s="27" t="n">
-        <v>1.389105</v>
+        <v>1.44843</v>
       </c>
       <c r="N250" s="28" t="n">
-        <v>0.719888</v>
+        <v>0.690402</v>
       </c>
       <c r="O250" s="28" t="n">
-        <v>0.555003</v>
+        <v>0.633161</v>
       </c>
       <c r="P250" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q250" s="28" t="n">
-        <v>-0.164885</v>
+        <v>-0.057241</v>
       </c>
       <c r="R250" s="26" t="n">
         <v>0</v>
@@ -73586,7 +73634,7 @@
       <c r="AD250" s="24" t="n"/>
       <c r="AE250" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Alex Michelsen p=0.555 vs Daniel Merida. Executable ask 0.7200 (aec-atp-danagu-alemic-2026-08-07).</t>
+          <t>Surface-blended Elo on Hard: Naomi Osaka p=0.633 vs Elise Mertens. Executable ask 0.6900 (aec-wta-elimer-naoosa-2026-08-06).</t>
         </is>
       </c>
       <c r="AF250" s="31" t="inlineStr">
@@ -73627,32 +73675,32 @@
       </c>
       <c r="AP250" s="24" t="inlineStr">
         <is>
-          <t>Alex Michelsen</t>
+          <t>Naomi Osaka</t>
         </is>
       </c>
       <c r="AQ250" s="24" t="inlineStr">
         <is>
-          <t>Alex Michelsen</t>
+          <t>Naomi Osaka</t>
         </is>
       </c>
       <c r="AR250" s="24" t="inlineStr">
         <is>
-          <t>Alex Michelsen</t>
+          <t>Naomi Osaka</t>
         </is>
       </c>
       <c r="AS250" s="24" t="inlineStr">
         <is>
-          <t>Daniel Merida</t>
+          <t>Elise Mertens</t>
         </is>
       </c>
       <c r="AT250" s="24" t="inlineStr">
         <is>
-          <t>Daniel Merida</t>
+          <t>Elise Mertens</t>
         </is>
       </c>
       <c r="AU250" s="24" t="inlineStr">
         <is>
-          <t>Daniel Merida</t>
+          <t>Elise Mertens</t>
         </is>
       </c>
       <c r="AV250" s="24" t="n"/>
@@ -73705,7 +73753,7 @@
       </c>
       <c r="BH250" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:51.879770Z</t>
+          <t>2026-08-07T18:28:08.316689Z</t>
         </is>
       </c>
       <c r="BI250" s="24" t="inlineStr">
@@ -73715,13 +73763,13 @@
       </c>
       <c r="BJ250" s="25" t="n"/>
       <c r="BK250" s="26" t="n">
-        <v>-257</v>
+        <v>-223</v>
       </c>
       <c r="BL250" s="27" t="n">
-        <v>1.389105</v>
+        <v>1.44843</v>
       </c>
       <c r="BM250" s="28" t="n">
-        <v>0.719888</v>
+        <v>0.690402</v>
       </c>
       <c r="BN250" s="28" t="n"/>
       <c r="BO250" s="28" t="n"/>
@@ -73763,22 +73811,22 @@
     <row r="251" ht="36" customHeight="1">
       <c r="A251" s="24" t="inlineStr">
         <is>
-          <t>41de4fbbaf384439</t>
+          <t>8be0b8ae7507407a</t>
         </is>
       </c>
       <c r="B251" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:22:21.644116Z</t>
+          <t>2026-08-07T18:29:30.567007Z</t>
         </is>
       </c>
       <c r="C251" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T18:00Z</t>
+          <t>2026-08-07T22:30Z</t>
         </is>
       </c>
       <c r="D251" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181754</t>
+          <t>421-2026:182212</t>
         </is>
       </c>
       <c r="E251" s="24" t="inlineStr">
@@ -73788,12 +73836,12 @@
       </c>
       <c r="F251" s="24" t="inlineStr">
         <is>
-          <t>Ben Shelton</t>
+          <t>Belinda Bencic</t>
         </is>
       </c>
       <c r="G251" s="24" t="inlineStr">
         <is>
-          <t>Zizou Bergs</t>
+          <t>Taylor Townsend</t>
         </is>
       </c>
       <c r="H251" s="24" t="inlineStr">
@@ -73822,16 +73870,16 @@
         <v>0.72973</v>
       </c>
       <c r="O251" s="28" t="n">
-        <v>0.76591</v>
+        <v>0.67718</v>
       </c>
       <c r="P251" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q251" s="28" t="n">
-        <v>0.03618</v>
+        <v>-0.05255</v>
       </c>
       <c r="R251" s="26" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="S251" s="29" t="n">
         <v>0</v>
@@ -73857,7 +73905,7 @@
       <c r="AD251" s="24" t="n"/>
       <c r="AE251" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Ben Shelton p=0.766 vs Zizou Bergs. Executable ask 0.7300 (aec-atp-zizber-benshe-2026-08-07).</t>
+          <t>Surface-blended Elo on Hard: Belinda Bencic p=0.677 vs Taylor Townsend. Executable ask 0.7300 (aec-wta-taytow-belben-2026-08-06).</t>
         </is>
       </c>
       <c r="AF251" s="31" t="inlineStr">
@@ -73898,32 +73946,32 @@
       </c>
       <c r="AP251" s="24" t="inlineStr">
         <is>
-          <t>Ben Shelton</t>
+          <t>Belinda Bencic</t>
         </is>
       </c>
       <c r="AQ251" s="24" t="inlineStr">
         <is>
-          <t>Ben Shelton</t>
+          <t>Belinda Bencic</t>
         </is>
       </c>
       <c r="AR251" s="24" t="inlineStr">
         <is>
-          <t>Ben Shelton</t>
+          <t>Belinda Bencic</t>
         </is>
       </c>
       <c r="AS251" s="24" t="inlineStr">
         <is>
-          <t>Zizou Bergs</t>
+          <t>Taylor Townsend</t>
         </is>
       </c>
       <c r="AT251" s="24" t="inlineStr">
         <is>
-          <t>Zizou Bergs</t>
+          <t>Taylor Townsend</t>
         </is>
       </c>
       <c r="AU251" s="24" t="inlineStr">
         <is>
-          <t>Zizou Bergs</t>
+          <t>Taylor Townsend</t>
         </is>
       </c>
       <c r="AV251" s="24" t="n"/>
@@ -73976,7 +74024,7 @@
       </c>
       <c r="BH251" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:53.852912Z</t>
+          <t>2026-08-07T18:28:06.394719Z</t>
         </is>
       </c>
       <c r="BI251" s="24" t="inlineStr">
@@ -74027,29 +74075,29 @@
       <c r="CR251" s="24" t="n"/>
       <c r="CS251" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="252" ht="36" customHeight="1">
       <c r="A252" s="24" t="inlineStr">
         <is>
-          <t>050eb285078c4188</t>
+          <t>2330d7c29a304b31</t>
         </is>
       </c>
       <c r="B252" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:22:21.644116Z</t>
+          <t>2026-08-07T18:29:30.567007Z</t>
         </is>
       </c>
       <c r="C252" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T18:00Z</t>
+          <t>2026-08-07T23:00Z</t>
         </is>
       </c>
       <c r="D252" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181771</t>
+          <t>421-2026:182222</t>
         </is>
       </c>
       <c r="E252" s="24" t="inlineStr">
@@ -74059,12 +74107,12 @@
       </c>
       <c r="F252" s="24" t="inlineStr">
         <is>
-          <t>Hubert Hurkacz</t>
+          <t>Coco Gauff</t>
         </is>
       </c>
       <c r="G252" s="24" t="inlineStr">
         <is>
-          <t>Botic Van De Zandschulp</t>
+          <t>Maria Sakkari</t>
         </is>
       </c>
       <c r="H252" s="24" t="inlineStr">
@@ -74074,7 +74122,7 @@
       </c>
       <c r="I252" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J252" s="25" t="n"/>
@@ -74084,28 +74132,28 @@
         </is>
       </c>
       <c r="L252" s="26" t="n">
-        <v>186</v>
+        <v>-355</v>
       </c>
       <c r="M252" s="27" t="n">
-        <v>2.86</v>
+        <v>1.28169</v>
       </c>
       <c r="N252" s="28" t="n">
-        <v>0.34965</v>
+        <v>0.78022</v>
       </c>
       <c r="O252" s="28" t="n">
-        <v>0.505166</v>
+        <v>0.801053</v>
       </c>
       <c r="P252" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q252" s="28" t="n">
-        <v>0.155516</v>
+        <v>0.020833</v>
       </c>
       <c r="R252" s="26" t="n">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="S252" s="29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T252" s="24" t="inlineStr">
         <is>
@@ -74128,7 +74176,7 @@
       <c r="AD252" s="24" t="n"/>
       <c r="AE252" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Hubert Hurkacz p=0.495 vs Botic Van De Zandschulp. Executable ask 0.3500 (aec-atp-botzan-hubhur-2026-08-07).</t>
+          <t>Surface-blended Elo on Hard: Coco Gauff p=0.801 vs Maria Sakkari. Executable ask 0.7800 (aec-wta-marsak-cocgau-2026-08-06).</t>
         </is>
       </c>
       <c r="AF252" s="31" t="inlineStr">
@@ -74164,37 +74212,37 @@
       </c>
       <c r="AO252" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
         </is>
       </c>
       <c r="AP252" s="24" t="inlineStr">
         <is>
-          <t>Hubert Hurkacz</t>
+          <t>Coco Gauff</t>
         </is>
       </c>
       <c r="AQ252" s="24" t="inlineStr">
         <is>
-          <t>Hubert Hurkacz</t>
+          <t>Coco Gauff</t>
         </is>
       </c>
       <c r="AR252" s="24" t="inlineStr">
         <is>
-          <t>Hubert Hurkacz</t>
+          <t>Coco Gauff</t>
         </is>
       </c>
       <c r="AS252" s="24" t="inlineStr">
         <is>
-          <t>Botic Van De Zandschulp</t>
+          <t>Maria Sakkari</t>
         </is>
       </c>
       <c r="AT252" s="24" t="inlineStr">
         <is>
-          <t>Botic Van De Zandschulp</t>
+          <t>Maria Sakkari</t>
         </is>
       </c>
       <c r="AU252" s="24" t="inlineStr">
         <is>
-          <t>Botic Van De Zandschulp</t>
+          <t>Maria Sakkari</t>
         </is>
       </c>
       <c r="AV252" s="24" t="n"/>
@@ -74247,7 +74295,7 @@
       </c>
       <c r="BH252" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:52.687497Z</t>
+          <t>2026-08-07T18:28:09.476094Z</t>
         </is>
       </c>
       <c r="BI252" s="24" t="inlineStr">
@@ -74257,13 +74305,13 @@
       </c>
       <c r="BJ252" s="25" t="n"/>
       <c r="BK252" s="26" t="n">
-        <v>186</v>
+        <v>-355</v>
       </c>
       <c r="BL252" s="27" t="n">
-        <v>2.86</v>
+        <v>1.28169</v>
       </c>
       <c r="BM252" s="28" t="n">
-        <v>0.34965</v>
+        <v>0.78022</v>
       </c>
       <c r="BN252" s="28" t="n"/>
       <c r="BO252" s="28" t="n"/>
@@ -74305,12 +74353,12 @@
     <row r="253" ht="36" customHeight="1">
       <c r="A253" s="24" t="inlineStr">
         <is>
-          <t>f7b69e721e1f4e3e</t>
+          <t>dde470785f644644</t>
         </is>
       </c>
       <c r="B253" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:22:21.644116Z</t>
+          <t>2026-08-07T18:29:30.567007Z</t>
         </is>
       </c>
       <c r="C253" s="24" t="inlineStr">
@@ -74355,13 +74403,13 @@
         </is>
       </c>
       <c r="L253" s="26" t="n">
-        <v>-194</v>
+        <v>-203</v>
       </c>
       <c r="M253" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.492611</v>
       </c>
       <c r="N253" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.669967</v>
       </c>
       <c r="O253" s="28" t="n">
         <v>0.706207</v>
@@ -74370,10 +74418,10 @@
         <v>0.05</v>
       </c>
       <c r="Q253" s="28" t="n">
-        <v>0.046343</v>
+        <v>0.03624</v>
       </c>
       <c r="R253" s="26" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="S253" s="29" t="n">
         <v>0</v>
@@ -74399,7 +74447,7 @@
       <c r="AD253" s="24" t="n"/>
       <c r="AE253" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Jakub Mensik p=0.706 vs Terence Atmane. Executable ask 0.6600 (aec-atp-teratm-jakmen-2026-08-07).</t>
+          <t>Surface-blended Elo on Hard: Jakub Mensik p=0.706 vs Terence Atmane. Executable ask 0.6700 (aec-atp-teratm-jakmen-2026-08-07).</t>
         </is>
       </c>
       <c r="AF253" s="31" t="inlineStr">
@@ -74518,7 +74566,7 @@
       </c>
       <c r="BH253" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:54.631361Z</t>
+          <t>2026-08-07T18:28:14.931621Z</t>
         </is>
       </c>
       <c r="BI253" s="24" t="inlineStr">
@@ -74528,13 +74576,13 @@
       </c>
       <c r="BJ253" s="25" t="n"/>
       <c r="BK253" s="26" t="n">
-        <v>-194</v>
+        <v>-203</v>
       </c>
       <c r="BL253" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.492611</v>
       </c>
       <c r="BM253" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.669967</v>
       </c>
       <c r="BN253" s="28" t="n"/>
       <c r="BO253" s="28" t="n"/>
@@ -74576,12 +74624,12 @@
     <row r="254" ht="36" customHeight="1">
       <c r="A254" s="24" t="inlineStr">
         <is>
-          <t>1b69bfb5eb70469b</t>
+          <t>75b5cd42d7314e23</t>
         </is>
       </c>
       <c r="B254" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:22:21.644116Z</t>
+          <t>2026-08-07T18:29:30.567007Z</t>
         </is>
       </c>
       <c r="C254" s="24" t="inlineStr">
@@ -74789,7 +74837,7 @@
       </c>
       <c r="BH254" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:49.016308Z</t>
+          <t>2026-08-07T18:28:10.393455Z</t>
         </is>
       </c>
       <c r="BI254" s="24" t="inlineStr">
@@ -74847,12 +74895,12 @@
     <row r="255" ht="36" customHeight="1">
       <c r="A255" s="24" t="inlineStr">
         <is>
-          <t>3a11fb656ed64eef</t>
+          <t>bb17fe4986614071</t>
         </is>
       </c>
       <c r="B255" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:22:21.644116Z</t>
+          <t>2026-08-07T18:29:30.567007Z</t>
         </is>
       </c>
       <c r="C255" s="24" t="inlineStr">
@@ -75060,7 +75108,7 @@
       </c>
       <c r="BH255" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:55.272443Z</t>
+          <t>2026-08-07T18:28:15.652471Z</t>
         </is>
       </c>
       <c r="BI255" s="24" t="inlineStr">
@@ -75118,12 +75166,12 @@
     <row r="256" ht="36" customHeight="1">
       <c r="A256" s="24" t="inlineStr">
         <is>
-          <t>c193433168e44ffd</t>
+          <t>6af2174549ee4eee</t>
         </is>
       </c>
       <c r="B256" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:22:21.644116Z</t>
+          <t>2026-08-07T18:29:30.567007Z</t>
         </is>
       </c>
       <c r="C256" s="24" t="inlineStr">
@@ -75168,13 +75216,13 @@
         </is>
       </c>
       <c r="L256" s="26" t="n">
-        <v>-178</v>
+        <v>-163</v>
       </c>
       <c r="M256" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.613497</v>
       </c>
       <c r="N256" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.619772</v>
       </c>
       <c r="O256" s="28" t="n">
         <v>0.573609</v>
@@ -75183,7 +75231,7 @@
         <v>0.05</v>
       </c>
       <c r="Q256" s="28" t="n">
-        <v>-0.066679</v>
+        <v>-0.046163</v>
       </c>
       <c r="R256" s="26" t="n">
         <v>0</v>
@@ -75212,7 +75260,7 @@
       <c r="AD256" s="24" t="n"/>
       <c r="AE256" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Tommy Paul p=0.574 vs Learner Tien. Executable ask 0.6400 (aec-atp-leatie-tompau-2026-08-07).</t>
+          <t>Surface-blended Elo on Hard: Tommy Paul p=0.574 vs Learner Tien. Executable ask 0.6200 (aec-atp-leatie-tompau-2026-08-07).</t>
         </is>
       </c>
       <c r="AF256" s="31" t="inlineStr">
@@ -75331,7 +75379,7 @@
       </c>
       <c r="BH256" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:56.385531Z</t>
+          <t>2026-08-07T18:28:16.728202Z</t>
         </is>
       </c>
       <c r="BI256" s="24" t="inlineStr">
@@ -75341,13 +75389,13 @@
       </c>
       <c r="BJ256" s="25" t="n"/>
       <c r="BK256" s="26" t="n">
-        <v>-178</v>
+        <v>-163</v>
       </c>
       <c r="BL256" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.613497</v>
       </c>
       <c r="BM256" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.619772</v>
       </c>
       <c r="BN256" s="28" t="n"/>
       <c r="BO256" s="28" t="n"/>
